--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="127">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,147 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>02:05:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Toluca</t>
+  </si>
+  <si>
+    <t>Pachuca</t>
+  </si>
+  <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
+    <t>Queretaro</t>
+  </si>
+  <si>
+    <t>Otelul Galati</t>
+  </si>
+  <si>
+    <t>FC Petrzalka</t>
+  </si>
+  <si>
+    <t>HB Koge</t>
+  </si>
+  <si>
+    <t>Jonkopings Sodra</t>
+  </si>
+  <si>
+    <t>Vasalunds IF</t>
+  </si>
+  <si>
+    <t>Angelholms</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>ACS Petrolul 52</t>
+  </si>
+  <si>
+    <t>Manta FC</t>
+  </si>
+  <si>
+    <t>Santos Laguna</t>
+  </si>
+  <si>
+    <t>Tijuana</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medellin</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>FC Hunedoara</t>
+  </si>
+  <si>
+    <t>Pohronie</t>
+  </si>
+  <si>
+    <t>Hobro</t>
+  </si>
+  <si>
+    <t>Skovde Aik</t>
+  </si>
+  <si>
+    <t>Assyriska FF</t>
+  </si>
+  <si>
+    <t>Eskilsminne</t>
+  </si>
+  <si>
+    <t>Atl Tucuman</t>
+  </si>
+  <si>
+    <t>Csikszereda</t>
+  </si>
+  <si>
+    <t>Orense Sporting Club</t>
+  </si>
+  <si>
+    <t>2026-09-19 01:58:55</t>
   </si>
 </sst>
 </file>
@@ -585,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +969,3394 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2">
+        <v>1.28</v>
+      </c>
+      <c r="G2">
+        <v>1.32</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>11</v>
+      </c>
+      <c r="J2">
+        <v>7.2</v>
+      </c>
+      <c r="K2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>7.6</v>
+      </c>
+      <c r="O2">
+        <v>1.12</v>
+      </c>
+      <c r="P2">
+        <v>3.35</v>
+      </c>
+      <c r="Q2">
+        <v>1.37</v>
+      </c>
+      <c r="R2">
+        <v>1.92</v>
+      </c>
+      <c r="S2">
+        <v>1.89</v>
+      </c>
+      <c r="T2">
+        <v>1.71</v>
+      </c>
+      <c r="U2">
+        <v>2.12</v>
+      </c>
+      <c r="V2">
+        <v>1.1</v>
+      </c>
+      <c r="W2">
+        <v>4.1</v>
+      </c>
+      <c r="X2">
+        <v>50</v>
+      </c>
+      <c r="Y2">
+        <v>50</v>
+      </c>
+      <c r="Z2">
+        <v>120</v>
+      </c>
+      <c r="AA2">
+        <v>350</v>
+      </c>
+      <c r="AB2">
+        <v>15</v>
+      </c>
+      <c r="AC2">
+        <v>19</v>
+      </c>
+      <c r="AD2">
+        <v>40</v>
+      </c>
+      <c r="AE2">
+        <v>150</v>
+      </c>
+      <c r="AF2">
+        <v>11.5</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>110</v>
+      </c>
+      <c r="AJ2">
+        <v>13</v>
+      </c>
+      <c r="AK2">
+        <v>14</v>
+      </c>
+      <c r="AL2">
+        <v>29</v>
+      </c>
+      <c r="AM2">
+        <v>120</v>
+      </c>
+      <c r="AN2">
+        <v>3.65</v>
+      </c>
+      <c r="AO2">
+        <v>120</v>
+      </c>
+      <c r="AP2">
+        <v>32</v>
+      </c>
+      <c r="AQ2">
+        <v>32</v>
+      </c>
+      <c r="AR2">
+        <v>8.6</v>
+      </c>
+      <c r="AS2">
+        <v>9</v>
+      </c>
+      <c r="AT2">
+        <v>12.5</v>
+      </c>
+      <c r="AU2">
+        <v>14.5</v>
+      </c>
+      <c r="AV2">
+        <v>7.6</v>
+      </c>
+      <c r="AW2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX2">
+        <v>9.6</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>19.5</v>
+      </c>
+      <c r="BA2">
+        <v>8.6</v>
+      </c>
+      <c r="BB2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC2">
+        <v>11.5</v>
+      </c>
+      <c r="BD2">
+        <v>7</v>
+      </c>
+      <c r="BE2">
+        <v>8.6</v>
+      </c>
+      <c r="BF2">
+        <v>3.1</v>
+      </c>
+      <c r="BG2">
+        <v>8.6</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>3.05</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3">
+        <v>1.79</v>
+      </c>
+      <c r="G3">
+        <v>1.97</v>
+      </c>
+      <c r="H3">
+        <v>3.95</v>
+      </c>
+      <c r="I3">
+        <v>5.6</v>
+      </c>
+      <c r="J3">
+        <v>3.85</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>1.31</v>
+      </c>
+      <c r="M3">
+        <v>1.02</v>
+      </c>
+      <c r="N3">
+        <v>3.9</v>
+      </c>
+      <c r="O3">
+        <v>1.25</v>
+      </c>
+      <c r="P3">
+        <v>2.02</v>
+      </c>
+      <c r="Q3">
+        <v>1.73</v>
+      </c>
+      <c r="R3">
+        <v>1.41</v>
+      </c>
+      <c r="S3">
+        <v>2.82</v>
+      </c>
+      <c r="T3">
+        <v>1.73</v>
+      </c>
+      <c r="U3">
+        <v>2.04</v>
+      </c>
+      <c r="V3">
+        <v>1.22</v>
+      </c>
+      <c r="W3">
+        <v>2.02</v>
+      </c>
+      <c r="X3">
+        <v>55</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>17.5</v>
+      </c>
+      <c r="AC3">
+        <v>15</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>21</v>
+      </c>
+      <c r="AG3">
+        <v>19</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>14.5</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>11</v>
+      </c>
+      <c r="AQ3">
+        <v>11.5</v>
+      </c>
+      <c r="AR3">
+        <v>1.45</v>
+      </c>
+      <c r="AS3">
+        <v>1.45</v>
+      </c>
+      <c r="AT3">
+        <v>7.2</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>1.45</v>
+      </c>
+      <c r="AW3">
+        <v>1.45</v>
+      </c>
+      <c r="AX3">
+        <v>7.8</v>
+      </c>
+      <c r="AY3">
+        <v>7.4</v>
+      </c>
+      <c r="AZ3">
+        <v>11.5</v>
+      </c>
+      <c r="BA3">
+        <v>1.45</v>
+      </c>
+      <c r="BB3">
+        <v>11.5</v>
+      </c>
+      <c r="BC3">
+        <v>1.45</v>
+      </c>
+      <c r="BD3">
+        <v>1.45</v>
+      </c>
+      <c r="BE3">
+        <v>1.45</v>
+      </c>
+      <c r="BF3">
+        <v>7</v>
+      </c>
+      <c r="BG3">
+        <v>1.45</v>
+      </c>
+      <c r="BH3">
+        <v>4.3</v>
+      </c>
+      <c r="BI3">
+        <v>3.15</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>5.9</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>6.4</v>
+      </c>
+      <c r="BO3">
+        <v>3.65</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>7.6</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>14.5</v>
+      </c>
+      <c r="BU3">
+        <v>6.4</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>2.16</v>
+      </c>
+      <c r="G4">
+        <v>2.46</v>
+      </c>
+      <c r="H4">
+        <v>3.7</v>
+      </c>
+      <c r="I4">
+        <v>4.6</v>
+      </c>
+      <c r="J4">
+        <v>2.76</v>
+      </c>
+      <c r="K4">
+        <v>3.6</v>
+      </c>
+      <c r="L4">
+        <v>1.63</v>
+      </c>
+      <c r="M4">
+        <v>1.11</v>
+      </c>
+      <c r="N4">
+        <v>2.26</v>
+      </c>
+      <c r="O4">
+        <v>1.57</v>
+      </c>
+      <c r="P4">
+        <v>1.39</v>
+      </c>
+      <c r="Q4">
+        <v>2.8</v>
+      </c>
+      <c r="R4">
+        <v>1.13</v>
+      </c>
+      <c r="S4">
+        <v>5.3</v>
+      </c>
+      <c r="T4">
+        <v>2.28</v>
+      </c>
+      <c r="U4">
+        <v>1.56</v>
+      </c>
+      <c r="V4">
+        <v>1.3</v>
+      </c>
+      <c r="W4">
+        <v>1.68</v>
+      </c>
+      <c r="X4">
+        <v>10.5</v>
+      </c>
+      <c r="Y4">
+        <v>16</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>9</v>
+      </c>
+      <c r="AC4">
+        <v>10.5</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>24</v>
+      </c>
+      <c r="AG4">
+        <v>36</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>5.6</v>
+      </c>
+      <c r="AQ4">
+        <v>6.8</v>
+      </c>
+      <c r="AR4">
+        <v>1.76</v>
+      </c>
+      <c r="AS4">
+        <v>1.76</v>
+      </c>
+      <c r="AT4">
+        <v>5.2</v>
+      </c>
+      <c r="AU4">
+        <v>5.6</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>1.76</v>
+      </c>
+      <c r="AX4">
+        <v>8</v>
+      </c>
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>1.76</v>
+      </c>
+      <c r="BA4">
+        <v>1.76</v>
+      </c>
+      <c r="BB4">
+        <v>1.76</v>
+      </c>
+      <c r="BC4">
+        <v>1.76</v>
+      </c>
+      <c r="BD4">
+        <v>1.76</v>
+      </c>
+      <c r="BE4">
+        <v>1.76</v>
+      </c>
+      <c r="BF4">
+        <v>1.76</v>
+      </c>
+      <c r="BG4">
+        <v>1.76</v>
+      </c>
+      <c r="BH4">
+        <v>2.68</v>
+      </c>
+      <c r="BI4">
+        <v>2.18</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>7.2</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>5.9</v>
+      </c>
+      <c r="BO4">
+        <v>3.95</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>5.4</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5">
+        <v>4.6</v>
+      </c>
+      <c r="G5">
+        <v>6.2</v>
+      </c>
+      <c r="H5">
+        <v>1.76</v>
+      </c>
+      <c r="I5">
+        <v>1.94</v>
+      </c>
+      <c r="J5">
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <v>4.1</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>3.1</v>
+      </c>
+      <c r="O5">
+        <v>1.3</v>
+      </c>
+      <c r="P5">
+        <v>1.83</v>
+      </c>
+      <c r="Q5">
+        <v>1.96</v>
+      </c>
+      <c r="R5">
+        <v>1.28</v>
+      </c>
+      <c r="S5">
+        <v>3.3</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>2.06</v>
+      </c>
+      <c r="W5">
+        <v>1.2</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>11</v>
+      </c>
+      <c r="AQ5">
+        <v>7</v>
+      </c>
+      <c r="AR5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS5">
+        <v>16</v>
+      </c>
+      <c r="AT5">
+        <v>11.5</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>8.6</v>
+      </c>
+      <c r="AW5">
+        <v>15</v>
+      </c>
+      <c r="AX5">
+        <v>23</v>
+      </c>
+      <c r="AY5">
+        <v>13.5</v>
+      </c>
+      <c r="AZ5">
+        <v>15.5</v>
+      </c>
+      <c r="BA5">
+        <v>26</v>
+      </c>
+      <c r="BB5">
+        <v>40</v>
+      </c>
+      <c r="BC5">
+        <v>38</v>
+      </c>
+      <c r="BD5">
+        <v>40</v>
+      </c>
+      <c r="BE5">
+        <v>40</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6">
+        <v>2.48</v>
+      </c>
+      <c r="G6">
+        <v>2.76</v>
+      </c>
+      <c r="H6">
+        <v>2.76</v>
+      </c>
+      <c r="I6">
+        <v>3.05</v>
+      </c>
+      <c r="J6">
+        <v>3.55</v>
+      </c>
+      <c r="K6">
+        <v>4.3</v>
+      </c>
+      <c r="L6">
+        <v>1.31</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>4.4</v>
+      </c>
+      <c r="O6">
+        <v>1.24</v>
+      </c>
+      <c r="P6">
+        <v>2.14</v>
+      </c>
+      <c r="Q6">
+        <v>1.71</v>
+      </c>
+      <c r="R6">
+        <v>1.45</v>
+      </c>
+      <c r="S6">
+        <v>2.72</v>
+      </c>
+      <c r="T6">
+        <v>1.56</v>
+      </c>
+      <c r="U6">
+        <v>2.4</v>
+      </c>
+      <c r="V6">
+        <v>1.5</v>
+      </c>
+      <c r="W6">
+        <v>1.57</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>44</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>34</v>
+      </c>
+      <c r="AC6">
+        <v>13</v>
+      </c>
+      <c r="AD6">
+        <v>30</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>25</v>
+      </c>
+      <c r="AH6">
+        <v>70</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>11.5</v>
+      </c>
+      <c r="AQ6">
+        <v>9.4</v>
+      </c>
+      <c r="AR6">
+        <v>12</v>
+      </c>
+      <c r="AS6">
+        <v>1.27</v>
+      </c>
+      <c r="AT6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6">
+        <v>6.2</v>
+      </c>
+      <c r="AV6">
+        <v>8.6</v>
+      </c>
+      <c r="AW6">
+        <v>1.27</v>
+      </c>
+      <c r="AX6">
+        <v>11</v>
+      </c>
+      <c r="AY6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ6">
+        <v>10</v>
+      </c>
+      <c r="BA6">
+        <v>1.27</v>
+      </c>
+      <c r="BB6">
+        <v>1.27</v>
+      </c>
+      <c r="BC6">
+        <v>1.27</v>
+      </c>
+      <c r="BD6">
+        <v>1.27</v>
+      </c>
+      <c r="BE6">
+        <v>1.27</v>
+      </c>
+      <c r="BF6">
+        <v>10.5</v>
+      </c>
+      <c r="BG6">
+        <v>12</v>
+      </c>
+      <c r="BH6">
+        <v>4.2</v>
+      </c>
+      <c r="BI6">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6">
+        <v>15.5</v>
+      </c>
+      <c r="BK6">
+        <v>6.4</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO6">
+        <v>4.5</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>11</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>8</v>
+      </c>
+      <c r="BU6">
+        <v>4.8</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>12</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7">
+        <v>2.34</v>
+      </c>
+      <c r="G7">
+        <v>2.7</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>3.7</v>
+      </c>
+      <c r="J7">
+        <v>2.98</v>
+      </c>
+      <c r="K7">
+        <v>3.85</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.73</v>
+      </c>
+      <c r="Q7">
+        <v>2.04</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.73</v>
+      </c>
+      <c r="U7">
+        <v>2.02</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>970</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>970</v>
+      </c>
+      <c r="AC7">
+        <v>970</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>970</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.31</v>
+      </c>
+      <c r="AQ7">
+        <v>1.25</v>
+      </c>
+      <c r="AR7">
+        <v>1.31</v>
+      </c>
+      <c r="AS7">
+        <v>1.31</v>
+      </c>
+      <c r="AT7">
+        <v>1.21</v>
+      </c>
+      <c r="AU7">
+        <v>1.15</v>
+      </c>
+      <c r="AV7">
+        <v>1.31</v>
+      </c>
+      <c r="AW7">
+        <v>1.31</v>
+      </c>
+      <c r="AX7">
+        <v>1.31</v>
+      </c>
+      <c r="AY7">
+        <v>1.25</v>
+      </c>
+      <c r="AZ7">
+        <v>1.31</v>
+      </c>
+      <c r="BA7">
+        <v>1.31</v>
+      </c>
+      <c r="BB7">
+        <v>1.31</v>
+      </c>
+      <c r="BC7">
+        <v>1.31</v>
+      </c>
+      <c r="BD7">
+        <v>1.31</v>
+      </c>
+      <c r="BE7">
+        <v>1.31</v>
+      </c>
+      <c r="BF7">
+        <v>1.31</v>
+      </c>
+      <c r="BG7">
+        <v>1.31</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8">
+        <v>1.56</v>
+      </c>
+      <c r="G8">
+        <v>1.77</v>
+      </c>
+      <c r="H8">
+        <v>2.28</v>
+      </c>
+      <c r="I8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2.14</v>
+      </c>
+      <c r="Q8">
+        <v>1.64</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9">
+        <v>2.28</v>
+      </c>
+      <c r="G9">
+        <v>2.58</v>
+      </c>
+      <c r="H9">
+        <v>2.82</v>
+      </c>
+      <c r="I9">
+        <v>3.35</v>
+      </c>
+      <c r="J9">
+        <v>3.7</v>
+      </c>
+      <c r="K9">
+        <v>4.7</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.02</v>
+      </c>
+      <c r="N9">
+        <v>4.3</v>
+      </c>
+      <c r="O9">
+        <v>1.24</v>
+      </c>
+      <c r="P9">
+        <v>2.1</v>
+      </c>
+      <c r="Q9">
+        <v>1.7</v>
+      </c>
+      <c r="R9">
+        <v>1.44</v>
+      </c>
+      <c r="S9">
+        <v>2.68</v>
+      </c>
+      <c r="T9">
+        <v>1.57</v>
+      </c>
+      <c r="U9">
+        <v>2.26</v>
+      </c>
+      <c r="V9">
+        <v>1.43</v>
+      </c>
+      <c r="W9">
+        <v>1.63</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>13.5</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>10</v>
+      </c>
+      <c r="AY9">
+        <v>7.6</v>
+      </c>
+      <c r="AZ9">
+        <v>10</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>10</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>1.1</v>
+      </c>
+      <c r="G10">
+        <v>950</v>
+      </c>
+      <c r="H10">
+        <v>1.1</v>
+      </c>
+      <c r="I10">
+        <v>950</v>
+      </c>
+      <c r="J10">
+        <v>1.1</v>
+      </c>
+      <c r="K10">
+        <v>890</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.07</v>
+      </c>
+      <c r="O10">
+        <v>1.01</v>
+      </c>
+      <c r="P10">
+        <v>1.07</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>1.07</v>
+      </c>
+      <c r="S10">
+        <v>1.01</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.04</v>
+      </c>
+      <c r="W10">
+        <v>1.04</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11">
+        <v>1.1</v>
+      </c>
+      <c r="G11">
+        <v>1000</v>
+      </c>
+      <c r="H11">
+        <v>1.1</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>1.1</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.24</v>
+      </c>
+      <c r="Q11">
+        <v>1.01</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>1.52</v>
+      </c>
+      <c r="G12">
+        <v>3.1</v>
+      </c>
+      <c r="H12">
+        <v>1.55</v>
+      </c>
+      <c r="I12">
+        <v>3.15</v>
+      </c>
+      <c r="J12">
+        <v>2.76</v>
+      </c>
+      <c r="K12">
+        <v>870</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.25</v>
+      </c>
+      <c r="O12">
+        <v>1.01</v>
+      </c>
+      <c r="P12">
+        <v>1.25</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>1.24</v>
+      </c>
+      <c r="S12">
+        <v>1.01</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>1.5</v>
+      </c>
+      <c r="W12">
+        <v>1.53</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>2.86</v>
+      </c>
+      <c r="G13">
+        <v>4.2</v>
+      </c>
+      <c r="H13">
+        <v>2.12</v>
+      </c>
+      <c r="I13">
+        <v>3.05</v>
+      </c>
+      <c r="J13">
+        <v>2.76</v>
+      </c>
+      <c r="K13">
+        <v>3.4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.35</v>
+      </c>
+      <c r="Q13">
+        <v>2.62</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>1.88</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>4.4</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <v>3.3</v>
+      </c>
+      <c r="K14">
+        <v>4.1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.07</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.78</v>
+      </c>
+      <c r="Q14">
+        <v>1.98</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1.92</v>
+      </c>
+      <c r="U14">
+        <v>1.96</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>14.5</v>
+      </c>
+      <c r="Y14">
+        <v>17.5</v>
+      </c>
+      <c r="Z14">
+        <v>40</v>
+      </c>
+      <c r="AA14">
+        <v>130</v>
+      </c>
+      <c r="AB14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC14">
+        <v>9.4</v>
+      </c>
+      <c r="AD14">
+        <v>22</v>
+      </c>
+      <c r="AE14">
+        <v>80</v>
+      </c>
+      <c r="AF14">
+        <v>13.5</v>
+      </c>
+      <c r="AG14">
+        <v>12</v>
+      </c>
+      <c r="AH14">
+        <v>24</v>
+      </c>
+      <c r="AI14">
+        <v>85</v>
+      </c>
+      <c r="AJ14">
+        <v>26</v>
+      </c>
+      <c r="AK14">
+        <v>26</v>
+      </c>
+      <c r="AL14">
+        <v>48</v>
+      </c>
+      <c r="AM14">
+        <v>150</v>
+      </c>
+      <c r="AN14">
+        <v>18.5</v>
+      </c>
+      <c r="AO14">
+        <v>95</v>
+      </c>
+      <c r="AP14">
+        <v>11</v>
+      </c>
+      <c r="AQ14">
+        <v>13</v>
+      </c>
+      <c r="AR14">
+        <v>5.2</v>
+      </c>
+      <c r="AS14">
+        <v>5.7</v>
+      </c>
+      <c r="AT14">
+        <v>7.2</v>
+      </c>
+      <c r="AU14">
+        <v>7.2</v>
+      </c>
+      <c r="AV14">
+        <v>16.5</v>
+      </c>
+      <c r="AW14">
+        <v>5.6</v>
+      </c>
+      <c r="AX14">
+        <v>10</v>
+      </c>
+      <c r="AY14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14">
+        <v>12.5</v>
+      </c>
+      <c r="BA14">
+        <v>5.6</v>
+      </c>
+      <c r="BB14">
+        <v>18.5</v>
+      </c>
+      <c r="BC14">
+        <v>18.5</v>
+      </c>
+      <c r="BD14">
+        <v>5.3</v>
+      </c>
+      <c r="BE14">
+        <v>5.7</v>
+      </c>
+      <c r="BF14">
+        <v>13.5</v>
+      </c>
+      <c r="BG14">
+        <v>5.6</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <v>2.58</v>
+      </c>
+      <c r="G15">
+        <v>3.25</v>
+      </c>
+      <c r="H15">
+        <v>2.72</v>
+      </c>
+      <c r="I15">
+        <v>3.35</v>
+      </c>
+      <c r="J15">
+        <v>2.82</v>
+      </c>
+      <c r="K15">
+        <v>3.65</v>
+      </c>
+      <c r="L15">
+        <v>1.46</v>
+      </c>
+      <c r="M15">
+        <v>1.1</v>
+      </c>
+      <c r="N15">
+        <v>3.05</v>
+      </c>
+      <c r="O15">
+        <v>1.41</v>
+      </c>
+      <c r="P15">
+        <v>1.67</v>
+      </c>
+      <c r="Q15">
+        <v>2.24</v>
+      </c>
+      <c r="R15">
+        <v>1.23</v>
+      </c>
+      <c r="S15">
+        <v>4.1</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
+        <v>1.44</v>
+      </c>
+      <c r="W15">
+        <v>1.48</v>
+      </c>
+      <c r="X15">
+        <v>21</v>
+      </c>
+      <c r="Y15">
+        <v>21</v>
+      </c>
+      <c r="Z15">
+        <v>100</v>
+      </c>
+      <c r="AA15">
+        <v>900</v>
+      </c>
+      <c r="AB15">
+        <v>18.5</v>
+      </c>
+      <c r="AC15">
+        <v>42</v>
+      </c>
+      <c r="AD15">
+        <v>42</v>
+      </c>
+      <c r="AE15">
+        <v>240</v>
+      </c>
+      <c r="AF15">
+        <v>85</v>
+      </c>
+      <c r="AG15">
+        <v>22</v>
+      </c>
+      <c r="AH15">
+        <v>100</v>
+      </c>
+      <c r="AI15">
+        <v>290</v>
+      </c>
+      <c r="AJ15">
+        <v>900</v>
+      </c>
+      <c r="AK15">
+        <v>200</v>
+      </c>
+      <c r="AL15">
+        <v>180</v>
+      </c>
+      <c r="AM15">
+        <v>450</v>
+      </c>
+      <c r="AN15">
+        <v>60</v>
+      </c>
+      <c r="AO15">
+        <v>75</v>
+      </c>
+      <c r="AP15">
+        <v>2.5</v>
+      </c>
+      <c r="AQ15">
+        <v>2.5</v>
+      </c>
+      <c r="AR15">
+        <v>2.5</v>
+      </c>
+      <c r="AS15">
+        <v>2.5</v>
+      </c>
+      <c r="AT15">
+        <v>2.5</v>
+      </c>
+      <c r="AU15">
+        <v>4.2</v>
+      </c>
+      <c r="AV15">
+        <v>2.5</v>
+      </c>
+      <c r="AW15">
+        <v>2.5</v>
+      </c>
+      <c r="AX15">
+        <v>2.5</v>
+      </c>
+      <c r="AY15">
+        <v>2.5</v>
+      </c>
+      <c r="AZ15">
+        <v>2.5</v>
+      </c>
+      <c r="BA15">
+        <v>2.5</v>
+      </c>
+      <c r="BB15">
+        <v>2.5</v>
+      </c>
+      <c r="BC15">
+        <v>2.5</v>
+      </c>
+      <c r="BD15">
+        <v>2.5</v>
+      </c>
+      <c r="BE15">
+        <v>2.5</v>
+      </c>
+      <c r="BF15">
+        <v>1.76</v>
+      </c>
+      <c r="BG15">
+        <v>1.55</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -394,7 +394,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 01:58:55</t>
+    <t>2026-09-19 04:35:47</t>
   </si>
 </sst>
 </file>
@@ -991,19 +991,19 @@
         <v>1.28</v>
       </c>
       <c r="G2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J2">
         <v>7.2</v>
       </c>
       <c r="K2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1012,34 +1012,34 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O2">
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R2">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="T2">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
         <v>1.1</v>
       </c>
       <c r="W2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="X2">
         <v>50</v>
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="AD2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1078,7 +1078,7 @@
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK2">
         <v>14</v>
@@ -1090,7 +1090,7 @@
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AO2">
         <v>120</v>
@@ -1102,22 +1102,22 @@
         <v>32</v>
       </c>
       <c r="AR2">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AT2">
         <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AV2">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1129,25 +1129,25 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BB2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BF2">
         <v>3.1</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1230,22 +1230,22 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="G3">
         <v>1.97</v>
       </c>
       <c r="H3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J3">
         <v>3.85</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1269,16 +1269,16 @@
         <v>1.41</v>
       </c>
       <c r="S3">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T3">
         <v>1.73</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>2.02</v>
@@ -1356,7 +1356,7 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>1.45</v>
+        <v>11</v>
       </c>
       <c r="AW3">
         <v>1.45</v>
@@ -1377,7 +1377,7 @@
         <v>11.5</v>
       </c>
       <c r="BC3">
-        <v>1.45</v>
+        <v>11</v>
       </c>
       <c r="BD3">
         <v>1.45</v>
@@ -1472,7 +1472,7 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G4">
         <v>2.46</v>
@@ -1505,7 +1505,7 @@
         <v>1.39</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
         <v>1.13</v>
@@ -1583,7 +1583,7 @@
         <v>5.6</v>
       </c>
       <c r="AQ4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR4">
         <v>1.76</v>
@@ -1598,16 +1598,16 @@
         <v>5.6</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>1.76</v>
       </c>
       <c r="AW4">
         <v>1.76</v>
       </c>
       <c r="AX4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>1.68</v>
       </c>
       <c r="AZ4">
         <v>1.76</v>
@@ -1714,67 +1714,67 @@
         <v>115</v>
       </c>
       <c r="F5">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H5">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="I5">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
+        <v>1.31</v>
+      </c>
+      <c r="P5">
+        <v>1.92</v>
+      </c>
+      <c r="Q5">
+        <v>1.98</v>
+      </c>
+      <c r="R5">
         <v>1.3</v>
-      </c>
-      <c r="P5">
-        <v>1.83</v>
-      </c>
-      <c r="Q5">
-        <v>1.96</v>
-      </c>
-      <c r="R5">
-        <v>1.28</v>
       </c>
       <c r="S5">
         <v>3.3</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V5">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
         <v>1000</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1783,10 +1783,10 @@
         <v>1000</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1822,58 +1822,58 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>1.34</v>
       </c>
       <c r="AQ5">
-        <v>7</v>
+        <v>1.21</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="AS5">
-        <v>16</v>
+        <v>1.34</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>1.34</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>1.21</v>
       </c>
       <c r="AV5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AW5">
-        <v>15</v>
+        <v>1.34</v>
       </c>
       <c r="AX5">
-        <v>23</v>
+        <v>1.34</v>
       </c>
       <c r="AY5">
-        <v>13.5</v>
+        <v>1.34</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>1.34</v>
       </c>
       <c r="BA5">
-        <v>26</v>
+        <v>1.34</v>
       </c>
       <c r="BB5">
-        <v>40</v>
+        <v>1.34</v>
       </c>
       <c r="BC5">
-        <v>38</v>
+        <v>1.34</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>1.34</v>
       </c>
       <c r="BE5">
-        <v>40</v>
+        <v>1.34</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1959,7 +1959,7 @@
         <v>2.48</v>
       </c>
       <c r="G6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H6">
         <v>2.76</v>
@@ -1983,19 +1983,19 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
         <v>2.14</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R6">
         <v>1.45</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
         <v>1.56</v>
@@ -2073,7 +2073,7 @@
         <v>12</v>
       </c>
       <c r="AS6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AT6">
         <v>8.800000000000001</v>
@@ -2085,7 +2085,7 @@
         <v>8.6</v>
       </c>
       <c r="AW6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2097,19 +2097,19 @@
         <v>10</v>
       </c>
       <c r="BA6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BB6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BC6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BD6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BE6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BF6">
         <v>10.5</v>
@@ -2201,19 +2201,19 @@
         <v>2.34</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J7">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2240,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>1.77</v>
       </c>
       <c r="H8">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
         <v>9.199999999999999</v>
@@ -2455,7 +2455,7 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -2936,7 +2936,7 @@
         <v>950</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
         <v>890</v>
@@ -2972,10 +2972,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3181,7 +3181,7 @@
         <v>1.1</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3408,19 +3408,19 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G12">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="H12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I12">
         <v>3.15</v>
       </c>
       <c r="J12">
-        <v>2.76</v>
+        <v>1.12</v>
       </c>
       <c r="K12">
         <v>870</v>
@@ -3456,10 +3456,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3892,10 +3892,10 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H14">
         <v>4.4</v>
@@ -3904,7 +3904,7 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q14">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3970,7 +3970,7 @@
         <v>80</v>
       </c>
       <c r="AF14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG14">
         <v>12</v>
@@ -3982,10 +3982,10 @@
         <v>85</v>
       </c>
       <c r="AJ14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL14">
         <v>48</v>
@@ -4015,7 +4015,7 @@
         <v>7.2</v>
       </c>
       <c r="AU14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV14">
         <v>16.5</v>
@@ -4045,10 +4045,10 @@
         <v>5.3</v>
       </c>
       <c r="BE14">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF14">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG14">
         <v>5.6</v>
@@ -4134,28 +4134,28 @@
         <v>125</v>
       </c>
       <c r="F15">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="G15">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I15">
         <v>3.35</v>
       </c>
       <c r="J15">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N15">
         <v>3.05</v>
@@ -4167,13 +4167,13 @@
         <v>1.67</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R15">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4182,10 +4182,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X15">
         <v>21</v>
@@ -4236,10 +4236,10 @@
         <v>450</v>
       </c>
       <c r="AN15">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO15">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP15">
         <v>2.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -394,7 +394,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 04:35:47</t>
+    <t>2026-09-19 07:13:09</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>7.2</v>
@@ -1012,28 +1012,28 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O2">
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q2">
         <v>1.38</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
         <v>1.1</v>
@@ -1078,7 +1078,7 @@
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK2">
         <v>14</v>
@@ -1090,7 +1090,7 @@
         <v>120</v>
       </c>
       <c r="AN2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AO2">
         <v>120</v>
@@ -1102,22 +1102,22 @@
         <v>32</v>
       </c>
       <c r="AR2">
+        <v>10.5</v>
+      </c>
+      <c r="AS2">
         <v>11</v>
-      </c>
-      <c r="AS2">
-        <v>11.5</v>
       </c>
       <c r="AT2">
         <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1129,7 +1129,7 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB2">
         <v>10</v>
@@ -1138,16 +1138,16 @@
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>3.1</v>
       </c>
       <c r="BG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1230,10 +1230,10 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G3">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1242,7 +1242,7 @@
         <v>5.4</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>4.3</v>
@@ -1272,16 +1272,16 @@
         <v>2.88</v>
       </c>
       <c r="T3">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U3">
         <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X3">
         <v>55</v>
@@ -1472,7 +1472,7 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G4">
         <v>2.46</v>
@@ -1481,7 +1481,7 @@
         <v>3.7</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
         <v>2.76</v>
@@ -1496,13 +1496,13 @@
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="O4">
         <v>1.57</v>
       </c>
       <c r="P4">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Q4">
         <v>2.78</v>
@@ -1511,13 +1511,13 @@
         <v>1.13</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
         <v>1.3</v>
@@ -1598,13 +1598,13 @@
         <v>5.6</v>
       </c>
       <c r="AV4">
-        <v>1.76</v>
+        <v>11</v>
       </c>
       <c r="AW4">
         <v>1.76</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
         <v>1.68</v>
@@ -1714,7 +1714,7 @@
         <v>115</v>
       </c>
       <c r="F5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G5">
         <v>5.6</v>
@@ -1729,7 +1729,7 @@
         <v>3.3</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1738,13 +1738,13 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.31</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q5">
         <v>1.98</v>
@@ -1825,7 +1825,7 @@
         <v>1.34</v>
       </c>
       <c r="AQ5">
-        <v>1.21</v>
+        <v>5.9</v>
       </c>
       <c r="AR5">
         <v>1.26</v>
@@ -1965,7 +1965,7 @@
         <v>2.76</v>
       </c>
       <c r="I6">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J6">
         <v>3.55</v>
@@ -1983,7 +1983,7 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
         <v>2.14</v>
@@ -1998,13 +1998,13 @@
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
         <v>1.57</v>
@@ -2073,7 +2073,7 @@
         <v>12</v>
       </c>
       <c r="AS6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AT6">
         <v>8.800000000000001</v>
@@ -2085,7 +2085,7 @@
         <v>8.6</v>
       </c>
       <c r="AW6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2097,19 +2097,19 @@
         <v>10</v>
       </c>
       <c r="BA6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BB6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BC6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BD6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BE6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BF6">
         <v>10.5</v>
@@ -2198,13 +2198,13 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G7">
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I7">
         <v>3.75</v>
@@ -2443,10 +2443,10 @@
         <v>1.56</v>
       </c>
       <c r="G8">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I8">
         <v>9.199999999999999</v>
@@ -2706,7 +2706,7 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -2727,7 +2727,7 @@
         <v>1.57</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.43</v>
@@ -2951,19 +2951,19 @@
         <v>1.07</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
         <v>1.07</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R10">
         <v>1.07</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3408,13 +3408,13 @@
         <v>122</v>
       </c>
       <c r="F12">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>5.4</v>
       </c>
       <c r="H12">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="I12">
         <v>3.15</v>
@@ -3456,10 +3456,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3653,10 +3653,10 @@
         <v>2.86</v>
       </c>
       <c r="G13">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="H13">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="I13">
         <v>3.05</v>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="Q13">
         <v>2.62</v>
@@ -3892,19 +3892,19 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="G14">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U14">
         <v>1.86</v>
@@ -3946,13 +3946,13 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y14">
         <v>17.5</v>
       </c>
       <c r="Z14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA14">
         <v>130</v>
@@ -3994,7 +3994,7 @@
         <v>150</v>
       </c>
       <c r="AN14">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO14">
         <v>95</v>
@@ -4009,7 +4009,7 @@
         <v>5.2</v>
       </c>
       <c r="AS14">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT14">
         <v>7.2</v>
@@ -4033,7 +4033,7 @@
         <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB14">
         <v>18.5</v>
@@ -4042,7 +4042,7 @@
         <v>18.5</v>
       </c>
       <c r="BD14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE14">
         <v>5.8</v>
@@ -4051,7 +4051,7 @@
         <v>12.5</v>
       </c>
       <c r="BG14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4137,16 +4137,16 @@
         <v>2.52</v>
       </c>
       <c r="G15">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H15">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I15">
         <v>3.35</v>
       </c>
       <c r="J15">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K15">
         <v>3.7</v>
@@ -4155,7 +4155,7 @@
         <v>1.47</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
         <v>3.05</v>
@@ -4185,7 +4185,7 @@
         <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X15">
         <v>21</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -394,7 +394,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 07:13:09</t>
+    <t>2026-09-19 09:53:49</t>
   </si>
 </sst>
 </file>
@@ -997,7 +997,7 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J2">
         <v>7.2</v>
@@ -1015,139 +1015,139 @@
         <v>7.8</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P2">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="R2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="V2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W2">
         <v>4.3</v>
       </c>
       <c r="X2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AC2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
+        <v>22</v>
+      </c>
+      <c r="AK2">
+        <v>17</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>3.75</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>2.22</v>
+      </c>
+      <c r="AQ2">
+        <v>2.22</v>
+      </c>
+      <c r="AR2">
+        <v>2.22</v>
+      </c>
+      <c r="AS2">
+        <v>2.22</v>
+      </c>
+      <c r="AT2">
         <v>11.5</v>
       </c>
-      <c r="AK2">
-        <v>14</v>
-      </c>
-      <c r="AL2">
-        <v>29</v>
-      </c>
-      <c r="AM2">
-        <v>120</v>
-      </c>
-      <c r="AN2">
-        <v>3.55</v>
-      </c>
-      <c r="AO2">
-        <v>120</v>
-      </c>
-      <c r="AP2">
-        <v>32</v>
-      </c>
-      <c r="AQ2">
-        <v>32</v>
-      </c>
-      <c r="AR2">
-        <v>10.5</v>
-      </c>
-      <c r="AS2">
-        <v>11</v>
-      </c>
-      <c r="AT2">
-        <v>12.5</v>
-      </c>
       <c r="AU2">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AV2">
-        <v>30</v>
+        <v>2.22</v>
       </c>
       <c r="AW2">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>2.22</v>
       </c>
       <c r="BA2">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BC2">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>2.22</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="BF2">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1171,7 +1171,7 @@
         <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -1230,22 +1230,22 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G3">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
         <v>1.31</v>
@@ -1254,37 +1254,37 @@
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T3">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
         <v>1.25</v>
       </c>
       <c r="W3">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1344,10 +1344,10 @@
         <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AS3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1356,10 +1356,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>1.41</v>
       </c>
       <c r="AW3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1371,25 +1371,25 @@
         <v>11.5</v>
       </c>
       <c r="BA3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BB3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>11</v>
+        <v>1.41</v>
       </c>
       <c r="BD3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BE3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BF3">
         <v>7</v>
       </c>
       <c r="BG3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1401,7 +1401,7 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1410,7 +1410,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
         <v>3.65</v>
@@ -1472,10 +1472,10 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H4">
         <v>3.7</v>
@@ -1496,7 +1496,7 @@
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
         <v>1.57</v>
@@ -1514,7 +1514,7 @@
         <v>5.1</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
         <v>1.67</v>
@@ -1523,10 +1523,10 @@
         <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y4">
         <v>16</v>
@@ -1586,10 +1586,10 @@
         <v>7</v>
       </c>
       <c r="AR4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AS4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AT4">
         <v>5.2</v>
@@ -1598,40 +1598,40 @@
         <v>5.6</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>1.75</v>
       </c>
       <c r="AW4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AX4">
-        <v>8.199999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="AY4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AZ4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BA4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BB4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BC4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BD4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BE4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BF4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BG4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BH4">
         <v>2.68</v>
@@ -1714,7 +1714,7 @@
         <v>115</v>
       </c>
       <c r="F5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G5">
         <v>5.6</v>
@@ -1729,7 +1729,7 @@
         <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1738,13 +1738,13 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
         <v>1.31</v>
       </c>
       <c r="P5">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
         <v>1.98</v>
@@ -1759,7 +1759,7 @@
         <v>1.82</v>
       </c>
       <c r="U5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
         <v>2.02</v>
@@ -1840,7 +1840,7 @@
         <v>1.21</v>
       </c>
       <c r="AV5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AW5">
         <v>1.34</v>
@@ -1956,58 +1956,58 @@
         <v>116</v>
       </c>
       <c r="F6">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H6">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
         <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="T6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2124,7 +2124,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>6.4</v>
@@ -2136,7 +2136,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BO6">
         <v>4.5</v>
@@ -2198,19 +2198,19 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G7">
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
         <v>3.8</v>
@@ -2231,7 +2231,7 @@
         <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2473,7 +2473,7 @@
         <v>2.14</v>
       </c>
       <c r="Q8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2682,10 +2682,10 @@
         <v>119</v>
       </c>
       <c r="F9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H9">
         <v>2.82</v>
@@ -2712,7 +2712,7 @@
         <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q9">
         <v>1.7</v>
@@ -2730,10 +2730,10 @@
         <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2814,13 +2814,13 @@
         <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BA9">
         <v>1.01</v>
@@ -3411,7 +3411,7 @@
         <v>1.56</v>
       </c>
       <c r="G12">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="H12">
         <v>1.6</v>
@@ -3420,7 +3420,7 @@
         <v>3.15</v>
       </c>
       <c r="J12">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
         <v>870</v>
@@ -3432,7 +3432,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O12">
         <v>1.01</v>
@@ -3441,13 +3441,13 @@
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12">
         <v>1.24</v>
       </c>
       <c r="S12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3650,7 +3650,7 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G13">
         <v>3.75</v>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q13">
         <v>2.62</v>
@@ -3892,28 +3892,28 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H14">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I14">
         <v>5.1</v>
       </c>
       <c r="J14">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U14">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y14">
         <v>17.5</v>
@@ -3982,7 +3982,7 @@
         <v>85</v>
       </c>
       <c r="AJ14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14">
         <v>25</v>
@@ -4006,7 +4006,7 @@
         <v>13</v>
       </c>
       <c r="AR14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS14">
         <v>5.8</v>
@@ -4021,10 +4021,10 @@
         <v>16.5</v>
       </c>
       <c r="AW14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14">
         <v>9.199999999999999</v>
@@ -4045,7 +4045,7 @@
         <v>5.4</v>
       </c>
       <c r="BE14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF14">
         <v>12.5</v>
@@ -4137,16 +4137,16 @@
         <v>2.52</v>
       </c>
       <c r="G15">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H15">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I15">
         <v>3.35</v>
       </c>
       <c r="J15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>3.7</v>
@@ -4185,7 +4185,7 @@
         <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X15">
         <v>21</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="129">
   <si>
     <t>League</t>
   </si>
@@ -334,6 +334,9 @@
     <t>HB Koge</t>
   </si>
   <si>
+    <t>FC Arlanda</t>
+  </si>
+  <si>
     <t>Jonkopings Sodra</t>
   </si>
   <si>
@@ -376,6 +379,9 @@
     <t>Hobro</t>
   </si>
   <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
     <t>Skovde Aik</t>
   </si>
   <si>
@@ -394,7 +400,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 09:53:49</t>
+    <t>2026-09-19 12:25:55</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -985,19 +991,19 @@
         <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F2">
         <v>1.28</v>
       </c>
       <c r="G2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>7.2</v>
@@ -1015,139 +1021,139 @@
         <v>7.8</v>
       </c>
       <c r="O2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R2">
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB2">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP2">
-        <v>2.22</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>2.22</v>
+        <v>32</v>
       </c>
       <c r="AR2">
-        <v>2.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>2.22</v>
+        <v>26</v>
       </c>
       <c r="AW2">
-        <v>2.22</v>
+        <v>9</v>
       </c>
       <c r="AX2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>2.22</v>
+        <v>7.2</v>
       </c>
       <c r="BA2">
-        <v>2.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BC2">
+        <v>11.5</v>
+      </c>
+      <c r="BD2">
+        <v>22</v>
+      </c>
+      <c r="BE2">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD2">
-        <v>2.22</v>
-      </c>
-      <c r="BE2">
-        <v>2.22</v>
-      </c>
       <c r="BF2">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BG2">
-        <v>2.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1210,7 +1216,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1227,43 +1233,43 @@
         <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3">
         <v>1.79</v>
       </c>
       <c r="G3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H3">
         <v>4.3</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.31</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
         <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q3">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="R3">
         <v>1.44</v>
@@ -1275,10 +1281,10 @@
         <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
         <v>2.12</v>
@@ -1296,7 +1302,7 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC3">
         <v>15</v>
@@ -1308,10 +1314,10 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1332,7 +1338,7 @@
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1344,10 +1350,10 @@
         <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1356,10 +1362,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>1.41</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AX3">
         <v>7.8</v>
@@ -1368,28 +1374,28 @@
         <v>7.4</v>
       </c>
       <c r="AZ3">
-        <v>11.5</v>
+        <v>1.37</v>
       </c>
       <c r="BA3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BB3">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3">
-        <v>1.41</v>
+        <v>12.5</v>
       </c>
       <c r="BD3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BE3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BF3">
         <v>7</v>
       </c>
       <c r="BG3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BH3">
         <v>4.3</v>
@@ -1452,7 +1458,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1469,25 +1475,25 @@
         <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F4">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
         <v>1.63</v>
@@ -1502,7 +1508,7 @@
         <v>1.57</v>
       </c>
       <c r="P4">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Q4">
         <v>2.78</v>
@@ -1514,16 +1520,16 @@
         <v>5.1</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X4">
         <v>11</v>
@@ -1643,7 +1649,7 @@
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1694,7 +1700,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1711,19 +1717,19 @@
         <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F5">
         <v>4.3</v>
       </c>
       <c r="G5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H5">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>3.3</v>
@@ -1738,22 +1744,22 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.31</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q5">
         <v>1.98</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T5">
         <v>1.82</v>
@@ -1762,7 +1768,7 @@
         <v>1.9</v>
       </c>
       <c r="V5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W5">
         <v>1.22</v>
@@ -1825,7 +1831,7 @@
         <v>1.34</v>
       </c>
       <c r="AQ5">
-        <v>5.9</v>
+        <v>1.22</v>
       </c>
       <c r="AR5">
         <v>1.26</v>
@@ -1840,7 +1846,7 @@
         <v>1.21</v>
       </c>
       <c r="AV5">
-        <v>7.6</v>
+        <v>1.25</v>
       </c>
       <c r="AW5">
         <v>1.34</v>
@@ -1936,7 +1942,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1953,25 +1959,25 @@
         <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G6">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>3.3</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -1980,34 +1986,34 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T6">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U6">
         <v>2.3</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2022,7 +2028,7 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC6">
         <v>13</v>
@@ -2073,7 +2079,7 @@
         <v>12</v>
       </c>
       <c r="AS6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AT6">
         <v>8.800000000000001</v>
@@ -2085,7 +2091,7 @@
         <v>8.6</v>
       </c>
       <c r="AW6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AX6">
         <v>11</v>
@@ -2097,19 +2103,19 @@
         <v>10</v>
       </c>
       <c r="BA6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BB6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BC6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BD6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BE6">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BF6">
         <v>10.5</v>
@@ -2124,7 +2130,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6">
         <v>6.4</v>
@@ -2178,7 +2184,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2195,19 +2201,19 @@
         <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G7">
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2216,16 +2222,16 @@
         <v>3.8</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
         <v>1.73</v>
@@ -2234,10 +2240,10 @@
         <v>2.06</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T7">
         <v>1.72</v>
@@ -2246,10 +2252,10 @@
         <v>2.06</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2360,67 +2366,67 @@
         <v>1.31</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2437,7 +2443,7 @@
         <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F8">
         <v>1.56</v>
@@ -2449,220 +2455,220 @@
         <v>2.36</v>
       </c>
       <c r="I8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
         <v>880</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>2.14</v>
       </c>
       <c r="Q8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2679,10 +2685,10 @@
         <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G9">
         <v>2.6</v>
@@ -2706,7 +2712,7 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -2715,7 +2721,7 @@
         <v>2.08</v>
       </c>
       <c r="Q9">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2904,7 +2910,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2921,25 +2927,25 @@
         <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F10">
         <v>1.1</v>
       </c>
       <c r="G10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="H10">
         <v>1.1</v>
       </c>
       <c r="I10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>890</v>
+        <v>1000</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2948,22 +2954,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -2972,10 +2978,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3146,7 +3152,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3163,232 +3169,232 @@
         <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F11">
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3405,515 +3411,515 @@
         <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F12">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K12">
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F13">
-        <v>2.88</v>
+        <v>1.56</v>
       </c>
       <c r="G13">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="H13">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="I13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J13">
-        <v>2.76</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
-        <v>3.4</v>
+        <v>870</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>2.62</v>
+        <v>1.02</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F14">
-        <v>1.84</v>
+        <v>1.46</v>
       </c>
       <c r="G14">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="H14">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="I14">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="K14">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3922,10 +3928,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="Q14">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -3934,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3946,112 +3952,112 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BH14">
         <v>0</v>
@@ -4114,249 +4120,491 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15">
-        <v>2.52</v>
+        <v>1.83</v>
       </c>
       <c r="G15">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="H15">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="I15">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L15">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>1.08</v>
       </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.82</v>
+      </c>
+      <c r="Q15">
+        <v>2.06</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>1.92</v>
+      </c>
+      <c r="U15">
+        <v>1.94</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>15</v>
+      </c>
+      <c r="Y15">
+        <v>17.5</v>
+      </c>
+      <c r="Z15">
+        <v>38</v>
+      </c>
+      <c r="AA15">
+        <v>130</v>
+      </c>
+      <c r="AB15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15">
+        <v>9.4</v>
+      </c>
+      <c r="AD15">
+        <v>22</v>
+      </c>
+      <c r="AE15">
+        <v>80</v>
+      </c>
+      <c r="AF15">
+        <v>13</v>
+      </c>
+      <c r="AG15">
+        <v>12</v>
+      </c>
+      <c r="AH15">
+        <v>24</v>
+      </c>
+      <c r="AI15">
+        <v>85</v>
+      </c>
+      <c r="AJ15">
+        <v>24</v>
+      </c>
+      <c r="AK15">
+        <v>25</v>
+      </c>
+      <c r="AL15">
+        <v>48</v>
+      </c>
+      <c r="AM15">
+        <v>150</v>
+      </c>
+      <c r="AN15">
+        <v>17</v>
+      </c>
+      <c r="AO15">
+        <v>95</v>
+      </c>
+      <c r="AP15">
+        <v>11</v>
+      </c>
+      <c r="AQ15">
+        <v>13</v>
+      </c>
+      <c r="AR15">
+        <v>5.3</v>
+      </c>
+      <c r="AS15">
+        <v>5.8</v>
+      </c>
+      <c r="AT15">
+        <v>7.2</v>
+      </c>
+      <c r="AU15">
+        <v>7.4</v>
+      </c>
+      <c r="AV15">
+        <v>16.5</v>
+      </c>
+      <c r="AW15">
+        <v>5.7</v>
+      </c>
+      <c r="AX15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>4.9</v>
+      </c>
+      <c r="BA15">
+        <v>5.7</v>
+      </c>
+      <c r="BB15">
+        <v>17.5</v>
+      </c>
+      <c r="BC15">
+        <v>18.5</v>
+      </c>
+      <c r="BD15">
+        <v>5.4</v>
+      </c>
+      <c r="BE15">
+        <v>5.9</v>
+      </c>
+      <c r="BF15">
+        <v>12.5</v>
+      </c>
+      <c r="BG15">
+        <v>5.7</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16">
+        <v>2.54</v>
+      </c>
+      <c r="G16">
+        <v>2.96</v>
+      </c>
+      <c r="H16">
+        <v>2.82</v>
+      </c>
+      <c r="I16">
+        <v>3.35</v>
+      </c>
+      <c r="J16">
+        <v>2.86</v>
+      </c>
+      <c r="K16">
+        <v>3.7</v>
+      </c>
+      <c r="L16">
+        <v>1.47</v>
+      </c>
+      <c r="M16">
+        <v>1.12</v>
+      </c>
+      <c r="N16">
         <v>3.05</v>
       </c>
-      <c r="O15">
+      <c r="O16">
         <v>1.41</v>
       </c>
-      <c r="P15">
+      <c r="P16">
         <v>1.67</v>
       </c>
-      <c r="Q15">
-        <v>2.22</v>
-      </c>
-      <c r="R15">
+      <c r="Q16">
+        <v>2.2</v>
+      </c>
+      <c r="R16">
         <v>1.24</v>
       </c>
-      <c r="S15">
+      <c r="S16">
         <v>4</v>
       </c>
-      <c r="T15">
-        <v>1.01</v>
-      </c>
-      <c r="U15">
-        <v>1.01</v>
-      </c>
-      <c r="V15">
+      <c r="T16">
+        <v>1.01</v>
+      </c>
+      <c r="U16">
+        <v>1.01</v>
+      </c>
+      <c r="V16">
         <v>1.43</v>
       </c>
-      <c r="W15">
-        <v>1.58</v>
-      </c>
-      <c r="X15">
+      <c r="W16">
+        <v>1.52</v>
+      </c>
+      <c r="X16">
         <v>21</v>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <v>21</v>
       </c>
-      <c r="Z15">
+      <c r="Z16">
         <v>100</v>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <v>900</v>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <v>18.5</v>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <v>42</v>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <v>42</v>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <v>240</v>
       </c>
-      <c r="AF15">
+      <c r="AF16">
         <v>85</v>
       </c>
-      <c r="AG15">
+      <c r="AG16">
         <v>22</v>
       </c>
-      <c r="AH15">
+      <c r="AH16">
         <v>100</v>
       </c>
-      <c r="AI15">
+      <c r="AI16">
         <v>290</v>
       </c>
-      <c r="AJ15">
+      <c r="AJ16">
         <v>900</v>
       </c>
-      <c r="AK15">
+      <c r="AK16">
         <v>200</v>
       </c>
-      <c r="AL15">
+      <c r="AL16">
         <v>180</v>
       </c>
-      <c r="AM15">
+      <c r="AM16">
         <v>450</v>
       </c>
-      <c r="AN15">
+      <c r="AN16">
         <v>600</v>
       </c>
-      <c r="AO15">
+      <c r="AO16">
         <v>600</v>
       </c>
-      <c r="AP15">
+      <c r="AP16">
         <v>2.5</v>
       </c>
-      <c r="AQ15">
+      <c r="AQ16">
         <v>2.5</v>
       </c>
-      <c r="AR15">
+      <c r="AR16">
         <v>2.5</v>
       </c>
-      <c r="AS15">
+      <c r="AS16">
         <v>2.5</v>
       </c>
-      <c r="AT15">
+      <c r="AT16">
         <v>2.5</v>
       </c>
-      <c r="AU15">
+      <c r="AU16">
         <v>4.2</v>
       </c>
-      <c r="AV15">
+      <c r="AV16">
         <v>2.5</v>
       </c>
-      <c r="AW15">
+      <c r="AW16">
         <v>2.5</v>
       </c>
-      <c r="AX15">
+      <c r="AX16">
         <v>2.5</v>
       </c>
-      <c r="AY15">
+      <c r="AY16">
         <v>2.5</v>
       </c>
-      <c r="AZ15">
+      <c r="AZ16">
         <v>2.5</v>
       </c>
-      <c r="BA15">
+      <c r="BA16">
         <v>2.5</v>
       </c>
-      <c r="BB15">
+      <c r="BB16">
         <v>2.5</v>
       </c>
-      <c r="BC15">
+      <c r="BC16">
         <v>2.5</v>
       </c>
-      <c r="BD15">
+      <c r="BD16">
         <v>2.5</v>
       </c>
-      <c r="BE15">
+      <c r="BE16">
         <v>2.5</v>
       </c>
-      <c r="BF15">
+      <c r="BF16">
         <v>1.76</v>
       </c>
-      <c r="BG15">
+      <c r="BG16">
         <v>1.55</v>
       </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.01</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.01</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.01</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.01</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.01</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>1.01</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15">
-        <v>1000</v>
-      </c>
-      <c r="CA15">
-        <v>1.01</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>126</v>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -400,7 +400,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 12:25:55</t>
+    <t>2026-09-19 14:52:55</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1018,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O2">
         <v>1.12</v>
@@ -1033,7 +1033,7 @@
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T2">
         <v>1.79</v>
@@ -1045,7 +1045,7 @@
         <v>1.1</v>
       </c>
       <c r="W2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X2">
         <v>50</v>
@@ -1057,10 +1057,10 @@
         <v>130</v>
       </c>
       <c r="AA2">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
         <v>19</v>
@@ -1069,7 +1069,7 @@
         <v>38</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1078,7 +1078,7 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2">
         <v>110</v>
@@ -1090,52 +1090,52 @@
         <v>14</v>
       </c>
       <c r="AL2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM2">
         <v>130</v>
       </c>
       <c r="AN2">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AO2">
         <v>130</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
         <v>32</v>
       </c>
       <c r="AR2">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AV2">
         <v>26</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB2">
         <v>10</v>
@@ -1147,13 +1147,13 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
         <v>3.2</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1174,7 +1174,7 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
         <v>3.4</v>
@@ -1239,49 +1239,49 @@
         <v>1.79</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U3">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V3">
         <v>1.26</v>
@@ -1290,115 +1290,115 @@
         <v>2.12</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB3">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AG3">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP3">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR3">
-        <v>1.37</v>
+        <v>8</v>
       </c>
       <c r="AS3">
-        <v>1.37</v>
+        <v>9.4</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>1.37</v>
+        <v>9</v>
       </c>
       <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
+        <v>16.5</v>
+      </c>
+      <c r="BA3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB3">
+        <v>16.5</v>
+      </c>
+      <c r="BC3">
+        <v>16</v>
+      </c>
+      <c r="BD3">
         <v>7.8</v>
       </c>
-      <c r="AY3">
-        <v>7.4</v>
-      </c>
-      <c r="AZ3">
-        <v>1.37</v>
-      </c>
-      <c r="BA3">
-        <v>1.37</v>
-      </c>
-      <c r="BB3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC3">
-        <v>12.5</v>
-      </c>
-      <c r="BD3">
-        <v>1.37</v>
-      </c>
       <c r="BE3">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>1.37</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
         <v>3.15</v>
@@ -1416,7 +1416,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
         <v>3.65</v>
@@ -1434,7 +1434,7 @@
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
         <v>6.4</v>
@@ -1481,7 +1481,7 @@
         <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
         <v>3.9</v>
@@ -1490,7 +1490,7 @@
         <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K4">
         <v>3.15</v>
@@ -1499,148 +1499,148 @@
         <v>1.63</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O4">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="P4">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S4">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
+        <v>1.69</v>
+      </c>
+      <c r="V4">
+        <v>1.32</v>
+      </c>
+      <c r="W4">
         <v>1.7</v>
       </c>
-      <c r="V4">
-        <v>1.31</v>
-      </c>
-      <c r="W4">
-        <v>1.69</v>
-      </c>
       <c r="X4">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE4">
         <v>1000</v>
       </c>
       <c r="AF4">
+        <v>12.5</v>
+      </c>
+      <c r="AG4">
+        <v>13.5</v>
+      </c>
+      <c r="AH4">
+        <v>32</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>40</v>
+      </c>
+      <c r="AK4">
+        <v>44</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>290</v>
+      </c>
+      <c r="AN4">
+        <v>50</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>6.6</v>
+      </c>
+      <c r="AQ4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR4">
+        <v>16.5</v>
+      </c>
+      <c r="AS4">
+        <v>36</v>
+      </c>
+      <c r="AT4">
+        <v>6</v>
+      </c>
+      <c r="AU4">
+        <v>6.4</v>
+      </c>
+      <c r="AV4">
+        <v>16.5</v>
+      </c>
+      <c r="AW4">
+        <v>32</v>
+      </c>
+      <c r="AX4">
+        <v>11.5</v>
+      </c>
+      <c r="AY4">
+        <v>12</v>
+      </c>
+      <c r="AZ4">
+        <v>25</v>
+      </c>
+      <c r="BA4">
+        <v>42</v>
+      </c>
+      <c r="BB4">
+        <v>21</v>
+      </c>
+      <c r="BC4">
+        <v>23</v>
+      </c>
+      <c r="BD4">
+        <v>36</v>
+      </c>
+      <c r="BE4">
+        <v>55</v>
+      </c>
+      <c r="BF4">
         <v>24</v>
       </c>
-      <c r="AG4">
-        <v>36</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>5.6</v>
-      </c>
-      <c r="AQ4">
-        <v>7</v>
-      </c>
-      <c r="AR4">
-        <v>1.75</v>
-      </c>
-      <c r="AS4">
-        <v>1.75</v>
-      </c>
-      <c r="AT4">
-        <v>5.2</v>
-      </c>
-      <c r="AU4">
-        <v>5.6</v>
-      </c>
-      <c r="AV4">
-        <v>1.75</v>
-      </c>
-      <c r="AW4">
-        <v>1.75</v>
-      </c>
-      <c r="AX4">
-        <v>1.63</v>
-      </c>
-      <c r="AY4">
-        <v>1.67</v>
-      </c>
-      <c r="AZ4">
-        <v>1.75</v>
-      </c>
-      <c r="BA4">
-        <v>1.75</v>
-      </c>
-      <c r="BB4">
-        <v>1.75</v>
-      </c>
-      <c r="BC4">
-        <v>1.75</v>
-      </c>
-      <c r="BD4">
-        <v>1.75</v>
-      </c>
-      <c r="BE4">
-        <v>1.75</v>
-      </c>
-      <c r="BF4">
-        <v>1.75</v>
-      </c>
       <c r="BG4">
-        <v>1.75</v>
+        <v>40</v>
       </c>
       <c r="BH4">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
         <v>2.18</v>
@@ -1658,7 +1658,7 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
         <v>3.95</v>
@@ -1720,10 +1720,10 @@
         <v>116</v>
       </c>
       <c r="F5">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G5">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H5">
         <v>1.85</v>
@@ -1735,7 +1735,7 @@
         <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1744,7 +1744,7 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
         <v>1.31</v>
@@ -1753,13 +1753,13 @@
         <v>1.91</v>
       </c>
       <c r="Q5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="T5">
         <v>1.82</v>
@@ -1771,7 +1771,7 @@
         <v>2</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1962,19 +1962,19 @@
         <v>117</v>
       </c>
       <c r="F6">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H6">
         <v>2.76</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
         <v>3.95</v>
@@ -1989,7 +1989,7 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
         <v>2.18</v>
@@ -1998,7 +1998,7 @@
         <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S6">
         <v>2.82</v>
@@ -2007,130 +2007,130 @@
         <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y6">
+        <v>14.5</v>
+      </c>
+      <c r="Z6">
+        <v>22</v>
+      </c>
+      <c r="AA6">
+        <v>55</v>
+      </c>
+      <c r="AB6">
+        <v>13.5</v>
+      </c>
+      <c r="AC6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>13.5</v>
+      </c>
+      <c r="AE6">
+        <v>30</v>
+      </c>
+      <c r="AF6">
+        <v>19</v>
+      </c>
+      <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
+        <v>16</v>
+      </c>
+      <c r="AI6">
+        <v>42</v>
+      </c>
+      <c r="AJ6">
         <v>44</v>
       </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>36</v>
-      </c>
-      <c r="AC6">
-        <v>13</v>
-      </c>
-      <c r="AD6">
-        <v>30</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>25</v>
-      </c>
-      <c r="AH6">
-        <v>70</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP6">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6">
+        <v>12.5</v>
+      </c>
+      <c r="AR6">
+        <v>18.5</v>
+      </c>
+      <c r="AS6">
+        <v>7.6</v>
+      </c>
+      <c r="AT6">
         <v>11.5</v>
       </c>
-      <c r="AQ6">
-        <v>9.4</v>
-      </c>
-      <c r="AR6">
-        <v>12</v>
-      </c>
-      <c r="AS6">
-        <v>1.33</v>
-      </c>
-      <c r="AT6">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>1.33</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AY6">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="BB6">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="BC6">
-        <v>1.33</v>
+        <v>6.8</v>
       </c>
       <c r="BD6">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="BE6">
-        <v>1.33</v>
+        <v>8</v>
       </c>
       <c r="BF6">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BG6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
         <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
         <v>6.4</v>
@@ -2142,7 +2142,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
         <v>4.5</v>
@@ -2160,7 +2160,7 @@
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
         <v>4.8</v>
@@ -2204,166 +2204,166 @@
         <v>118</v>
       </c>
       <c r="F7">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G7">
         <v>2.56</v>
       </c>
       <c r="H7">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>2.16</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
         <v>1.64</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP7">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="AR7">
-        <v>1.31</v>
+        <v>18.5</v>
       </c>
       <c r="AS7">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="AT7">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>1.31</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="AX7">
-        <v>1.31</v>
+        <v>14</v>
       </c>
       <c r="AY7">
-        <v>1.25</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>1.31</v>
+        <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>1.31</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>1.31</v>
+        <v>5.8</v>
       </c>
       <c r="BC7">
-        <v>1.31</v>
+        <v>5.6</v>
       </c>
       <c r="BD7">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>1.31</v>
+        <v>6.2</v>
       </c>
       <c r="BF7">
-        <v>1.31</v>
+        <v>5.7</v>
       </c>
       <c r="BG7">
-        <v>1.31</v>
+        <v>6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2470,7 +2470,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
         <v>1.01</v>
@@ -2494,7 +2494,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
         <v>2.3</v>
@@ -2691,13 +2691,13 @@
         <v>2.28</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I9">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
         <v>3.7</v>
@@ -2709,7 +2709,7 @@
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
         <v>4.1</v>
@@ -2718,16 +2718,16 @@
         <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R9">
         <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T9">
         <v>1.57</v>
@@ -2736,10 +2736,10 @@
         <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2957,19 +2957,19 @@
         <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
         <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R10">
         <v>1.24</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3432,202 +3432,202 @@
         <v>900</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
+        <v>1.25</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
         <v>1.24</v>
       </c>
-      <c r="Q12">
-        <v>1.01</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>125</v>
       </c>
       <c r="F14">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="G14">
         <v>3.65</v>
@@ -3907,13 +3907,13 @@
         <v>2.52</v>
       </c>
       <c r="I14">
+        <v>2.78</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
         <v>3.1</v>
-      </c>
-      <c r="J14">
-        <v>2.78</v>
-      </c>
-      <c r="K14">
-        <v>3.4</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>1.5</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4140,10 +4140,10 @@
         <v>126</v>
       </c>
       <c r="F15">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G15">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H15">
         <v>4.7</v>
@@ -4155,7 +4155,7 @@
         <v>3.65</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>1.82</v>
       </c>
       <c r="Q15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC15">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD15">
         <v>22</v>
@@ -4254,10 +4254,10 @@
         <v>13</v>
       </c>
       <c r="AR15">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS15">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT15">
         <v>7.2</v>
@@ -4269,7 +4269,7 @@
         <v>16.5</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX15">
         <v>9.800000000000001</v>
@@ -4278,10 +4278,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BA15">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
         <v>17.5</v>
@@ -4290,16 +4290,16 @@
         <v>18.5</v>
       </c>
       <c r="BD15">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE15">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF15">
         <v>12.5</v>
       </c>
       <c r="BG15">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH15">
         <v>0</v>
@@ -4382,166 +4382,166 @@
         <v>127</v>
       </c>
       <c r="F16">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G16">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="H16">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="I16">
+        <v>3.1</v>
+      </c>
+      <c r="J16">
+        <v>3.15</v>
+      </c>
+      <c r="K16">
         <v>3.35</v>
-      </c>
-      <c r="J16">
-        <v>2.86</v>
-      </c>
-      <c r="K16">
-        <v>3.7</v>
       </c>
       <c r="L16">
         <v>1.47</v>
       </c>
       <c r="M16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
         <v>1.41</v>
       </c>
       <c r="P16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q16">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T16">
         <v>1.01</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X16">
+        <v>11.5</v>
+      </c>
+      <c r="Y16">
+        <v>11</v>
+      </c>
+      <c r="Z16">
         <v>21</v>
       </c>
-      <c r="Y16">
-        <v>21</v>
-      </c>
-      <c r="Z16">
-        <v>100</v>
-      </c>
       <c r="AA16">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AC16">
+        <v>7.8</v>
+      </c>
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16">
         <v>42</v>
       </c>
-      <c r="AD16">
-        <v>42</v>
-      </c>
-      <c r="AE16">
-        <v>240</v>
-      </c>
       <c r="AF16">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="AG16">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AI16">
         <v>290</v>
       </c>
       <c r="AJ16">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AK16">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="AL16">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="AM16">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN16">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AO16">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AP16">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ16">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16">
-        <v>2.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT16">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU16">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV16">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX16">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="BA16">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB16">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC16">
-        <v>2.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE16">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16">
-        <v>1.76</v>
+        <v>7.2</v>
       </c>
       <c r="BG16">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH16">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -400,7 +400,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 14:52:55</t>
+    <t>2026-09-19 17:17:41</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J2">
         <v>7.2</v>
@@ -1030,7 +1030,7 @@
         <v>1.38</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
         <v>1.96</v>
@@ -1045,10 +1045,10 @@
         <v>1.1</v>
       </c>
       <c r="W2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Y2">
         <v>50</v>
@@ -1063,7 +1063,7 @@
         <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AD2">
         <v>38</v>
@@ -1075,70 +1075,70 @@
         <v>11</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
+        <v>27</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+      <c r="AJ2">
+        <v>11.5</v>
+      </c>
+      <c r="AK2">
+        <v>12.5</v>
+      </c>
+      <c r="AL2">
         <v>28</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>110</v>
       </c>
-      <c r="AJ2">
-        <v>12</v>
-      </c>
-      <c r="AK2">
-        <v>14</v>
-      </c>
-      <c r="AL2">
-        <v>29</v>
-      </c>
-      <c r="AM2">
-        <v>130</v>
-      </c>
       <c r="AN2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AO2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU2">
         <v>16</v>
       </c>
       <c r="AV2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AW2">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>22</v>
       </c>
       <c r="BA2">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
@@ -1147,13 +1147,13 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BF2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1236,10 +1236,10 @@
         <v>114</v>
       </c>
       <c r="F3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G3">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H3">
         <v>4.5</v>
@@ -1260,7 +1260,7 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
         <v>1.27</v>
@@ -1269,7 +1269,7 @@
         <v>2.14</v>
       </c>
       <c r="Q3">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
         <v>1.45</v>
@@ -1278,7 +1278,7 @@
         <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
         <v>2.18</v>
@@ -1287,7 +1287,7 @@
         <v>1.26</v>
       </c>
       <c r="W3">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1311,7 +1311,7 @@
         <v>19</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF3">
         <v>12</v>
@@ -1326,7 +1326,7 @@
         <v>90</v>
       </c>
       <c r="AJ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK3">
         <v>19</v>
@@ -1344,16 +1344,16 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
       </c>
       <c r="AR3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT3">
         <v>9</v>
@@ -1377,7 +1377,7 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
@@ -1389,13 +1389,13 @@
         <v>7.8</v>
       </c>
       <c r="BE3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
         <v>9.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1493,7 +1493,7 @@
         <v>2.94</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
         <v>1.63</v>
@@ -1502,22 +1502,22 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P4">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
         <v>3</v>
       </c>
       <c r="R4">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T4">
         <v>2.36</v>
@@ -1538,7 +1538,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1586,7 +1586,7 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
         <v>8.800000000000001</v>
@@ -1598,7 +1598,7 @@
         <v>36</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
@@ -1723,34 +1723,34 @@
         <v>4.6</v>
       </c>
       <c r="G5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
         <v>1.85</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="J5">
         <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
         <v>2</v>
@@ -1768,16 +1768,16 @@
         <v>1.9</v>
       </c>
       <c r="V5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X5">
         <v>1000</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z5">
         <v>22</v>
@@ -1789,7 +1789,7 @@
         <v>1000</v>
       </c>
       <c r="AC5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>18.5</v>
@@ -1813,7 +1813,7 @@
         <v>1000</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL5">
         <v>1000</v>
@@ -1825,61 +1825,61 @@
         <v>1000</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP5">
-        <v>1.34</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5">
-        <v>1.22</v>
+        <v>7.2</v>
       </c>
       <c r="AR5">
-        <v>1.26</v>
+        <v>9.6</v>
       </c>
       <c r="AS5">
-        <v>1.34</v>
+        <v>18</v>
       </c>
       <c r="AT5">
-        <v>1.34</v>
+        <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>1.21</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>1.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5">
-        <v>1.34</v>
+        <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AY5">
-        <v>1.34</v>
+        <v>16</v>
       </c>
       <c r="AZ5">
-        <v>1.34</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="BB5">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="BC5">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="BD5">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="BE5">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="BF5">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="BG5">
-        <v>1.34</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1974,7 +1974,7 @@
         <v>2.98</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K6">
         <v>3.95</v>
@@ -1986,28 +1986,28 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
         <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
         <v>2.82</v>
       </c>
       <c r="T6">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
         <v>1.51</v>
@@ -2052,7 +2052,7 @@
         <v>42</v>
       </c>
       <c r="AJ6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK6">
         <v>32</v>
@@ -2067,7 +2067,7 @@
         <v>17.5</v>
       </c>
       <c r="AO6">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
@@ -2079,7 +2079,7 @@
         <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6">
         <v>11.5</v>
@@ -2091,7 +2091,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
         <v>16</v>
@@ -2103,25 +2103,25 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
+        <v>7.6</v>
+      </c>
+      <c r="BB6">
+        <v>7.6</v>
+      </c>
+      <c r="BC6">
         <v>7.2</v>
       </c>
-      <c r="BB6">
-        <v>7.2</v>
-      </c>
-      <c r="BC6">
-        <v>6.8</v>
-      </c>
       <c r="BD6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF6">
         <v>15</v>
       </c>
       <c r="BG6">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2216,7 +2216,7 @@
         <v>3.35</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
         <v>3.55</v>
@@ -2246,7 +2246,7 @@
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
         <v>2.08</v>
@@ -2267,13 +2267,13 @@
         <v>25</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7">
         <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
         <v>14</v>
@@ -2324,7 +2324,7 @@
         <v>6</v>
       </c>
       <c r="AT7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
@@ -2333,37 +2333,37 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AX7">
         <v>14</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB7">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD7">
         <v>6</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF7">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2455,7 +2455,7 @@
         <v>2.36</v>
       </c>
       <c r="I8">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>4.1</v>
@@ -2691,13 +2691,13 @@
         <v>2.28</v>
       </c>
       <c r="G9">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H9">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J9">
         <v>3.7</v>
@@ -2712,7 +2712,7 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -2724,10 +2724,10 @@
         <v>1.69</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T9">
         <v>1.57</v>
@@ -2739,7 +2739,7 @@
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2978,10 +2978,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3447,7 +3447,7 @@
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12">
         <v>1.24</v>
@@ -3898,226 +3898,226 @@
         <v>125</v>
       </c>
       <c r="F14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G14">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H14">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I14">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
       <c r="K14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q14">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="CB14" t="s">
         <v>128</v>
@@ -4143,7 +4143,7 @@
         <v>1.84</v>
       </c>
       <c r="G15">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H15">
         <v>4.7</v>
@@ -4152,22 +4152,22 @@
         <v>5.1</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
         <v>3.85</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
         <v>1.82</v>
@@ -4176,10 +4176,10 @@
         <v>2.08</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T15">
         <v>1.92</v>
@@ -4188,10 +4188,10 @@
         <v>1.94</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X15">
         <v>15</v>
@@ -4278,7 +4278,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
         <v>6.2</v>
@@ -4302,64 +4302,64 @@
         <v>6.2</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>128</v>
@@ -4382,31 +4382,31 @@
         <v>127</v>
       </c>
       <c r="F16">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G16">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H16">
         <v>2.9</v>
       </c>
       <c r="I16">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J16">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K16">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L16">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.11</v>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>1.41</v>
@@ -4421,19 +4421,19 @@
         <v>1.25</v>
       </c>
       <c r="S16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U16">
         <v>1.96</v>
       </c>
       <c r="V16">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X16">
         <v>11.5</v>
@@ -4445,13 +4445,13 @@
         <v>21</v>
       </c>
       <c r="AA16">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD16">
         <v>14</v>
@@ -4469,7 +4469,7 @@
         <v>20</v>
       </c>
       <c r="AI16">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
         <v>46</v>
@@ -4481,7 +4481,7 @@
         <v>55</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="AN16">
         <v>36</v>
@@ -4493,25 +4493,25 @@
         <v>9.4</v>
       </c>
       <c r="AQ16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR16">
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT16">
         <v>8.199999999999999</v>
       </c>
       <c r="AU16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV16">
         <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX16">
         <v>14.5</v>
@@ -4523,25 +4523,25 @@
         <v>16</v>
       </c>
       <c r="BA16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB16">
         <v>7.8</v>
       </c>
-      <c r="BB16">
+      <c r="BC16">
         <v>7.4</v>
       </c>
-      <c r="BC16">
-        <v>14.5</v>
-      </c>
       <c r="BD16">
+        <v>8</v>
+      </c>
+      <c r="BE16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF16">
         <v>7.4</v>
       </c>
-      <c r="BE16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF16">
-        <v>7.2</v>
-      </c>
       <c r="BG16">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH16">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -400,7 +400,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 17:17:41</t>
+    <t>2026-09-19 19:42:56</t>
   </si>
 </sst>
 </file>
@@ -994,10 +994,10 @@
         <v>113</v>
       </c>
       <c r="F2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -1012,40 +1012,40 @@
         <v>8</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2">
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q2">
         <v>1.38</v>
       </c>
       <c r="R2">
+        <v>1.96</v>
+      </c>
+      <c r="S2">
         <v>1.97</v>
       </c>
-      <c r="S2">
-        <v>1.96</v>
-      </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
         <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X2">
         <v>46</v>
@@ -1096,22 +1096,22 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
         <v>44</v>
       </c>
       <c r="AR2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1123,10 +1123,10 @@
         <v>34</v>
       </c>
       <c r="AW2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1135,10 +1135,10 @@
         <v>22</v>
       </c>
       <c r="BA2">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
@@ -1150,16 +1150,16 @@
         <v>60</v>
       </c>
       <c r="BF2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
@@ -1183,7 +1183,7 @@
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1236,19 +1236,19 @@
         <v>114</v>
       </c>
       <c r="F3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G3">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
         <v>4.9</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
         <v>4.3</v>
@@ -1263,13 +1263,13 @@
         <v>4.3</v>
       </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R3">
         <v>1.45</v>
@@ -1287,7 +1287,7 @@
         <v>1.26</v>
       </c>
       <c r="W3">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1296,10 +1296,10 @@
         <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1344,16 +1344,16 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
       </c>
       <c r="AR3">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AS3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3">
         <v>9</v>
@@ -1386,16 +1386,16 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
         <v>9.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1487,7 +1487,7 @@
         <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
         <v>2.94</v>
@@ -1502,7 +1502,7 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O4">
         <v>1.66</v>
@@ -1520,10 +1520,10 @@
         <v>6.6</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V4">
         <v>1.32</v>
@@ -1619,7 +1619,7 @@
         <v>25</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB4">
         <v>21</v>
@@ -1667,7 +1667,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1729,13 +1729,13 @@
         <v>1.85</v>
       </c>
       <c r="I5">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1744,10 +1744,10 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
         <v>1.89</v>
@@ -1762,10 +1762,10 @@
         <v>3.4</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
         <v>2.04</v>
@@ -1774,58 +1774,58 @@
         <v>1.23</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK5">
         <v>85</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP5">
         <v>11.5</v>
@@ -1843,7 +1843,7 @@
         <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>8.800000000000001</v>
@@ -1852,31 +1852,31 @@
         <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>1.57</v>
+        <v>4.6</v>
       </c>
       <c r="AY5">
         <v>16</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>1.57</v>
+        <v>4.7</v>
       </c>
       <c r="BB5">
-        <v>1.57</v>
+        <v>5</v>
       </c>
       <c r="BC5">
-        <v>1.54</v>
+        <v>4.9</v>
       </c>
       <c r="BD5">
-        <v>1.57</v>
+        <v>4.9</v>
       </c>
       <c r="BE5">
-        <v>1.57</v>
+        <v>5</v>
       </c>
       <c r="BF5">
-        <v>1.57</v>
+        <v>4.9</v>
       </c>
       <c r="BG5">
         <v>11.5</v>
@@ -1965,7 +1965,7 @@
         <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H6">
         <v>2.76</v>
@@ -1986,28 +1986,28 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
         <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="T6">
         <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
         <v>1.51</v>
@@ -2037,7 +2037,7 @@
         <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF6">
         <v>19</v>
@@ -2058,7 +2058,7 @@
         <v>32</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6">
         <v>85</v>
@@ -2228,22 +2228,22 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Q7">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
         <v>1.83</v>
@@ -2273,7 +2273,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
         <v>14</v>
@@ -2321,7 +2321,7 @@
         <v>18.5</v>
       </c>
       <c r="AS7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT7">
         <v>8.6</v>
@@ -2333,7 +2333,7 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX7">
         <v>14</v>
@@ -2345,25 +2345,25 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
+        <v>6.4</v>
+      </c>
+      <c r="BB7">
         <v>6</v>
       </c>
-      <c r="BB7">
-        <v>5.7</v>
-      </c>
       <c r="BC7">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2452,13 +2452,13 @@
         <v>1.76</v>
       </c>
       <c r="H8">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>880</v>
@@ -2688,22 +2688,22 @@
         <v>120</v>
       </c>
       <c r="F9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G9">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H9">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
         <v>3.7</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2727,7 +2727,7 @@
         <v>1.45</v>
       </c>
       <c r="S9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T9">
         <v>1.57</v>
@@ -2739,7 +2739,7 @@
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3441,7 +3441,7 @@
         <v>1.25</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
         <v>1.25</v>
@@ -3659,10 +3659,10 @@
         <v>1.56</v>
       </c>
       <c r="G13">
-        <v>5.4</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I13">
         <v>3.15</v>
@@ -3901,10 +3901,10 @@
         <v>3.3</v>
       </c>
       <c r="G14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H14">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I14">
         <v>2.74</v>
@@ -3922,22 +3922,22 @@
         <v>1.12</v>
       </c>
       <c r="N14">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O14">
         <v>1.57</v>
       </c>
       <c r="P14">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q14">
         <v>2.78</v>
       </c>
       <c r="R14">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S14">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>2.2</v>
@@ -3946,10 +3946,10 @@
         <v>1.72</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -4006,7 +4006,7 @@
         <v>60</v>
       </c>
       <c r="AP14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ14">
         <v>6.8</v>
@@ -4045,7 +4045,7 @@
         <v>9.4</v>
       </c>
       <c r="BC14">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BD14">
         <v>9.6</v>
@@ -4140,13 +4140,13 @@
         <v>126</v>
       </c>
       <c r="F15">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G15">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H15">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
         <v>5.1</v>
@@ -4164,10 +4164,10 @@
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P15">
         <v>1.82</v>
@@ -4179,7 +4179,7 @@
         <v>1.31</v>
       </c>
       <c r="S15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T15">
         <v>1.92</v>
@@ -4191,7 +4191,7 @@
         <v>1.24</v>
       </c>
       <c r="W15">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X15">
         <v>15</v>
@@ -4242,7 +4242,7 @@
         <v>150</v>
       </c>
       <c r="AN15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15">
         <v>95</v>
@@ -4254,7 +4254,7 @@
         <v>13</v>
       </c>
       <c r="AR15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS15">
         <v>6.2</v>
@@ -4278,10 +4278,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB15">
         <v>17.5</v>
@@ -4290,7 +4290,7 @@
         <v>18.5</v>
       </c>
       <c r="BD15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE15">
         <v>6.2</v>
@@ -4299,7 +4299,7 @@
         <v>12.5</v>
       </c>
       <c r="BG15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4382,13 +4382,13 @@
         <v>127</v>
       </c>
       <c r="F16">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G16">
         <v>2.9</v>
       </c>
       <c r="H16">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
         <v>3.15</v>
@@ -4397,7 +4397,7 @@
         <v>3.05</v>
       </c>
       <c r="K16">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4415,7 +4415,7 @@
         <v>1.68</v>
       </c>
       <c r="Q16">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R16">
         <v>1.25</v>
@@ -4427,7 +4427,7 @@
         <v>1.88</v>
       </c>
       <c r="U16">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V16">
         <v>1.46</v>
@@ -4439,7 +4439,7 @@
         <v>11.5</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z16">
         <v>21</v>
@@ -4481,7 +4481,7 @@
         <v>55</v>
       </c>
       <c r="AM16">
-        <v>530</v>
+        <v>430</v>
       </c>
       <c r="AN16">
         <v>36</v>
@@ -4493,16 +4493,16 @@
         <v>9.4</v>
       </c>
       <c r="AQ16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16">
         <v>16.5</v>
       </c>
       <c r="AS16">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
         <v>6.4</v>
@@ -4511,37 +4511,37 @@
         <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16">
         <v>14.5</v>
       </c>
       <c r="AY16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
         <v>16</v>
       </c>
       <c r="BA16">
+        <v>8.4</v>
+      </c>
+      <c r="BB16">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB16">
-        <v>7.8</v>
-      </c>
       <c r="BC16">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD16">
+        <v>8.4</v>
+      </c>
+      <c r="BE16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16">
         <v>8</v>
       </c>
-      <c r="BE16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF16">
-        <v>7.4</v>
-      </c>
       <c r="BG16">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH16">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -400,7 +400,7 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 19:42:56</t>
+    <t>2026-09-19 22:06:37</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
         <v>113</v>
       </c>
       <c r="F2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G2">
         <v>1.3</v>
@@ -1009,10 +1009,10 @@
         <v>7.2</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L2">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="M2">
         <v>1.01</v>
@@ -1024,22 +1024,22 @@
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R2">
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="T2">
         <v>1.78</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.09</v>
@@ -1051,25 +1051,25 @@
         <v>46</v>
       </c>
       <c r="Y2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Z2">
         <v>130</v>
       </c>
       <c r="AA2">
-        <v>360</v>
+        <v>490</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
         <v>17.5</v>
       </c>
       <c r="AD2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1081,10 +1081,10 @@
         <v>27</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK2">
         <v>12.5</v>
@@ -1096,34 +1096,34 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AO2">
         <v>110</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AQ2">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AT2">
         <v>13</v>
       </c>
       <c r="AU2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV2">
         <v>34</v>
       </c>
       <c r="AW2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1132,13 +1132,13 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
@@ -1147,73 +1147,73 @@
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG2">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.4</v>
+        <v>1.18</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.3</v>
+        <v>1.22</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="CB2" t="s">
         <v>128</v>
@@ -1236,19 +1236,19 @@
         <v>114</v>
       </c>
       <c r="F3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H3">
         <v>4.3</v>
       </c>
       <c r="I3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.3</v>
@@ -1257,7 +1257,7 @@
         <v>1.33</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
         <v>4.3</v>
@@ -1275,16 +1275,16 @@
         <v>1.45</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U3">
         <v>2.18</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
         <v>2.12</v>
@@ -1344,7 +1344,7 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
@@ -1401,61 +1401,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>1.51</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.65</v>
+        <v>1.61</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>2.32</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>1.94</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="CB3" t="s">
         <v>128</v>
@@ -1490,7 +1490,7 @@
         <v>4.1</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K4">
         <v>3.1</v>
@@ -1511,7 +1511,7 @@
         <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R4">
         <v>1.16</v>
@@ -1550,7 +1550,7 @@
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1571,7 +1571,7 @@
         <v>40</v>
       </c>
       <c r="AK4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1601,10 +1601,10 @@
         <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW4">
         <v>32</v>
@@ -1613,7 +1613,7 @@
         <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
         <v>25</v>
@@ -1729,7 +1729,7 @@
         <v>1.85</v>
       </c>
       <c r="I5">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="J5">
         <v>3.6</v>
@@ -1744,7 +1744,7 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>1.34</v>
@@ -1753,19 +1753,19 @@
         <v>1.89</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
         <v>2.04</v>
@@ -1861,22 +1861,22 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC5">
+        <v>4.8</v>
+      </c>
+      <c r="BD5">
+        <v>4.8</v>
+      </c>
+      <c r="BE5">
         <v>4.9</v>
       </c>
-      <c r="BD5">
-        <v>4.9</v>
-      </c>
-      <c r="BE5">
-        <v>5</v>
-      </c>
       <c r="BF5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG5">
         <v>11.5</v>
@@ -1965,7 +1965,7 @@
         <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H6">
         <v>2.76</v>
@@ -1980,19 +1980,19 @@
         <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
         <v>1.73</v>
@@ -2001,7 +2001,7 @@
         <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
         <v>1.64</v>
@@ -2124,64 +2124,64 @@
         <v>18.5</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO6">
         <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
         <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW6">
+        <v>14.5</v>
+      </c>
+      <c r="BX6">
+        <v>44</v>
+      </c>
+      <c r="BY6">
+        <v>17.5</v>
+      </c>
+      <c r="BZ6">
+        <v>30</v>
+      </c>
+      <c r="CA6">
         <v>12</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.01</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>128</v>
@@ -2204,22 +2204,22 @@
         <v>118</v>
       </c>
       <c r="F7">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G7">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2234,136 +2234,136 @@
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
         <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
         <v>1.64</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>1.24</v>
       </c>
       <c r="AR7">
-        <v>18.5</v>
+        <v>1.3</v>
       </c>
       <c r="AS7">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="AT7">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>1.15</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>1.3</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>1.3</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="AZ7">
-        <v>15.5</v>
+        <v>1.3</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="BB7">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="BC7">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="BD7">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="BF7">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="BG7">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2688,22 +2688,22 @@
         <v>120</v>
       </c>
       <c r="F9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G9">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="H9">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="I9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J9">
         <v>3.7</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2736,10 +2736,10 @@
         <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -4009,7 +4009,7 @@
         <v>7</v>
       </c>
       <c r="AQ14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR14">
         <v>13</v>
@@ -4027,7 +4027,7 @@
         <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AX14">
         <v>18</v>
@@ -4140,7 +4140,7 @@
         <v>126</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G15">
         <v>1.91</v>
@@ -4164,22 +4164,22 @@
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O15">
         <v>1.37</v>
       </c>
       <c r="P15">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R15">
         <v>1.31</v>
       </c>
       <c r="S15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T15">
         <v>1.92</v>
@@ -4212,7 +4212,7 @@
         <v>8.4</v>
       </c>
       <c r="AD15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE15">
         <v>80</v>
@@ -4242,7 +4242,7 @@
         <v>150</v>
       </c>
       <c r="AN15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO15">
         <v>95</v>
@@ -4254,10 +4254,10 @@
         <v>13</v>
       </c>
       <c r="AR15">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT15">
         <v>7.2</v>
@@ -4269,7 +4269,7 @@
         <v>16.5</v>
       </c>
       <c r="AW15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX15">
         <v>9.800000000000001</v>
@@ -4278,10 +4278,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
         <v>17.5</v>
@@ -4290,16 +4290,16 @@
         <v>18.5</v>
       </c>
       <c r="BD15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF15">
         <v>12.5</v>
       </c>
       <c r="BG15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
         <v>127</v>
       </c>
       <c r="F16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G16">
         <v>2.9</v>
@@ -4412,7 +4412,7 @@
         <v>1.41</v>
       </c>
       <c r="P16">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q16">
         <v>2.24</v>
@@ -4481,7 +4481,7 @@
         <v>55</v>
       </c>
       <c r="AM16">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="AN16">
         <v>36</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="143">
   <si>
     <t>League</t>
   </si>
@@ -265,21 +265,30 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Honduras Liga Nacional</t>
+  </si>
+  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
     <t>Slovakian 2 Liga</t>
   </si>
   <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
     <t>Danish 1st Division</t>
   </si>
   <si>
-    <t>Swedish Division 1</t>
-  </si>
-  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
     <t>2026-09-21</t>
   </si>
   <si>
@@ -292,6 +301,9 @@
     <t>01:15:00</t>
   </si>
   <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
     <t>02:05:00</t>
   </si>
   <si>
@@ -310,6 +322,12 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>Toluca</t>
   </si>
   <si>
@@ -322,6 +340,9 @@
     <t>Llaneros FC</t>
   </si>
   <si>
+    <t>Juticalpa</t>
+  </si>
+  <si>
     <t>Queretaro</t>
   </si>
   <si>
@@ -331,21 +352,21 @@
     <t>FC Petrzalka</t>
   </si>
   <si>
+    <t>Angelholms</t>
+  </si>
+  <si>
+    <t>Vasalunds IF</t>
+  </si>
+  <si>
+    <t>FC Arlanda</t>
+  </si>
+  <si>
     <t>HB Koge</t>
   </si>
   <si>
-    <t>FC Arlanda</t>
-  </si>
-  <si>
     <t>Jonkopings Sodra</t>
   </si>
   <si>
-    <t>Vasalunds IF</t>
-  </si>
-  <si>
-    <t>Angelholms</t>
-  </si>
-  <si>
     <t>Aldosivi</t>
   </si>
   <si>
@@ -355,6 +376,15 @@
     <t>Manta FC</t>
   </si>
   <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Criciuma</t>
+  </si>
+  <si>
+    <t>Central Espanol</t>
+  </si>
+  <si>
     <t>Santos Laguna</t>
   </si>
   <si>
@@ -367,6 +397,9 @@
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
+    <t>CD Marathon</t>
+  </si>
+  <si>
     <t>Leon</t>
   </si>
   <si>
@@ -376,21 +409,21 @@
     <t>Pohronie</t>
   </si>
   <si>
+    <t>Eskilsminne</t>
+  </si>
+  <si>
+    <t>Assyriska FF</t>
+  </si>
+  <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
     <t>Hobro</t>
   </si>
   <si>
-    <t>Hammarby TFF</t>
-  </si>
-  <si>
     <t>Skovde Aik</t>
   </si>
   <si>
-    <t>Assyriska FF</t>
-  </si>
-  <si>
-    <t>Eskilsminne</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -400,7 +433,16 @@
     <t>Orense Sporting Club</t>
   </si>
   <si>
-    <t>2026-09-19 22:06:37</t>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>2026-09-20 00:28:44</t>
   </si>
 </sst>
 </file>
@@ -732,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -982,22 +1024,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>1.28</v>
       </c>
       <c r="G2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -1018,7 +1060,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O2">
         <v>1.12</v>
@@ -1027,16 +1069,16 @@
         <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R2">
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="T2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
         <v>2.2</v>
@@ -1045,13 +1087,13 @@
         <v>1.09</v>
       </c>
       <c r="W2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z2">
         <v>130</v>
@@ -1060,16 +1102,16 @@
         <v>490</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
         <v>17.5</v>
       </c>
       <c r="AD2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1084,7 +1126,7 @@
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK2">
         <v>12.5</v>
@@ -1096,7 +1138,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AO2">
         <v>110</v>
@@ -1105,118 +1147,118 @@
         <v>30</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT2">
         <v>13</v>
       </c>
       <c r="AU2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV2">
         <v>34</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BF2">
         <v>3.25</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.22</v>
+        <v>4.5</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="CB2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1224,28 +1266,28 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G3">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H3">
         <v>4.3</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1260,10 +1302,10 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3">
         <v>2.16</v>
@@ -1275,28 +1317,28 @@
         <v>1.45</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T3">
         <v>1.78</v>
       </c>
       <c r="U3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V3">
         <v>1.27</v>
       </c>
       <c r="W3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y3">
         <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA3">
         <v>120</v>
@@ -1308,13 +1350,13 @@
         <v>9.4</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE3">
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1338,13 +1380,13 @@
         <v>110</v>
       </c>
       <c r="AN3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO3">
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
@@ -1353,7 +1395,7 @@
         <v>23</v>
       </c>
       <c r="AS3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3">
         <v>9</v>
@@ -1365,7 +1407,7 @@
         <v>16</v>
       </c>
       <c r="AW3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1377,7 +1419,7 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
@@ -1386,10 +1428,10 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3">
         <v>9.199999999999999</v>
@@ -1458,7 +1500,7 @@
         <v>1.17</v>
       </c>
       <c r="CB3" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1466,43 +1508,43 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F4">
         <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
         <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M4">
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O4">
         <v>1.66</v>
@@ -1529,7 +1571,7 @@
         <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1544,13 +1586,13 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1559,7 +1601,7 @@
         <v>12.5</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
         <v>32</v>
@@ -1580,7 +1622,7 @@
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1604,7 +1646,7 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
         <v>32</v>
@@ -1619,13 +1661,13 @@
         <v>25</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB4">
         <v>21</v>
       </c>
       <c r="BC4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4">
         <v>36</v>
@@ -1649,7 +1691,7 @@
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1667,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1700,7 +1742,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1708,16 +1750,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>4.6</v>
@@ -1732,34 +1774,34 @@
         <v>1.97</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
         <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T5">
         <v>1.88</v>
@@ -1786,7 +1828,7 @@
         <v>26</v>
       </c>
       <c r="AB5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC5">
         <v>8.800000000000001</v>
@@ -1831,7 +1873,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR5">
         <v>9.6</v>
@@ -1861,34 +1903,34 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB5">
+        <v>5</v>
+      </c>
+      <c r="BC5">
         <v>4.9</v>
       </c>
-      <c r="BC5">
-        <v>4.8</v>
-      </c>
       <c r="BD5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE5">
+        <v>5</v>
+      </c>
+      <c r="BF5">
         <v>4.9</v>
-      </c>
-      <c r="BF5">
-        <v>4.8</v>
       </c>
       <c r="BG5">
         <v>11.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
@@ -1900,482 +1942,482 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>110</v>
+      </c>
+      <c r="H6">
+        <v>1.28</v>
+      </c>
+      <c r="I6">
+        <v>1.98</v>
+      </c>
+      <c r="J6">
+        <v>3.1</v>
+      </c>
+      <c r="K6">
+        <v>910</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>3.85</v>
+      </c>
+      <c r="O6">
+        <v>1.01</v>
+      </c>
+      <c r="P6">
+        <v>1.26</v>
+      </c>
+      <c r="Q6">
+        <v>1.29</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>2.02</v>
+      </c>
+      <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>900</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
         <v>2.5</v>
       </c>
-      <c r="G6">
-        <v>2.66</v>
-      </c>
-      <c r="H6">
-        <v>2.76</v>
-      </c>
-      <c r="I6">
-        <v>2.98</v>
-      </c>
-      <c r="J6">
-        <v>3.65</v>
-      </c>
-      <c r="K6">
-        <v>3.95</v>
-      </c>
-      <c r="L6">
-        <v>1.33</v>
-      </c>
-      <c r="M6">
-        <v>1.05</v>
-      </c>
-      <c r="N6">
-        <v>4.6</v>
-      </c>
-      <c r="O6">
-        <v>1.24</v>
-      </c>
-      <c r="P6">
-        <v>2.2</v>
-      </c>
-      <c r="Q6">
-        <v>1.73</v>
-      </c>
-      <c r="R6">
-        <v>1.47</v>
-      </c>
-      <c r="S6">
-        <v>2.8</v>
-      </c>
-      <c r="T6">
-        <v>1.64</v>
-      </c>
-      <c r="U6">
-        <v>2.46</v>
-      </c>
-      <c r="V6">
-        <v>1.51</v>
-      </c>
-      <c r="W6">
-        <v>1.6</v>
-      </c>
-      <c r="X6">
-        <v>23</v>
-      </c>
-      <c r="Y6">
-        <v>14.5</v>
-      </c>
-      <c r="Z6">
-        <v>22</v>
-      </c>
-      <c r="AA6">
-        <v>55</v>
-      </c>
-      <c r="AB6">
-        <v>13.5</v>
-      </c>
-      <c r="AC6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6">
-        <v>13.5</v>
-      </c>
-      <c r="AE6">
-        <v>29</v>
-      </c>
-      <c r="AF6">
-        <v>19</v>
-      </c>
-      <c r="AG6">
-        <v>12.5</v>
-      </c>
-      <c r="AH6">
-        <v>16</v>
-      </c>
-      <c r="AI6">
-        <v>42</v>
-      </c>
-      <c r="AJ6">
-        <v>42</v>
-      </c>
-      <c r="AK6">
-        <v>32</v>
-      </c>
-      <c r="AL6">
-        <v>38</v>
-      </c>
-      <c r="AM6">
-        <v>85</v>
-      </c>
-      <c r="AN6">
-        <v>17.5</v>
-      </c>
-      <c r="AO6">
-        <v>22</v>
-      </c>
-      <c r="AP6">
-        <v>16.5</v>
-      </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AR6">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="AS6">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="AX6">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="AY6">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="AZ6">
-        <v>13.5</v>
+        <v>2.5</v>
       </c>
       <c r="BA6">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BB6">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BC6">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD6">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F7">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G7">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="R7">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP7">
-        <v>1.3</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7">
-        <v>1.24</v>
+        <v>12.5</v>
       </c>
       <c r="AR7">
-        <v>1.3</v>
+        <v>18.5</v>
       </c>
       <c r="AS7">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
-        <v>1.2</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>1.15</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="AX7">
-        <v>1.3</v>
+        <v>16</v>
       </c>
       <c r="AY7">
-        <v>1.24</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="BD7">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="BE7">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>1.3</v>
+        <v>15</v>
       </c>
       <c r="BG7">
-        <v>1.3</v>
+        <v>18.5</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2387,13 +2429,13 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2405,13 +2447,13 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2426,7 +2468,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2434,178 +2476,178 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>2.46</v>
       </c>
       <c r="G8">
-        <v>1.76</v>
+        <v>2.56</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>880</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P8">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2668,7 +2710,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2676,70 +2718,70 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I9">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>4.7</v>
+        <v>880</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
         <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2757,7 +2799,7 @@
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2796,7 +2838,7 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
         <v>1.01</v>
@@ -2820,13 +2862,13 @@
         <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
         <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
         <v>1.01</v>
@@ -2844,7 +2886,7 @@
         <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
         <v>1.01</v>
@@ -2910,7 +2952,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2918,34 +2960,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.59</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.61</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2954,10 +2996,10 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
         <v>1.25</v>
@@ -2978,10 +3020,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3152,7 +3194,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3160,34 +3202,34 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F11">
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>950</v>
+        <v>190</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K11">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3196,34 +3238,34 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
         <v>1.02</v>
       </c>
       <c r="P11">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
         <v>1.02</v>
       </c>
       <c r="R11">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
+        <v>1.02</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
         <v>1.03</v>
       </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.06</v>
-      </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3388,13 +3430,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3402,34 +3444,34 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F12">
         <v>1.1</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12">
         <v>1.1</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12">
         <v>1.1</v>
       </c>
       <c r="K12">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3453,7 +3495,7 @@
         <v>1.24</v>
       </c>
       <c r="S12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3462,10 +3504,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3630,84 +3672,84 @@
         <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>2.56</v>
       </c>
       <c r="H13">
-        <v>1.61</v>
+        <v>2.84</v>
       </c>
       <c r="I13">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>870</v>
+        <v>4.7</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q13">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="R13">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S13">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3725,7 +3767,7 @@
         <v>1000</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD13">
         <v>1000</v>
@@ -3878,733 +3920,1701 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14">
+        <v>1.12</v>
+      </c>
+      <c r="G14">
         <v>110</v>
       </c>
-      <c r="E14" t="s">
-        <v>125</v>
-      </c>
-      <c r="F14">
-        <v>3.3</v>
-      </c>
-      <c r="G14">
-        <v>3.55</v>
-      </c>
       <c r="H14">
-        <v>2.52</v>
+        <v>1.12</v>
       </c>
       <c r="I14">
-        <v>2.74</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="K14">
-        <v>3.2</v>
+        <v>890</v>
       </c>
       <c r="L14">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.46</v>
+        <v>1.07</v>
       </c>
       <c r="O14">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="P14">
-        <v>1.49</v>
+        <v>1.07</v>
       </c>
       <c r="Q14">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="R14">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="S14">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="W14">
-        <v>1.39</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F15">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="G15">
-        <v>1.91</v>
+        <v>3.55</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>2.46</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>3.2</v>
+      </c>
+      <c r="L15">
+        <v>1.64</v>
+      </c>
+      <c r="M15">
+        <v>1.12</v>
+      </c>
+      <c r="N15">
+        <v>2.34</v>
+      </c>
+      <c r="O15">
+        <v>1.54</v>
+      </c>
+      <c r="P15">
+        <v>1.48</v>
+      </c>
+      <c r="Q15">
+        <v>2.64</v>
+      </c>
+      <c r="R15">
+        <v>1.13</v>
+      </c>
+      <c r="S15">
+        <v>5.7</v>
+      </c>
+      <c r="T15">
+        <v>2.1</v>
+      </c>
+      <c r="U15">
+        <v>1.65</v>
+      </c>
+      <c r="V15">
+        <v>1.58</v>
+      </c>
+      <c r="W15">
+        <v>1.39</v>
+      </c>
+      <c r="X15">
+        <v>11.5</v>
+      </c>
+      <c r="Y15">
+        <v>9.6</v>
+      </c>
+      <c r="Z15">
+        <v>44</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>14</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>34</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>18</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>5.9</v>
+      </c>
+      <c r="AQ15">
+        <v>5.6</v>
+      </c>
+      <c r="AR15">
+        <v>9.4</v>
+      </c>
+      <c r="AS15">
+        <v>1.88</v>
+      </c>
+      <c r="AT15">
+        <v>6.4</v>
+      </c>
+      <c r="AU15">
+        <v>5.5</v>
+      </c>
+      <c r="AV15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15">
+        <v>1.88</v>
+      </c>
+      <c r="AX15">
+        <v>12</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
+        <v>1.88</v>
+      </c>
+      <c r="BA15">
+        <v>1.88</v>
+      </c>
+      <c r="BB15">
+        <v>1.88</v>
+      </c>
+      <c r="BC15">
+        <v>1.88</v>
+      </c>
+      <c r="BD15">
+        <v>1.88</v>
+      </c>
+      <c r="BE15">
+        <v>1.88</v>
+      </c>
+      <c r="BF15">
+        <v>1.7</v>
+      </c>
+      <c r="BG15">
+        <v>1.7</v>
+      </c>
+      <c r="BH15">
+        <v>2.96</v>
+      </c>
+      <c r="BI15">
+        <v>2.12</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>2.32</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>2.32</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>4.2</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>2.32</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>2.32</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
         <v>3.6</v>
       </c>
-      <c r="K15">
-        <v>3.85</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.08</v>
-      </c>
-      <c r="N15">
-        <v>3.35</v>
-      </c>
-      <c r="O15">
-        <v>1.37</v>
-      </c>
-      <c r="P15">
-        <v>1.8</v>
-      </c>
-      <c r="Q15">
-        <v>2.06</v>
-      </c>
-      <c r="R15">
-        <v>1.31</v>
-      </c>
-      <c r="S15">
-        <v>3.75</v>
-      </c>
-      <c r="T15">
-        <v>1.92</v>
-      </c>
-      <c r="U15">
-        <v>1.94</v>
-      </c>
-      <c r="V15">
-        <v>1.24</v>
-      </c>
-      <c r="W15">
-        <v>2.08</v>
-      </c>
-      <c r="X15">
-        <v>15</v>
-      </c>
-      <c r="Y15">
-        <v>17.5</v>
-      </c>
-      <c r="Z15">
-        <v>38</v>
-      </c>
-      <c r="AA15">
-        <v>130</v>
-      </c>
-      <c r="AB15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC15">
-        <v>8.4</v>
-      </c>
-      <c r="AD15">
-        <v>21</v>
-      </c>
-      <c r="AE15">
-        <v>80</v>
-      </c>
-      <c r="AF15">
-        <v>13</v>
-      </c>
-      <c r="AG15">
-        <v>12</v>
-      </c>
-      <c r="AH15">
-        <v>24</v>
-      </c>
-      <c r="AI15">
-        <v>85</v>
-      </c>
-      <c r="AJ15">
-        <v>24</v>
-      </c>
-      <c r="AK15">
-        <v>25</v>
-      </c>
-      <c r="AL15">
-        <v>48</v>
-      </c>
-      <c r="AM15">
-        <v>150</v>
-      </c>
-      <c r="AN15">
-        <v>17</v>
-      </c>
-      <c r="AO15">
-        <v>95</v>
-      </c>
-      <c r="AP15">
-        <v>11</v>
-      </c>
-      <c r="AQ15">
-        <v>13</v>
-      </c>
-      <c r="AR15">
-        <v>5.7</v>
-      </c>
-      <c r="AS15">
-        <v>6.4</v>
-      </c>
-      <c r="AT15">
-        <v>7.2</v>
-      </c>
-      <c r="AU15">
-        <v>7.4</v>
-      </c>
-      <c r="AV15">
-        <v>16.5</v>
-      </c>
-      <c r="AW15">
-        <v>6.2</v>
-      </c>
-      <c r="AX15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>5.2</v>
-      </c>
-      <c r="BA15">
-        <v>6.2</v>
-      </c>
-      <c r="BB15">
-        <v>17.5</v>
-      </c>
-      <c r="BC15">
-        <v>18.5</v>
-      </c>
-      <c r="BD15">
-        <v>5.9</v>
-      </c>
-      <c r="BE15">
-        <v>6.4</v>
-      </c>
-      <c r="BF15">
-        <v>12.5</v>
-      </c>
-      <c r="BG15">
-        <v>6.2</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.01</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.01</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>1.01</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>1.01</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.01</v>
-      </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="CB15" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16">
+        <v>1.83</v>
+      </c>
+      <c r="G16">
+        <v>1.91</v>
+      </c>
+      <c r="H16">
+        <v>4.6</v>
+      </c>
+      <c r="I16">
+        <v>5.1</v>
+      </c>
+      <c r="J16">
+        <v>3.65</v>
+      </c>
+      <c r="K16">
+        <v>3.85</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.35</v>
+      </c>
+      <c r="O16">
+        <v>1.37</v>
+      </c>
+      <c r="P16">
+        <v>1.81</v>
+      </c>
+      <c r="Q16">
+        <v>1.97</v>
+      </c>
+      <c r="R16">
+        <v>1.27</v>
+      </c>
+      <c r="S16">
+        <v>3.6</v>
+      </c>
+      <c r="T16">
+        <v>1.92</v>
+      </c>
+      <c r="U16">
+        <v>1.94</v>
+      </c>
+      <c r="V16">
+        <v>1.24</v>
+      </c>
+      <c r="W16">
+        <v>2.08</v>
+      </c>
+      <c r="X16">
+        <v>15</v>
+      </c>
+      <c r="Y16">
+        <v>17.5</v>
+      </c>
+      <c r="Z16">
+        <v>38</v>
+      </c>
+      <c r="AA16">
+        <v>130</v>
+      </c>
+      <c r="AB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16">
+        <v>8.4</v>
+      </c>
+      <c r="AD16">
+        <v>21</v>
+      </c>
+      <c r="AE16">
+        <v>80</v>
+      </c>
+      <c r="AF16">
+        <v>13</v>
+      </c>
+      <c r="AG16">
+        <v>12</v>
+      </c>
+      <c r="AH16">
+        <v>24</v>
+      </c>
+      <c r="AI16">
+        <v>85</v>
+      </c>
+      <c r="AJ16">
+        <v>24</v>
+      </c>
+      <c r="AK16">
+        <v>25</v>
+      </c>
+      <c r="AL16">
+        <v>48</v>
+      </c>
+      <c r="AM16">
+        <v>150</v>
+      </c>
+      <c r="AN16">
+        <v>18</v>
+      </c>
+      <c r="AO16">
+        <v>95</v>
+      </c>
+      <c r="AP16">
+        <v>11</v>
+      </c>
+      <c r="AQ16">
+        <v>13</v>
+      </c>
+      <c r="AR16">
+        <v>5.7</v>
+      </c>
+      <c r="AS16">
+        <v>6.4</v>
+      </c>
+      <c r="AT16">
+        <v>7.2</v>
+      </c>
+      <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
+        <v>16.5</v>
+      </c>
+      <c r="AW16">
+        <v>6.2</v>
+      </c>
+      <c r="AX16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ16">
+        <v>5.2</v>
+      </c>
+      <c r="BA16">
+        <v>6.2</v>
+      </c>
+      <c r="BB16">
+        <v>17.5</v>
+      </c>
+      <c r="BC16">
+        <v>18.5</v>
+      </c>
+      <c r="BD16">
+        <v>5.9</v>
+      </c>
+      <c r="BE16">
+        <v>6.4</v>
+      </c>
+      <c r="BF16">
+        <v>12.5</v>
+      </c>
+      <c r="BG16">
+        <v>6.2</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.86</v>
+      </c>
+      <c r="BJ16">
+        <v>14.5</v>
+      </c>
+      <c r="BK16">
+        <v>1.65</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.86</v>
+      </c>
+      <c r="BN16">
+        <v>5.9</v>
+      </c>
+      <c r="BO16">
+        <v>3.45</v>
+      </c>
+      <c r="BP16">
+        <v>18.5</v>
+      </c>
+      <c r="BQ16">
+        <v>1.69</v>
+      </c>
+      <c r="BR16">
+        <v>40</v>
+      </c>
+      <c r="BS16">
+        <v>1.78</v>
+      </c>
+      <c r="BT16">
+        <v>11</v>
+      </c>
+      <c r="BU16">
+        <v>5.4</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.81</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.82</v>
+      </c>
+      <c r="BZ16">
+        <v>38</v>
+      </c>
+      <c r="CA16">
+        <v>1.78</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
         <v>88</v>
       </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>127</v>
-      </c>
-      <c r="F16">
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17">
+        <v>2.56</v>
+      </c>
+      <c r="G17">
+        <v>3.05</v>
+      </c>
+      <c r="H17">
+        <v>2.76</v>
+      </c>
+      <c r="I17">
+        <v>3.45</v>
+      </c>
+      <c r="J17">
+        <v>2.96</v>
+      </c>
+      <c r="K17">
+        <v>3.5</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.06</v>
+      </c>
+      <c r="N17">
+        <v>2.8</v>
+      </c>
+      <c r="O17">
+        <v>1.42</v>
+      </c>
+      <c r="P17">
+        <v>1.69</v>
+      </c>
+      <c r="Q17">
+        <v>2.16</v>
+      </c>
+      <c r="R17">
+        <v>1.24</v>
+      </c>
+      <c r="S17">
+        <v>3.75</v>
+      </c>
+      <c r="T17">
+        <v>1.84</v>
+      </c>
+      <c r="U17">
+        <v>1.87</v>
+      </c>
+      <c r="V17">
+        <v>1.43</v>
+      </c>
+      <c r="W17">
+        <v>1.5</v>
+      </c>
+      <c r="X17">
+        <v>11.5</v>
+      </c>
+      <c r="Y17">
+        <v>10.5</v>
+      </c>
+      <c r="Z17">
+        <v>21</v>
+      </c>
+      <c r="AA17">
+        <v>90</v>
+      </c>
+      <c r="AB17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>14</v>
+      </c>
+      <c r="AE17">
+        <v>42</v>
+      </c>
+      <c r="AF17">
+        <v>18</v>
+      </c>
+      <c r="AG17">
+        <v>13.5</v>
+      </c>
+      <c r="AH17">
+        <v>20</v>
+      </c>
+      <c r="AI17">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
+        <v>46</v>
+      </c>
+      <c r="AK17">
+        <v>36</v>
+      </c>
+      <c r="AL17">
+        <v>55</v>
+      </c>
+      <c r="AM17">
+        <v>290</v>
+      </c>
+      <c r="AN17">
+        <v>36</v>
+      </c>
+      <c r="AO17">
+        <v>44</v>
+      </c>
+      <c r="AP17">
+        <v>1.58</v>
+      </c>
+      <c r="AQ17">
+        <v>4.6</v>
+      </c>
+      <c r="AR17">
+        <v>1.36</v>
+      </c>
+      <c r="AS17">
+        <v>1.34</v>
+      </c>
+      <c r="AT17">
+        <v>1.73</v>
+      </c>
+      <c r="AU17">
+        <v>1.48</v>
+      </c>
+      <c r="AV17">
+        <v>1.58</v>
+      </c>
+      <c r="AW17">
+        <v>1.32</v>
+      </c>
+      <c r="AX17">
+        <v>2.04</v>
+      </c>
+      <c r="AY17">
+        <v>1.58</v>
+      </c>
+      <c r="AZ17">
+        <v>1.46</v>
+      </c>
+      <c r="BA17">
+        <v>1.33</v>
+      </c>
+      <c r="BB17">
+        <v>1.32</v>
+      </c>
+      <c r="BC17">
+        <v>1.31</v>
+      </c>
+      <c r="BD17">
+        <v>1.33</v>
+      </c>
+      <c r="BE17">
+        <v>1.36</v>
+      </c>
+      <c r="BF17">
+        <v>1.31</v>
+      </c>
+      <c r="BG17">
+        <v>1.32</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18">
+        <v>3.45</v>
+      </c>
+      <c r="G18">
+        <v>3.7</v>
+      </c>
+      <c r="H18">
+        <v>2.48</v>
+      </c>
+      <c r="I18">
         <v>2.64</v>
       </c>
-      <c r="G16">
-        <v>2.9</v>
-      </c>
-      <c r="H16">
+      <c r="J18">
+        <v>2.94</v>
+      </c>
+      <c r="K18">
+        <v>3.15</v>
+      </c>
+      <c r="L18">
+        <v>1.58</v>
+      </c>
+      <c r="M18">
+        <v>1.14</v>
+      </c>
+      <c r="N18">
+        <v>2.46</v>
+      </c>
+      <c r="O18">
+        <v>1.51</v>
+      </c>
+      <c r="P18">
+        <v>1.45</v>
+      </c>
+      <c r="Q18">
+        <v>2.64</v>
+      </c>
+      <c r="R18">
+        <v>1.16</v>
+      </c>
+      <c r="S18">
+        <v>5.5</v>
+      </c>
+      <c r="T18">
+        <v>2.08</v>
+      </c>
+      <c r="U18">
+        <v>1.68</v>
+      </c>
+      <c r="V18">
+        <v>1.62</v>
+      </c>
+      <c r="W18">
+        <v>1.37</v>
+      </c>
+      <c r="X18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y18">
+        <v>7.6</v>
+      </c>
+      <c r="Z18">
+        <v>15</v>
+      </c>
+      <c r="AA18">
+        <v>42</v>
+      </c>
+      <c r="AB18">
+        <v>9.6</v>
+      </c>
+      <c r="AC18">
+        <v>7.2</v>
+      </c>
+      <c r="AD18">
+        <v>13.5</v>
+      </c>
+      <c r="AE18">
+        <v>40</v>
+      </c>
+      <c r="AF18">
+        <v>24</v>
+      </c>
+      <c r="AG18">
+        <v>17</v>
+      </c>
+      <c r="AH18">
+        <v>25</v>
+      </c>
+      <c r="AI18">
+        <v>85</v>
+      </c>
+      <c r="AJ18">
+        <v>90</v>
+      </c>
+      <c r="AK18">
+        <v>65</v>
+      </c>
+      <c r="AL18">
+        <v>110</v>
+      </c>
+      <c r="AM18">
+        <v>240</v>
+      </c>
+      <c r="AN18">
+        <v>110</v>
+      </c>
+      <c r="AO18">
+        <v>44</v>
+      </c>
+      <c r="AP18">
+        <v>7.4</v>
+      </c>
+      <c r="AQ18">
+        <v>6.8</v>
+      </c>
+      <c r="AR18">
+        <v>12.5</v>
+      </c>
+      <c r="AS18">
+        <v>28</v>
+      </c>
+      <c r="AT18">
+        <v>8.6</v>
+      </c>
+      <c r="AU18">
+        <v>6.4</v>
+      </c>
+      <c r="AV18">
+        <v>11</v>
+      </c>
+      <c r="AW18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX18">
+        <v>20</v>
+      </c>
+      <c r="AY18">
+        <v>14</v>
+      </c>
+      <c r="AZ18">
+        <v>20</v>
+      </c>
+      <c r="BA18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB18">
+        <v>10</v>
+      </c>
+      <c r="BC18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD18">
+        <v>10.5</v>
+      </c>
+      <c r="BE18">
+        <v>11</v>
+      </c>
+      <c r="BF18">
+        <v>10.5</v>
+      </c>
+      <c r="BG18">
+        <v>32</v>
+      </c>
+      <c r="BH18">
+        <v>3.05</v>
+      </c>
+      <c r="BI18">
+        <v>2.28</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>6.8</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>5.1</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>3.7</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19">
+        <v>1.72</v>
+      </c>
+      <c r="G19">
+        <v>1.88</v>
+      </c>
+      <c r="H19">
+        <v>5.3</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>3.2</v>
+      </c>
+      <c r="K19">
+        <v>4.3</v>
+      </c>
+      <c r="L19">
+        <v>1.5</v>
+      </c>
+      <c r="M19">
+        <v>1.11</v>
+      </c>
+      <c r="N19">
         <v>2.84</v>
       </c>
-      <c r="I16">
-        <v>3.15</v>
-      </c>
-      <c r="J16">
-        <v>3.05</v>
-      </c>
-      <c r="K16">
-        <v>3.5</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.11</v>
-      </c>
-      <c r="N16">
+      <c r="O19">
+        <v>1.45</v>
+      </c>
+      <c r="P19">
+        <v>1.61</v>
+      </c>
+      <c r="Q19">
+        <v>2.22</v>
+      </c>
+      <c r="R19">
+        <v>1.21</v>
+      </c>
+      <c r="S19">
+        <v>4.2</v>
+      </c>
+      <c r="T19">
+        <v>2.1</v>
+      </c>
+      <c r="U19">
+        <v>1.65</v>
+      </c>
+      <c r="V19">
+        <v>1.17</v>
+      </c>
+      <c r="W19">
+        <v>2.12</v>
+      </c>
+      <c r="X19">
+        <v>970</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>970</v>
+      </c>
+      <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>970</v>
+      </c>
+      <c r="AG19">
+        <v>970</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>44</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>7.8</v>
+      </c>
+      <c r="AQ19">
+        <v>1.62</v>
+      </c>
+      <c r="AR19">
+        <v>1.62</v>
+      </c>
+      <c r="AS19">
+        <v>1.62</v>
+      </c>
+      <c r="AT19">
+        <v>5.2</v>
+      </c>
+      <c r="AU19">
+        <v>6.2</v>
+      </c>
+      <c r="AV19">
+        <v>1.62</v>
+      </c>
+      <c r="AW19">
+        <v>1.62</v>
+      </c>
+      <c r="AX19">
+        <v>6.8</v>
+      </c>
+      <c r="AY19">
+        <v>7.6</v>
+      </c>
+      <c r="AZ19">
+        <v>1.62</v>
+      </c>
+      <c r="BA19">
+        <v>1.62</v>
+      </c>
+      <c r="BB19">
+        <v>1.62</v>
+      </c>
+      <c r="BC19">
+        <v>1.62</v>
+      </c>
+      <c r="BD19">
+        <v>1.62</v>
+      </c>
+      <c r="BE19">
+        <v>1.62</v>
+      </c>
+      <c r="BF19">
+        <v>1.56</v>
+      </c>
+      <c r="BG19">
+        <v>1.62</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.27</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.47</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20">
+        <v>3.65</v>
+      </c>
+      <c r="G20">
+        <v>4.7</v>
+      </c>
+      <c r="H20">
+        <v>1.97</v>
+      </c>
+      <c r="I20">
+        <v>2.26</v>
+      </c>
+      <c r="J20">
+        <v>3.3</v>
+      </c>
+      <c r="K20">
+        <v>4.2</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.05</v>
+      </c>
+      <c r="N20">
         <v>3</v>
       </c>
-      <c r="O16">
-        <v>1.41</v>
-      </c>
-      <c r="P16">
-        <v>1.69</v>
-      </c>
-      <c r="Q16">
-        <v>2.24</v>
-      </c>
-      <c r="R16">
-        <v>1.25</v>
-      </c>
-      <c r="S16">
-        <v>4.2</v>
-      </c>
-      <c r="T16">
-        <v>1.88</v>
-      </c>
-      <c r="U16">
-        <v>1.97</v>
-      </c>
-      <c r="V16">
-        <v>1.46</v>
-      </c>
-      <c r="W16">
-        <v>1.53</v>
-      </c>
-      <c r="X16">
-        <v>11.5</v>
-      </c>
-      <c r="Y16">
+      <c r="O20">
+        <v>1.39</v>
+      </c>
+      <c r="P20">
+        <v>1.65</v>
+      </c>
+      <c r="Q20">
+        <v>2.12</v>
+      </c>
+      <c r="R20">
+        <v>1.23</v>
+      </c>
+      <c r="S20">
+        <v>3.75</v>
+      </c>
+      <c r="T20">
+        <v>1.84</v>
+      </c>
+      <c r="U20">
+        <v>1.86</v>
+      </c>
+      <c r="V20">
+        <v>1.79</v>
+      </c>
+      <c r="W20">
+        <v>1.27</v>
+      </c>
+      <c r="X20">
+        <v>24</v>
+      </c>
+      <c r="Y20">
+        <v>15</v>
+      </c>
+      <c r="Z20">
+        <v>24</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>34</v>
+      </c>
+      <c r="AC20">
         <v>10.5</v>
       </c>
-      <c r="Z16">
-        <v>21</v>
-      </c>
-      <c r="AA16">
-        <v>90</v>
-      </c>
-      <c r="AB16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC16">
-        <v>7.6</v>
-      </c>
-      <c r="AD16">
-        <v>14</v>
-      </c>
-      <c r="AE16">
-        <v>42</v>
-      </c>
-      <c r="AF16">
-        <v>18</v>
-      </c>
-      <c r="AG16">
-        <v>13.5</v>
-      </c>
-      <c r="AH16">
-        <v>20</v>
-      </c>
-      <c r="AI16">
-        <v>60</v>
-      </c>
-      <c r="AJ16">
-        <v>46</v>
-      </c>
-      <c r="AK16">
-        <v>36</v>
-      </c>
-      <c r="AL16">
-        <v>55</v>
-      </c>
-      <c r="AM16">
-        <v>320</v>
-      </c>
-      <c r="AN16">
-        <v>36</v>
-      </c>
-      <c r="AO16">
-        <v>44</v>
-      </c>
-      <c r="AP16">
-        <v>9.4</v>
-      </c>
-      <c r="AQ16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR16">
-        <v>16.5</v>
-      </c>
-      <c r="AS16">
-        <v>8.4</v>
-      </c>
-      <c r="AT16">
-        <v>8.4</v>
-      </c>
-      <c r="AU16">
-        <v>6.4</v>
-      </c>
-      <c r="AV16">
-        <v>11.5</v>
-      </c>
-      <c r="AW16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX16">
-        <v>14.5</v>
-      </c>
-      <c r="AY16">
+      <c r="AD20">
+        <v>19</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>8.6</v>
+      </c>
+      <c r="AQ20">
+        <v>6</v>
+      </c>
+      <c r="AR20">
+        <v>8</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>7</v>
+      </c>
+      <c r="AU20">
+        <v>5.7</v>
+      </c>
+      <c r="AV20">
+        <v>7.4</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>10</v>
+      </c>
+      <c r="AZ20">
+        <v>12</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.01</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
         <v>11</v>
       </c>
-      <c r="AZ16">
-        <v>16</v>
-      </c>
-      <c r="BA16">
-        <v>8.4</v>
-      </c>
-      <c r="BB16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC16">
-        <v>8</v>
-      </c>
-      <c r="BD16">
-        <v>8.4</v>
-      </c>
-      <c r="BE16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16">
-        <v>8</v>
-      </c>
-      <c r="BG16">
-        <v>8.4</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.01</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.01</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.01</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.01</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.01</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.01</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.01</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.01</v>
-      </c>
-      <c r="BZ16">
-        <v>1000</v>
-      </c>
-      <c r="CA16">
-        <v>1.01</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>128</v>
+      <c r="BH20">
+        <v>3.75</v>
+      </c>
+      <c r="BI20">
+        <v>2.48</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.37</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.37</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.37</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.37</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.37</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.37</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.37</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.37</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.37</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
   <si>
     <t>League</t>
   </si>
@@ -265,9 +265,6 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
-    <t>Honduras Liga Nacional</t>
-  </si>
-  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -301,9 +298,6 @@
     <t>01:15:00</t>
   </si>
   <si>
-    <t>01:30:00</t>
-  </si>
-  <si>
     <t>02:05:00</t>
   </si>
   <si>
@@ -340,9 +334,6 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>Juticalpa</t>
-  </si>
-  <si>
     <t>Queretaro</t>
   </si>
   <si>
@@ -397,9 +388,6 @@
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
-    <t>CD Marathon</t>
-  </si>
-  <si>
     <t>Leon</t>
   </si>
   <si>
@@ -442,7 +430,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 00:28:44</t>
+    <t>2026-09-20 02:49:47</t>
   </si>
 </sst>
 </file>
@@ -774,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1024,25 +1012,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
         <v>91</v>
       </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G2">
         <v>1.31</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I2">
         <v>11.5</v>
@@ -1051,13 +1039,13 @@
         <v>7.2</v>
       </c>
       <c r="K2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L2">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
         <v>8</v>
@@ -1069,16 +1057,16 @@
         <v>3.4</v>
       </c>
       <c r="Q2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R2">
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
         <v>2.2</v>
@@ -1096,10 +1084,10 @@
         <v>55</v>
       </c>
       <c r="Z2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA2">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AB2">
         <v>14.5</v>
@@ -1150,10 +1138,10 @@
         <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1177,22 +1165,22 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BE2">
         <v>14</v>
       </c>
       <c r="BF2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG2">
         <v>14</v>
@@ -1201,64 +1189,64 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>4.5</v>
+        <v>1.27</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.19</v>
+        <v>3.45</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1266,19 +1254,19 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
         <v>1.9</v>
@@ -1293,16 +1281,16 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
         <v>1.27</v>
@@ -1314,10 +1302,10 @@
         <v>1.81</v>
       </c>
       <c r="R3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T3">
         <v>1.78</v>
@@ -1326,7 +1314,7 @@
         <v>2.2</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
         <v>2.1</v>
@@ -1341,7 +1329,7 @@
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1356,7 +1344,7 @@
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1386,7 +1374,7 @@
         <v>85</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
@@ -1395,7 +1383,7 @@
         <v>23</v>
       </c>
       <c r="AS3">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3">
         <v>9</v>
@@ -1404,10 +1392,10 @@
         <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1419,7 +1407,7 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
@@ -1428,10 +1416,10 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3">
         <v>9.199999999999999</v>
@@ -1500,7 +1488,7 @@
         <v>1.17</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,16 +1496,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F4">
         <v>2.32</v>
@@ -1529,7 +1517,7 @@
         <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1538,28 +1526,28 @@
         <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="M4">
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O4">
         <v>1.66</v>
       </c>
       <c r="P4">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q4">
         <v>3.05</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T4">
         <v>2.38</v>
@@ -1742,7 +1730,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1750,37 +1738,37 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F5">
         <v>4.6</v>
       </c>
       <c r="G5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H5">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I5">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1792,46 +1780,46 @@
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
         <v>1.88</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X5">
         <v>16.5</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>14</v>
       </c>
       <c r="AA5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB5">
         <v>19</v>
       </c>
       <c r="AC5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
         <v>12.5</v>
@@ -1903,19 +1891,19 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC5">
+        <v>4.8</v>
+      </c>
+      <c r="BD5">
+        <v>4.8</v>
+      </c>
+      <c r="BE5">
         <v>4.9</v>
-      </c>
-      <c r="BD5">
-        <v>4.9</v>
-      </c>
-      <c r="BE5">
-        <v>5</v>
       </c>
       <c r="BF5">
         <v>4.9</v>
@@ -1924,16 +1912,16 @@
         <v>11.5</v>
       </c>
       <c r="BH5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1945,7 +1933,7 @@
         <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP5">
         <v>50</v>
@@ -1960,16 +1948,16 @@
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BU5">
         <v>3.5</v>
       </c>
       <c r="BV5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>36</v>
@@ -1984,198 +1972,198 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>2.8</v>
       </c>
       <c r="H6">
+        <v>2.7</v>
+      </c>
+      <c r="I6">
+        <v>2.76</v>
+      </c>
+      <c r="J6">
+        <v>3.6</v>
+      </c>
+      <c r="K6">
+        <v>3.8</v>
+      </c>
+      <c r="L6">
+        <v>1.37</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>4.4</v>
+      </c>
+      <c r="O6">
         <v>1.28</v>
       </c>
-      <c r="I6">
-        <v>1.98</v>
-      </c>
-      <c r="J6">
+      <c r="P6">
+        <v>2.12</v>
+      </c>
+      <c r="Q6">
+        <v>1.84</v>
+      </c>
+      <c r="R6">
+        <v>1.44</v>
+      </c>
+      <c r="S6">
         <v>3.1</v>
       </c>
-      <c r="K6">
-        <v>910</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>3.85</v>
-      </c>
-      <c r="O6">
-        <v>1.01</v>
-      </c>
-      <c r="P6">
-        <v>1.26</v>
-      </c>
-      <c r="Q6">
-        <v>1.29</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
-      <c r="S6">
-        <v>1.29</v>
-      </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP6">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="AQ6">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR6">
-        <v>2.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS6">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AW6">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX6">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY6">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6">
-        <v>2.5</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB6">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC6">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD6">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>2.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2187,13 +2175,13 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2205,13 +2193,13 @@
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2226,198 +2214,198 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="G7">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="H7">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I7">
+        <v>3.85</v>
+      </c>
+      <c r="J7">
         <v>2.98</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>3.55</v>
       </c>
-      <c r="K7">
-        <v>4.1</v>
-      </c>
       <c r="L7">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
+        <v>1.38</v>
+      </c>
+      <c r="P7">
+        <v>1.74</v>
+      </c>
+      <c r="Q7">
+        <v>2.02</v>
+      </c>
+      <c r="R7">
+        <v>1.26</v>
+      </c>
+      <c r="S7">
+        <v>3.6</v>
+      </c>
+      <c r="T7">
+        <v>1.75</v>
+      </c>
+      <c r="U7">
+        <v>2.1</v>
+      </c>
+      <c r="V7">
+        <v>1.37</v>
+      </c>
+      <c r="W7">
+        <v>1.57</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>970</v>
+      </c>
+      <c r="AC7">
+        <v>970</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>970</v>
+      </c>
+      <c r="AH7">
+        <v>970</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.33</v>
+      </c>
+      <c r="AQ7">
+        <v>1.33</v>
+      </c>
+      <c r="AR7">
+        <v>1.34</v>
+      </c>
+      <c r="AS7">
+        <v>1.34</v>
+      </c>
+      <c r="AT7">
+        <v>1.23</v>
+      </c>
+      <c r="AU7">
+        <v>1.18</v>
+      </c>
+      <c r="AV7">
+        <v>1.33</v>
+      </c>
+      <c r="AW7">
+        <v>1.34</v>
+      </c>
+      <c r="AX7">
+        <v>1.33</v>
+      </c>
+      <c r="AY7">
+        <v>1.28</v>
+      </c>
+      <c r="AZ7">
         <v>1.25</v>
       </c>
-      <c r="P7">
-        <v>2.22</v>
-      </c>
-      <c r="Q7">
-        <v>1.73</v>
-      </c>
-      <c r="R7">
-        <v>1.5</v>
-      </c>
-      <c r="S7">
-        <v>2.8</v>
-      </c>
-      <c r="T7">
-        <v>1.64</v>
-      </c>
-      <c r="U7">
-        <v>2.46</v>
-      </c>
-      <c r="V7">
-        <v>1.51</v>
-      </c>
-      <c r="W7">
-        <v>1.6</v>
-      </c>
-      <c r="X7">
-        <v>23</v>
-      </c>
-      <c r="Y7">
-        <v>14.5</v>
-      </c>
-      <c r="Z7">
-        <v>22</v>
-      </c>
-      <c r="AA7">
-        <v>55</v>
-      </c>
-      <c r="AB7">
-        <v>13.5</v>
-      </c>
-      <c r="AC7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD7">
-        <v>13</v>
-      </c>
-      <c r="AE7">
-        <v>29</v>
-      </c>
-      <c r="AF7">
-        <v>18.5</v>
-      </c>
-      <c r="AG7">
-        <v>12.5</v>
-      </c>
-      <c r="AH7">
-        <v>15.5</v>
-      </c>
-      <c r="AI7">
-        <v>42</v>
-      </c>
-      <c r="AJ7">
-        <v>40</v>
-      </c>
-      <c r="AK7">
-        <v>32</v>
-      </c>
-      <c r="AL7">
-        <v>38</v>
-      </c>
-      <c r="AM7">
-        <v>85</v>
-      </c>
-      <c r="AN7">
-        <v>17</v>
-      </c>
-      <c r="AO7">
-        <v>22</v>
-      </c>
-      <c r="AP7">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7">
-        <v>12.5</v>
-      </c>
-      <c r="AR7">
-        <v>18.5</v>
-      </c>
-      <c r="AS7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7">
-        <v>11.5</v>
-      </c>
-      <c r="AU7">
-        <v>7.8</v>
-      </c>
-      <c r="AV7">
-        <v>11.5</v>
-      </c>
-      <c r="AW7">
-        <v>7.6</v>
-      </c>
-      <c r="AX7">
-        <v>16</v>
-      </c>
-      <c r="AY7">
-        <v>10.5</v>
-      </c>
-      <c r="AZ7">
-        <v>13.5</v>
-      </c>
       <c r="BA7">
-        <v>8.199999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="BB7">
-        <v>8.199999999999999</v>
+        <v>1.34</v>
       </c>
       <c r="BC7">
-        <v>7.8</v>
+        <v>1.34</v>
       </c>
       <c r="BD7">
-        <v>8</v>
+        <v>1.34</v>
       </c>
       <c r="BE7">
-        <v>9.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>1.34</v>
       </c>
       <c r="BG7">
-        <v>18.5</v>
+        <v>1.34</v>
       </c>
       <c r="BH7">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2429,13 +2417,13 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2447,13 +2435,13 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2468,7 +2456,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2476,178 +2464,178 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="H8">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>880</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S8">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="X8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2710,7 +2698,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2718,34 +2706,34 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>1.76</v>
+        <v>4.7</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>1.63</v>
       </c>
       <c r="I9">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>1.12</v>
       </c>
       <c r="K9">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2754,22 +2742,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.02</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>1.03</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2778,10 +2766,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2952,42 +2940,42 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>4.9</v>
+        <v>190</v>
       </c>
       <c r="H10">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2996,10 +2984,10 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
         <v>1.25</v>
@@ -3011,7 +2999,7 @@
         <v>1.24</v>
       </c>
       <c r="S10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3020,10 +3008,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="W10">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3188,48 +3176,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F11">
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J11">
         <v>1.1</v>
       </c>
       <c r="K11">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3253,7 +3241,7 @@
         <v>1.24</v>
       </c>
       <c r="S11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3262,10 +3250,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3430,13 +3418,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3444,70 +3432,70 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>2.56</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="J12">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S12">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V12">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3525,7 +3513,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3678,78 +3666,78 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="G13">
-        <v>2.56</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>2.84</v>
+        <v>1.12</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>1.19</v>
       </c>
       <c r="K13">
-        <v>4.7</v>
+        <v>890</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>1.07</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>2.14</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="R13">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="T13">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="W13">
-        <v>1.64</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3767,7 +3755,7 @@
         <v>1000</v>
       </c>
       <c r="AC13">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
         <v>1000</v>
@@ -3920,99 +3908,99 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>3.7</v>
       </c>
       <c r="H14">
-        <v>1.12</v>
+        <v>2.42</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>2.76</v>
       </c>
       <c r="J14">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>890</v>
+        <v>3.4</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N14">
-        <v>1.07</v>
+        <v>2.34</v>
       </c>
       <c r="O14">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="R14">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="S14">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V14">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE14">
         <v>1000</v>
@@ -4021,7 +4009,7 @@
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH14">
         <v>1000</v>
@@ -4048,796 +4036,796 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F15">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="G15">
+        <v>1.92</v>
+      </c>
+      <c r="H15">
+        <v>4.6</v>
+      </c>
+      <c r="I15">
+        <v>5.1</v>
+      </c>
+      <c r="J15">
+        <v>3.6</v>
+      </c>
+      <c r="K15">
+        <v>3.85</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.08</v>
+      </c>
+      <c r="N15">
+        <v>3.45</v>
+      </c>
+      <c r="O15">
+        <v>1.37</v>
+      </c>
+      <c r="P15">
+        <v>1.85</v>
+      </c>
+      <c r="Q15">
+        <v>2.08</v>
+      </c>
+      <c r="R15">
+        <v>1.31</v>
+      </c>
+      <c r="S15">
+        <v>3.8</v>
+      </c>
+      <c r="T15">
+        <v>1.92</v>
+      </c>
+      <c r="U15">
+        <v>1.94</v>
+      </c>
+      <c r="V15">
+        <v>1.24</v>
+      </c>
+      <c r="W15">
+        <v>2.08</v>
+      </c>
+      <c r="X15">
+        <v>15</v>
+      </c>
+      <c r="Y15">
+        <v>17.5</v>
+      </c>
+      <c r="Z15">
+        <v>38</v>
+      </c>
+      <c r="AA15">
+        <v>130</v>
+      </c>
+      <c r="AB15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>21</v>
+      </c>
+      <c r="AE15">
+        <v>80</v>
+      </c>
+      <c r="AF15">
+        <v>13</v>
+      </c>
+      <c r="AG15">
+        <v>12</v>
+      </c>
+      <c r="AH15">
+        <v>24</v>
+      </c>
+      <c r="AI15">
+        <v>85</v>
+      </c>
+      <c r="AJ15">
+        <v>24</v>
+      </c>
+      <c r="AK15">
+        <v>25</v>
+      </c>
+      <c r="AL15">
+        <v>48</v>
+      </c>
+      <c r="AM15">
+        <v>150</v>
+      </c>
+      <c r="AN15">
+        <v>18</v>
+      </c>
+      <c r="AO15">
+        <v>95</v>
+      </c>
+      <c r="AP15">
+        <v>11</v>
+      </c>
+      <c r="AQ15">
+        <v>13</v>
+      </c>
+      <c r="AR15">
+        <v>5.7</v>
+      </c>
+      <c r="AS15">
+        <v>6.4</v>
+      </c>
+      <c r="AT15">
+        <v>7.2</v>
+      </c>
+      <c r="AU15">
+        <v>7.4</v>
+      </c>
+      <c r="AV15">
+        <v>16.5</v>
+      </c>
+      <c r="AW15">
+        <v>6.2</v>
+      </c>
+      <c r="AX15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>5.2</v>
+      </c>
+      <c r="BA15">
+        <v>6.2</v>
+      </c>
+      <c r="BB15">
+        <v>17.5</v>
+      </c>
+      <c r="BC15">
+        <v>18.5</v>
+      </c>
+      <c r="BD15">
+        <v>5.9</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
+        <v>12.5</v>
+      </c>
+      <c r="BG15">
+        <v>6.2</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.85</v>
+      </c>
+      <c r="BJ15">
+        <v>14.5</v>
+      </c>
+      <c r="BK15">
+        <v>1.65</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.85</v>
+      </c>
+      <c r="BN15">
+        <v>5.9</v>
+      </c>
+      <c r="BO15">
         <v>3.55</v>
       </c>
-      <c r="H15">
-        <v>2.46</v>
-      </c>
-      <c r="I15">
-        <v>2.7</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15">
-        <v>3.2</v>
-      </c>
-      <c r="L15">
-        <v>1.64</v>
-      </c>
-      <c r="M15">
-        <v>1.12</v>
-      </c>
-      <c r="N15">
-        <v>2.34</v>
-      </c>
-      <c r="O15">
-        <v>1.54</v>
-      </c>
-      <c r="P15">
-        <v>1.48</v>
-      </c>
-      <c r="Q15">
-        <v>2.64</v>
-      </c>
-      <c r="R15">
-        <v>1.13</v>
-      </c>
-      <c r="S15">
-        <v>5.7</v>
-      </c>
-      <c r="T15">
-        <v>2.1</v>
-      </c>
-      <c r="U15">
-        <v>1.65</v>
-      </c>
-      <c r="V15">
-        <v>1.58</v>
-      </c>
-      <c r="W15">
-        <v>1.39</v>
-      </c>
-      <c r="X15">
-        <v>11.5</v>
-      </c>
-      <c r="Y15">
-        <v>9.6</v>
-      </c>
-      <c r="Z15">
+      <c r="BP15">
+        <v>19</v>
+      </c>
+      <c r="BQ15">
+        <v>1.69</v>
+      </c>
+      <c r="BR15">
         <v>44</v>
       </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>14</v>
-      </c>
-      <c r="AC15">
-        <v>10</v>
-      </c>
-      <c r="AD15">
-        <v>34</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>18</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>5.9</v>
-      </c>
-      <c r="AQ15">
-        <v>5.6</v>
-      </c>
-      <c r="AR15">
-        <v>9.4</v>
-      </c>
-      <c r="AS15">
-        <v>1.88</v>
-      </c>
-      <c r="AT15">
-        <v>6.4</v>
-      </c>
-      <c r="AU15">
-        <v>5.5</v>
-      </c>
-      <c r="AV15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW15">
-        <v>1.88</v>
-      </c>
-      <c r="AX15">
-        <v>12</v>
-      </c>
-      <c r="AY15">
-        <v>10</v>
-      </c>
-      <c r="AZ15">
-        <v>1.88</v>
-      </c>
-      <c r="BA15">
-        <v>1.88</v>
-      </c>
-      <c r="BB15">
-        <v>1.88</v>
-      </c>
-      <c r="BC15">
-        <v>1.88</v>
-      </c>
-      <c r="BD15">
-        <v>1.88</v>
-      </c>
-      <c r="BE15">
-        <v>1.88</v>
-      </c>
-      <c r="BF15">
-        <v>1.7</v>
-      </c>
-      <c r="BG15">
-        <v>1.7</v>
-      </c>
-      <c r="BH15">
-        <v>2.96</v>
-      </c>
-      <c r="BI15">
-        <v>2.12</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>2.32</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>2.32</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>4.2</v>
-      </c>
-      <c r="BP15">
-        <v>1000</v>
-      </c>
-      <c r="BQ15">
-        <v>2.32</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
       <c r="BS15">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU15">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA15">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F16">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="G16">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="H16">
+        <v>2.76</v>
+      </c>
+      <c r="I16">
+        <v>3.4</v>
+      </c>
+      <c r="J16">
+        <v>2.98</v>
+      </c>
+      <c r="K16">
+        <v>3.8</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.06</v>
+      </c>
+      <c r="N16">
+        <v>2.8</v>
+      </c>
+      <c r="O16">
+        <v>1.42</v>
+      </c>
+      <c r="P16">
+        <v>1.69</v>
+      </c>
+      <c r="Q16">
+        <v>2.12</v>
+      </c>
+      <c r="R16">
+        <v>1.25</v>
+      </c>
+      <c r="S16">
+        <v>3.75</v>
+      </c>
+      <c r="T16">
+        <v>1.84</v>
+      </c>
+      <c r="U16">
+        <v>1.87</v>
+      </c>
+      <c r="V16">
+        <v>1.44</v>
+      </c>
+      <c r="W16">
+        <v>1.49</v>
+      </c>
+      <c r="X16">
+        <v>970</v>
+      </c>
+      <c r="Y16">
+        <v>970</v>
+      </c>
+      <c r="Z16">
+        <v>21</v>
+      </c>
+      <c r="AA16">
+        <v>90</v>
+      </c>
+      <c r="AB16">
+        <v>970</v>
+      </c>
+      <c r="AC16">
+        <v>970</v>
+      </c>
+      <c r="AD16">
+        <v>970</v>
+      </c>
+      <c r="AE16">
+        <v>42</v>
+      </c>
+      <c r="AF16">
+        <v>970</v>
+      </c>
+      <c r="AG16">
+        <v>970</v>
+      </c>
+      <c r="AH16">
+        <v>20</v>
+      </c>
+      <c r="AI16">
+        <v>60</v>
+      </c>
+      <c r="AJ16">
+        <v>46</v>
+      </c>
+      <c r="AK16">
+        <v>36</v>
+      </c>
+      <c r="AL16">
+        <v>55</v>
+      </c>
+      <c r="AM16">
+        <v>290</v>
+      </c>
+      <c r="AN16">
+        <v>36</v>
+      </c>
+      <c r="AO16">
+        <v>44</v>
+      </c>
+      <c r="AP16">
+        <v>1.59</v>
+      </c>
+      <c r="AQ16">
         <v>4.6</v>
       </c>
-      <c r="I16">
-        <v>5.1</v>
-      </c>
-      <c r="J16">
-        <v>3.65</v>
-      </c>
-      <c r="K16">
-        <v>3.85</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.08</v>
-      </c>
-      <c r="N16">
-        <v>3.35</v>
-      </c>
-      <c r="O16">
+      <c r="AR16">
+        <v>1.38</v>
+      </c>
+      <c r="AS16">
+        <v>1.35</v>
+      </c>
+      <c r="AT16">
+        <v>1.74</v>
+      </c>
+      <c r="AU16">
+        <v>1.49</v>
+      </c>
+      <c r="AV16">
+        <v>1.59</v>
+      </c>
+      <c r="AW16">
+        <v>1.33</v>
+      </c>
+      <c r="AX16">
+        <v>2.06</v>
+      </c>
+      <c r="AY16">
+        <v>1.59</v>
+      </c>
+      <c r="AZ16">
+        <v>1.47</v>
+      </c>
+      <c r="BA16">
+        <v>1.34</v>
+      </c>
+      <c r="BB16">
+        <v>1.34</v>
+      </c>
+      <c r="BC16">
+        <v>1.32</v>
+      </c>
+      <c r="BD16">
+        <v>1.34</v>
+      </c>
+      <c r="BE16">
         <v>1.37</v>
       </c>
-      <c r="P16">
-        <v>1.81</v>
-      </c>
-      <c r="Q16">
-        <v>1.97</v>
-      </c>
-      <c r="R16">
-        <v>1.27</v>
-      </c>
-      <c r="S16">
-        <v>3.6</v>
-      </c>
-      <c r="T16">
-        <v>1.92</v>
-      </c>
-      <c r="U16">
-        <v>1.94</v>
-      </c>
-      <c r="V16">
-        <v>1.24</v>
-      </c>
-      <c r="W16">
-        <v>2.08</v>
-      </c>
-      <c r="X16">
-        <v>15</v>
-      </c>
-      <c r="Y16">
-        <v>17.5</v>
-      </c>
-      <c r="Z16">
-        <v>38</v>
-      </c>
-      <c r="AA16">
-        <v>130</v>
-      </c>
-      <c r="AB16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC16">
-        <v>8.4</v>
-      </c>
-      <c r="AD16">
-        <v>21</v>
-      </c>
-      <c r="AE16">
-        <v>80</v>
-      </c>
-      <c r="AF16">
-        <v>13</v>
-      </c>
-      <c r="AG16">
-        <v>12</v>
-      </c>
-      <c r="AH16">
-        <v>24</v>
-      </c>
-      <c r="AI16">
-        <v>85</v>
-      </c>
-      <c r="AJ16">
-        <v>24</v>
-      </c>
-      <c r="AK16">
-        <v>25</v>
-      </c>
-      <c r="AL16">
-        <v>48</v>
-      </c>
-      <c r="AM16">
-        <v>150</v>
-      </c>
-      <c r="AN16">
-        <v>18</v>
-      </c>
-      <c r="AO16">
-        <v>95</v>
-      </c>
-      <c r="AP16">
-        <v>11</v>
-      </c>
-      <c r="AQ16">
-        <v>13</v>
-      </c>
-      <c r="AR16">
-        <v>5.7</v>
-      </c>
-      <c r="AS16">
-        <v>6.4</v>
-      </c>
-      <c r="AT16">
-        <v>7.2</v>
-      </c>
-      <c r="AU16">
-        <v>7.4</v>
-      </c>
-      <c r="AV16">
-        <v>16.5</v>
-      </c>
-      <c r="AW16">
-        <v>6.2</v>
-      </c>
-      <c r="AX16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ16">
-        <v>5.2</v>
-      </c>
-      <c r="BA16">
-        <v>6.2</v>
-      </c>
-      <c r="BB16">
-        <v>17.5</v>
-      </c>
-      <c r="BC16">
-        <v>18.5</v>
-      </c>
-      <c r="BD16">
-        <v>5.9</v>
-      </c>
-      <c r="BE16">
-        <v>6.4</v>
-      </c>
       <c r="BF16">
-        <v>12.5</v>
+        <v>1.32</v>
       </c>
       <c r="BG16">
-        <v>6.2</v>
+        <v>1.33</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F17">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="G17">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="H17">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="I17">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="J17">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K17">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="O17">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="P17">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="Q17">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="R17">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="S17">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="T17">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="U17">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="X17">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y17">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA17">
+        <v>42</v>
+      </c>
+      <c r="AB17">
+        <v>9.6</v>
+      </c>
+      <c r="AC17">
+        <v>7.2</v>
+      </c>
+      <c r="AD17">
+        <v>13.5</v>
+      </c>
+      <c r="AE17">
+        <v>40</v>
+      </c>
+      <c r="AF17">
+        <v>24</v>
+      </c>
+      <c r="AG17">
+        <v>17</v>
+      </c>
+      <c r="AH17">
+        <v>25</v>
+      </c>
+      <c r="AI17">
+        <v>85</v>
+      </c>
+      <c r="AJ17">
         <v>90</v>
       </c>
-      <c r="AB17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC17">
-        <v>10.5</v>
-      </c>
-      <c r="AD17">
-        <v>14</v>
-      </c>
-      <c r="AE17">
-        <v>42</v>
-      </c>
-      <c r="AF17">
-        <v>18</v>
-      </c>
-      <c r="AG17">
-        <v>13.5</v>
-      </c>
-      <c r="AH17">
-        <v>20</v>
-      </c>
-      <c r="AI17">
-        <v>60</v>
-      </c>
-      <c r="AJ17">
-        <v>46</v>
-      </c>
       <c r="AK17">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AL17">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM17">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AN17">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AO17">
         <v>44</v>
       </c>
       <c r="AP17">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR17">
-        <v>1.36</v>
+        <v>12.5</v>
       </c>
       <c r="AS17">
-        <v>1.34</v>
+        <v>9</v>
       </c>
       <c r="AT17">
-        <v>1.73</v>
+        <v>8.6</v>
       </c>
       <c r="AU17">
-        <v>1.48</v>
+        <v>6.4</v>
       </c>
       <c r="AV17">
-        <v>1.58</v>
+        <v>11</v>
       </c>
       <c r="AW17">
-        <v>1.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17">
-        <v>2.04</v>
+        <v>20</v>
       </c>
       <c r="AY17">
-        <v>1.58</v>
+        <v>14</v>
       </c>
       <c r="AZ17">
-        <v>1.46</v>
+        <v>20</v>
       </c>
       <c r="BA17">
-        <v>1.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB17">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="BC17">
-        <v>1.31</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD17">
-        <v>1.33</v>
+        <v>10.5</v>
       </c>
       <c r="BE17">
-        <v>1.36</v>
+        <v>11</v>
       </c>
       <c r="BF17">
-        <v>1.31</v>
+        <v>10.5</v>
       </c>
       <c r="BG17">
-        <v>1.32</v>
+        <v>32</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -4849,7 +4837,7 @@
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP17">
         <v>1000</v>
@@ -4867,7 +4855,7 @@
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV17">
         <v>1000</v>
@@ -4888,198 +4876,198 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F18">
-        <v>3.45</v>
+        <v>1.72</v>
       </c>
       <c r="G18">
-        <v>3.7</v>
+        <v>1.88</v>
       </c>
       <c r="H18">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="I18">
-        <v>2.64</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="K18">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="L18">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="M18">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="O18">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="P18">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q18">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="R18">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S18">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="T18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V18">
+        <v>1.17</v>
+      </c>
+      <c r="W18">
+        <v>2.12</v>
+      </c>
+      <c r="X18">
+        <v>970</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>970</v>
+      </c>
+      <c r="AC18">
+        <v>970</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>970</v>
+      </c>
+      <c r="AG18">
+        <v>970</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>44</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>7</v>
+      </c>
+      <c r="AQ18">
+        <v>1.7</v>
+      </c>
+      <c r="AR18">
         <v>1.62</v>
       </c>
-      <c r="W18">
-        <v>1.37</v>
-      </c>
-      <c r="X18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y18">
+      <c r="AS18">
+        <v>1.62</v>
+      </c>
+      <c r="AT18">
+        <v>5.2</v>
+      </c>
+      <c r="AU18">
+        <v>6.2</v>
+      </c>
+      <c r="AV18">
+        <v>1.62</v>
+      </c>
+      <c r="AW18">
+        <v>1.62</v>
+      </c>
+      <c r="AX18">
+        <v>6.8</v>
+      </c>
+      <c r="AY18">
         <v>7.6</v>
       </c>
-      <c r="Z18">
-        <v>15</v>
-      </c>
-      <c r="AA18">
-        <v>42</v>
-      </c>
-      <c r="AB18">
-        <v>9.6</v>
-      </c>
-      <c r="AC18">
-        <v>7.2</v>
-      </c>
-      <c r="AD18">
-        <v>13.5</v>
-      </c>
-      <c r="AE18">
-        <v>40</v>
-      </c>
-      <c r="AF18">
-        <v>24</v>
-      </c>
-      <c r="AG18">
-        <v>17</v>
-      </c>
-      <c r="AH18">
-        <v>25</v>
-      </c>
-      <c r="AI18">
-        <v>85</v>
-      </c>
-      <c r="AJ18">
-        <v>90</v>
-      </c>
-      <c r="AK18">
-        <v>65</v>
-      </c>
-      <c r="AL18">
-        <v>110</v>
-      </c>
-      <c r="AM18">
-        <v>240</v>
-      </c>
-      <c r="AN18">
-        <v>110</v>
-      </c>
-      <c r="AO18">
-        <v>44</v>
-      </c>
-      <c r="AP18">
-        <v>7.4</v>
-      </c>
-      <c r="AQ18">
-        <v>6.8</v>
-      </c>
-      <c r="AR18">
-        <v>12.5</v>
-      </c>
-      <c r="AS18">
-        <v>28</v>
-      </c>
-      <c r="AT18">
-        <v>8.6</v>
-      </c>
-      <c r="AU18">
-        <v>6.4</v>
-      </c>
-      <c r="AV18">
-        <v>11</v>
-      </c>
-      <c r="AW18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX18">
-        <v>20</v>
-      </c>
-      <c r="AY18">
-        <v>14</v>
-      </c>
       <c r="AZ18">
-        <v>20</v>
+        <v>1.62</v>
       </c>
       <c r="BA18">
-        <v>9.800000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="BB18">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="BC18">
-        <v>9.800000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="BD18">
-        <v>10.5</v>
+        <v>1.62</v>
       </c>
       <c r="BE18">
-        <v>11</v>
+        <v>1.62</v>
       </c>
       <c r="BF18">
-        <v>10.5</v>
+        <v>1.64</v>
       </c>
       <c r="BG18">
-        <v>32</v>
+        <v>1.62</v>
       </c>
       <c r="BH18">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.28</v>
+        <v>1.27</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5091,7 +5079,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>5.1</v>
+        <v>1.47</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5109,7 +5097,7 @@
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
         <v>1000</v>
@@ -5130,7 +5118,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5138,483 +5126,241 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>3.7</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>4.9</v>
       </c>
       <c r="H19">
-        <v>5.3</v>
+        <v>1.97</v>
       </c>
       <c r="I19">
+        <v>2.22</v>
+      </c>
+      <c r="J19">
+        <v>3.3</v>
+      </c>
+      <c r="K19">
+        <v>3.65</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>3.2</v>
+      </c>
+      <c r="O19">
+        <v>1.39</v>
+      </c>
+      <c r="P19">
+        <v>1.65</v>
+      </c>
+      <c r="Q19">
+        <v>2.12</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>3.6</v>
+      </c>
+      <c r="T19">
+        <v>1.9</v>
+      </c>
+      <c r="U19">
+        <v>1.81</v>
+      </c>
+      <c r="V19">
+        <v>1.82</v>
+      </c>
+      <c r="W19">
+        <v>1.26</v>
+      </c>
+      <c r="X19">
+        <v>24</v>
+      </c>
+      <c r="Y19">
+        <v>15</v>
+      </c>
+      <c r="Z19">
+        <v>24</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>34</v>
+      </c>
+      <c r="AC19">
+        <v>10.5</v>
+      </c>
+      <c r="AD19">
+        <v>19</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>8.6</v>
+      </c>
+      <c r="AQ19">
+        <v>6</v>
+      </c>
+      <c r="AR19">
+        <v>8</v>
+      </c>
+      <c r="AS19">
+        <v>1.01</v>
+      </c>
+      <c r="AT19">
         <v>7</v>
       </c>
-      <c r="J19">
-        <v>3.2</v>
-      </c>
-      <c r="K19">
-        <v>4.3</v>
-      </c>
-      <c r="L19">
-        <v>1.5</v>
-      </c>
-      <c r="M19">
-        <v>1.11</v>
-      </c>
-      <c r="N19">
-        <v>2.84</v>
-      </c>
-      <c r="O19">
-        <v>1.45</v>
-      </c>
-      <c r="P19">
-        <v>1.61</v>
-      </c>
-      <c r="Q19">
-        <v>2.22</v>
-      </c>
-      <c r="R19">
-        <v>1.21</v>
-      </c>
-      <c r="S19">
-        <v>4.2</v>
-      </c>
-      <c r="T19">
-        <v>2.1</v>
-      </c>
-      <c r="U19">
-        <v>1.65</v>
-      </c>
-      <c r="V19">
-        <v>1.17</v>
-      </c>
-      <c r="W19">
-        <v>2.12</v>
-      </c>
-      <c r="X19">
-        <v>970</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>970</v>
-      </c>
-      <c r="AC19">
-        <v>970</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>970</v>
-      </c>
-      <c r="AG19">
-        <v>970</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>44</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>7.8</v>
-      </c>
-      <c r="AQ19">
-        <v>1.62</v>
-      </c>
-      <c r="AR19">
-        <v>1.62</v>
-      </c>
-      <c r="AS19">
-        <v>1.62</v>
-      </c>
-      <c r="AT19">
-        <v>5.2</v>
-      </c>
       <c r="AU19">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV19">
-        <v>1.62</v>
+        <v>7.4</v>
       </c>
       <c r="AW19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI19">
-        <v>1.27</v>
+        <v>2.48</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="CB19" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:80">
-      <c r="A20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>141</v>
-      </c>
-      <c r="F20">
-        <v>3.65</v>
-      </c>
-      <c r="G20">
-        <v>4.7</v>
-      </c>
-      <c r="H20">
-        <v>1.97</v>
-      </c>
-      <c r="I20">
-        <v>2.26</v>
-      </c>
-      <c r="J20">
-        <v>3.3</v>
-      </c>
-      <c r="K20">
-        <v>4.2</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.05</v>
-      </c>
-      <c r="N20">
-        <v>3</v>
-      </c>
-      <c r="O20">
-        <v>1.39</v>
-      </c>
-      <c r="P20">
-        <v>1.65</v>
-      </c>
-      <c r="Q20">
-        <v>2.12</v>
-      </c>
-      <c r="R20">
-        <v>1.23</v>
-      </c>
-      <c r="S20">
-        <v>3.75</v>
-      </c>
-      <c r="T20">
-        <v>1.84</v>
-      </c>
-      <c r="U20">
-        <v>1.86</v>
-      </c>
-      <c r="V20">
-        <v>1.79</v>
-      </c>
-      <c r="W20">
-        <v>1.27</v>
-      </c>
-      <c r="X20">
-        <v>24</v>
-      </c>
-      <c r="Y20">
-        <v>15</v>
-      </c>
-      <c r="Z20">
-        <v>24</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
-        <v>34</v>
-      </c>
-      <c r="AC20">
-        <v>10.5</v>
-      </c>
-      <c r="AD20">
-        <v>19</v>
-      </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>1000</v>
-      </c>
-      <c r="AG20">
-        <v>1000</v>
-      </c>
-      <c r="AH20">
-        <v>1000</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>1000</v>
-      </c>
-      <c r="AK20">
-        <v>1000</v>
-      </c>
-      <c r="AL20">
-        <v>1000</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>1000</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>8.6</v>
-      </c>
-      <c r="AQ20">
-        <v>6</v>
-      </c>
-      <c r="AR20">
-        <v>8</v>
-      </c>
-      <c r="AS20">
-        <v>1.01</v>
-      </c>
-      <c r="AT20">
-        <v>7</v>
-      </c>
-      <c r="AU20">
-        <v>5.7</v>
-      </c>
-      <c r="AV20">
-        <v>7.4</v>
-      </c>
-      <c r="AW20">
-        <v>1.01</v>
-      </c>
-      <c r="AX20">
-        <v>1.01</v>
-      </c>
-      <c r="AY20">
-        <v>10</v>
-      </c>
-      <c r="AZ20">
-        <v>12</v>
-      </c>
-      <c r="BA20">
-        <v>1.01</v>
-      </c>
-      <c r="BB20">
-        <v>1.01</v>
-      </c>
-      <c r="BC20">
-        <v>1.01</v>
-      </c>
-      <c r="BD20">
-        <v>1.01</v>
-      </c>
-      <c r="BE20">
-        <v>1.01</v>
-      </c>
-      <c r="BF20">
-        <v>1.01</v>
-      </c>
-      <c r="BG20">
-        <v>11</v>
-      </c>
-      <c r="BH20">
-        <v>3.75</v>
-      </c>
-      <c r="BI20">
-        <v>2.48</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.37</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.37</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.37</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.37</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.37</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.37</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.37</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.37</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.37</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="143">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Honduras Liga Nacional</t>
+  </si>
+  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -298,6 +301,9 @@
     <t>01:15:00</t>
   </si>
   <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
     <t>02:05:00</t>
   </si>
   <si>
@@ -334,6 +340,9 @@
     <t>Llaneros FC</t>
   </si>
   <si>
+    <t>Juticalpa</t>
+  </si>
+  <si>
     <t>Queretaro</t>
   </si>
   <si>
@@ -388,6 +397,9 @@
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
+    <t>CD Marathon</t>
+  </si>
+  <si>
     <t>Leon</t>
   </si>
   <si>
@@ -430,7 +442,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 02:49:47</t>
+    <t>2026-09-20 05:11:28</t>
   </si>
 </sst>
 </file>
@@ -762,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1012,16 +1024,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>1.29</v>
@@ -1030,10 +1042,10 @@
         <v>1.31</v>
       </c>
       <c r="H2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>7.2</v>
@@ -1054,25 +1066,25 @@
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q2">
         <v>1.39</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T2">
         <v>1.78</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W2">
         <v>4.2</v>
@@ -1096,10 +1108,10 @@
         <v>17.5</v>
       </c>
       <c r="AD2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1123,25 +1135,25 @@
         <v>28</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2">
         <v>3.55</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS2">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1153,7 +1165,7 @@
         <v>34</v>
       </c>
       <c r="AW2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -1165,7 +1177,7 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB2">
         <v>10.5</v>
@@ -1177,13 +1189,13 @@
         <v>23</v>
       </c>
       <c r="BE2">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="BF2">
         <v>3.3</v>
       </c>
       <c r="BG2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1207,7 +1219,7 @@
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -1246,7 +1258,7 @@
         <v>1.27</v>
       </c>
       <c r="CB2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1254,76 +1266,76 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>1.37</v>
+      </c>
+      <c r="M3">
+        <v>1.06</v>
+      </c>
+      <c r="N3">
         <v>4.2</v>
       </c>
-      <c r="L3">
-        <v>1.36</v>
-      </c>
-      <c r="M3">
-        <v>1.05</v>
-      </c>
-      <c r="N3">
-        <v>4.5</v>
-      </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P3">
+        <v>2.08</v>
+      </c>
+      <c r="Q3">
+        <v>1.89</v>
+      </c>
+      <c r="R3">
+        <v>1.42</v>
+      </c>
+      <c r="S3">
+        <v>3.25</v>
+      </c>
+      <c r="T3">
+        <v>1.82</v>
+      </c>
+      <c r="U3">
         <v>2.16</v>
-      </c>
-      <c r="Q3">
-        <v>1.81</v>
-      </c>
-      <c r="R3">
-        <v>1.44</v>
-      </c>
-      <c r="S3">
-        <v>3.1</v>
-      </c>
-      <c r="T3">
-        <v>1.78</v>
-      </c>
-      <c r="U3">
-        <v>2.2</v>
       </c>
       <c r="V3">
         <v>1.28</v>
       </c>
       <c r="W3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>36</v>
@@ -1332,16 +1344,16 @@
         <v>110</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
         <v>18</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
@@ -1350,52 +1362,52 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
         <v>21</v>
       </c>
       <c r="AK3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM3">
         <v>110</v>
       </c>
       <c r="AN3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR3">
         <v>23</v>
       </c>
       <c r="AS3">
+        <v>10.5</v>
+      </c>
+      <c r="AT3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU3">
+        <v>8</v>
+      </c>
+      <c r="AV3">
+        <v>15</v>
+      </c>
+      <c r="AW3">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AT3">
-        <v>9</v>
-      </c>
-      <c r="AU3">
-        <v>8.4</v>
-      </c>
-      <c r="AV3">
-        <v>14.5</v>
-      </c>
-      <c r="AW3">
-        <v>9</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1407,7 +1419,7 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
@@ -1416,10 +1428,10 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
         <v>9.199999999999999</v>
@@ -1488,7 +1500,7 @@
         <v>1.17</v>
       </c>
       <c r="CB3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1496,37 +1508,37 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
         <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M4">
         <v>1.15</v>
@@ -1538,13 +1550,13 @@
         <v>1.66</v>
       </c>
       <c r="P4">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S4">
         <v>6.8</v>
@@ -1556,10 +1568,10 @@
         <v>1.68</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1580,7 +1592,7 @@
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1673,13 +1685,13 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1697,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1709,7 +1721,7 @@
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1730,7 +1742,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1738,16 +1750,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F5">
         <v>4.6</v>
@@ -1756,10 +1768,10 @@
         <v>5.1</v>
       </c>
       <c r="H5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="I5">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="J5">
         <v>3.65</v>
@@ -1774,13 +1786,13 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
         <v>2.04</v>
@@ -1792,13 +1804,13 @@
         <v>3.7</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2</v>
       </c>
       <c r="V5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W5">
         <v>1.25</v>
@@ -1807,13 +1819,13 @@
         <v>16.5</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Z5">
         <v>14</v>
       </c>
       <c r="AA5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB5">
         <v>19</v>
@@ -1873,7 +1885,7 @@
         <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
         <v>8.800000000000001</v>
@@ -1882,7 +1894,7 @@
         <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY5">
         <v>16</v>
@@ -1891,25 +1903,25 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB5">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC5">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD5">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE5">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH5">
         <v>3.8</v>
@@ -1921,31 +1933,31 @@
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN5">
         <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BP5">
         <v>50</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR5">
         <v>65</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT5">
         <v>5.3</v>
@@ -1954,216 +1966,216 @@
         <v>3.5</v>
       </c>
       <c r="BV5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="BX5">
         <v>36</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F6">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="G6">
-        <v>2.8</v>
+        <v>95</v>
       </c>
       <c r="H6">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="I6">
-        <v>2.76</v>
+        <v>1.76</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>14</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="Q6">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>1.01</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
         <v>1.44</v>
       </c>
-      <c r="S6">
-        <v>3.1</v>
-      </c>
-      <c r="T6">
-        <v>1.68</v>
-      </c>
-      <c r="U6">
-        <v>2.38</v>
-      </c>
-      <c r="V6">
-        <v>1.56</v>
-      </c>
       <c r="W6">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>25</v>
+        <v>350</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>32</v>
+        <v>480</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>380</v>
       </c>
       <c r="AM6">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AP6">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>7.2</v>
+        <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>18</v>
+        <v>2.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2175,13 +2187,13 @@
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2193,13 +2205,13 @@
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2214,198 +2226,198 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7">
+        <v>2.72</v>
+      </c>
+      <c r="G7">
+        <v>2.78</v>
+      </c>
+      <c r="H7">
+        <v>2.7</v>
+      </c>
+      <c r="I7">
+        <v>2.78</v>
+      </c>
+      <c r="J7">
+        <v>3.6</v>
+      </c>
+      <c r="K7">
+        <v>3.8</v>
+      </c>
+      <c r="L7">
+        <v>1.37</v>
+      </c>
+      <c r="M7">
+        <v>1.06</v>
+      </c>
+      <c r="N7">
+        <v>4.4</v>
+      </c>
+      <c r="O7">
+        <v>1.28</v>
+      </c>
+      <c r="P7">
+        <v>2.12</v>
+      </c>
+      <c r="Q7">
+        <v>1.84</v>
+      </c>
+      <c r="R7">
+        <v>1.44</v>
+      </c>
+      <c r="S7">
+        <v>3.1</v>
+      </c>
+      <c r="T7">
+        <v>1.68</v>
+      </c>
+      <c r="U7">
+        <v>2.38</v>
+      </c>
+      <c r="V7">
+        <v>1.56</v>
+      </c>
+      <c r="W7">
+        <v>1.56</v>
+      </c>
+      <c r="X7">
+        <v>17</v>
+      </c>
+      <c r="Y7">
+        <v>13</v>
+      </c>
+      <c r="Z7">
+        <v>19.5</v>
+      </c>
+      <c r="AA7">
+        <v>48</v>
+      </c>
+      <c r="AB7">
+        <v>13</v>
+      </c>
+      <c r="AC7">
+        <v>8.4</v>
+      </c>
+      <c r="AD7">
+        <v>12.5</v>
+      </c>
+      <c r="AE7">
+        <v>28</v>
+      </c>
+      <c r="AF7">
+        <v>25</v>
+      </c>
+      <c r="AG7">
+        <v>12.5</v>
+      </c>
+      <c r="AH7">
+        <v>16</v>
+      </c>
+      <c r="AI7">
+        <v>46</v>
+      </c>
+      <c r="AJ7">
+        <v>55</v>
+      </c>
+      <c r="AK7">
+        <v>32</v>
+      </c>
+      <c r="AL7">
+        <v>46</v>
+      </c>
+      <c r="AM7">
         <v>90</v>
       </c>
-      <c r="C7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7">
-        <v>2.32</v>
-      </c>
-      <c r="G7">
-        <v>2.8</v>
-      </c>
-      <c r="H7">
-        <v>2.9</v>
-      </c>
-      <c r="I7">
-        <v>3.85</v>
-      </c>
-      <c r="J7">
-        <v>2.98</v>
-      </c>
-      <c r="K7">
-        <v>3.55</v>
-      </c>
-      <c r="L7">
-        <v>1.4</v>
-      </c>
-      <c r="M7">
-        <v>1.08</v>
-      </c>
-      <c r="N7">
-        <v>3.25</v>
-      </c>
-      <c r="O7">
-        <v>1.38</v>
-      </c>
-      <c r="P7">
-        <v>1.74</v>
-      </c>
-      <c r="Q7">
-        <v>2.02</v>
-      </c>
-      <c r="R7">
-        <v>1.26</v>
-      </c>
-      <c r="S7">
-        <v>3.6</v>
-      </c>
-      <c r="T7">
-        <v>1.75</v>
-      </c>
-      <c r="U7">
-        <v>2.1</v>
-      </c>
-      <c r="V7">
-        <v>1.37</v>
-      </c>
-      <c r="W7">
-        <v>1.57</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>970</v>
-      </c>
-      <c r="AC7">
-        <v>970</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>970</v>
-      </c>
-      <c r="AH7">
-        <v>970</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>11.5</v>
       </c>
       <c r="AR7">
-        <v>1.34</v>
+        <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>1.34</v>
+        <v>8.6</v>
       </c>
       <c r="AT7">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>1.18</v>
+        <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>1.33</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>1.34</v>
+        <v>7.6</v>
       </c>
       <c r="AX7">
-        <v>1.33</v>
+        <v>17</v>
       </c>
       <c r="AY7">
-        <v>1.28</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>1.25</v>
+        <v>14</v>
       </c>
       <c r="BA7">
-        <v>1.34</v>
+        <v>8.6</v>
       </c>
       <c r="BB7">
-        <v>1.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7">
-        <v>1.34</v>
+        <v>7.8</v>
       </c>
       <c r="BD7">
-        <v>1.34</v>
+        <v>8.6</v>
       </c>
       <c r="BE7">
-        <v>1.34</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>1.34</v>
+        <v>19</v>
       </c>
       <c r="BG7">
-        <v>1.34</v>
+        <v>18</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2417,46 +2429,46 @@
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2464,76 +2476,76 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>2.42</v>
       </c>
       <c r="G8">
-        <v>1.76</v>
+        <v>2.64</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>880</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P8">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V8">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z8">
         <v>1000</v>
@@ -2542,13 +2554,13 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE8">
         <v>1000</v>
@@ -2557,10 +2569,10 @@
         <v>1000</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI8">
         <v>1000</v>
@@ -2584,64 +2596,64 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2698,7 +2710,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2706,34 +2718,34 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
-        <v>4.7</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>1.63</v>
+        <v>2.82</v>
       </c>
       <c r="I9">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2742,22 +2754,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
         <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.02</v>
+        <v>1.66</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2766,10 +2778,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2940,42 +2952,42 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G10">
-        <v>190</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2987,7 +2999,7 @@
         <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
         <v>1.25</v>
@@ -2999,7 +3011,7 @@
         <v>1.24</v>
       </c>
       <c r="S10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -3008,10 +3020,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3176,48 +3188,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F11">
         <v>1.1</v>
       </c>
       <c r="G11">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="H11">
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>980</v>
       </c>
       <c r="J11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3241,7 +3253,7 @@
         <v>1.24</v>
       </c>
       <c r="S11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3250,10 +3262,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3418,13 +3430,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3432,70 +3444,70 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F12">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>2.56</v>
+        <v>110</v>
       </c>
       <c r="H12">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
-        <v>3.35</v>
+        <v>110</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>1.12</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>900</v>
       </c>
       <c r="L12">
         <v>1.01</v>
       </c>
       <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>1.25</v>
+      </c>
+      <c r="O12">
+        <v>1.02</v>
+      </c>
+      <c r="P12">
+        <v>1.25</v>
+      </c>
+      <c r="Q12">
+        <v>1.02</v>
+      </c>
+      <c r="R12">
+        <v>1.24</v>
+      </c>
+      <c r="S12">
+        <v>1.03</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
         <v>1.05</v>
       </c>
-      <c r="N12">
-        <v>3.9</v>
-      </c>
-      <c r="O12">
-        <v>1.24</v>
-      </c>
-      <c r="P12">
-        <v>2.14</v>
-      </c>
-      <c r="Q12">
-        <v>1.69</v>
-      </c>
-      <c r="R12">
-        <v>1.45</v>
-      </c>
-      <c r="S12">
-        <v>2.66</v>
-      </c>
-      <c r="T12">
-        <v>1.57</v>
-      </c>
-      <c r="U12">
-        <v>2.28</v>
-      </c>
-      <c r="V12">
-        <v>1.43</v>
-      </c>
       <c r="W12">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3513,7 +3525,7 @@
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3666,78 +3678,78 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>1.12</v>
+        <v>2.3</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>2.58</v>
       </c>
       <c r="H13">
-        <v>1.12</v>
+        <v>2.84</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="J13">
-        <v>1.19</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>890</v>
+        <v>4.7</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>1.07</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q13">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="R13">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="S13">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3755,10 +3767,10 @@
         <v>1000</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE13">
         <v>1000</v>
@@ -3767,7 +3779,7 @@
         <v>1000</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH13">
         <v>1000</v>
@@ -3908,99 +3920,99 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>3.1</v>
+        <v>1.13</v>
       </c>
       <c r="G14">
-        <v>3.7</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>2.42</v>
+        <v>1.13</v>
       </c>
       <c r="I14">
-        <v>2.76</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1.22</v>
       </c>
       <c r="K14">
-        <v>3.4</v>
+        <v>890</v>
       </c>
       <c r="L14">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.07</v>
+      </c>
+      <c r="O14">
+        <v>1.02</v>
+      </c>
+      <c r="P14">
+        <v>1.07</v>
+      </c>
+      <c r="Q14">
+        <v>1.02</v>
+      </c>
+      <c r="R14">
+        <v>1.07</v>
+      </c>
+      <c r="S14">
+        <v>1.03</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
         <v>1.1</v>
       </c>
-      <c r="N14">
-        <v>2.34</v>
-      </c>
-      <c r="O14">
-        <v>1.54</v>
-      </c>
-      <c r="P14">
-        <v>1.48</v>
-      </c>
-      <c r="Q14">
-        <v>2.68</v>
-      </c>
-      <c r="R14">
-        <v>1.13</v>
-      </c>
-      <c r="S14">
-        <v>5.7</v>
-      </c>
-      <c r="T14">
-        <v>2.1</v>
-      </c>
-      <c r="U14">
-        <v>1.65</v>
-      </c>
-      <c r="V14">
-        <v>1.57</v>
-      </c>
       <c r="W14">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
         <v>1000</v>
@@ -4009,7 +4021,7 @@
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
         <v>1000</v>
@@ -4036,796 +4048,796 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F15">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="G15">
-        <v>1.92</v>
+        <v>3.7</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>2.76</v>
       </c>
       <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>3.4</v>
+      </c>
+      <c r="L15">
+        <v>1.64</v>
+      </c>
+      <c r="M15">
+        <v>1.1</v>
+      </c>
+      <c r="N15">
+        <v>2.34</v>
+      </c>
+      <c r="O15">
+        <v>1.54</v>
+      </c>
+      <c r="P15">
+        <v>1.48</v>
+      </c>
+      <c r="Q15">
+        <v>2.68</v>
+      </c>
+      <c r="R15">
+        <v>1.13</v>
+      </c>
+      <c r="S15">
+        <v>5.7</v>
+      </c>
+      <c r="T15">
+        <v>2.18</v>
+      </c>
+      <c r="U15">
+        <v>1.63</v>
+      </c>
+      <c r="V15">
+        <v>1.57</v>
+      </c>
+      <c r="W15">
+        <v>1.37</v>
+      </c>
+      <c r="X15">
+        <v>11.5</v>
+      </c>
+      <c r="Y15">
+        <v>10.5</v>
+      </c>
+      <c r="Z15">
+        <v>42</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>13</v>
+      </c>
+      <c r="AC15">
+        <v>9.6</v>
+      </c>
+      <c r="AD15">
+        <v>34</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>80</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>5.9</v>
+      </c>
+      <c r="AQ15">
+        <v>5.6</v>
+      </c>
+      <c r="AR15">
+        <v>9.4</v>
+      </c>
+      <c r="AS15">
+        <v>2.04</v>
+      </c>
+      <c r="AT15">
+        <v>6.4</v>
+      </c>
+      <c r="AU15">
+        <v>5.4</v>
+      </c>
+      <c r="AV15">
+        <v>9</v>
+      </c>
+      <c r="AW15">
+        <v>2.04</v>
+      </c>
+      <c r="AX15">
+        <v>12.5</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
+        <v>2.04</v>
+      </c>
+      <c r="BA15">
+        <v>2.04</v>
+      </c>
+      <c r="BB15">
+        <v>1.89</v>
+      </c>
+      <c r="BC15">
+        <v>2.04</v>
+      </c>
+      <c r="BD15">
+        <v>1.89</v>
+      </c>
+      <c r="BE15">
+        <v>1.89</v>
+      </c>
+      <c r="BF15">
+        <v>1.75</v>
+      </c>
+      <c r="BG15">
+        <v>1.89</v>
+      </c>
+      <c r="BH15">
+        <v>2.96</v>
+      </c>
+      <c r="BI15">
+        <v>2.12</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>2.32</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>2.32</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>4.2</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>2.32</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>2.32</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
         <v>3.6</v>
       </c>
-      <c r="K15">
-        <v>3.85</v>
-      </c>
-      <c r="L15">
-        <v>1.01</v>
-      </c>
-      <c r="M15">
-        <v>1.08</v>
-      </c>
-      <c r="N15">
-        <v>3.45</v>
-      </c>
-      <c r="O15">
-        <v>1.37</v>
-      </c>
-      <c r="P15">
-        <v>1.85</v>
-      </c>
-      <c r="Q15">
-        <v>2.08</v>
-      </c>
-      <c r="R15">
-        <v>1.31</v>
-      </c>
-      <c r="S15">
-        <v>3.8</v>
-      </c>
-      <c r="T15">
-        <v>1.92</v>
-      </c>
-      <c r="U15">
-        <v>1.94</v>
-      </c>
-      <c r="V15">
-        <v>1.24</v>
-      </c>
-      <c r="W15">
-        <v>2.08</v>
-      </c>
-      <c r="X15">
-        <v>15</v>
-      </c>
-      <c r="Y15">
-        <v>17.5</v>
-      </c>
-      <c r="Z15">
-        <v>38</v>
-      </c>
-      <c r="AA15">
-        <v>130</v>
-      </c>
-      <c r="AB15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC15">
-        <v>8.4</v>
-      </c>
-      <c r="AD15">
-        <v>21</v>
-      </c>
-      <c r="AE15">
-        <v>80</v>
-      </c>
-      <c r="AF15">
-        <v>13</v>
-      </c>
-      <c r="AG15">
-        <v>12</v>
-      </c>
-      <c r="AH15">
-        <v>24</v>
-      </c>
-      <c r="AI15">
-        <v>85</v>
-      </c>
-      <c r="AJ15">
-        <v>24</v>
-      </c>
-      <c r="AK15">
-        <v>25</v>
-      </c>
-      <c r="AL15">
-        <v>48</v>
-      </c>
-      <c r="AM15">
-        <v>150</v>
-      </c>
-      <c r="AN15">
-        <v>18</v>
-      </c>
-      <c r="AO15">
-        <v>95</v>
-      </c>
-      <c r="AP15">
-        <v>11</v>
-      </c>
-      <c r="AQ15">
-        <v>13</v>
-      </c>
-      <c r="AR15">
-        <v>5.7</v>
-      </c>
-      <c r="AS15">
-        <v>6.4</v>
-      </c>
-      <c r="AT15">
-        <v>7.2</v>
-      </c>
-      <c r="AU15">
-        <v>7.4</v>
-      </c>
-      <c r="AV15">
-        <v>16.5</v>
-      </c>
-      <c r="AW15">
-        <v>6.2</v>
-      </c>
-      <c r="AX15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15">
-        <v>5.2</v>
-      </c>
-      <c r="BA15">
-        <v>6.2</v>
-      </c>
-      <c r="BB15">
-        <v>17.5</v>
-      </c>
-      <c r="BC15">
-        <v>18.5</v>
-      </c>
-      <c r="BD15">
-        <v>5.9</v>
-      </c>
-      <c r="BE15">
-        <v>6.4</v>
-      </c>
-      <c r="BF15">
-        <v>12.5</v>
-      </c>
-      <c r="BG15">
-        <v>6.2</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.85</v>
-      </c>
-      <c r="BJ15">
-        <v>14.5</v>
-      </c>
-      <c r="BK15">
-        <v>1.65</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.85</v>
-      </c>
-      <c r="BN15">
-        <v>5.9</v>
-      </c>
-      <c r="BO15">
-        <v>3.55</v>
-      </c>
-      <c r="BP15">
-        <v>19</v>
-      </c>
-      <c r="BQ15">
-        <v>1.69</v>
-      </c>
-      <c r="BR15">
-        <v>44</v>
-      </c>
-      <c r="BS15">
-        <v>1.78</v>
-      </c>
-      <c r="BT15">
-        <v>11</v>
-      </c>
-      <c r="BU15">
-        <v>5.3</v>
-      </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="BZ15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="CB15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="G16">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
       <c r="H16">
-        <v>2.76</v>
+        <v>4.7</v>
       </c>
       <c r="I16">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J16">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O16">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q16">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R16">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S16">
         <v>3.75</v>
       </c>
       <c r="T16">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="U16">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="W16">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="X16">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y16">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z16">
+        <v>38</v>
+      </c>
+      <c r="AA16">
+        <v>130</v>
+      </c>
+      <c r="AB16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16">
+        <v>8.4</v>
+      </c>
+      <c r="AD16">
         <v>21</v>
       </c>
-      <c r="AA16">
-        <v>90</v>
-      </c>
-      <c r="AB16">
-        <v>970</v>
-      </c>
-      <c r="AC16">
-        <v>970</v>
-      </c>
-      <c r="AD16">
-        <v>970</v>
-      </c>
       <c r="AE16">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AF16">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG16">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH16">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI16">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ16">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM16">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AN16">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AO16">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AP16">
-        <v>1.59</v>
+        <v>11.5</v>
       </c>
       <c r="AQ16">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>1.38</v>
+        <v>6.4</v>
       </c>
       <c r="AS16">
-        <v>1.35</v>
+        <v>7.2</v>
       </c>
       <c r="AT16">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="AU16">
-        <v>1.49</v>
+        <v>7.4</v>
       </c>
       <c r="AV16">
-        <v>1.59</v>
+        <v>16.5</v>
       </c>
       <c r="AW16">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="AX16">
-        <v>2.06</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16">
-        <v>1.59</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>1.47</v>
+        <v>5.7</v>
       </c>
       <c r="BA16">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="BB16">
-        <v>1.34</v>
+        <v>17.5</v>
       </c>
       <c r="BC16">
-        <v>1.32</v>
+        <v>18.5</v>
       </c>
       <c r="BD16">
-        <v>1.34</v>
+        <v>6.6</v>
       </c>
       <c r="BE16">
-        <v>1.37</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
-        <v>1.32</v>
+        <v>12.5</v>
       </c>
       <c r="BG16">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="CB16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17">
+        <v>2.5</v>
+      </c>
+      <c r="G17">
+        <v>2.96</v>
+      </c>
+      <c r="H17">
+        <v>2.78</v>
+      </c>
+      <c r="I17">
+        <v>3.4</v>
+      </c>
+      <c r="J17">
+        <v>3.1</v>
+      </c>
+      <c r="K17">
+        <v>3.4</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.06</v>
+      </c>
+      <c r="N17">
+        <v>2.8</v>
+      </c>
+      <c r="O17">
+        <v>1.42</v>
+      </c>
+      <c r="P17">
+        <v>1.69</v>
+      </c>
+      <c r="Q17">
+        <v>2.24</v>
+      </c>
+      <c r="R17">
+        <v>1.24</v>
+      </c>
+      <c r="S17">
+        <v>3.75</v>
+      </c>
+      <c r="T17">
+        <v>1.84</v>
+      </c>
+      <c r="U17">
+        <v>1.91</v>
+      </c>
+      <c r="V17">
+        <v>1.44</v>
+      </c>
+      <c r="W17">
+        <v>1.52</v>
+      </c>
+      <c r="X17">
+        <v>970</v>
+      </c>
+      <c r="Y17">
+        <v>970</v>
+      </c>
+      <c r="Z17">
+        <v>21</v>
+      </c>
+      <c r="AA17">
         <v>90</v>
       </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" t="s">
-        <v>135</v>
-      </c>
-      <c r="F17">
-        <v>3.35</v>
-      </c>
-      <c r="G17">
-        <v>3.7</v>
-      </c>
-      <c r="H17">
-        <v>2.44</v>
-      </c>
-      <c r="I17">
-        <v>2.66</v>
-      </c>
-      <c r="J17">
-        <v>2.92</v>
-      </c>
-      <c r="K17">
-        <v>3.15</v>
-      </c>
-      <c r="L17">
-        <v>1.58</v>
-      </c>
-      <c r="M17">
-        <v>1.12</v>
-      </c>
-      <c r="N17">
-        <v>2.46</v>
-      </c>
-      <c r="O17">
-        <v>1.56</v>
-      </c>
-      <c r="P17">
-        <v>1.45</v>
-      </c>
-      <c r="Q17">
-        <v>2.64</v>
-      </c>
-      <c r="R17">
-        <v>1.15</v>
-      </c>
-      <c r="S17">
-        <v>5.3</v>
-      </c>
-      <c r="T17">
-        <v>2.08</v>
-      </c>
-      <c r="U17">
-        <v>1.68</v>
-      </c>
-      <c r="V17">
-        <v>1.62</v>
-      </c>
-      <c r="W17">
-        <v>1.37</v>
-      </c>
-      <c r="X17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y17">
-        <v>7.6</v>
-      </c>
-      <c r="Z17">
-        <v>15</v>
-      </c>
-      <c r="AA17">
+      <c r="AB17">
+        <v>970</v>
+      </c>
+      <c r="AC17">
+        <v>970</v>
+      </c>
+      <c r="AD17">
+        <v>970</v>
+      </c>
+      <c r="AE17">
         <v>42</v>
       </c>
-      <c r="AB17">
-        <v>9.6</v>
-      </c>
-      <c r="AC17">
-        <v>7.2</v>
-      </c>
-      <c r="AD17">
-        <v>13.5</v>
-      </c>
-      <c r="AE17">
-        <v>40</v>
-      </c>
       <c r="AF17">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AG17">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH17">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI17">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ17">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL17">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AM17">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AN17">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AO17">
         <v>44</v>
       </c>
       <c r="AP17">
-        <v>7.4</v>
+        <v>1.59</v>
       </c>
       <c r="AQ17">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR17">
-        <v>12.5</v>
+        <v>1.38</v>
       </c>
       <c r="AS17">
-        <v>9</v>
+        <v>1.35</v>
       </c>
       <c r="AT17">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="AU17">
-        <v>6.4</v>
+        <v>1.49</v>
       </c>
       <c r="AV17">
-        <v>11</v>
+        <v>1.59</v>
       </c>
       <c r="AW17">
-        <v>8.800000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="AX17">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="AY17">
-        <v>14</v>
+        <v>1.59</v>
       </c>
       <c r="AZ17">
-        <v>20</v>
+        <v>1.47</v>
       </c>
       <c r="BA17">
-        <v>9.800000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="BB17">
-        <v>10</v>
+        <v>1.34</v>
       </c>
       <c r="BC17">
-        <v>9.800000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="BD17">
-        <v>10.5</v>
+        <v>1.34</v>
       </c>
       <c r="BE17">
-        <v>11</v>
+        <v>1.37</v>
       </c>
       <c r="BF17">
-        <v>10.5</v>
+        <v>1.32</v>
       </c>
       <c r="BG17">
-        <v>32</v>
+        <v>1.33</v>
       </c>
       <c r="BH17">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -4837,7 +4849,7 @@
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
         <v>1000</v>
@@ -4855,7 +4867,7 @@
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
@@ -4876,199 +4888,199 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18">
+        <v>3.35</v>
+      </c>
+      <c r="G18">
+        <v>3.75</v>
+      </c>
+      <c r="H18">
+        <v>2.44</v>
+      </c>
+      <c r="I18">
+        <v>2.66</v>
+      </c>
+      <c r="J18">
+        <v>2.86</v>
+      </c>
+      <c r="K18">
+        <v>3.15</v>
+      </c>
+      <c r="L18">
+        <v>1.58</v>
+      </c>
+      <c r="M18">
+        <v>1.12</v>
+      </c>
+      <c r="N18">
+        <v>2.46</v>
+      </c>
+      <c r="O18">
+        <v>1.51</v>
+      </c>
+      <c r="P18">
+        <v>1.45</v>
+      </c>
+      <c r="Q18">
+        <v>2.64</v>
+      </c>
+      <c r="R18">
+        <v>1.15</v>
+      </c>
+      <c r="S18">
+        <v>5.4</v>
+      </c>
+      <c r="T18">
+        <v>2.08</v>
+      </c>
+      <c r="U18">
+        <v>1.68</v>
+      </c>
+      <c r="V18">
+        <v>1.62</v>
+      </c>
+      <c r="W18">
+        <v>1.37</v>
+      </c>
+      <c r="X18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y18">
+        <v>7.6</v>
+      </c>
+      <c r="Z18">
+        <v>15</v>
+      </c>
+      <c r="AA18">
+        <v>42</v>
+      </c>
+      <c r="AB18">
+        <v>9.6</v>
+      </c>
+      <c r="AC18">
+        <v>7.2</v>
+      </c>
+      <c r="AD18">
+        <v>13.5</v>
+      </c>
+      <c r="AE18">
+        <v>40</v>
+      </c>
+      <c r="AF18">
+        <v>24</v>
+      </c>
+      <c r="AG18">
+        <v>17</v>
+      </c>
+      <c r="AH18">
+        <v>25</v>
+      </c>
+      <c r="AI18">
+        <v>85</v>
+      </c>
+      <c r="AJ18">
         <v>90</v>
       </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18">
-        <v>1.72</v>
-      </c>
-      <c r="G18">
-        <v>1.88</v>
-      </c>
-      <c r="H18">
-        <v>5.3</v>
-      </c>
-      <c r="I18">
-        <v>7</v>
-      </c>
-      <c r="J18">
-        <v>3.2</v>
-      </c>
-      <c r="K18">
-        <v>3.8</v>
-      </c>
-      <c r="L18">
-        <v>1.5</v>
-      </c>
-      <c r="M18">
-        <v>1.09</v>
-      </c>
-      <c r="N18">
-        <v>2.84</v>
-      </c>
-      <c r="O18">
-        <v>1.45</v>
-      </c>
-      <c r="P18">
-        <v>1.61</v>
-      </c>
-      <c r="Q18">
-        <v>2.24</v>
-      </c>
-      <c r="R18">
-        <v>1.21</v>
-      </c>
-      <c r="S18">
-        <v>4.2</v>
-      </c>
-      <c r="T18">
-        <v>2.1</v>
-      </c>
-      <c r="U18">
-        <v>1.65</v>
-      </c>
-      <c r="V18">
-        <v>1.17</v>
-      </c>
-      <c r="W18">
-        <v>2.12</v>
-      </c>
-      <c r="X18">
-        <v>970</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>970</v>
-      </c>
-      <c r="AC18">
-        <v>970</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>970</v>
-      </c>
-      <c r="AG18">
-        <v>970</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN18">
+        <v>110</v>
+      </c>
+      <c r="AO18">
         <v>44</v>
       </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
       <c r="AP18">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ18">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="AR18">
-        <v>1.62</v>
+        <v>12.5</v>
       </c>
       <c r="AS18">
-        <v>1.62</v>
+        <v>9</v>
       </c>
       <c r="AT18">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV18">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>1.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18">
+        <v>20</v>
+      </c>
+      <c r="AY18">
+        <v>14</v>
+      </c>
+      <c r="AZ18">
+        <v>20</v>
+      </c>
+      <c r="BA18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB18">
+        <v>10</v>
+      </c>
+      <c r="BC18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD18">
+        <v>10.5</v>
+      </c>
+      <c r="BE18">
+        <v>11</v>
+      </c>
+      <c r="BF18">
+        <v>10.5</v>
+      </c>
+      <c r="BG18">
+        <v>32</v>
+      </c>
+      <c r="BH18">
+        <v>3.05</v>
+      </c>
+      <c r="BI18">
+        <v>2.28</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
         <v>6.8</v>
       </c>
-      <c r="AY18">
-        <v>7.6</v>
-      </c>
-      <c r="AZ18">
-        <v>1.62</v>
-      </c>
-      <c r="BA18">
-        <v>1.62</v>
-      </c>
-      <c r="BB18">
-        <v>1.7</v>
-      </c>
-      <c r="BC18">
-        <v>1.62</v>
-      </c>
-      <c r="BD18">
-        <v>1.62</v>
-      </c>
-      <c r="BE18">
-        <v>1.62</v>
-      </c>
-      <c r="BF18">
-        <v>1.64</v>
-      </c>
-      <c r="BG18">
-        <v>1.62</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.27</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.01</v>
-      </c>
       <c r="BL18">
         <v>1000</v>
       </c>
@@ -5079,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.47</v>
+        <v>5.1</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5097,7 +5109,7 @@
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV18">
         <v>1000</v>
@@ -5118,7 +5130,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5126,241 +5138,483 @@
         <v>89</v>
       </c>
       <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19">
+        <v>1.72</v>
+      </c>
+      <c r="G19">
+        <v>1.88</v>
+      </c>
+      <c r="H19">
+        <v>5.3</v>
+      </c>
+      <c r="I19">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>3.2</v>
+      </c>
+      <c r="K19">
+        <v>3.8</v>
+      </c>
+      <c r="L19">
+        <v>1.5</v>
+      </c>
+      <c r="M19">
+        <v>1.06</v>
+      </c>
+      <c r="N19">
+        <v>2.84</v>
+      </c>
+      <c r="O19">
+        <v>1.45</v>
+      </c>
+      <c r="P19">
+        <v>1.61</v>
+      </c>
+      <c r="Q19">
+        <v>2.26</v>
+      </c>
+      <c r="R19">
+        <v>1.21</v>
+      </c>
+      <c r="S19">
+        <v>4.2</v>
+      </c>
+      <c r="T19">
+        <v>2.1</v>
+      </c>
+      <c r="U19">
+        <v>1.65</v>
+      </c>
+      <c r="V19">
+        <v>1.17</v>
+      </c>
+      <c r="W19">
+        <v>2.12</v>
+      </c>
+      <c r="X19">
+        <v>970</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>970</v>
+      </c>
+      <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>970</v>
+      </c>
+      <c r="AG19">
+        <v>970</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>44</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>7</v>
+      </c>
+      <c r="AQ19">
+        <v>1.73</v>
+      </c>
+      <c r="AR19">
+        <v>1.62</v>
+      </c>
+      <c r="AS19">
+        <v>1.62</v>
+      </c>
+      <c r="AT19">
+        <v>5.2</v>
+      </c>
+      <c r="AU19">
+        <v>6.2</v>
+      </c>
+      <c r="AV19">
+        <v>1.62</v>
+      </c>
+      <c r="AW19">
+        <v>1.62</v>
+      </c>
+      <c r="AX19">
+        <v>6.8</v>
+      </c>
+      <c r="AY19">
+        <v>7.6</v>
+      </c>
+      <c r="AZ19">
+        <v>1.62</v>
+      </c>
+      <c r="BA19">
+        <v>1.62</v>
+      </c>
+      <c r="BB19">
+        <v>1.73</v>
+      </c>
+      <c r="BC19">
+        <v>1.62</v>
+      </c>
+      <c r="BD19">
+        <v>1.62</v>
+      </c>
+      <c r="BE19">
+        <v>1.62</v>
+      </c>
+      <c r="BF19">
+        <v>1.66</v>
+      </c>
+      <c r="BG19">
+        <v>1.62</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.27</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.47</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
         <v>90</v>
       </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F19">
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20">
         <v>3.7</v>
       </c>
-      <c r="G19">
+      <c r="G20">
         <v>4.9</v>
       </c>
-      <c r="H19">
-        <v>1.97</v>
-      </c>
-      <c r="I19">
+      <c r="H20">
+        <v>1.98</v>
+      </c>
+      <c r="I20">
         <v>2.22</v>
       </c>
-      <c r="J19">
+      <c r="J20">
         <v>3.3</v>
       </c>
-      <c r="K19">
+      <c r="K20">
         <v>3.65</v>
       </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
         <v>1.05</v>
       </c>
-      <c r="N19">
+      <c r="N20">
         <v>3.2</v>
       </c>
-      <c r="O19">
+      <c r="O20">
         <v>1.39</v>
       </c>
-      <c r="P19">
+      <c r="P20">
         <v>1.65</v>
       </c>
-      <c r="Q19">
+      <c r="Q20">
         <v>2.12</v>
       </c>
-      <c r="R19">
+      <c r="R20">
         <v>1.25</v>
       </c>
-      <c r="S19">
+      <c r="S20">
         <v>3.6</v>
       </c>
-      <c r="T19">
+      <c r="T20">
         <v>1.9</v>
       </c>
-      <c r="U19">
+      <c r="U20">
         <v>1.81</v>
       </c>
-      <c r="V19">
+      <c r="V20">
         <v>1.82</v>
       </c>
-      <c r="W19">
+      <c r="W20">
         <v>1.26</v>
       </c>
-      <c r="X19">
+      <c r="X20">
         <v>24</v>
       </c>
-      <c r="Y19">
-        <v>15</v>
-      </c>
-      <c r="Z19">
+      <c r="Y20">
+        <v>970</v>
+      </c>
+      <c r="Z20">
         <v>24</v>
       </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
         <v>34</v>
       </c>
-      <c r="AC19">
-        <v>10.5</v>
-      </c>
-      <c r="AD19">
-        <v>19</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>8.6</v>
-      </c>
-      <c r="AQ19">
-        <v>6</v>
-      </c>
-      <c r="AR19">
-        <v>8</v>
-      </c>
-      <c r="AS19">
-        <v>1.01</v>
-      </c>
-      <c r="AT19">
+      <c r="AC20">
+        <v>970</v>
+      </c>
+      <c r="AD20">
+        <v>970</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.4</v>
+      </c>
+      <c r="AQ20">
+        <v>1.35</v>
+      </c>
+      <c r="AR20">
+        <v>1.4</v>
+      </c>
+      <c r="AS20">
+        <v>1.49</v>
+      </c>
+      <c r="AT20">
         <v>7</v>
       </c>
-      <c r="AU19">
-        <v>5.7</v>
-      </c>
-      <c r="AV19">
+      <c r="AU20">
+        <v>1.3</v>
+      </c>
+      <c r="AV20">
         <v>7.4</v>
       </c>
-      <c r="AW19">
-        <v>1.01</v>
-      </c>
-      <c r="AX19">
-        <v>1.01</v>
-      </c>
-      <c r="AY19">
-        <v>10</v>
-      </c>
-      <c r="AZ19">
-        <v>1.01</v>
-      </c>
-      <c r="BA19">
-        <v>1.01</v>
-      </c>
-      <c r="BB19">
-        <v>1.01</v>
-      </c>
-      <c r="BC19">
-        <v>1.01</v>
-      </c>
-      <c r="BD19">
-        <v>1.01</v>
-      </c>
-      <c r="BE19">
-        <v>1.01</v>
-      </c>
-      <c r="BF19">
-        <v>1.01</v>
-      </c>
-      <c r="BG19">
+      <c r="AW20">
+        <v>1.49</v>
+      </c>
+      <c r="AX20">
+        <v>1.49</v>
+      </c>
+      <c r="AY20">
+        <v>1.49</v>
+      </c>
+      <c r="AZ20">
+        <v>1.49</v>
+      </c>
+      <c r="BA20">
+        <v>1.49</v>
+      </c>
+      <c r="BB20">
+        <v>1.49</v>
+      </c>
+      <c r="BC20">
+        <v>1.49</v>
+      </c>
+      <c r="BD20">
+        <v>1.49</v>
+      </c>
+      <c r="BE20">
+        <v>1.49</v>
+      </c>
+      <c r="BF20">
+        <v>1.49</v>
+      </c>
+      <c r="BG20">
         <v>11</v>
       </c>
-      <c r="BH19">
+      <c r="BH20">
         <v>3.75</v>
       </c>
-      <c r="BI19">
+      <c r="BI20">
         <v>2.48</v>
       </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
         <v>1.37</v>
       </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
         <v>1.37</v>
       </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
         <v>1.37</v>
       </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
         <v>1.37</v>
       </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
         <v>1.37</v>
       </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
-      <c r="BU19">
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
         <v>1.37</v>
       </c>
-      <c r="BV19">
-        <v>1000</v>
-      </c>
-      <c r="BW19">
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
         <v>1.37</v>
       </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
         <v>1.37</v>
       </c>
-      <c r="BZ19">
-        <v>1000</v>
-      </c>
-      <c r="CA19">
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
         <v>1.37</v>
       </c>
-      <c r="CB19" t="s">
-        <v>138</v>
+      <c r="CB20" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="146">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Swedish Division 1</t>
   </si>
   <si>
+    <t>Georgian Umaglesi Liga</t>
+  </si>
+  <si>
     <t>Danish 1st Division</t>
   </si>
   <si>
@@ -358,15 +361,18 @@
     <t>Vasalunds IF</t>
   </si>
   <si>
+    <t>Jonkopings Sodra</t>
+  </si>
+  <si>
+    <t>FC Spaeri</t>
+  </si>
+  <si>
+    <t>HB Koge</t>
+  </si>
+  <si>
     <t>FC Arlanda</t>
   </si>
   <si>
-    <t>HB Koge</t>
-  </si>
-  <si>
-    <t>Jonkopings Sodra</t>
-  </si>
-  <si>
     <t>Aldosivi</t>
   </si>
   <si>
@@ -415,15 +421,18 @@
     <t>Assyriska FF</t>
   </si>
   <si>
+    <t>Skovde Aik</t>
+  </si>
+  <si>
+    <t>Dila Gori</t>
+  </si>
+  <si>
+    <t>Hobro</t>
+  </si>
+  <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
-    <t>Hobro</t>
-  </si>
-  <si>
-    <t>Skovde Aik</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -442,7 +451,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 05:11:28</t>
+    <t>2026-09-20 07:32:55</t>
   </si>
 </sst>
 </file>
@@ -774,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1024,16 +1033,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F2">
         <v>1.29</v>
@@ -1063,10 +1072,10 @@
         <v>8</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
         <v>1.39</v>
@@ -1075,7 +1084,7 @@
         <v>1.97</v>
       </c>
       <c r="S2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T2">
         <v>1.78</v>
@@ -1093,7 +1102,7 @@
         <v>44</v>
       </c>
       <c r="Y2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z2">
         <v>120</v>
@@ -1111,7 +1120,7 @@
         <v>38</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1141,7 +1150,7 @@
         <v>3.55</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP2">
         <v>36</v>
@@ -1153,7 +1162,7 @@
         <v>15.5</v>
       </c>
       <c r="AS2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1165,7 +1174,7 @@
         <v>34</v>
       </c>
       <c r="AW2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -1174,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA2">
         <v>15</v>
@@ -1258,7 +1267,7 @@
         <v>1.27</v>
       </c>
       <c r="CB2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1266,22 +1275,22 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F3">
         <v>1.87</v>
       </c>
       <c r="G3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H3">
         <v>4.4</v>
@@ -1308,43 +1317,43 @@
         <v>1.29</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.42</v>
       </c>
       <c r="S3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
         <v>1.82</v>
       </c>
       <c r="U3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V3">
         <v>1.28</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA3">
         <v>110</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>8.800000000000001</v>
@@ -1353,7 +1362,7 @@
         <v>18</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
@@ -1374,7 +1383,7 @@
         <v>21</v>
       </c>
       <c r="AL3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3">
         <v>110</v>
@@ -1383,7 +1392,7 @@
         <v>12</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
@@ -1395,7 +1404,7 @@
         <v>23</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT3">
         <v>8.800000000000001</v>
@@ -1404,10 +1413,10 @@
         <v>8</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1428,10 +1437,10 @@
         <v>16</v>
       </c>
       <c r="BD3">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF3">
         <v>9.199999999999999</v>
@@ -1500,7 +1509,7 @@
         <v>1.17</v>
       </c>
       <c r="CB3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,16 +1517,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F4">
         <v>2.34</v>
@@ -1535,7 +1544,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
         <v>1.69</v>
@@ -1544,7 +1553,7 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O4">
         <v>1.66</v>
@@ -1577,7 +1586,7 @@
         <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
         <v>27</v>
@@ -1682,67 +1691,67 @@
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI4">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="CB4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1750,16 +1759,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F5">
         <v>4.6</v>
@@ -1768,10 +1777,10 @@
         <v>5.1</v>
       </c>
       <c r="H5">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="I5">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J5">
         <v>3.65</v>
@@ -1792,25 +1801,25 @@
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q5">
         <v>2.04</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
         <v>3.7</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="W5">
         <v>1.25</v>
@@ -1837,7 +1846,7 @@
         <v>12.5</v>
       </c>
       <c r="AE5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF5">
         <v>44</v>
@@ -1885,7 +1894,7 @@
         <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>8.800000000000001</v>
@@ -1984,7 +1993,7 @@
         <v>4.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1992,34 +2001,34 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F6">
+        <v>4.9</v>
+      </c>
+      <c r="G6">
+        <v>36</v>
+      </c>
+      <c r="H6">
+        <v>1.4</v>
+      </c>
+      <c r="I6">
+        <v>1.74</v>
+      </c>
+      <c r="J6">
         <v>4.1</v>
       </c>
-      <c r="G6">
-        <v>95</v>
-      </c>
-      <c r="H6">
-        <v>1.28</v>
-      </c>
-      <c r="I6">
-        <v>1.76</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
       <c r="K6">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2034,10 +2043,10 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="R6">
         <v>1.18</v>
@@ -2052,7 +2061,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -2061,10 +2070,10 @@
         <v>1000</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA6">
         <v>900</v>
@@ -2076,10 +2085,10 @@
         <v>1000</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF6">
         <v>350</v>
@@ -2091,7 +2100,7 @@
         <v>1000</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
@@ -2112,52 +2121,52 @@
         <v>29</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT6">
         <v>2.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BF6">
         <v>1.55</v>
@@ -2226,7 +2235,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2234,19 +2243,19 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G7">
         <v>2.78</v>
@@ -2363,7 +2372,7 @@
         <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2375,7 +2384,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
         <v>17</v>
@@ -2399,7 +2408,7 @@
         <v>8.6</v>
       </c>
       <c r="BE7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF7">
         <v>19</v>
@@ -2414,10 +2423,10 @@
         <v>3.1</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2432,43 +2441,43 @@
         <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2476,67 +2485,67 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H8">
         <v>3</v>
       </c>
       <c r="I8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
         <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
         <v>1.38</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R8">
         <v>1.26</v>
       </c>
       <c r="S8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T8">
         <v>1.75</v>
       </c>
       <c r="U8">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
         <v>1.6</v>
@@ -2557,7 +2566,7 @@
         <v>970</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <v>970</v>
@@ -2599,61 +2608,61 @@
         <v>1.48</v>
       </c>
       <c r="AQ8">
+        <v>1.49</v>
+      </c>
+      <c r="AR8">
+        <v>1.6</v>
+      </c>
+      <c r="AS8">
+        <v>1.6</v>
+      </c>
+      <c r="AT8">
+        <v>1.45</v>
+      </c>
+      <c r="AU8">
+        <v>1.38</v>
+      </c>
+      <c r="AV8">
+        <v>1.54</v>
+      </c>
+      <c r="AW8">
+        <v>1.6</v>
+      </c>
+      <c r="AX8">
+        <v>1.59</v>
+      </c>
+      <c r="AY8">
+        <v>1.49</v>
+      </c>
+      <c r="AZ8">
         <v>1.47</v>
       </c>
-      <c r="AR8">
-        <v>1.58</v>
-      </c>
-      <c r="AS8">
-        <v>1.58</v>
-      </c>
-      <c r="AT8">
-        <v>1.43</v>
-      </c>
-      <c r="AU8">
-        <v>1.36</v>
-      </c>
-      <c r="AV8">
-        <v>1.52</v>
-      </c>
-      <c r="AW8">
-        <v>1.58</v>
-      </c>
-      <c r="AX8">
-        <v>1.57</v>
-      </c>
-      <c r="AY8">
-        <v>1.48</v>
-      </c>
-      <c r="AZ8">
-        <v>1.46</v>
-      </c>
       <c r="BA8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BB8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BC8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BD8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BE8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BG8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2710,7 +2719,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2718,19 +2727,19 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G9">
         <v>1.76</v>
@@ -2739,7 +2748,7 @@
         <v>2.82</v>
       </c>
       <c r="I9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2763,13 +2772,13 @@
         <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R9">
         <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2952,7 +2961,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2960,31 +2969,31 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F10">
         <v>1.6</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H10">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I10">
         <v>3.15</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
         <v>870</v>
@@ -3020,10 +3029,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3194,7 +3203,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3202,16 +3211,16 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F11">
         <v>1.1</v>
@@ -3223,10 +3232,10 @@
         <v>1.1</v>
       </c>
       <c r="I11">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="J11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K11">
         <v>900</v>
@@ -3238,7 +3247,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
         <v>1.02</v>
@@ -3262,10 +3271,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3436,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3444,34 +3453,34 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G12">
         <v>110</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I12">
         <v>110</v>
       </c>
       <c r="J12">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="K12">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3480,19 +3489,19 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="O12">
         <v>1.02</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Q12">
         <v>1.02</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="S12">
         <v>1.03</v>
@@ -3504,10 +3513,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3678,7 +3687,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3686,70 +3695,70 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="O13">
+        <v>1.01</v>
+      </c>
+      <c r="P13">
         <v>1.24</v>
       </c>
-      <c r="P13">
-        <v>2.16</v>
-      </c>
       <c r="Q13">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="T13">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3767,10 +3776,10 @@
         <v>1000</v>
       </c>
       <c r="AC13">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
         <v>1000</v>
@@ -3779,7 +3788,7 @@
         <v>1000</v>
       </c>
       <c r="AG13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
         <v>1000</v>
@@ -3920,78 +3929,78 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>2.58</v>
       </c>
       <c r="H14">
-        <v>1.13</v>
+        <v>2.84</v>
       </c>
       <c r="I14">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="J14">
-        <v>1.22</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
-        <v>890</v>
+        <v>4.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>1.07</v>
+        <v>4.2</v>
       </c>
       <c r="O14">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q14">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="S14">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4009,10 +4018,10 @@
         <v>1000</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE14">
         <v>1000</v>
@@ -4021,7 +4030,7 @@
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH14">
         <v>1000</v>
@@ -4162,99 +4171,99 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
         <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="G15">
-        <v>3.7</v>
+        <v>110</v>
       </c>
       <c r="H15">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="I15">
-        <v>2.76</v>
+        <v>110</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>1.15</v>
       </c>
       <c r="K15">
-        <v>3.4</v>
+        <v>900</v>
       </c>
       <c r="L15">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="O15">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="R15">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="S15">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="T15">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="W15">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
         <v>1000</v>
@@ -4263,7 +4272,7 @@
         <v>1000</v>
       </c>
       <c r="AG15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
         <v>1000</v>
@@ -4290,796 +4299,796 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="G16">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="H16">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="I16">
-        <v>5.1</v>
+        <v>2.76</v>
       </c>
       <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>3.3</v>
+      </c>
+      <c r="L16">
+        <v>1.59</v>
+      </c>
+      <c r="M16">
+        <v>1.1</v>
+      </c>
+      <c r="N16">
+        <v>2.34</v>
+      </c>
+      <c r="O16">
+        <v>1.54</v>
+      </c>
+      <c r="P16">
+        <v>1.48</v>
+      </c>
+      <c r="Q16">
+        <v>2.72</v>
+      </c>
+      <c r="R16">
+        <v>1.13</v>
+      </c>
+      <c r="S16">
+        <v>5.7</v>
+      </c>
+      <c r="T16">
+        <v>2.18</v>
+      </c>
+      <c r="U16">
+        <v>1.64</v>
+      </c>
+      <c r="V16">
+        <v>1.57</v>
+      </c>
+      <c r="W16">
+        <v>1.37</v>
+      </c>
+      <c r="X16">
+        <v>11.5</v>
+      </c>
+      <c r="Y16">
+        <v>10.5</v>
+      </c>
+      <c r="Z16">
+        <v>40</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>14</v>
+      </c>
+      <c r="AC16">
+        <v>10</v>
+      </c>
+      <c r="AD16">
+        <v>36</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>100</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>5.9</v>
+      </c>
+      <c r="AQ16">
+        <v>6</v>
+      </c>
+      <c r="AR16">
+        <v>9.4</v>
+      </c>
+      <c r="AS16">
+        <v>1.72</v>
+      </c>
+      <c r="AT16">
+        <v>6.4</v>
+      </c>
+      <c r="AU16">
+        <v>5.4</v>
+      </c>
+      <c r="AV16">
+        <v>9</v>
+      </c>
+      <c r="AW16">
+        <v>1.72</v>
+      </c>
+      <c r="AX16">
+        <v>12</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>1.72</v>
+      </c>
+      <c r="BA16">
+        <v>1.72</v>
+      </c>
+      <c r="BB16">
+        <v>1.72</v>
+      </c>
+      <c r="BC16">
+        <v>1.72</v>
+      </c>
+      <c r="BD16">
+        <v>1.72</v>
+      </c>
+      <c r="BE16">
+        <v>1.72</v>
+      </c>
+      <c r="BF16">
+        <v>1.72</v>
+      </c>
+      <c r="BG16">
+        <v>1.72</v>
+      </c>
+      <c r="BH16">
+        <v>2.96</v>
+      </c>
+      <c r="BI16">
+        <v>2.12</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>2.32</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>2.32</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>4.2</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>2.32</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>2.32</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
         <v>3.6</v>
       </c>
-      <c r="K16">
-        <v>3.85</v>
-      </c>
-      <c r="L16">
-        <v>1.4</v>
-      </c>
-      <c r="M16">
-        <v>1.08</v>
-      </c>
-      <c r="N16">
-        <v>3.35</v>
-      </c>
-      <c r="O16">
-        <v>1.37</v>
-      </c>
-      <c r="P16">
-        <v>1.82</v>
-      </c>
-      <c r="Q16">
-        <v>2.06</v>
-      </c>
-      <c r="R16">
-        <v>1.31</v>
-      </c>
-      <c r="S16">
-        <v>3.75</v>
-      </c>
-      <c r="T16">
-        <v>1.92</v>
-      </c>
-      <c r="U16">
-        <v>1.96</v>
-      </c>
-      <c r="V16">
-        <v>1.24</v>
-      </c>
-      <c r="W16">
-        <v>2.08</v>
-      </c>
-      <c r="X16">
-        <v>15</v>
-      </c>
-      <c r="Y16">
-        <v>17.5</v>
-      </c>
-      <c r="Z16">
-        <v>38</v>
-      </c>
-      <c r="AA16">
-        <v>130</v>
-      </c>
-      <c r="AB16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC16">
-        <v>8.4</v>
-      </c>
-      <c r="AD16">
-        <v>21</v>
-      </c>
-      <c r="AE16">
-        <v>80</v>
-      </c>
-      <c r="AF16">
-        <v>11</v>
-      </c>
-      <c r="AG16">
-        <v>12</v>
-      </c>
-      <c r="AH16">
-        <v>24</v>
-      </c>
-      <c r="AI16">
-        <v>85</v>
-      </c>
-      <c r="AJ16">
-        <v>24</v>
-      </c>
-      <c r="AK16">
-        <v>25</v>
-      </c>
-      <c r="AL16">
-        <v>48</v>
-      </c>
-      <c r="AM16">
-        <v>150</v>
-      </c>
-      <c r="AN16">
-        <v>17</v>
-      </c>
-      <c r="AO16">
-        <v>95</v>
-      </c>
-      <c r="AP16">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16">
-        <v>13</v>
-      </c>
-      <c r="AR16">
-        <v>6.4</v>
-      </c>
-      <c r="AS16">
-        <v>7.2</v>
-      </c>
-      <c r="AT16">
-        <v>7.2</v>
-      </c>
-      <c r="AU16">
-        <v>7.4</v>
-      </c>
-      <c r="AV16">
-        <v>16.5</v>
-      </c>
-      <c r="AW16">
-        <v>7</v>
-      </c>
-      <c r="AX16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ16">
-        <v>5.7</v>
-      </c>
-      <c r="BA16">
-        <v>7</v>
-      </c>
-      <c r="BB16">
-        <v>17.5</v>
-      </c>
-      <c r="BC16">
-        <v>18.5</v>
-      </c>
-      <c r="BD16">
-        <v>6.6</v>
-      </c>
-      <c r="BE16">
-        <v>7.2</v>
-      </c>
-      <c r="BF16">
-        <v>12.5</v>
-      </c>
-      <c r="BG16">
-        <v>7</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.86</v>
-      </c>
-      <c r="BJ16">
-        <v>14.5</v>
-      </c>
-      <c r="BK16">
-        <v>3.1</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.86</v>
-      </c>
-      <c r="BN16">
-        <v>5.9</v>
-      </c>
-      <c r="BO16">
-        <v>3.65</v>
-      </c>
-      <c r="BP16">
-        <v>19</v>
-      </c>
-      <c r="BQ16">
-        <v>1.69</v>
-      </c>
-      <c r="BR16">
-        <v>40</v>
-      </c>
-      <c r="BS16">
-        <v>1.79</v>
-      </c>
-      <c r="BT16">
-        <v>11</v>
-      </c>
-      <c r="BU16">
-        <v>5.4</v>
-      </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="BZ16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="CB16" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
         <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="G17">
-        <v>2.96</v>
+        <v>1.93</v>
       </c>
       <c r="H17">
-        <v>2.78</v>
+        <v>4.8</v>
       </c>
       <c r="I17">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J17">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
+        <v>1.82</v>
+      </c>
+      <c r="Q17">
+        <v>2.06</v>
+      </c>
+      <c r="R17">
+        <v>1.32</v>
+      </c>
+      <c r="S17">
+        <v>3.8</v>
+      </c>
+      <c r="T17">
+        <v>1.93</v>
+      </c>
+      <c r="U17">
+        <v>1.96</v>
+      </c>
+      <c r="V17">
+        <v>1.23</v>
+      </c>
+      <c r="W17">
+        <v>2.06</v>
+      </c>
+      <c r="X17">
+        <v>15</v>
+      </c>
+      <c r="Y17">
+        <v>17.5</v>
+      </c>
+      <c r="Z17">
+        <v>38</v>
+      </c>
+      <c r="AA17">
+        <v>130</v>
+      </c>
+      <c r="AB17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC17">
+        <v>8.4</v>
+      </c>
+      <c r="AD17">
+        <v>21</v>
+      </c>
+      <c r="AE17">
+        <v>80</v>
+      </c>
+      <c r="AF17">
+        <v>11</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>24</v>
+      </c>
+      <c r="AI17">
+        <v>85</v>
+      </c>
+      <c r="AJ17">
+        <v>24</v>
+      </c>
+      <c r="AK17">
+        <v>25</v>
+      </c>
+      <c r="AL17">
+        <v>48</v>
+      </c>
+      <c r="AM17">
+        <v>150</v>
+      </c>
+      <c r="AN17">
+        <v>17</v>
+      </c>
+      <c r="AO17">
+        <v>95</v>
+      </c>
+      <c r="AP17">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17">
+        <v>13</v>
+      </c>
+      <c r="AR17">
+        <v>6.4</v>
+      </c>
+      <c r="AS17">
+        <v>7.2</v>
+      </c>
+      <c r="AT17">
+        <v>7.2</v>
+      </c>
+      <c r="AU17">
+        <v>7.4</v>
+      </c>
+      <c r="AV17">
+        <v>16.5</v>
+      </c>
+      <c r="AW17">
+        <v>7</v>
+      </c>
+      <c r="AX17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>5.7</v>
+      </c>
+      <c r="BA17">
+        <v>7</v>
+      </c>
+      <c r="BB17">
+        <v>17.5</v>
+      </c>
+      <c r="BC17">
+        <v>18.5</v>
+      </c>
+      <c r="BD17">
+        <v>6.6</v>
+      </c>
+      <c r="BE17">
+        <v>7.2</v>
+      </c>
+      <c r="BF17">
+        <v>12.5</v>
+      </c>
+      <c r="BG17">
+        <v>7</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.87</v>
+      </c>
+      <c r="BJ17">
+        <v>14.5</v>
+      </c>
+      <c r="BK17">
+        <v>3.35</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.86</v>
+      </c>
+      <c r="BN17">
+        <v>5.9</v>
+      </c>
+      <c r="BO17">
+        <v>3.75</v>
+      </c>
+      <c r="BP17">
+        <v>18.5</v>
+      </c>
+      <c r="BQ17">
         <v>1.69</v>
       </c>
-      <c r="Q17">
-        <v>2.24</v>
-      </c>
-      <c r="R17">
-        <v>1.24</v>
-      </c>
-      <c r="S17">
-        <v>3.75</v>
-      </c>
-      <c r="T17">
-        <v>1.84</v>
-      </c>
-      <c r="U17">
-        <v>1.91</v>
-      </c>
-      <c r="V17">
-        <v>1.44</v>
-      </c>
-      <c r="W17">
-        <v>1.52</v>
-      </c>
-      <c r="X17">
-        <v>970</v>
-      </c>
-      <c r="Y17">
-        <v>970</v>
-      </c>
-      <c r="Z17">
-        <v>21</v>
-      </c>
-      <c r="AA17">
-        <v>90</v>
-      </c>
-      <c r="AB17">
-        <v>970</v>
-      </c>
-      <c r="AC17">
-        <v>970</v>
-      </c>
-      <c r="AD17">
-        <v>970</v>
-      </c>
-      <c r="AE17">
-        <v>42</v>
-      </c>
-      <c r="AF17">
-        <v>970</v>
-      </c>
-      <c r="AG17">
-        <v>970</v>
-      </c>
-      <c r="AH17">
-        <v>20</v>
-      </c>
-      <c r="AI17">
-        <v>60</v>
-      </c>
-      <c r="AJ17">
-        <v>46</v>
-      </c>
-      <c r="AK17">
-        <v>36</v>
-      </c>
-      <c r="AL17">
-        <v>55</v>
-      </c>
-      <c r="AM17">
-        <v>290</v>
-      </c>
-      <c r="AN17">
-        <v>36</v>
-      </c>
-      <c r="AO17">
-        <v>44</v>
-      </c>
-      <c r="AP17">
-        <v>1.59</v>
-      </c>
-      <c r="AQ17">
-        <v>4.6</v>
-      </c>
-      <c r="AR17">
-        <v>1.38</v>
-      </c>
-      <c r="AS17">
-        <v>1.35</v>
-      </c>
-      <c r="AT17">
-        <v>1.74</v>
-      </c>
-      <c r="AU17">
-        <v>1.49</v>
-      </c>
-      <c r="AV17">
-        <v>1.59</v>
-      </c>
-      <c r="AW17">
-        <v>1.33</v>
-      </c>
-      <c r="AX17">
-        <v>2.06</v>
-      </c>
-      <c r="AY17">
-        <v>1.59</v>
-      </c>
-      <c r="AZ17">
-        <v>1.47</v>
-      </c>
-      <c r="BA17">
-        <v>1.34</v>
-      </c>
-      <c r="BB17">
-        <v>1.34</v>
-      </c>
-      <c r="BC17">
-        <v>1.32</v>
-      </c>
-      <c r="BD17">
-        <v>1.34</v>
-      </c>
-      <c r="BE17">
-        <v>1.37</v>
-      </c>
-      <c r="BF17">
-        <v>1.32</v>
-      </c>
-      <c r="BG17">
-        <v>1.33</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.01</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
-      <c r="BO17">
-        <v>1.01</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>1.01</v>
-      </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="CB17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
         <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F18">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="G18">
+        <v>2.94</v>
+      </c>
+      <c r="H18">
+        <v>2.72</v>
+      </c>
+      <c r="I18">
+        <v>3.3</v>
+      </c>
+      <c r="J18">
+        <v>3.1</v>
+      </c>
+      <c r="K18">
+        <v>3.55</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>2.8</v>
+      </c>
+      <c r="O18">
+        <v>1.42</v>
+      </c>
+      <c r="P18">
+        <v>1.69</v>
+      </c>
+      <c r="Q18">
+        <v>2.18</v>
+      </c>
+      <c r="R18">
+        <v>1.24</v>
+      </c>
+      <c r="S18">
         <v>3.75</v>
       </c>
-      <c r="H18">
-        <v>2.44</v>
-      </c>
-      <c r="I18">
-        <v>2.66</v>
-      </c>
-      <c r="J18">
-        <v>2.86</v>
-      </c>
-      <c r="K18">
-        <v>3.15</v>
-      </c>
-      <c r="L18">
-        <v>1.58</v>
-      </c>
-      <c r="M18">
-        <v>1.12</v>
-      </c>
-      <c r="N18">
-        <v>2.46</v>
-      </c>
-      <c r="O18">
+      <c r="T18">
+        <v>1.84</v>
+      </c>
+      <c r="U18">
+        <v>1.85</v>
+      </c>
+      <c r="V18">
+        <v>1.43</v>
+      </c>
+      <c r="W18">
         <v>1.51</v>
       </c>
-      <c r="P18">
-        <v>1.45</v>
-      </c>
-      <c r="Q18">
-        <v>2.64</v>
-      </c>
-      <c r="R18">
-        <v>1.15</v>
-      </c>
-      <c r="S18">
-        <v>5.4</v>
-      </c>
-      <c r="T18">
-        <v>2.08</v>
-      </c>
-      <c r="U18">
-        <v>1.68</v>
-      </c>
-      <c r="V18">
-        <v>1.62</v>
-      </c>
-      <c r="W18">
-        <v>1.37</v>
-      </c>
       <c r="X18">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y18">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA18">
+        <v>90</v>
+      </c>
+      <c r="AB18">
+        <v>970</v>
+      </c>
+      <c r="AC18">
+        <v>970</v>
+      </c>
+      <c r="AD18">
+        <v>970</v>
+      </c>
+      <c r="AE18">
         <v>42</v>
       </c>
-      <c r="AB18">
-        <v>9.6</v>
-      </c>
-      <c r="AC18">
-        <v>7.2</v>
-      </c>
-      <c r="AD18">
-        <v>13.5</v>
-      </c>
-      <c r="AE18">
-        <v>40</v>
-      </c>
       <c r="AF18">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AG18">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH18">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI18">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ18">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AK18">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL18">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AM18">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AN18">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="AO18">
         <v>44</v>
       </c>
       <c r="AP18">
-        <v>7.4</v>
+        <v>1.76</v>
       </c>
       <c r="AQ18">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR18">
-        <v>12.5</v>
+        <v>1.64</v>
       </c>
       <c r="AS18">
-        <v>9</v>
+        <v>1.61</v>
       </c>
       <c r="AT18">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="AU18">
-        <v>6.4</v>
+        <v>1.81</v>
       </c>
       <c r="AV18">
-        <v>11</v>
+        <v>1.64</v>
       </c>
       <c r="AW18">
-        <v>8.800000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="AX18">
-        <v>20</v>
+        <v>2.26</v>
       </c>
       <c r="AY18">
-        <v>14</v>
+        <v>1.64</v>
       </c>
       <c r="AZ18">
-        <v>20</v>
+        <v>1.64</v>
       </c>
       <c r="BA18">
-        <v>9.800000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="BB18">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="BC18">
-        <v>9.800000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="BD18">
-        <v>10.5</v>
+        <v>1.59</v>
       </c>
       <c r="BE18">
-        <v>11</v>
+        <v>1.63</v>
       </c>
       <c r="BF18">
-        <v>10.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG18">
-        <v>32</v>
+        <v>1.58</v>
       </c>
       <c r="BH18">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5091,7 +5100,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5109,7 +5118,7 @@
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
         <v>1000</v>
@@ -5130,120 +5139,120 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>3.45</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>3.65</v>
       </c>
       <c r="H19">
-        <v>5.3</v>
+        <v>2.48</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="J19">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L19">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="N19">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="O19">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="P19">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="R19">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="T19">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="U19">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V19">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="X19">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB19">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF19">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG19">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ19">
         <v>1000</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL19">
         <v>1000</v>
@@ -5252,77 +5261,77 @@
         <v>1000</v>
       </c>
       <c r="AN19">
+        <v>110</v>
+      </c>
+      <c r="AO19">
         <v>44</v>
       </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
       <c r="AP19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="AR19">
-        <v>1.62</v>
+        <v>12.5</v>
       </c>
       <c r="AS19">
-        <v>1.62</v>
+        <v>22</v>
       </c>
       <c r="AT19">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="AU19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV19">
-        <v>1.62</v>
+        <v>11.5</v>
       </c>
       <c r="AW19">
-        <v>1.62</v>
+        <v>23</v>
       </c>
       <c r="AX19">
+        <v>15</v>
+      </c>
+      <c r="AY19">
+        <v>14.5</v>
+      </c>
+      <c r="AZ19">
+        <v>21</v>
+      </c>
+      <c r="BA19">
+        <v>34</v>
+      </c>
+      <c r="BB19">
+        <v>32</v>
+      </c>
+      <c r="BC19">
+        <v>28</v>
+      </c>
+      <c r="BD19">
+        <v>38</v>
+      </c>
+      <c r="BE19">
+        <v>48</v>
+      </c>
+      <c r="BF19">
+        <v>34</v>
+      </c>
+      <c r="BG19">
+        <v>32</v>
+      </c>
+      <c r="BH19">
+        <v>3.05</v>
+      </c>
+      <c r="BI19">
+        <v>2.28</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
         <v>6.8</v>
       </c>
-      <c r="AY19">
-        <v>7.6</v>
-      </c>
-      <c r="AZ19">
-        <v>1.62</v>
-      </c>
-      <c r="BA19">
-        <v>1.62</v>
-      </c>
-      <c r="BB19">
-        <v>1.73</v>
-      </c>
-      <c r="BC19">
-        <v>1.62</v>
-      </c>
-      <c r="BD19">
-        <v>1.62</v>
-      </c>
-      <c r="BE19">
-        <v>1.62</v>
-      </c>
-      <c r="BF19">
-        <v>1.66</v>
-      </c>
-      <c r="BG19">
-        <v>1.62</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.27</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
       <c r="BL19">
         <v>1000</v>
       </c>
@@ -5333,7 +5342,7 @@
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.47</v>
+        <v>5.1</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5351,7 +5360,7 @@
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV19">
         <v>1000</v>
@@ -5372,7 +5381,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5380,100 +5389,100 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F20">
-        <v>3.7</v>
+        <v>1.72</v>
       </c>
       <c r="G20">
-        <v>4.9</v>
+        <v>1.88</v>
       </c>
       <c r="H20">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="I20">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K20">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O20">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="P20">
+        <v>1.61</v>
+      </c>
+      <c r="Q20">
+        <v>2.26</v>
+      </c>
+      <c r="R20">
+        <v>1.21</v>
+      </c>
+      <c r="S20">
+        <v>4.2</v>
+      </c>
+      <c r="T20">
+        <v>2.1</v>
+      </c>
+      <c r="U20">
         <v>1.65</v>
       </c>
-      <c r="Q20">
+      <c r="V20">
+        <v>1.17</v>
+      </c>
+      <c r="W20">
         <v>2.12</v>
       </c>
-      <c r="R20">
-        <v>1.25</v>
-      </c>
-      <c r="S20">
-        <v>3.6</v>
-      </c>
-      <c r="T20">
-        <v>1.9</v>
-      </c>
-      <c r="U20">
-        <v>1.81</v>
-      </c>
-      <c r="V20">
-        <v>1.82</v>
-      </c>
-      <c r="W20">
-        <v>1.26</v>
-      </c>
       <c r="X20">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
         <v>970</v>
-      </c>
-      <c r="Z20">
-        <v>24</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
-        <v>34</v>
       </c>
       <c r="AC20">
         <v>970</v>
       </c>
       <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
         <v>970</v>
       </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>1000</v>
-      </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH20">
         <v>1000</v>
@@ -5494,127 +5503,369 @@
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO20">
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="AQ20">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AR20">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AS20">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AT20">
+        <v>5.2</v>
+      </c>
+      <c r="AU20">
+        <v>6.2</v>
+      </c>
+      <c r="AV20">
+        <v>1.62</v>
+      </c>
+      <c r="AW20">
+        <v>1.62</v>
+      </c>
+      <c r="AX20">
         <v>7</v>
       </c>
-      <c r="AU20">
-        <v>1.3</v>
-      </c>
-      <c r="AV20">
-        <v>7.4</v>
-      </c>
-      <c r="AW20">
-        <v>1.49</v>
-      </c>
-      <c r="AX20">
-        <v>1.49</v>
-      </c>
       <c r="AY20">
-        <v>1.49</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BA20">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BB20">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="BC20">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BD20">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BE20">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BF20">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="BG20">
+        <v>1.62</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.27</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.47</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21">
+        <v>3.7</v>
+      </c>
+      <c r="G21">
+        <v>4.9</v>
+      </c>
+      <c r="H21">
+        <v>1.98</v>
+      </c>
+      <c r="I21">
+        <v>2.22</v>
+      </c>
+      <c r="J21">
+        <v>3.3</v>
+      </c>
+      <c r="K21">
+        <v>3.65</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.05</v>
+      </c>
+      <c r="N21">
+        <v>3.2</v>
+      </c>
+      <c r="O21">
+        <v>1.39</v>
+      </c>
+      <c r="P21">
+        <v>1.65</v>
+      </c>
+      <c r="Q21">
+        <v>2.12</v>
+      </c>
+      <c r="R21">
+        <v>1.25</v>
+      </c>
+      <c r="S21">
+        <v>3.6</v>
+      </c>
+      <c r="T21">
+        <v>1.9</v>
+      </c>
+      <c r="U21">
+        <v>1.81</v>
+      </c>
+      <c r="V21">
+        <v>1.82</v>
+      </c>
+      <c r="W21">
+        <v>1.26</v>
+      </c>
+      <c r="X21">
+        <v>160</v>
+      </c>
+      <c r="Y21">
+        <v>120</v>
+      </c>
+      <c r="Z21">
+        <v>190</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>970</v>
+      </c>
+      <c r="AD21">
+        <v>960</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ21">
+        <v>6.2</v>
+      </c>
+      <c r="AR21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS21">
+        <v>2.64</v>
+      </c>
+      <c r="AT21">
+        <v>8.6</v>
+      </c>
+      <c r="AU21">
+        <v>5.8</v>
+      </c>
+      <c r="AV21">
+        <v>7.6</v>
+      </c>
+      <c r="AW21">
+        <v>2.64</v>
+      </c>
+      <c r="AX21">
+        <v>2.64</v>
+      </c>
+      <c r="AY21">
+        <v>1.52</v>
+      </c>
+      <c r="AZ21">
+        <v>2.64</v>
+      </c>
+      <c r="BA21">
+        <v>2.68</v>
+      </c>
+      <c r="BB21">
+        <v>2.72</v>
+      </c>
+      <c r="BC21">
+        <v>2.68</v>
+      </c>
+      <c r="BD21">
+        <v>2.72</v>
+      </c>
+      <c r="BE21">
+        <v>1.59</v>
+      </c>
+      <c r="BF21">
+        <v>1.52</v>
+      </c>
+      <c r="BG21">
         <v>11</v>
       </c>
-      <c r="BH20">
+      <c r="BH21">
         <v>3.75</v>
       </c>
-      <c r="BI20">
+      <c r="BI21">
         <v>2.48</v>
       </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
         <v>1.37</v>
       </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
         <v>1.37</v>
       </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
         <v>1.37</v>
       </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
         <v>1.37</v>
       </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
         <v>1.37</v>
       </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
         <v>1.37</v>
       </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
         <v>1.37</v>
       </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
         <v>1.37</v>
       </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
         <v>1.37</v>
       </c>
-      <c r="CB20" t="s">
-        <v>142</v>
+      <c r="CB21" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Brazilian Serie B</t>
   </si>
   <si>
@@ -364,15 +367,15 @@
     <t>Jonkopings Sodra</t>
   </si>
   <si>
+    <t>FC Arlanda</t>
+  </si>
+  <si>
     <t>FC Spaeri</t>
   </si>
   <si>
     <t>HB Koge</t>
   </si>
   <si>
-    <t>FC Arlanda</t>
-  </si>
-  <si>
     <t>Aldosivi</t>
   </si>
   <si>
@@ -385,6 +388,9 @@
     <t>Barracas Central</t>
   </si>
   <si>
+    <t>Real Soacha Cundinamarca FC</t>
+  </si>
+  <si>
     <t>Criciuma</t>
   </si>
   <si>
@@ -424,15 +430,15 @@
     <t>Skovde Aik</t>
   </si>
   <si>
+    <t>Hammarby TFF</t>
+  </si>
+  <si>
     <t>Dila Gori</t>
   </si>
   <si>
     <t>Hobro</t>
   </si>
   <si>
-    <t>Hammarby TFF</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
@@ -445,13 +451,16 @@
     <t>Independiente Rivadavia</t>
   </si>
   <si>
+    <t>Quindio</t>
+  </si>
+  <si>
     <t>Operario PR</t>
   </si>
   <si>
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 07:32:55</t>
+    <t>2026-09-20 09:53:02</t>
   </si>
 </sst>
 </file>
@@ -783,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1033,16 +1042,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F2">
         <v>1.29</v>
@@ -1090,7 +1099,7 @@
         <v>1.78</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.1</v>
@@ -1105,7 +1114,7 @@
         <v>50</v>
       </c>
       <c r="Z2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA2">
         <v>470</v>
@@ -1132,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>11.5</v>
@@ -1144,7 +1153,7 @@
         <v>28</v>
       </c>
       <c r="AM2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN2">
         <v>3.55</v>
@@ -1159,10 +1168,10 @@
         <v>44</v>
       </c>
       <c r="AR2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1186,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="BA2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB2">
         <v>10.5</v>
@@ -1267,7 +1276,7 @@
         <v>1.27</v>
       </c>
       <c r="CB2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1275,22 +1284,22 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H3">
         <v>4.4</v>
@@ -1299,52 +1308,52 @@
         <v>4.5</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
         <v>1.28</v>
       </c>
       <c r="W3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
         <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
         <v>34</v>
@@ -1371,7 +1380,7 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
         <v>60</v>
@@ -1383,7 +1392,7 @@
         <v>21</v>
       </c>
       <c r="AL3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM3">
         <v>110</v>
@@ -1407,16 +1416,16 @@
         <v>11</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
         <v>8</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1428,22 +1437,22 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BB3">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3">
         <v>11</v>
       </c>
       <c r="BF3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG3">
         <v>40</v>
@@ -1458,58 +1467,58 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="CB3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1517,28 +1526,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1553,7 +1562,7 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O4">
         <v>1.66</v>
@@ -1562,7 +1571,7 @@
         <v>1.47</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R4">
         <v>1.16</v>
@@ -1577,16 +1586,16 @@
         <v>1.68</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
         <v>27</v>
@@ -1601,7 +1610,7 @@
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1613,16 +1622,16 @@
         <v>13</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI4">
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1631,7 +1640,7 @@
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1640,10 +1649,10 @@
         <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR4">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS4">
         <v>36</v>
@@ -1667,10 +1676,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB4">
         <v>21</v>
@@ -1679,7 +1688,7 @@
         <v>22</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BE4">
         <v>55</v>
@@ -1691,67 +1700,67 @@
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1759,16 +1768,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F5">
         <v>4.6</v>
@@ -1786,7 +1795,7 @@
         <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.42</v>
@@ -1801,25 +1810,25 @@
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
         <v>2.04</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T5">
         <v>1.89</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
         <v>1.25</v>
@@ -1852,7 +1861,7 @@
         <v>44</v>
       </c>
       <c r="AG5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AH5">
         <v>24</v>
@@ -1903,7 +1912,7 @@
         <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY5">
         <v>16</v>
@@ -1912,88 +1921,88 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG5">
         <v>12.5</v>
       </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2001,28 +2010,28 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H6">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="I6">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="J6">
         <v>4.1</v>
@@ -2037,31 +2046,31 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Q6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="V6">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -2130,7 +2139,7 @@
         <v>1.22</v>
       </c>
       <c r="AS6">
-        <v>1.24</v>
+        <v>6.2</v>
       </c>
       <c r="AT6">
         <v>2.5</v>
@@ -2235,7 +2244,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2243,28 +2252,28 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
         <v>2.78</v>
       </c>
       <c r="H7">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J7">
         <v>3.6</v>
@@ -2294,16 +2303,16 @@
         <v>1.44</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T7">
         <v>1.68</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
         <v>1.56</v>
@@ -2318,7 +2327,7 @@
         <v>19.5</v>
       </c>
       <c r="AA7">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB7">
         <v>13</v>
@@ -2333,7 +2342,7 @@
         <v>28</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
@@ -2342,16 +2351,16 @@
         <v>16</v>
       </c>
       <c r="AI7">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AK7">
         <v>32</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM7">
         <v>90</v>
@@ -2372,7 +2381,7 @@
         <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2384,7 +2393,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AX7">
         <v>17</v>
@@ -2396,22 +2405,22 @@
         <v>14</v>
       </c>
       <c r="BA7">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BB7">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC7">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="BD7">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE7">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BF7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BG7">
         <v>18</v>
@@ -2426,7 +2435,7 @@
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2456,7 +2465,7 @@
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2477,7 +2486,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2485,58 +2494,58 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G8">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I8">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
         <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q8">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T8">
         <v>1.75</v>
@@ -2548,7 +2557,7 @@
         <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X8">
         <v>970</v>
@@ -2566,7 +2575,7 @@
         <v>970</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD8">
         <v>970</v>
@@ -2605,58 +2614,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AQ8">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AR8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AS8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT8">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AU8">
         <v>1.38</v>
       </c>
       <c r="AV8">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AW8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AX8">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AY8">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AZ8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BA8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BB8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BC8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BD8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BE8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BF8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BG8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2719,7 +2728,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2727,34 +2736,34 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G9">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="I9">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="K9">
-        <v>880</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2763,7 +2772,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O9">
         <v>1.01</v>
@@ -2772,25 +2781,25 @@
         <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2847,52 +2856,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2961,7 +2970,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2969,25 +2978,25 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F10">
         <v>1.6</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="H10">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I10">
         <v>3.15</v>
@@ -3032,7 +3041,7 @@
         <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3203,7 +3212,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3211,31 +3220,31 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G11">
         <v>190</v>
       </c>
       <c r="H11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I11">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="J11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K11">
         <v>900</v>
@@ -3271,10 +3280,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3445,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3453,31 +3462,31 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F12">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G12">
         <v>110</v>
       </c>
       <c r="H12">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I12">
         <v>110</v>
       </c>
       <c r="J12">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="K12">
         <v>890</v>
@@ -3513,10 +3522,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3687,42 +3696,42 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3731,22 +3740,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3755,10 +3764,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3929,78 +3938,78 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F14">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="G14">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="H14">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="I14">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>4.2</v>
+        <v>1.26</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="P14">
-        <v>2.16</v>
+        <v>1.26</v>
       </c>
       <c r="Q14">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="R14">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T14">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4018,10 +4027,10 @@
         <v>1000</v>
       </c>
       <c r="AC14">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
         <v>1000</v>
@@ -4030,7 +4039,7 @@
         <v>1000</v>
       </c>
       <c r="AG14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
         <v>1000</v>
@@ -4057,52 +4066,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4171,186 +4180,186 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="G15">
-        <v>110</v>
+        <v>2.62</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="I15">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="J15">
-        <v>1.15</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
-        <v>900</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="R15">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
+        <v>1.47</v>
+      </c>
+      <c r="W15">
+        <v>1.62</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>970</v>
+      </c>
+      <c r="AD15">
+        <v>36</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>23</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.17</v>
+      </c>
+      <c r="AQ15">
+        <v>1.17</v>
+      </c>
+      <c r="AR15">
+        <v>1.17</v>
+      </c>
+      <c r="AS15">
+        <v>1.17</v>
+      </c>
+      <c r="AT15">
+        <v>1.17</v>
+      </c>
+      <c r="AU15">
         <v>1.07</v>
       </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>1.01</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>1.01</v>
-      </c>
-      <c r="AT15">
-        <v>1.01</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4413,7 +4422,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4421,178 +4430,178 @@
         <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G16">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H16">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I16">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J16">
         <v>3</v>
       </c>
       <c r="K16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16">
         <v>1.59</v>
       </c>
       <c r="M16">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N16">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="O16">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P16">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q16">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R16">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
         <v>5.7</v>
       </c>
       <c r="T16">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U16">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W16">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X16">
+        <v>8</v>
+      </c>
+      <c r="Y16">
+        <v>7.6</v>
+      </c>
+      <c r="Z16">
+        <v>15.5</v>
+      </c>
+      <c r="AA16">
+        <v>55</v>
+      </c>
+      <c r="AB16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC16">
+        <v>7.2</v>
+      </c>
+      <c r="AD16">
+        <v>13.5</v>
+      </c>
+      <c r="AE16">
+        <v>50</v>
+      </c>
+      <c r="AF16">
+        <v>21</v>
+      </c>
+      <c r="AG16">
+        <v>19.5</v>
+      </c>
+      <c r="AH16">
+        <v>25</v>
+      </c>
+      <c r="AI16">
+        <v>90</v>
+      </c>
+      <c r="AJ16">
+        <v>90</v>
+      </c>
+      <c r="AK16">
+        <v>70</v>
+      </c>
+      <c r="AL16">
+        <v>110</v>
+      </c>
+      <c r="AM16">
+        <v>260</v>
+      </c>
+      <c r="AN16">
+        <v>100</v>
+      </c>
+      <c r="AO16">
+        <v>60</v>
+      </c>
+      <c r="AP16">
+        <v>7</v>
+      </c>
+      <c r="AQ16">
+        <v>6.8</v>
+      </c>
+      <c r="AR16">
+        <v>13</v>
+      </c>
+      <c r="AS16">
+        <v>36</v>
+      </c>
+      <c r="AT16">
+        <v>8</v>
+      </c>
+      <c r="AU16">
+        <v>6.4</v>
+      </c>
+      <c r="AV16">
         <v>11.5</v>
       </c>
-      <c r="Y16">
-        <v>10.5</v>
-      </c>
-      <c r="Z16">
-        <v>40</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
+      <c r="AW16">
+        <v>34</v>
+      </c>
+      <c r="AX16">
+        <v>18.5</v>
+      </c>
+      <c r="AY16">
         <v>14</v>
       </c>
-      <c r="AC16">
-        <v>10</v>
-      </c>
-      <c r="AD16">
-        <v>36</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>100</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>5.9</v>
-      </c>
-      <c r="AQ16">
-        <v>6</v>
-      </c>
-      <c r="AR16">
+      <c r="AZ16">
+        <v>7</v>
+      </c>
+      <c r="BA16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC16">
+        <v>8.6</v>
+      </c>
+      <c r="BD16">
+        <v>9</v>
+      </c>
+      <c r="BE16">
         <v>9.4</v>
       </c>
-      <c r="AS16">
-        <v>1.72</v>
-      </c>
-      <c r="AT16">
-        <v>6.4</v>
-      </c>
-      <c r="AU16">
-        <v>5.4</v>
-      </c>
-      <c r="AV16">
+      <c r="BF16">
         <v>9</v>
       </c>
-      <c r="AW16">
-        <v>1.72</v>
-      </c>
-      <c r="AX16">
-        <v>12</v>
-      </c>
-      <c r="AY16">
-        <v>10</v>
-      </c>
-      <c r="AZ16">
-        <v>1.72</v>
-      </c>
-      <c r="BA16">
-        <v>1.72</v>
-      </c>
-      <c r="BB16">
-        <v>1.72</v>
-      </c>
-      <c r="BC16">
-        <v>1.72</v>
-      </c>
-      <c r="BD16">
-        <v>1.72</v>
-      </c>
-      <c r="BE16">
-        <v>1.72</v>
-      </c>
-      <c r="BF16">
-        <v>1.72</v>
-      </c>
       <c r="BG16">
-        <v>1.72</v>
+        <v>27</v>
       </c>
       <c r="BH16">
         <v>2.96</v>
@@ -4655,7 +4664,7 @@
         <v>2.32</v>
       </c>
       <c r="CB16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4663,28 +4672,28 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F17">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G17">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H17">
         <v>4.8</v>
       </c>
       <c r="I17">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J17">
         <v>3.6</v>
@@ -4699,7 +4708,7 @@
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
         <v>1.37</v>
@@ -4711,7 +4720,7 @@
         <v>2.06</v>
       </c>
       <c r="R17">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S17">
         <v>3.8</v>
@@ -4723,10 +4732,10 @@
         <v>1.96</v>
       </c>
       <c r="V17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W17">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X17">
         <v>15</v>
@@ -4840,7 +4849,7 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BJ17">
         <v>14.5</v>
@@ -4858,7 +4867,7 @@
         <v>5.9</v>
       </c>
       <c r="BO17">
-        <v>3.75</v>
+        <v>1.42</v>
       </c>
       <c r="BP17">
         <v>18.5</v>
@@ -4870,7 +4879,7 @@
         <v>40</v>
       </c>
       <c r="BS17">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BT17">
         <v>11</v>
@@ -4882,13 +4891,13 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BZ17">
         <v>38</v>
@@ -4897,7 +4906,7 @@
         <v>1.78</v>
       </c>
       <c r="CB17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4905,34 +4914,34 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F18">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G18">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H18">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="I18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J18">
         <v>3.1</v>
       </c>
       <c r="K18">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4941,34 +4950,34 @@
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
         <v>1.42</v>
       </c>
       <c r="P18">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="Q18">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R18">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S18">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T18">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U18">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V18">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W18">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X18">
         <v>970</v>
@@ -5028,55 +5037,55 @@
         <v>1.76</v>
       </c>
       <c r="AQ18">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="AR18">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AS18">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AT18">
+        <v>4.4</v>
+      </c>
+      <c r="AU18">
+        <v>2.8</v>
+      </c>
+      <c r="AV18">
+        <v>1.79</v>
+      </c>
+      <c r="AW18">
+        <v>1.72</v>
+      </c>
+      <c r="AX18">
+        <v>1.79</v>
+      </c>
+      <c r="AY18">
+        <v>1.79</v>
+      </c>
+      <c r="AZ18">
+        <v>1.79</v>
+      </c>
+      <c r="BA18">
         <v>1.74</v>
       </c>
-      <c r="AU18">
-        <v>1.81</v>
-      </c>
-      <c r="AV18">
-        <v>1.64</v>
-      </c>
-      <c r="AW18">
-        <v>1.58</v>
-      </c>
-      <c r="AX18">
-        <v>2.26</v>
-      </c>
-      <c r="AY18">
-        <v>1.64</v>
-      </c>
-      <c r="AZ18">
-        <v>1.64</v>
-      </c>
-      <c r="BA18">
-        <v>1.59</v>
-      </c>
       <c r="BB18">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="BC18">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BD18">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="BE18">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="BF18">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BG18">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5139,7 +5148,7 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5147,16 +5156,16 @@
         <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F19">
         <v>3.45</v>
@@ -5183,31 +5192,31 @@
         <v>1.14</v>
       </c>
       <c r="N19">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P19">
         <v>1.52</v>
       </c>
       <c r="Q19">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R19">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T19">
         <v>2.22</v>
       </c>
       <c r="U19">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
         <v>1.38</v>
@@ -5222,13 +5231,13 @@
         <v>14.5</v>
       </c>
       <c r="AA19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB19">
         <v>9.4</v>
       </c>
       <c r="AC19">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD19">
         <v>13.5</v>
@@ -5240,7 +5249,7 @@
         <v>23</v>
       </c>
       <c r="AG19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH19">
         <v>25</v>
@@ -5261,22 +5270,22 @@
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR19">
         <v>12.5</v>
       </c>
       <c r="AS19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT19">
         <v>8.6</v>
@@ -5288,10 +5297,10 @@
         <v>11.5</v>
       </c>
       <c r="AW19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY19">
         <v>14.5</v>
@@ -5381,7 +5390,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5389,73 +5398,73 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
         <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F20">
-        <v>1.72</v>
+        <v>1.1</v>
       </c>
       <c r="G20">
-        <v>1.88</v>
+        <v>1000</v>
       </c>
       <c r="H20">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J20">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K20">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="L20">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.92</v>
+        <v>1.08</v>
       </c>
       <c r="O20">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
-        <v>1.61</v>
+        <v>1.08</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R20">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="S20">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="T20">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
         <v>1000</v>
@@ -5467,10 +5476,10 @@
         <v>1000</v>
       </c>
       <c r="AB20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
         <v>1000</v>
@@ -5479,10 +5488,10 @@
         <v>1000</v>
       </c>
       <c r="AF20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
         <v>1000</v>
@@ -5503,70 +5512,70 @@
         <v>1000</v>
       </c>
       <c r="AN20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
@@ -5584,7 +5593,7 @@
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
         <v>1000</v>
@@ -5623,7 +5632,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5631,100 +5640,100 @@
         <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F21">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="G21">
-        <v>4.9</v>
+        <v>1.86</v>
       </c>
       <c r="H21">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="I21">
-        <v>2.22</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K21">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M21">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O21">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="P21">
+        <v>1.61</v>
+      </c>
+      <c r="Q21">
+        <v>2.28</v>
+      </c>
+      <c r="R21">
+        <v>1.21</v>
+      </c>
+      <c r="S21">
+        <v>4.2</v>
+      </c>
+      <c r="T21">
+        <v>2.1</v>
+      </c>
+      <c r="U21">
         <v>1.65</v>
       </c>
-      <c r="Q21">
-        <v>2.12</v>
-      </c>
-      <c r="R21">
-        <v>1.25</v>
-      </c>
-      <c r="S21">
-        <v>3.6</v>
-      </c>
-      <c r="T21">
-        <v>1.9</v>
-      </c>
-      <c r="U21">
-        <v>1.81</v>
-      </c>
       <c r="V21">
-        <v>1.82</v>
+        <v>1.18</v>
       </c>
       <c r="W21">
-        <v>1.26</v>
+        <v>2.16</v>
       </c>
       <c r="X21">
-        <v>160</v>
+        <v>970</v>
       </c>
       <c r="Y21">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
         <v>1000</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC21">
         <v>970</v>
       </c>
       <c r="AD21">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
         <v>1000</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH21">
         <v>1000</v>
@@ -5751,121 +5760,363 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AQ21">
+        <v>1.66</v>
+      </c>
+      <c r="AR21">
+        <v>1.56</v>
+      </c>
+      <c r="AS21">
+        <v>1.56</v>
+      </c>
+      <c r="AT21">
+        <v>5.2</v>
+      </c>
+      <c r="AU21">
         <v>6.2</v>
       </c>
-      <c r="AR21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS21">
-        <v>2.64</v>
-      </c>
-      <c r="AT21">
-        <v>8.6</v>
-      </c>
-      <c r="AU21">
-        <v>5.8</v>
-      </c>
       <c r="AV21">
+        <v>1.56</v>
+      </c>
+      <c r="AW21">
+        <v>1.56</v>
+      </c>
+      <c r="AX21">
+        <v>1.5</v>
+      </c>
+      <c r="AY21">
         <v>7.6</v>
       </c>
-      <c r="AW21">
-        <v>2.64</v>
-      </c>
-      <c r="AX21">
-        <v>2.64</v>
-      </c>
-      <c r="AY21">
+      <c r="AZ21">
+        <v>1.56</v>
+      </c>
+      <c r="BA21">
+        <v>1.56</v>
+      </c>
+      <c r="BB21">
+        <v>1.66</v>
+      </c>
+      <c r="BC21">
+        <v>1.56</v>
+      </c>
+      <c r="BD21">
+        <v>1.56</v>
+      </c>
+      <c r="BE21">
+        <v>1.56</v>
+      </c>
+      <c r="BF21">
+        <v>1.66</v>
+      </c>
+      <c r="BG21">
+        <v>1.56</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.27</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.47</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>2.1</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22">
+        <v>3.7</v>
+      </c>
+      <c r="G22">
+        <v>4.9</v>
+      </c>
+      <c r="H22">
+        <v>1.97</v>
+      </c>
+      <c r="I22">
+        <v>2.2</v>
+      </c>
+      <c r="J22">
+        <v>3.3</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.05</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22">
+        <v>1.39</v>
+      </c>
+      <c r="P22">
+        <v>1.65</v>
+      </c>
+      <c r="Q22">
+        <v>2.12</v>
+      </c>
+      <c r="R22">
+        <v>1.25</v>
+      </c>
+      <c r="S22">
+        <v>3.6</v>
+      </c>
+      <c r="T22">
+        <v>1.9</v>
+      </c>
+      <c r="U22">
+        <v>1.81</v>
+      </c>
+      <c r="V22">
+        <v>1.83</v>
+      </c>
+      <c r="W22">
+        <v>1.26</v>
+      </c>
+      <c r="X22">
+        <v>120</v>
+      </c>
+      <c r="Y22">
+        <v>85</v>
+      </c>
+      <c r="Z22">
+        <v>130</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>150</v>
+      </c>
+      <c r="AC22">
+        <v>890</v>
+      </c>
+      <c r="AD22">
+        <v>110</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.43</v>
+      </c>
+      <c r="AQ22">
+        <v>1.37</v>
+      </c>
+      <c r="AR22">
+        <v>1.43</v>
+      </c>
+      <c r="AS22">
+        <v>3.3</v>
+      </c>
+      <c r="AT22">
+        <v>10</v>
+      </c>
+      <c r="AU22">
+        <v>1.33</v>
+      </c>
+      <c r="AV22">
+        <v>7.4</v>
+      </c>
+      <c r="AW22">
+        <v>3.3</v>
+      </c>
+      <c r="AX22">
+        <v>3.3</v>
+      </c>
+      <c r="AY22">
         <v>1.52</v>
       </c>
-      <c r="AZ21">
-        <v>2.64</v>
-      </c>
-      <c r="BA21">
-        <v>2.68</v>
-      </c>
-      <c r="BB21">
+      <c r="AZ22">
+        <v>3.3</v>
+      </c>
+      <c r="BA22">
+        <v>3.4</v>
+      </c>
+      <c r="BB22">
+        <v>3.5</v>
+      </c>
+      <c r="BC22">
+        <v>3.4</v>
+      </c>
+      <c r="BD22">
+        <v>3.5</v>
+      </c>
+      <c r="BE22">
         <v>2.72</v>
       </c>
-      <c r="BC21">
-        <v>2.68</v>
-      </c>
-      <c r="BD21">
-        <v>2.72</v>
-      </c>
-      <c r="BE21">
-        <v>1.59</v>
-      </c>
-      <c r="BF21">
+      <c r="BF22">
         <v>1.52</v>
       </c>
-      <c r="BG21">
+      <c r="BG22">
         <v>11</v>
       </c>
-      <c r="BH21">
+      <c r="BH22">
         <v>3.75</v>
       </c>
-      <c r="BI21">
+      <c r="BI22">
         <v>2.48</v>
       </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
         <v>1.37</v>
       </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
         <v>1.37</v>
       </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
         <v>1.37</v>
       </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
         <v>1.37</v>
       </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
         <v>1.37</v>
       </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
         <v>1.37</v>
       </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
         <v>1.37</v>
       </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
         <v>1.37</v>
       </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
-      <c r="CA21">
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
         <v>1.37</v>
       </c>
-      <c r="CB21" t="s">
-        <v>145</v>
+      <c r="CB22" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="167">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Honduras Liga Nacional</t>
   </si>
   <si>
+    <t>Serbian First League</t>
+  </si>
+  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
@@ -277,12 +280,12 @@
     <t>Swedish Division 1</t>
   </si>
   <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
     <t>Georgian Umaglesi Liga</t>
   </si>
   <si>
-    <t>Danish 1st Division</t>
-  </si>
-  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
@@ -313,9 +316,15 @@
     <t>02:05:00</t>
   </si>
   <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -328,6 +337,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -352,12 +364,27 @@
     <t>Queretaro</t>
   </si>
   <si>
+    <t>FK Vrsac</t>
+  </si>
+  <si>
+    <t>FK Backa Topola</t>
+  </si>
+  <si>
     <t>Otelul Galati</t>
   </si>
   <si>
     <t>FC Petrzalka</t>
   </si>
   <si>
+    <t>FK Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Metalac Gornji Milanovac</t>
+  </si>
+  <si>
+    <t>FK Napredak</t>
+  </si>
+  <si>
     <t>Angelholms</t>
   </si>
   <si>
@@ -367,24 +394,30 @@
     <t>Jonkopings Sodra</t>
   </si>
   <si>
+    <t>HB Koge</t>
+  </si>
+  <si>
+    <t>FC Spaeri</t>
+  </si>
+  <si>
     <t>FC Arlanda</t>
   </si>
   <si>
-    <t>FC Spaeri</t>
-  </si>
-  <si>
-    <t>HB Koge</t>
-  </si>
-  <si>
     <t>Aldosivi</t>
   </si>
   <si>
     <t>ACS Petrolul 52</t>
   </si>
   <si>
+    <t>FK Spartak</t>
+  </si>
+  <si>
     <t>Manta FC</t>
   </si>
   <si>
+    <t>Bogota</t>
+  </si>
+  <si>
     <t>Barracas Central</t>
   </si>
   <si>
@@ -415,12 +448,27 @@
     <t>Leon</t>
   </si>
   <si>
+    <t>FK Bor 1919</t>
+  </si>
+  <si>
+    <t>FK Dubocica</t>
+  </si>
+  <si>
     <t>FC Hunedoara</t>
   </si>
   <si>
     <t>Pohronie</t>
   </si>
   <si>
+    <t>FK Loznica</t>
+  </si>
+  <si>
+    <t>FK Graficar</t>
+  </si>
+  <si>
+    <t>Fk Smederevo</t>
+  </si>
+  <si>
     <t>Eskilsminne</t>
   </si>
   <si>
@@ -430,24 +478,30 @@
     <t>Skovde Aik</t>
   </si>
   <si>
+    <t>Hobro</t>
+  </si>
+  <si>
+    <t>Dila Gori</t>
+  </si>
+  <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
-    <t>Dila Gori</t>
-  </si>
-  <si>
-    <t>Hobro</t>
-  </si>
-  <si>
     <t>Atl Tucuman</t>
   </si>
   <si>
     <t>Csikszereda</t>
   </si>
   <si>
+    <t>Vozdovac</t>
+  </si>
+  <si>
     <t>Orense Sporting Club</t>
   </si>
   <si>
+    <t>Barranquilla</t>
+  </si>
+  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
@@ -460,7 +514,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 09:53:02</t>
+    <t>2026-09-20 12:11:10</t>
   </si>
 </sst>
 </file>
@@ -792,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1042,16 +1096,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F2">
         <v>1.29</v>
@@ -1078,7 +1132,7 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2">
         <v>1.13</v>
@@ -1123,13 +1177,13 @@
         <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AD2">
         <v>38</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AF2">
         <v>11</v>
@@ -1150,13 +1204,13 @@
         <v>12.5</v>
       </c>
       <c r="AL2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AO2">
         <v>100</v>
@@ -1165,13 +1219,13 @@
         <v>36</v>
       </c>
       <c r="AQ2">
-        <v>44</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT2">
         <v>13</v>
@@ -1183,10 +1237,10 @@
         <v>34</v>
       </c>
       <c r="AW2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1195,7 +1249,7 @@
         <v>22</v>
       </c>
       <c r="BA2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB2">
         <v>10.5</v>
@@ -1204,13 +1258,13 @@
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="BF2">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BG2">
         <v>75</v>
@@ -1276,7 +1330,7 @@
         <v>1.27</v>
       </c>
       <c r="CB2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1284,37 +1338,37 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F3">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="G3">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="H3">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1323,73 +1377,73 @@
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.41</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="X3">
         <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>21</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
         <v>36</v>
@@ -1398,61 +1452,61 @@
         <v>110</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW3">
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA3">
         <v>46</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
+        <v>15.5</v>
+      </c>
+      <c r="BE3">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE3">
-        <v>11</v>
-      </c>
       <c r="BF3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG3">
         <v>40</v>
@@ -1461,7 +1515,7 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1473,52 +1527,52 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="CB3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1526,49 +1580,49 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
         <v>3.95</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
         <v>1.69</v>
       </c>
       <c r="M4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N4">
         <v>2.46</v>
       </c>
       <c r="O4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
         <v>3.05</v>
@@ -1583,13 +1637,13 @@
         <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1598,7 +1652,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1610,7 +1664,7 @@
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
         <v>1000</v>
@@ -1628,19 +1682,19 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AK4">
+        <v>42</v>
+      </c>
+      <c r="AL4">
         <v>75</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
       </c>
       <c r="AM4">
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1649,7 +1703,7 @@
         <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4">
         <v>19.5</v>
@@ -1667,7 +1721,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
@@ -1682,13 +1736,13 @@
         <v>40</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD4">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE4">
         <v>55</v>
@@ -1700,67 +1754,67 @@
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI4">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1768,31 +1822,31 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F5">
         <v>4.6</v>
       </c>
       <c r="G5">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I5">
         <v>1.91</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
         <v>3.9</v>
@@ -1813,16 +1867,16 @@
         <v>1.9</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U5">
         <v>2</v>
@@ -1840,19 +1894,19 @@
         <v>8.6</v>
       </c>
       <c r="Z5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC5">
         <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE5">
         <v>25</v>
@@ -1876,7 +1930,7 @@
         <v>85</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM5">
         <v>140</v>
@@ -1903,16 +1957,16 @@
         <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW5">
         <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="AY5">
         <v>16</v>
@@ -1921,22 +1975,22 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BB5">
-        <v>5.5</v>
+        <v>70</v>
       </c>
       <c r="BC5">
-        <v>5.4</v>
+        <v>42</v>
       </c>
       <c r="BD5">
-        <v>5.4</v>
+        <v>46</v>
       </c>
       <c r="BE5">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
-        <v>5.4</v>
+        <v>46</v>
       </c>
       <c r="BG5">
         <v>12.5</v>
@@ -2002,7 +2056,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2010,76 +2064,76 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="G6">
-        <v>44</v>
+        <v>7.4</v>
       </c>
       <c r="H6">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="I6">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
+        <v>1.75</v>
+      </c>
+      <c r="R6">
         <v>1.3</v>
       </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
       <c r="S6">
-        <v>1.06</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.05</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
         <v>1.04</v>
       </c>
       <c r="V6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
         <v>1000</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
         <v>970</v>
@@ -2088,7 +2142,7 @@
         <v>900</v>
       </c>
       <c r="AB6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AC6">
         <v>1000</v>
@@ -2097,28 +2151,28 @@
         <v>970</v>
       </c>
       <c r="AE6">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AF6">
-        <v>350</v>
+        <v>210</v>
       </c>
       <c r="AG6">
+        <v>160</v>
+      </c>
+      <c r="AH6">
         <v>130</v>
       </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
       <c r="AI6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2130,52 +2184,52 @@
         <v>29</v>
       </c>
       <c r="AP6">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AQ6">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AR6">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AS6">
         <v>6.2</v>
       </c>
       <c r="AT6">
-        <v>2.5</v>
+        <v>1.14</v>
       </c>
       <c r="AU6">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AV6">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AW6">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AX6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AY6">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AZ6">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="BA6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BB6">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="BC6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BD6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BE6">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="BF6">
         <v>1.55</v>
@@ -2244,7 +2298,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2252,22 +2306,22 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F7">
         <v>2.68</v>
       </c>
       <c r="G7">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H7">
         <v>2.72</v>
@@ -2279,7 +2333,7 @@
         <v>3.6</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.37</v>
@@ -2294,16 +2348,16 @@
         <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T7">
         <v>1.68</v>
@@ -2381,7 +2435,7 @@
         <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2393,7 +2447,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AX7">
         <v>17</v>
@@ -2408,7 +2462,7 @@
         <v>18.5</v>
       </c>
       <c r="BB7">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BC7">
         <v>14</v>
@@ -2420,7 +2474,7 @@
         <v>13</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BG7">
         <v>18</v>
@@ -2486,7 +2540,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2494,76 +2548,76 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F8">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="G8">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L8">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>1.07</v>
       </c>
       <c r="O8">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.07</v>
       </c>
       <c r="Q8">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="S8">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
         <v>1000</v>
@@ -2572,13 +2626,13 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
         <v>1000</v>
@@ -2587,10 +2641,10 @@
         <v>1000</v>
       </c>
       <c r="AG8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
         <v>1000</v>
@@ -2614,58 +2668,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.47</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.52</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.63</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2728,42 +2782,42 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F9">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>1.56</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2772,34 +2826,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>1.07</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>1.06</v>
       </c>
       <c r="Q9">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="R9">
-        <v>1.47</v>
+        <v>1.06</v>
       </c>
       <c r="S9">
-        <v>2.54</v>
+        <v>1.15</v>
       </c>
       <c r="T9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2856,52 +2910,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2970,84 +3024,84 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F10">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="G10">
-        <v>55</v>
+        <v>2.56</v>
       </c>
       <c r="H10">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K10">
-        <v>870</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q10">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S10">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z10">
         <v>1000</v>
@@ -3056,25 +3110,25 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -3098,58 +3152,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3212,7 +3266,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3220,70 +3274,70 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F11">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="G11">
-        <v>190</v>
+        <v>1.56</v>
       </c>
       <c r="H11">
-        <v>1.11</v>
+        <v>5.8</v>
       </c>
       <c r="I11">
-        <v>980</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
+        <v>4.8</v>
+      </c>
+      <c r="K11">
+        <v>5.3</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>4.7</v>
+      </c>
+      <c r="O11">
+        <v>1.01</v>
+      </c>
+      <c r="P11">
+        <v>2.14</v>
+      </c>
+      <c r="Q11">
+        <v>1.61</v>
+      </c>
+      <c r="R11">
+        <v>1.44</v>
+      </c>
+      <c r="S11">
+        <v>2.54</v>
+      </c>
+      <c r="T11">
+        <v>1.03</v>
+      </c>
+      <c r="U11">
+        <v>1.07</v>
+      </c>
+      <c r="V11">
         <v>1.17</v>
       </c>
-      <c r="K11">
-        <v>900</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>3.6</v>
-      </c>
-      <c r="O11">
-        <v>1.02</v>
-      </c>
-      <c r="P11">
-        <v>1.25</v>
-      </c>
-      <c r="Q11">
-        <v>1.02</v>
-      </c>
-      <c r="R11">
-        <v>1.24</v>
-      </c>
-      <c r="S11">
-        <v>1.02</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.08</v>
-      </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>2.78</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3340,52 +3394,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3448,48 +3502,48 @@
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F12">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K12">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3501,19 +3555,19 @@
         <v>1.07</v>
       </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
         <v>1.07</v>
       </c>
       <c r="Q12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
         <v>1.07</v>
       </c>
       <c r="S12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3522,10 +3576,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3582,52 +3636,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3696,42 +3750,42 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F13">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
-        <v>6.6</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3740,22 +3794,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.15</v>
+        <v>1.07</v>
       </c>
       <c r="O13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>2.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3764,10 +3818,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3824,52 +3878,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -3938,24 +3992,24 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F14">
         <v>1.1</v>
@@ -3973,7 +4027,7 @@
         <v>1.1</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3982,22 +4036,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="O14">
         <v>1.01</v>
       </c>
       <c r="P14">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="Q14">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S14">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4066,52 +4120,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4180,186 +4234,186 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F15">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G15">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H15">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="I15">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J15">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
         <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
         <v>1.62</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC15">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD15">
+        <v>16</v>
+      </c>
+      <c r="AE15">
         <v>36</v>
       </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG15">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4422,670 +4476,670 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F16">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="G16">
-        <v>3.6</v>
+        <v>180</v>
       </c>
       <c r="H16">
-        <v>2.54</v>
+        <v>1.12</v>
       </c>
       <c r="I16">
-        <v>2.7</v>
+        <v>970</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>1.22</v>
       </c>
       <c r="K16">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="P16">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S16">
-        <v>5.7</v>
+        <v>1.02</v>
       </c>
       <c r="T16">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="W16">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F17">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="G17">
+        <v>1.76</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>9.4</v>
+      </c>
+      <c r="J17">
+        <v>3.9</v>
+      </c>
+      <c r="K17">
+        <v>7.2</v>
+      </c>
+      <c r="L17">
+        <v>1.31</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>3.2</v>
+      </c>
+      <c r="O17">
+        <v>1.02</v>
+      </c>
+      <c r="P17">
+        <v>1.92</v>
+      </c>
+      <c r="Q17">
         <v>1.9</v>
       </c>
-      <c r="H17">
-        <v>4.8</v>
-      </c>
-      <c r="I17">
-        <v>5.2</v>
-      </c>
-      <c r="J17">
-        <v>3.6</v>
-      </c>
-      <c r="K17">
-        <v>3.9</v>
-      </c>
-      <c r="L17">
-        <v>1.4</v>
-      </c>
-      <c r="M17">
-        <v>1.08</v>
-      </c>
-      <c r="N17">
-        <v>3.4</v>
-      </c>
-      <c r="O17">
-        <v>1.37</v>
-      </c>
-      <c r="P17">
-        <v>1.82</v>
-      </c>
-      <c r="Q17">
-        <v>2.06</v>
-      </c>
       <c r="R17">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S17">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="T17">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="W17">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="X17">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F18">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="G18">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="H18">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="I18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J18">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K18">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="P18">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="Q18">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="R18">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S18">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="T18">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="U18">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="Z18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
         <v>970</v>
       </c>
       <c r="AD18">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AH18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="AR18">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AS18">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="AT18">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="AU18">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="AV18">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="AW18">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="AX18">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AY18">
-        <v>1.79</v>
+        <v>1.14</v>
       </c>
       <c r="AZ18">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="BA18">
-        <v>1.74</v>
+        <v>1.2</v>
       </c>
       <c r="BB18">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="BC18">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="BD18">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="BE18">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="BF18">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="BG18">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5148,120 +5202,120 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F19">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="G19">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="H19">
-        <v>2.48</v>
+        <v>1.1</v>
       </c>
       <c r="I19">
-        <v>2.6</v>
+        <v>950</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="K19">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L19">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>1.27</v>
       </c>
       <c r="O19">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="Q19">
-        <v>2.78</v>
+        <v>1.31</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>5.8</v>
+        <v>2.78</v>
       </c>
       <c r="T19">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="W19">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
         <v>1000</v>
       </c>
       <c r="AK19">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
         <v>1000</v>
@@ -5270,76 +5324,76 @@
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5351,7 +5405,7 @@
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5369,7 +5423,7 @@
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
         <v>1000</v>
@@ -5390,42 +5444,42 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F20">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H20">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="I20">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J20">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5434,22 +5488,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.08</v>
+        <v>3.45</v>
       </c>
       <c r="O20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P20">
-        <v>1.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R20">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="S20">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5458,10 +5512,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5518,52 +5572,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5632,491 +5686,2185 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="G21">
-        <v>1.86</v>
+        <v>3.6</v>
       </c>
       <c r="H21">
-        <v>5.3</v>
+        <v>2.54</v>
       </c>
       <c r="I21">
-        <v>6.4</v>
+        <v>2.72</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K21">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L21">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M21">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="O21">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="P21">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Q21">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="R21">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U21">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="V21">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
-        <v>2.16</v>
+        <v>1.39</v>
       </c>
       <c r="X21">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB21">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF21">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AG21">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP21">
         <v>7</v>
       </c>
       <c r="AQ21">
-        <v>1.66</v>
+        <v>6.8</v>
       </c>
       <c r="AR21">
-        <v>1.56</v>
+        <v>13</v>
       </c>
       <c r="AS21">
-        <v>1.56</v>
+        <v>36</v>
       </c>
       <c r="AT21">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AU21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>1.56</v>
+        <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>1.56</v>
+        <v>34</v>
       </c>
       <c r="AX21">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY21">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AZ21">
-        <v>1.56</v>
+        <v>7.2</v>
       </c>
       <c r="BA21">
-        <v>1.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21">
-        <v>1.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC21">
-        <v>1.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD21">
-        <v>1.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE21">
-        <v>1.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF21">
-        <v>1.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG21">
-        <v>1.56</v>
+        <v>27</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI21">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="CB21" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F22">
-        <v>3.7</v>
+        <v>1.84</v>
       </c>
       <c r="G22">
+        <v>1.91</v>
+      </c>
+      <c r="H22">
+        <v>4.8</v>
+      </c>
+      <c r="I22">
+        <v>5.2</v>
+      </c>
+      <c r="J22">
+        <v>3.6</v>
+      </c>
+      <c r="K22">
+        <v>3.9</v>
+      </c>
+      <c r="L22">
+        <v>1.4</v>
+      </c>
+      <c r="M22">
+        <v>1.08</v>
+      </c>
+      <c r="N22">
+        <v>3.45</v>
+      </c>
+      <c r="O22">
+        <v>1.37</v>
+      </c>
+      <c r="P22">
+        <v>1.82</v>
+      </c>
+      <c r="Q22">
+        <v>2.06</v>
+      </c>
+      <c r="R22">
+        <v>1.32</v>
+      </c>
+      <c r="S22">
+        <v>3.85</v>
+      </c>
+      <c r="T22">
+        <v>1.93</v>
+      </c>
+      <c r="U22">
+        <v>1.96</v>
+      </c>
+      <c r="V22">
+        <v>1.24</v>
+      </c>
+      <c r="W22">
+        <v>2.08</v>
+      </c>
+      <c r="X22">
+        <v>15</v>
+      </c>
+      <c r="Y22">
+        <v>18</v>
+      </c>
+      <c r="Z22">
+        <v>38</v>
+      </c>
+      <c r="AA22">
+        <v>130</v>
+      </c>
+      <c r="AB22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC22">
+        <v>8.4</v>
+      </c>
+      <c r="AD22">
+        <v>21</v>
+      </c>
+      <c r="AE22">
+        <v>80</v>
+      </c>
+      <c r="AF22">
+        <v>11</v>
+      </c>
+      <c r="AG22">
+        <v>12</v>
+      </c>
+      <c r="AH22">
+        <v>24</v>
+      </c>
+      <c r="AI22">
+        <v>85</v>
+      </c>
+      <c r="AJ22">
+        <v>24</v>
+      </c>
+      <c r="AK22">
+        <v>25</v>
+      </c>
+      <c r="AL22">
+        <v>48</v>
+      </c>
+      <c r="AM22">
+        <v>150</v>
+      </c>
+      <c r="AN22">
+        <v>17</v>
+      </c>
+      <c r="AO22">
+        <v>95</v>
+      </c>
+      <c r="AP22">
+        <v>11.5</v>
+      </c>
+      <c r="AQ22">
+        <v>13</v>
+      </c>
+      <c r="AR22">
+        <v>6.8</v>
+      </c>
+      <c r="AS22">
+        <v>7.2</v>
+      </c>
+      <c r="AT22">
+        <v>7.2</v>
+      </c>
+      <c r="AU22">
+        <v>7.4</v>
+      </c>
+      <c r="AV22">
+        <v>16.5</v>
+      </c>
+      <c r="AW22">
+        <v>7</v>
+      </c>
+      <c r="AX22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22">
+        <v>6</v>
+      </c>
+      <c r="BA22">
+        <v>7</v>
+      </c>
+      <c r="BB22">
+        <v>17.5</v>
+      </c>
+      <c r="BC22">
+        <v>18.5</v>
+      </c>
+      <c r="BD22">
+        <v>6.6</v>
+      </c>
+      <c r="BE22">
+        <v>7.2</v>
+      </c>
+      <c r="BF22">
+        <v>12.5</v>
+      </c>
+      <c r="BG22">
+        <v>7</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.95</v>
+      </c>
+      <c r="BJ22">
+        <v>14.5</v>
+      </c>
+      <c r="BK22">
+        <v>3.35</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.86</v>
+      </c>
+      <c r="BN22">
+        <v>5.9</v>
+      </c>
+      <c r="BO22">
+        <v>1.42</v>
+      </c>
+      <c r="BP22">
+        <v>18.5</v>
+      </c>
+      <c r="BQ22">
+        <v>1.69</v>
+      </c>
+      <c r="BR22">
+        <v>40</v>
+      </c>
+      <c r="BS22">
+        <v>1.78</v>
+      </c>
+      <c r="BT22">
+        <v>11</v>
+      </c>
+      <c r="BU22">
+        <v>5.4</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.9</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.91</v>
+      </c>
+      <c r="BZ22">
+        <v>38</v>
+      </c>
+      <c r="CA22">
+        <v>1.78</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23">
+        <v>1.1</v>
+      </c>
+      <c r="G23">
+        <v>1000</v>
+      </c>
+      <c r="H23">
+        <v>1.1</v>
+      </c>
+      <c r="I23">
+        <v>1000</v>
+      </c>
+      <c r="J23">
+        <v>1.1</v>
+      </c>
+      <c r="K23">
+        <v>950</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>1.07</v>
+      </c>
+      <c r="O23">
+        <v>1.01</v>
+      </c>
+      <c r="P23">
+        <v>1.07</v>
+      </c>
+      <c r="Q23">
+        <v>1.01</v>
+      </c>
+      <c r="R23">
+        <v>1.07</v>
+      </c>
+      <c r="S23">
+        <v>1.01</v>
+      </c>
+      <c r="T23">
+        <v>1.01</v>
+      </c>
+      <c r="U23">
+        <v>1.01</v>
+      </c>
+      <c r="V23">
+        <v>1.01</v>
+      </c>
+      <c r="W23">
+        <v>1.01</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23">
+        <v>1.03</v>
+      </c>
+      <c r="AR23">
+        <v>1.03</v>
+      </c>
+      <c r="AS23">
+        <v>1.03</v>
+      </c>
+      <c r="AT23">
+        <v>1.03</v>
+      </c>
+      <c r="AU23">
+        <v>1.03</v>
+      </c>
+      <c r="AV23">
+        <v>1.03</v>
+      </c>
+      <c r="AW23">
+        <v>1.03</v>
+      </c>
+      <c r="AX23">
+        <v>1.03</v>
+      </c>
+      <c r="AY23">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23">
+        <v>1.03</v>
+      </c>
+      <c r="BA23">
+        <v>1.03</v>
+      </c>
+      <c r="BB23">
+        <v>1.03</v>
+      </c>
+      <c r="BC23">
+        <v>1.03</v>
+      </c>
+      <c r="BD23">
+        <v>1.03</v>
+      </c>
+      <c r="BE23">
+        <v>1.03</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24">
+        <v>2.66</v>
+      </c>
+      <c r="G24">
+        <v>2.84</v>
+      </c>
+      <c r="H24">
+        <v>2.9</v>
+      </c>
+      <c r="I24">
+        <v>3.1</v>
+      </c>
+      <c r="J24">
+        <v>3.15</v>
+      </c>
+      <c r="K24">
+        <v>3.3</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.09</v>
+      </c>
+      <c r="N24">
+        <v>3.1</v>
+      </c>
+      <c r="O24">
+        <v>1.42</v>
+      </c>
+      <c r="P24">
+        <v>1.63</v>
+      </c>
+      <c r="Q24">
+        <v>2.16</v>
+      </c>
+      <c r="R24">
+        <v>1.23</v>
+      </c>
+      <c r="S24">
+        <v>3.9</v>
+      </c>
+      <c r="T24">
+        <v>1.84</v>
+      </c>
+      <c r="U24">
+        <v>1.99</v>
+      </c>
+      <c r="V24">
+        <v>1.47</v>
+      </c>
+      <c r="W24">
+        <v>1.54</v>
+      </c>
+      <c r="X24">
+        <v>970</v>
+      </c>
+      <c r="Y24">
+        <v>970</v>
+      </c>
+      <c r="Z24">
+        <v>21</v>
+      </c>
+      <c r="AA24">
+        <v>90</v>
+      </c>
+      <c r="AB24">
+        <v>970</v>
+      </c>
+      <c r="AC24">
+        <v>970</v>
+      </c>
+      <c r="AD24">
+        <v>970</v>
+      </c>
+      <c r="AE24">
+        <v>42</v>
+      </c>
+      <c r="AF24">
+        <v>970</v>
+      </c>
+      <c r="AG24">
+        <v>970</v>
+      </c>
+      <c r="AH24">
+        <v>20</v>
+      </c>
+      <c r="AI24">
+        <v>60</v>
+      </c>
+      <c r="AJ24">
+        <v>46</v>
+      </c>
+      <c r="AK24">
+        <v>36</v>
+      </c>
+      <c r="AL24">
+        <v>55</v>
+      </c>
+      <c r="AM24">
+        <v>290</v>
+      </c>
+      <c r="AN24">
+        <v>36</v>
+      </c>
+      <c r="AO24">
+        <v>44</v>
+      </c>
+      <c r="AP24">
+        <v>1.79</v>
+      </c>
+      <c r="AQ24">
+        <v>1.8</v>
+      </c>
+      <c r="AR24">
+        <v>14</v>
+      </c>
+      <c r="AS24">
+        <v>2.44</v>
+      </c>
+      <c r="AT24">
+        <v>4.5</v>
+      </c>
+      <c r="AU24">
+        <v>5.8</v>
+      </c>
+      <c r="AV24">
+        <v>1.99</v>
+      </c>
+      <c r="AW24">
+        <v>4</v>
+      </c>
+      <c r="AX24">
+        <v>1.99</v>
+      </c>
+      <c r="AY24">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24">
+        <v>13.5</v>
+      </c>
+      <c r="BA24">
+        <v>2.14</v>
+      </c>
+      <c r="BB24">
+        <v>2.38</v>
+      </c>
+      <c r="BC24">
+        <v>6.8</v>
+      </c>
+      <c r="BD24">
+        <v>2.4</v>
+      </c>
+      <c r="BE24">
+        <v>1.98</v>
+      </c>
+      <c r="BF24">
+        <v>6.8</v>
+      </c>
+      <c r="BG24">
+        <v>3.6</v>
+      </c>
+      <c r="BH24">
+        <v>1000</v>
+      </c>
+      <c r="BI24">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>1.01</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>1000</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25">
+        <v>1.74</v>
+      </c>
+      <c r="G25">
+        <v>2.1</v>
+      </c>
+      <c r="H25">
+        <v>3.55</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>3.05</v>
+      </c>
+      <c r="K25">
+        <v>7</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>2.74</v>
+      </c>
+      <c r="O25">
+        <v>1.35</v>
+      </c>
+      <c r="P25">
+        <v>1.7</v>
+      </c>
+      <c r="Q25">
+        <v>1.86</v>
+      </c>
+      <c r="R25">
+        <v>1.21</v>
+      </c>
+      <c r="S25">
+        <v>2.86</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
+        <v>1.2</v>
+      </c>
+      <c r="W25">
+        <v>1.9</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25">
+        <v>1.01</v>
+      </c>
+      <c r="AR25">
+        <v>1.01</v>
+      </c>
+      <c r="AS25">
+        <v>1.01</v>
+      </c>
+      <c r="AT25">
+        <v>1.01</v>
+      </c>
+      <c r="AU25">
+        <v>1.01</v>
+      </c>
+      <c r="AV25">
+        <v>1.01</v>
+      </c>
+      <c r="AW25">
+        <v>1.01</v>
+      </c>
+      <c r="AX25">
+        <v>1.01</v>
+      </c>
+      <c r="AY25">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25">
+        <v>1.01</v>
+      </c>
+      <c r="BA25">
+        <v>1.01</v>
+      </c>
+      <c r="BB25">
+        <v>1.01</v>
+      </c>
+      <c r="BC25">
+        <v>1.01</v>
+      </c>
+      <c r="BD25">
+        <v>1.01</v>
+      </c>
+      <c r="BE25">
+        <v>1.01</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26">
+        <v>3.45</v>
+      </c>
+      <c r="G26">
+        <v>3.65</v>
+      </c>
+      <c r="H26">
+        <v>2.48</v>
+      </c>
+      <c r="I26">
+        <v>2.58</v>
+      </c>
+      <c r="J26">
+        <v>3</v>
+      </c>
+      <c r="K26">
+        <v>3.15</v>
+      </c>
+      <c r="L26">
+        <v>1.58</v>
+      </c>
+      <c r="M26">
+        <v>1.13</v>
+      </c>
+      <c r="N26">
+        <v>2.66</v>
+      </c>
+      <c r="O26">
+        <v>1.57</v>
+      </c>
+      <c r="P26">
+        <v>1.54</v>
+      </c>
+      <c r="Q26">
+        <v>2.72</v>
+      </c>
+      <c r="R26">
+        <v>1.19</v>
+      </c>
+      <c r="S26">
+        <v>5.7</v>
+      </c>
+      <c r="T26">
+        <v>2.2</v>
+      </c>
+      <c r="U26">
+        <v>1.79</v>
+      </c>
+      <c r="V26">
+        <v>1.64</v>
+      </c>
+      <c r="W26">
+        <v>1.37</v>
+      </c>
+      <c r="X26">
+        <v>8.4</v>
+      </c>
+      <c r="Y26">
+        <v>7.6</v>
+      </c>
+      <c r="Z26">
+        <v>14.5</v>
+      </c>
+      <c r="AA26">
+        <v>40</v>
+      </c>
+      <c r="AB26">
+        <v>9.6</v>
+      </c>
+      <c r="AC26">
+        <v>7.2</v>
+      </c>
+      <c r="AD26">
+        <v>13</v>
+      </c>
+      <c r="AE26">
+        <v>40</v>
+      </c>
+      <c r="AF26">
+        <v>23</v>
+      </c>
+      <c r="AG26">
+        <v>16.5</v>
+      </c>
+      <c r="AH26">
+        <v>25</v>
+      </c>
+      <c r="AI26">
+        <v>85</v>
+      </c>
+      <c r="AJ26">
+        <v>85</v>
+      </c>
+      <c r="AK26">
+        <v>65</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>100</v>
+      </c>
+      <c r="AO26">
+        <v>42</v>
+      </c>
+      <c r="AP26">
+        <v>7.6</v>
+      </c>
+      <c r="AQ26">
+        <v>7</v>
+      </c>
+      <c r="AR26">
+        <v>12.5</v>
+      </c>
+      <c r="AS26">
+        <v>22</v>
+      </c>
+      <c r="AT26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU26">
+        <v>6.6</v>
+      </c>
+      <c r="AV26">
+        <v>11</v>
+      </c>
+      <c r="AW26">
+        <v>22</v>
+      </c>
+      <c r="AX26">
+        <v>15.5</v>
+      </c>
+      <c r="AY26">
+        <v>14.5</v>
+      </c>
+      <c r="AZ26">
+        <v>17</v>
+      </c>
+      <c r="BA26">
+        <v>34</v>
+      </c>
+      <c r="BB26">
+        <v>30</v>
+      </c>
+      <c r="BC26">
+        <v>27</v>
+      </c>
+      <c r="BD26">
+        <v>36</v>
+      </c>
+      <c r="BE26">
+        <v>48</v>
+      </c>
+      <c r="BF26">
+        <v>32</v>
+      </c>
+      <c r="BG26">
+        <v>32</v>
+      </c>
+      <c r="BH26">
+        <v>3.05</v>
+      </c>
+      <c r="BI26">
+        <v>2.28</v>
+      </c>
+      <c r="BJ26">
+        <v>16</v>
+      </c>
+      <c r="BK26">
+        <v>3.6</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>4.4</v>
+      </c>
+      <c r="BN26">
+        <v>7.6</v>
+      </c>
+      <c r="BO26">
+        <v>5.2</v>
+      </c>
+      <c r="BP26">
+        <v>50</v>
+      </c>
+      <c r="BQ26">
+        <v>4</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>4.2</v>
+      </c>
+      <c r="BT26">
+        <v>6.2</v>
+      </c>
+      <c r="BU26">
+        <v>2.84</v>
+      </c>
+      <c r="BV26">
+        <v>32</v>
+      </c>
+      <c r="BW26">
+        <v>3.9</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>4.1</v>
+      </c>
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
+        <v>4.2</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27">
+        <v>2.52</v>
+      </c>
+      <c r="G27">
+        <v>2.62</v>
+      </c>
+      <c r="H27">
+        <v>3.2</v>
+      </c>
+      <c r="I27">
         <v>4.9</v>
       </c>
-      <c r="H22">
-        <v>1.97</v>
-      </c>
-      <c r="I22">
-        <v>2.2</v>
-      </c>
-      <c r="J22">
+      <c r="J27">
+        <v>2.62</v>
+      </c>
+      <c r="K27">
+        <v>3.25</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.08</v>
+      </c>
+      <c r="N27">
+        <v>2.24</v>
+      </c>
+      <c r="O27">
+        <v>1.49</v>
+      </c>
+      <c r="P27">
+        <v>1.43</v>
+      </c>
+      <c r="Q27">
+        <v>2.36</v>
+      </c>
+      <c r="R27">
+        <v>1.13</v>
+      </c>
+      <c r="S27">
+        <v>1.05</v>
+      </c>
+      <c r="T27">
+        <v>1.96</v>
+      </c>
+      <c r="U27">
+        <v>1.74</v>
+      </c>
+      <c r="V27">
+        <v>1.32</v>
+      </c>
+      <c r="W27">
+        <v>1.62</v>
+      </c>
+      <c r="X27">
+        <v>1000</v>
+      </c>
+      <c r="Y27">
+        <v>1000</v>
+      </c>
+      <c r="Z27">
+        <v>1000</v>
+      </c>
+      <c r="AA27">
+        <v>1000</v>
+      </c>
+      <c r="AB27">
+        <v>1000</v>
+      </c>
+      <c r="AC27">
+        <v>1000</v>
+      </c>
+      <c r="AD27">
+        <v>1000</v>
+      </c>
+      <c r="AE27">
+        <v>1000</v>
+      </c>
+      <c r="AF27">
+        <v>1000</v>
+      </c>
+      <c r="AG27">
+        <v>1000</v>
+      </c>
+      <c r="AH27">
+        <v>1000</v>
+      </c>
+      <c r="AI27">
+        <v>1000</v>
+      </c>
+      <c r="AJ27">
+        <v>1000</v>
+      </c>
+      <c r="AK27">
+        <v>1000</v>
+      </c>
+      <c r="AL27">
+        <v>1000</v>
+      </c>
+      <c r="AM27">
+        <v>1000</v>
+      </c>
+      <c r="AN27">
+        <v>1000</v>
+      </c>
+      <c r="AO27">
+        <v>1000</v>
+      </c>
+      <c r="AP27">
+        <v>1.03</v>
+      </c>
+      <c r="AQ27">
+        <v>1.03</v>
+      </c>
+      <c r="AR27">
+        <v>1.03</v>
+      </c>
+      <c r="AS27">
+        <v>1.03</v>
+      </c>
+      <c r="AT27">
+        <v>1.01</v>
+      </c>
+      <c r="AU27">
+        <v>1.03</v>
+      </c>
+      <c r="AV27">
+        <v>1.03</v>
+      </c>
+      <c r="AW27">
+        <v>1.03</v>
+      </c>
+      <c r="AX27">
+        <v>1.03</v>
+      </c>
+      <c r="AY27">
+        <v>1.03</v>
+      </c>
+      <c r="AZ27">
+        <v>1.03</v>
+      </c>
+      <c r="BA27">
+        <v>1.03</v>
+      </c>
+      <c r="BB27">
+        <v>1.03</v>
+      </c>
+      <c r="BC27">
+        <v>1.03</v>
+      </c>
+      <c r="BD27">
+        <v>1.03</v>
+      </c>
+      <c r="BE27">
+        <v>1.03</v>
+      </c>
+      <c r="BF27">
+        <v>1.01</v>
+      </c>
+      <c r="BG27">
+        <v>1.01</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.01</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.01</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.01</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.01</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.01</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.01</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.01</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28">
+        <v>1.73</v>
+      </c>
+      <c r="G28">
+        <v>1.87</v>
+      </c>
+      <c r="H28">
+        <v>5.3</v>
+      </c>
+      <c r="I28">
+        <v>6.4</v>
+      </c>
+      <c r="J28">
+        <v>3.25</v>
+      </c>
+      <c r="K28">
+        <v>4.3</v>
+      </c>
+      <c r="L28">
+        <v>1.5</v>
+      </c>
+      <c r="M28">
+        <v>1.1</v>
+      </c>
+      <c r="N28">
+        <v>2.84</v>
+      </c>
+      <c r="O28">
+        <v>1.44</v>
+      </c>
+      <c r="P28">
+        <v>1.61</v>
+      </c>
+      <c r="Q28">
+        <v>2.3</v>
+      </c>
+      <c r="R28">
+        <v>1.21</v>
+      </c>
+      <c r="S28">
+        <v>4.3</v>
+      </c>
+      <c r="T28">
+        <v>2.14</v>
+      </c>
+      <c r="U28">
+        <v>1.65</v>
+      </c>
+      <c r="V28">
+        <v>1.2</v>
+      </c>
+      <c r="W28">
+        <v>2.12</v>
+      </c>
+      <c r="X28">
+        <v>970</v>
+      </c>
+      <c r="Y28">
+        <v>1000</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>970</v>
+      </c>
+      <c r="AC28">
+        <v>970</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>970</v>
+      </c>
+      <c r="AG28">
+        <v>970</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>7.2</v>
+      </c>
+      <c r="AQ28">
+        <v>1.56</v>
+      </c>
+      <c r="AR28">
+        <v>1.56</v>
+      </c>
+      <c r="AS28">
+        <v>1.56</v>
+      </c>
+      <c r="AT28">
+        <v>5.2</v>
+      </c>
+      <c r="AU28">
+        <v>6.2</v>
+      </c>
+      <c r="AV28">
+        <v>1.56</v>
+      </c>
+      <c r="AW28">
+        <v>1.56</v>
+      </c>
+      <c r="AX28">
+        <v>6.8</v>
+      </c>
+      <c r="AY28">
+        <v>7.6</v>
+      </c>
+      <c r="AZ28">
+        <v>1.56</v>
+      </c>
+      <c r="BA28">
+        <v>1.56</v>
+      </c>
+      <c r="BB28">
+        <v>1.56</v>
+      </c>
+      <c r="BC28">
+        <v>1.56</v>
+      </c>
+      <c r="BD28">
+        <v>1.56</v>
+      </c>
+      <c r="BE28">
+        <v>1.56</v>
+      </c>
+      <c r="BF28">
+        <v>1.56</v>
+      </c>
+      <c r="BG28">
+        <v>1.56</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.27</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.01</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.5</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.01</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.01</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>2.18</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.01</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29">
+        <v>3.75</v>
+      </c>
+      <c r="G29">
+        <v>4.7</v>
+      </c>
+      <c r="H29">
+        <v>1.99</v>
+      </c>
+      <c r="I29">
+        <v>2.18</v>
+      </c>
+      <c r="J29">
         <v>3.3</v>
       </c>
-      <c r="K22">
-        <v>4</v>
-      </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.05</v>
-      </c>
-      <c r="N22">
+      <c r="K29">
+        <v>3.65</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.09</v>
+      </c>
+      <c r="N29">
         <v>3</v>
       </c>
-      <c r="O22">
+      <c r="O29">
         <v>1.39</v>
       </c>
-      <c r="P22">
+      <c r="P29">
         <v>1.65</v>
       </c>
-      <c r="Q22">
-        <v>2.12</v>
-      </c>
-      <c r="R22">
-        <v>1.25</v>
-      </c>
-      <c r="S22">
+      <c r="Q29">
+        <v>2.1</v>
+      </c>
+      <c r="R29">
+        <v>1.22</v>
+      </c>
+      <c r="S29">
         <v>3.6</v>
       </c>
-      <c r="T22">
+      <c r="T29">
         <v>1.9</v>
       </c>
-      <c r="U22">
-        <v>1.81</v>
-      </c>
-      <c r="V22">
-        <v>1.83</v>
-      </c>
-      <c r="W22">
-        <v>1.26</v>
-      </c>
-      <c r="X22">
-        <v>120</v>
-      </c>
-      <c r="Y22">
-        <v>85</v>
-      </c>
-      <c r="Z22">
-        <v>130</v>
-      </c>
-      <c r="AA22">
-        <v>1000</v>
-      </c>
-      <c r="AB22">
-        <v>150</v>
-      </c>
-      <c r="AC22">
-        <v>890</v>
-      </c>
-      <c r="AD22">
-        <v>110</v>
-      </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>1000</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.43</v>
-      </c>
-      <c r="AQ22">
+      <c r="U29">
+        <v>1.84</v>
+      </c>
+      <c r="V29">
+        <v>1.84</v>
+      </c>
+      <c r="W29">
+        <v>1.27</v>
+      </c>
+      <c r="X29">
+        <v>46</v>
+      </c>
+      <c r="Y29">
+        <v>34</v>
+      </c>
+      <c r="Z29">
+        <v>15</v>
+      </c>
+      <c r="AA29">
+        <v>960</v>
+      </c>
+      <c r="AB29">
+        <v>70</v>
+      </c>
+      <c r="AC29">
+        <v>9</v>
+      </c>
+      <c r="AD29">
+        <v>48</v>
+      </c>
+      <c r="AE29">
+        <v>960</v>
+      </c>
+      <c r="AF29">
+        <v>44</v>
+      </c>
+      <c r="AG29">
+        <v>25</v>
+      </c>
+      <c r="AH29">
+        <v>29</v>
+      </c>
+      <c r="AI29">
+        <v>960</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>970</v>
+      </c>
+      <c r="AL29">
+        <v>960</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>960</v>
+      </c>
+      <c r="AO29">
+        <v>28</v>
+      </c>
+      <c r="AP29">
+        <v>2.4</v>
+      </c>
+      <c r="AQ29">
+        <v>7</v>
+      </c>
+      <c r="AR29">
+        <v>2.48</v>
+      </c>
+      <c r="AS29">
+        <v>18.5</v>
+      </c>
+      <c r="AT29">
+        <v>7</v>
+      </c>
+      <c r="AU29">
+        <v>2.26</v>
+      </c>
+      <c r="AV29">
+        <v>7.4</v>
+      </c>
+      <c r="AW29">
+        <v>17.5</v>
+      </c>
+      <c r="AX29">
+        <v>4.6</v>
+      </c>
+      <c r="AY29">
+        <v>12.5</v>
+      </c>
+      <c r="AZ29">
+        <v>14.5</v>
+      </c>
+      <c r="BA29">
+        <v>2.88</v>
+      </c>
+      <c r="BB29">
+        <v>6.6</v>
+      </c>
+      <c r="BC29">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD29">
+        <v>2.92</v>
+      </c>
+      <c r="BE29">
+        <v>3</v>
+      </c>
+      <c r="BF29">
+        <v>2.92</v>
+      </c>
+      <c r="BG29">
+        <v>11</v>
+      </c>
+      <c r="BH29">
+        <v>3.75</v>
+      </c>
+      <c r="BI29">
+        <v>2.48</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
         <v>1.37</v>
       </c>
-      <c r="AR22">
-        <v>1.43</v>
-      </c>
-      <c r="AS22">
-        <v>3.3</v>
-      </c>
-      <c r="AT22">
-        <v>10</v>
-      </c>
-      <c r="AU22">
-        <v>1.33</v>
-      </c>
-      <c r="AV22">
-        <v>7.4</v>
-      </c>
-      <c r="AW22">
-        <v>3.3</v>
-      </c>
-      <c r="AX22">
-        <v>3.3</v>
-      </c>
-      <c r="AY22">
-        <v>1.52</v>
-      </c>
-      <c r="AZ22">
-        <v>3.3</v>
-      </c>
-      <c r="BA22">
-        <v>3.4</v>
-      </c>
-      <c r="BB22">
-        <v>3.5</v>
-      </c>
-      <c r="BC22">
-        <v>3.4</v>
-      </c>
-      <c r="BD22">
-        <v>3.5</v>
-      </c>
-      <c r="BE22">
-        <v>2.72</v>
-      </c>
-      <c r="BF22">
-        <v>1.52</v>
-      </c>
-      <c r="BG22">
-        <v>11</v>
-      </c>
-      <c r="BH22">
-        <v>3.75</v>
-      </c>
-      <c r="BI22">
-        <v>2.48</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
         <v>1.37</v>
       </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
         <v>1.37</v>
       </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
-      <c r="BO22">
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
         <v>1.37</v>
       </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
         <v>1.37</v>
       </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
         <v>1.37</v>
       </c>
-      <c r="BT22">
-        <v>1000</v>
-      </c>
-      <c r="BU22">
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
         <v>1.37</v>
       </c>
-      <c r="BV22">
-        <v>1000</v>
-      </c>
-      <c r="BW22">
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
         <v>1.37</v>
       </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
         <v>1.37</v>
       </c>
-      <c r="BZ22">
-        <v>1000</v>
-      </c>
-      <c r="CA22">
-        <v>1.37</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>148</v>
+      <c r="CB29" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="169">
   <si>
     <t>League</t>
   </si>
@@ -271,12 +271,12 @@
     <t>Serbian First League</t>
   </si>
   <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
     <t>Romanian Liga I</t>
   </si>
   <si>
-    <t>Slovakian 2 Liga</t>
-  </si>
-  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
@@ -370,18 +370,21 @@
     <t>FK Backa Topola</t>
   </si>
   <si>
+    <t>FC Petrzalka</t>
+  </si>
+  <si>
     <t>Otelul Galati</t>
   </si>
   <si>
-    <t>FC Petrzalka</t>
-  </si>
-  <si>
     <t>FK Jedinstvo Ub</t>
   </si>
   <si>
     <t>Metalac Gornji Milanovac</t>
   </si>
   <si>
+    <t>FK Javor Ivanjica</t>
+  </si>
+  <si>
     <t>FK Napredak</t>
   </si>
   <si>
@@ -454,18 +457,21 @@
     <t>FK Dubocica</t>
   </si>
   <si>
+    <t>Pohronie</t>
+  </si>
+  <si>
     <t>FC Hunedoara</t>
   </si>
   <si>
-    <t>Pohronie</t>
-  </si>
-  <si>
     <t>FK Loznica</t>
   </si>
   <si>
     <t>FK Graficar</t>
   </si>
   <si>
+    <t>FK Proleter Zrenjanin</t>
+  </si>
+  <si>
     <t>Fk Smederevo</t>
   </si>
   <si>
@@ -514,7 +520,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 12:11:10</t>
+    <t>2026-09-20 14:26:14</t>
   </si>
 </sst>
 </file>
@@ -846,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB29"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1105,25 +1111,25 @@
         <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F2">
+        <v>1.27</v>
+      </c>
+      <c r="G2">
         <v>1.29</v>
       </c>
-      <c r="G2">
-        <v>1.31</v>
-      </c>
       <c r="H2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="K2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="L2">
         <v>1.21</v>
@@ -1135,52 +1141,52 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R2">
+        <v>1.98</v>
+      </c>
+      <c r="S2">
         <v>1.97</v>
       </c>
-      <c r="S2">
-        <v>2</v>
-      </c>
       <c r="T2">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="X2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AA2">
-        <v>470</v>
+        <v>380</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE2">
         <v>150</v>
@@ -1189,13 +1195,13 @@
         <v>11</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
         <v>11.5</v>
@@ -1204,67 +1210,67 @@
         <v>12.5</v>
       </c>
       <c r="AL2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN2">
         <v>3.45</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AP2">
         <v>36</v>
       </c>
       <c r="AQ2">
+        <v>26</v>
+      </c>
+      <c r="AR2">
+        <v>14.5</v>
+      </c>
+      <c r="AS2">
         <v>15.5</v>
       </c>
-      <c r="AR2">
-        <v>17</v>
-      </c>
-      <c r="AS2">
-        <v>18</v>
-      </c>
       <c r="AT2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AV2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AX2">
+        <v>9.6</v>
+      </c>
+      <c r="AY2">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2">
+        <v>24</v>
+      </c>
+      <c r="BA2">
+        <v>14</v>
+      </c>
+      <c r="BB2">
         <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>22</v>
-      </c>
-      <c r="BA2">
-        <v>16.5</v>
-      </c>
-      <c r="BB2">
-        <v>10.5</v>
       </c>
       <c r="BC2">
         <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BE2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="BF2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG2">
         <v>75</v>
@@ -1273,25 +1279,25 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -1303,34 +1309,34 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="CB2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1347,169 +1353,169 @@
         <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F3">
         <v>1.76</v>
       </c>
       <c r="G3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q3">
+        <v>1.97</v>
+      </c>
+      <c r="R3">
+        <v>1.39</v>
+      </c>
+      <c r="S3">
+        <v>3.45</v>
+      </c>
+      <c r="T3">
         <v>1.91</v>
       </c>
-      <c r="R3">
-        <v>1.41</v>
-      </c>
-      <c r="S3">
-        <v>3.3</v>
-      </c>
-      <c r="T3">
-        <v>1.85</v>
-      </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>40</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3">
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>10</v>
       </c>
       <c r="AH3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL3">
         <v>36</v>
       </c>
       <c r="AM3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN3">
         <v>11</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AS3">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
         <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AX3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
+        <v>19.5</v>
+      </c>
+      <c r="BA3">
+        <v>60</v>
+      </c>
+      <c r="BB3">
+        <v>16.5</v>
+      </c>
+      <c r="BC3">
         <v>17</v>
       </c>
-      <c r="BA3">
-        <v>46</v>
-      </c>
-      <c r="BB3">
-        <v>16</v>
-      </c>
-      <c r="BC3">
-        <v>16.5</v>
-      </c>
       <c r="BD3">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>9.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="BF3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1572,7 +1578,7 @@
         <v>2.36</v>
       </c>
       <c r="CB3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1589,13 +1595,13 @@
         <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F4">
         <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
         <v>3.95</v>
@@ -1643,7 +1649,7 @@
         <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1652,10 +1658,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
@@ -1667,7 +1673,7 @@
         <v>18.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF4">
         <v>12.5</v>
@@ -1688,13 +1694,13 @@
         <v>42</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1706,7 +1712,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS4">
         <v>36</v>
@@ -1739,13 +1745,13 @@
         <v>22</v>
       </c>
       <c r="BC4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF4">
         <v>24</v>
@@ -1754,67 +1760,67 @@
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>2.92</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>2.22</v>
       </c>
       <c r="BV4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1831,7 +1837,7 @@
         <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F5">
         <v>4.6</v>
@@ -1870,10 +1876,10 @@
         <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
         <v>1.93</v>
@@ -1939,7 +1945,7 @@
         <v>100</v>
       </c>
       <c r="AO5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP5">
         <v>11.5</v>
@@ -1966,7 +1972,7 @@
         <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY5">
         <v>16</v>
@@ -1975,7 +1981,7 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB5">
         <v>70</v>
@@ -1987,7 +1993,7 @@
         <v>46</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF5">
         <v>46</v>
@@ -2056,7 +2062,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2073,7 +2079,7 @@
         <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F6">
         <v>5.6</v>
@@ -2082,16 +2088,16 @@
         <v>7.4</v>
       </c>
       <c r="H6">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I6">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>1.32</v>
@@ -2103,10 +2109,10 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q6">
         <v>1.75</v>
@@ -2118,13 +2124,13 @@
         <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U6">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="V6">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="W6">
         <v>1.16</v>
@@ -2298,7 +2304,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2315,7 +2321,7 @@
         <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F7">
         <v>2.68</v>
@@ -2333,10 +2339,10 @@
         <v>3.6</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
         <v>1.06</v>
@@ -2351,16 +2357,16 @@
         <v>2.14</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R7">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U7">
         <v>2.36</v>
@@ -2372,7 +2378,7 @@
         <v>1.56</v>
       </c>
       <c r="X7">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="Y7">
         <v>13</v>
@@ -2393,7 +2399,7 @@
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
         <v>19.5</v>
@@ -2423,7 +2429,7 @@
         <v>22</v>
       </c>
       <c r="AO7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -2435,7 +2441,7 @@
         <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2459,22 +2465,22 @@
         <v>14</v>
       </c>
       <c r="BA7">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BC7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BD7">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE7">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="BG7">
         <v>18</v>
@@ -2540,7 +2546,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2557,19 +2563,19 @@
         <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
         <v>1.1</v>
@@ -2584,22 +2590,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R8">
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2608,10 +2614,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2782,7 +2788,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2799,25 +2805,25 @@
         <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
         <v>1.1</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2826,22 +2832,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>1.62</v>
       </c>
       <c r="O9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P9">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Q9">
         <v>1.15</v>
       </c>
       <c r="R9">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="S9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2850,10 +2856,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2910,52 +2916,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -3024,7 +3030,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3041,67 +3047,67 @@
         <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F10">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="G10">
-        <v>2.56</v>
+        <v>1.56</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="I10">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="K10">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="L10">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>1.61</v>
       </c>
       <c r="R10">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="X10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
         <v>1000</v>
@@ -3110,25 +3116,25 @@
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -3152,58 +3158,58 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.83</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3266,7 +3272,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3283,169 +3289,169 @@
         <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F11">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="G11">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="H11">
+        <v>3.3</v>
+      </c>
+      <c r="I11">
+        <v>3.55</v>
+      </c>
+      <c r="J11">
+        <v>3.2</v>
+      </c>
+      <c r="K11">
+        <v>3.55</v>
+      </c>
+      <c r="L11">
+        <v>1.42</v>
+      </c>
+      <c r="M11">
+        <v>1.09</v>
+      </c>
+      <c r="N11">
+        <v>3.25</v>
+      </c>
+      <c r="O11">
+        <v>1.39</v>
+      </c>
+      <c r="P11">
+        <v>1.77</v>
+      </c>
+      <c r="Q11">
+        <v>2.16</v>
+      </c>
+      <c r="R11">
+        <v>1.3</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>1.86</v>
+      </c>
+      <c r="U11">
+        <v>2.04</v>
+      </c>
+      <c r="V11">
+        <v>1.39</v>
+      </c>
+      <c r="W11">
+        <v>1.65</v>
+      </c>
+      <c r="X11">
+        <v>970</v>
+      </c>
+      <c r="Y11">
+        <v>12</v>
+      </c>
+      <c r="Z11">
+        <v>27</v>
+      </c>
+      <c r="AA11">
+        <v>85</v>
+      </c>
+      <c r="AB11">
+        <v>11</v>
+      </c>
+      <c r="AC11">
+        <v>7.6</v>
+      </c>
+      <c r="AD11">
+        <v>17</v>
+      </c>
+      <c r="AE11">
+        <v>50</v>
+      </c>
+      <c r="AF11">
+        <v>15.5</v>
+      </c>
+      <c r="AG11">
+        <v>12</v>
+      </c>
+      <c r="AH11">
+        <v>18.5</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>42</v>
+      </c>
+      <c r="AK11">
+        <v>34</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>130</v>
+      </c>
+      <c r="AN11">
+        <v>30</v>
+      </c>
+      <c r="AO11">
+        <v>55</v>
+      </c>
+      <c r="AP11">
+        <v>10</v>
+      </c>
+      <c r="AQ11">
+        <v>10.5</v>
+      </c>
+      <c r="AR11">
+        <v>20</v>
+      </c>
+      <c r="AS11">
+        <v>5.5</v>
+      </c>
+      <c r="AT11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11">
+        <v>6.6</v>
+      </c>
+      <c r="AV11">
+        <v>13</v>
+      </c>
+      <c r="AW11">
+        <v>5.2</v>
+      </c>
+      <c r="AX11">
+        <v>13.5</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>16</v>
+      </c>
+      <c r="BA11">
         <v>5.8</v>
       </c>
-      <c r="I11">
-        <v>6.8</v>
-      </c>
-      <c r="J11">
+      <c r="BB11">
+        <v>5.1</v>
+      </c>
+      <c r="BC11">
+        <v>5</v>
+      </c>
+      <c r="BD11">
+        <v>5.2</v>
+      </c>
+      <c r="BE11">
+        <v>5.6</v>
+      </c>
+      <c r="BF11">
         <v>4.8</v>
       </c>
-      <c r="K11">
-        <v>5.3</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.01</v>
-      </c>
-      <c r="N11">
-        <v>4.7</v>
-      </c>
-      <c r="O11">
-        <v>1.01</v>
-      </c>
-      <c r="P11">
-        <v>2.14</v>
-      </c>
-      <c r="Q11">
-        <v>1.61</v>
-      </c>
-      <c r="R11">
-        <v>1.44</v>
-      </c>
-      <c r="S11">
-        <v>2.54</v>
-      </c>
-      <c r="T11">
-        <v>1.03</v>
-      </c>
-      <c r="U11">
-        <v>1.07</v>
-      </c>
-      <c r="V11">
-        <v>1.17</v>
-      </c>
-      <c r="W11">
-        <v>2.78</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>1000</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>1000</v>
-      </c>
-      <c r="AG11">
-        <v>1000</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>1000</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>1.03</v>
-      </c>
-      <c r="AQ11">
-        <v>1.03</v>
-      </c>
-      <c r="AR11">
-        <v>1.03</v>
-      </c>
-      <c r="AS11">
-        <v>1.03</v>
-      </c>
-      <c r="AT11">
-        <v>1.03</v>
-      </c>
-      <c r="AU11">
-        <v>1.03</v>
-      </c>
-      <c r="AV11">
-        <v>1.03</v>
-      </c>
-      <c r="AW11">
-        <v>1.03</v>
-      </c>
-      <c r="AX11">
-        <v>1.03</v>
-      </c>
-      <c r="AY11">
-        <v>1.03</v>
-      </c>
-      <c r="AZ11">
-        <v>1.03</v>
-      </c>
-      <c r="BA11">
-        <v>1.03</v>
-      </c>
-      <c r="BB11">
-        <v>1.03</v>
-      </c>
-      <c r="BC11">
-        <v>1.03</v>
-      </c>
-      <c r="BD11">
-        <v>1.03</v>
-      </c>
-      <c r="BE11">
-        <v>1.03</v>
-      </c>
-      <c r="BF11">
-        <v>1.01</v>
-      </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3508,7 +3514,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3525,19 +3531,19 @@
         <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F12">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J12">
         <v>1.1</v>
@@ -3552,22 +3558,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O12">
         <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S12">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3576,10 +3582,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3750,7 +3756,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3767,19 +3773,19 @@
         <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J13">
         <v>1.1</v>
@@ -3794,22 +3800,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3818,10 +3824,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3992,7 +3998,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4009,7 +4015,7 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F14">
         <v>1.1</v>
@@ -4024,10 +4030,10 @@
         <v>1000</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4039,19 +4045,19 @@
         <v>1.07</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P14">
         <v>1.07</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="R14">
         <v>1.07</v>
       </c>
       <c r="S14">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4120,52 +4126,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4234,177 +4240,177 @@
         <v>1.01</v>
       </c>
       <c r="CB14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F15">
-        <v>2.32</v>
+        <v>1.13</v>
       </c>
       <c r="G15">
-        <v>2.64</v>
+        <v>950</v>
       </c>
       <c r="H15">
-        <v>2.7</v>
+        <v>1.13</v>
       </c>
       <c r="I15">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
-        <v>2.16</v>
+        <v>1.08</v>
       </c>
       <c r="Q15">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
         <v>1.03</v>
@@ -4476,7 +4482,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4493,160 +4499,160 @@
         <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F16">
-        <v>1.12</v>
+        <v>2.32</v>
       </c>
       <c r="G16">
-        <v>180</v>
+        <v>2.64</v>
       </c>
       <c r="H16">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="I16">
-        <v>970</v>
+        <v>3.15</v>
       </c>
       <c r="J16">
-        <v>1.22</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q16">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="R16">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="S16">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
         <v>1.03</v>
@@ -4658,67 +4664,67 @@
         <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="CB16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4735,49 +4741,49 @@
         <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F17">
-        <v>1.52</v>
+        <v>1.12</v>
       </c>
       <c r="G17">
-        <v>1.76</v>
+        <v>980</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>1.12</v>
       </c>
       <c r="I17">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>1.24</v>
       </c>
       <c r="K17">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="L17">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
         <v>1.02</v>
       </c>
       <c r="P17">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.9</v>
+        <v>1.02</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S17">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4786,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W17">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4954,18 +4960,18 @@
         <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>94</v>
@@ -4977,67 +4983,67 @@
         <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F18">
-        <v>2.34</v>
+        <v>1.57</v>
       </c>
       <c r="G18">
-        <v>2.54</v>
+        <v>1.76</v>
       </c>
       <c r="H18">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="J18">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="O18">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="P18">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="Q18">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="R18">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S18">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="T18">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="W18">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="X18">
         <v>1000</v>
       </c>
       <c r="Y18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
         <v>1000</v>
@@ -5049,10 +5055,10 @@
         <v>1000</v>
       </c>
       <c r="AC18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
         <v>1000</v>
@@ -5061,7 +5067,7 @@
         <v>1000</v>
       </c>
       <c r="AG18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
         <v>1000</v>
@@ -5088,58 +5094,58 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AR18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV18">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AW18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY18">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE18">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5202,12 +5208,12 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>94</v>
@@ -5219,169 +5225,169 @@
         <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F19">
+        <v>2.32</v>
+      </c>
+      <c r="G19">
+        <v>2.6</v>
+      </c>
+      <c r="H19">
+        <v>2.82</v>
+      </c>
+      <c r="I19">
+        <v>3.3</v>
+      </c>
+      <c r="J19">
+        <v>3.7</v>
+      </c>
+      <c r="K19">
+        <v>4.6</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
+        <v>4.4</v>
+      </c>
+      <c r="O19">
+        <v>1.28</v>
+      </c>
+      <c r="P19">
+        <v>2.16</v>
+      </c>
+      <c r="Q19">
+        <v>1.69</v>
+      </c>
+      <c r="R19">
+        <v>1.46</v>
+      </c>
+      <c r="S19">
+        <v>2.86</v>
+      </c>
+      <c r="T19">
+        <v>1.57</v>
+      </c>
+      <c r="U19">
+        <v>2.28</v>
+      </c>
+      <c r="V19">
+        <v>1.43</v>
+      </c>
+      <c r="W19">
+        <v>1.62</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>42</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>970</v>
+      </c>
+      <c r="AD19">
+        <v>36</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>23</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.2</v>
+      </c>
+      <c r="AQ19">
+        <v>1.17</v>
+      </c>
+      <c r="AR19">
+        <v>1.2</v>
+      </c>
+      <c r="AS19">
+        <v>1.2</v>
+      </c>
+      <c r="AT19">
+        <v>1.2</v>
+      </c>
+      <c r="AU19">
         <v>1.1</v>
       </c>
-      <c r="G19">
-        <v>950</v>
-      </c>
-      <c r="H19">
-        <v>1.1</v>
-      </c>
-      <c r="I19">
-        <v>950</v>
-      </c>
-      <c r="J19">
-        <v>1.1</v>
-      </c>
-      <c r="K19">
-        <v>950</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>1.27</v>
-      </c>
-      <c r="O19">
-        <v>1.01</v>
-      </c>
-      <c r="P19">
-        <v>1.26</v>
-      </c>
-      <c r="Q19">
-        <v>1.31</v>
-      </c>
-      <c r="R19">
-        <v>1.18</v>
-      </c>
-      <c r="S19">
-        <v>2.78</v>
-      </c>
-      <c r="T19">
-        <v>1.01</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.02</v>
-      </c>
-      <c r="W19">
-        <v>1.02</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.03</v>
-      </c>
-      <c r="AQ19">
-        <v>1.03</v>
-      </c>
-      <c r="AR19">
-        <v>1.03</v>
-      </c>
-      <c r="AS19">
-        <v>1.03</v>
-      </c>
-      <c r="AT19">
-        <v>1.03</v>
-      </c>
-      <c r="AU19">
-        <v>1.03</v>
-      </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5444,12 +5450,12 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>94</v>
@@ -5461,25 +5467,25 @@
         <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F20">
-        <v>3.7</v>
+        <v>1.16</v>
       </c>
       <c r="G20">
-        <v>5.5</v>
+        <v>110</v>
       </c>
       <c r="H20">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
       <c r="I20">
-        <v>2.04</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="K20">
-        <v>6.6</v>
+        <v>950</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5488,22 +5494,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.45</v>
+        <v>1.28</v>
       </c>
       <c r="O20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
-        <v>2.06</v>
+        <v>1.28</v>
       </c>
       <c r="Q20">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5512,10 +5518,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5686,496 +5692,496 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
         <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F21">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G21">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="H21">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="I21">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="J21">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="K21">
+        <v>5.2</v>
+      </c>
+      <c r="L21">
+        <v>1.28</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>3.45</v>
+      </c>
+      <c r="O21">
+        <v>1.22</v>
+      </c>
+      <c r="P21">
+        <v>2.06</v>
+      </c>
+      <c r="Q21">
+        <v>1.64</v>
+      </c>
+      <c r="R21">
+        <v>1.4</v>
+      </c>
+      <c r="S21">
+        <v>2.52</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.98</v>
+      </c>
+      <c r="V21">
+        <v>1.98</v>
+      </c>
+      <c r="W21">
+        <v>1.24</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21">
+        <v>1.03</v>
+      </c>
+      <c r="AR21">
+        <v>1.03</v>
+      </c>
+      <c r="AS21">
+        <v>1.03</v>
+      </c>
+      <c r="AT21">
+        <v>1.03</v>
+      </c>
+      <c r="AU21">
+        <v>1.03</v>
+      </c>
+      <c r="AV21">
+        <v>1.03</v>
+      </c>
+      <c r="AW21">
+        <v>1.03</v>
+      </c>
+      <c r="AX21">
+        <v>1.03</v>
+      </c>
+      <c r="AY21">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21">
+        <v>1.03</v>
+      </c>
+      <c r="BA21">
+        <v>1.03</v>
+      </c>
+      <c r="BB21">
+        <v>1.03</v>
+      </c>
+      <c r="BC21">
+        <v>1.03</v>
+      </c>
+      <c r="BD21">
+        <v>1.03</v>
+      </c>
+      <c r="BE21">
+        <v>1.03</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>4.7</v>
+      </c>
+      <c r="BI21">
+        <v>2.36</v>
+      </c>
+      <c r="BJ21">
+        <v>11.5</v>
+      </c>
+      <c r="BK21">
+        <v>3.35</v>
+      </c>
+      <c r="BL21">
+        <v>120</v>
+      </c>
+      <c r="BM21">
+        <v>4.6</v>
+      </c>
+      <c r="BN21">
+        <v>9.4</v>
+      </c>
+      <c r="BO21">
         <v>3.15</v>
       </c>
-      <c r="L21">
-        <v>1.59</v>
-      </c>
-      <c r="M21">
-        <v>1.14</v>
-      </c>
-      <c r="N21">
-        <v>2.52</v>
-      </c>
-      <c r="O21">
-        <v>1.57</v>
-      </c>
-      <c r="P21">
-        <v>1.5</v>
-      </c>
-      <c r="Q21">
-        <v>2.84</v>
-      </c>
-      <c r="R21">
-        <v>1.18</v>
-      </c>
-      <c r="S21">
-        <v>6</v>
-      </c>
-      <c r="T21">
-        <v>2.2</v>
-      </c>
-      <c r="U21">
-        <v>1.73</v>
-      </c>
-      <c r="V21">
-        <v>1.58</v>
-      </c>
-      <c r="W21">
-        <v>1.39</v>
-      </c>
-      <c r="X21">
-        <v>8</v>
-      </c>
-      <c r="Y21">
-        <v>7.6</v>
-      </c>
-      <c r="Z21">
-        <v>15.5</v>
-      </c>
-      <c r="AA21">
-        <v>55</v>
-      </c>
-      <c r="AB21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC21">
-        <v>7.2</v>
-      </c>
-      <c r="AD21">
-        <v>13.5</v>
-      </c>
-      <c r="AE21">
-        <v>50</v>
-      </c>
-      <c r="AF21">
+      <c r="BP21">
+        <v>42</v>
+      </c>
+      <c r="BQ21">
+        <v>4.3</v>
+      </c>
+      <c r="BR21">
+        <v>48</v>
+      </c>
+      <c r="BS21">
+        <v>4.3</v>
+      </c>
+      <c r="BT21">
+        <v>5.6</v>
+      </c>
+      <c r="BU21">
+        <v>2.58</v>
+      </c>
+      <c r="BV21">
+        <v>14</v>
+      </c>
+      <c r="BW21">
+        <v>3.55</v>
+      </c>
+      <c r="BX21">
+        <v>28</v>
+      </c>
+      <c r="BY21">
+        <v>4.1</v>
+      </c>
+      <c r="BZ21">
         <v>21</v>
       </c>
-      <c r="AG21">
-        <v>18.5</v>
-      </c>
-      <c r="AH21">
-        <v>25</v>
-      </c>
-      <c r="AI21">
-        <v>90</v>
-      </c>
-      <c r="AJ21">
-        <v>90</v>
-      </c>
-      <c r="AK21">
-        <v>70</v>
-      </c>
-      <c r="AL21">
-        <v>110</v>
-      </c>
-      <c r="AM21">
-        <v>260</v>
-      </c>
-      <c r="AN21">
-        <v>100</v>
-      </c>
-      <c r="AO21">
-        <v>60</v>
-      </c>
-      <c r="AP21">
-        <v>7</v>
-      </c>
-      <c r="AQ21">
-        <v>6.8</v>
-      </c>
-      <c r="AR21">
-        <v>13</v>
-      </c>
-      <c r="AS21">
-        <v>36</v>
-      </c>
-      <c r="AT21">
-        <v>8</v>
-      </c>
-      <c r="AU21">
-        <v>6.4</v>
-      </c>
-      <c r="AV21">
-        <v>11.5</v>
-      </c>
-      <c r="AW21">
-        <v>34</v>
-      </c>
-      <c r="AX21">
-        <v>18.5</v>
-      </c>
-      <c r="AY21">
-        <v>14</v>
-      </c>
-      <c r="AZ21">
-        <v>7.2</v>
-      </c>
-      <c r="BA21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC21">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG21">
-        <v>27</v>
-      </c>
-      <c r="BH21">
-        <v>2.96</v>
-      </c>
-      <c r="BI21">
-        <v>2.12</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>2.32</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>2.32</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>4.2</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>2.32</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>2.32</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>3.6</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>2.32</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>2.32</v>
-      </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
       <c r="CA21">
-        <v>2.32</v>
+        <v>3.9</v>
       </c>
       <c r="CB21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
         <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F22">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="H22">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="I22">
-        <v>5.2</v>
+        <v>2.72</v>
       </c>
       <c r="J22">
+        <v>2.94</v>
+      </c>
+      <c r="K22">
+        <v>3.15</v>
+      </c>
+      <c r="L22">
+        <v>1.59</v>
+      </c>
+      <c r="M22">
+        <v>1.14</v>
+      </c>
+      <c r="N22">
+        <v>2.48</v>
+      </c>
+      <c r="O22">
+        <v>1.58</v>
+      </c>
+      <c r="P22">
+        <v>1.49</v>
+      </c>
+      <c r="Q22">
+        <v>2.84</v>
+      </c>
+      <c r="R22">
+        <v>1.17</v>
+      </c>
+      <c r="S22">
+        <v>6</v>
+      </c>
+      <c r="T22">
+        <v>2.2</v>
+      </c>
+      <c r="U22">
+        <v>1.73</v>
+      </c>
+      <c r="V22">
+        <v>1.58</v>
+      </c>
+      <c r="W22">
+        <v>1.39</v>
+      </c>
+      <c r="X22">
+        <v>8</v>
+      </c>
+      <c r="Y22">
+        <v>7.6</v>
+      </c>
+      <c r="Z22">
+        <v>15.5</v>
+      </c>
+      <c r="AA22">
+        <v>55</v>
+      </c>
+      <c r="AB22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC22">
+        <v>7.2</v>
+      </c>
+      <c r="AD22">
+        <v>13.5</v>
+      </c>
+      <c r="AE22">
+        <v>50</v>
+      </c>
+      <c r="AF22">
+        <v>21</v>
+      </c>
+      <c r="AG22">
+        <v>18.5</v>
+      </c>
+      <c r="AH22">
+        <v>25</v>
+      </c>
+      <c r="AI22">
+        <v>90</v>
+      </c>
+      <c r="AJ22">
+        <v>90</v>
+      </c>
+      <c r="AK22">
+        <v>70</v>
+      </c>
+      <c r="AL22">
+        <v>110</v>
+      </c>
+      <c r="AM22">
+        <v>260</v>
+      </c>
+      <c r="AN22">
+        <v>100</v>
+      </c>
+      <c r="AO22">
+        <v>60</v>
+      </c>
+      <c r="AP22">
+        <v>7</v>
+      </c>
+      <c r="AQ22">
+        <v>6.8</v>
+      </c>
+      <c r="AR22">
+        <v>13</v>
+      </c>
+      <c r="AS22">
+        <v>36</v>
+      </c>
+      <c r="AT22">
+        <v>8</v>
+      </c>
+      <c r="AU22">
+        <v>6.4</v>
+      </c>
+      <c r="AV22">
+        <v>11.5</v>
+      </c>
+      <c r="AW22">
+        <v>34</v>
+      </c>
+      <c r="AX22">
+        <v>18.5</v>
+      </c>
+      <c r="AY22">
+        <v>14</v>
+      </c>
+      <c r="AZ22">
+        <v>7.2</v>
+      </c>
+      <c r="BA22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG22">
+        <v>27</v>
+      </c>
+      <c r="BH22">
+        <v>2.96</v>
+      </c>
+      <c r="BI22">
+        <v>2.14</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>2.96</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>2.02</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>4.2</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>2.02</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>2.02</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
         <v>3.6</v>
       </c>
-      <c r="K22">
-        <v>3.9</v>
-      </c>
-      <c r="L22">
-        <v>1.4</v>
-      </c>
-      <c r="M22">
-        <v>1.08</v>
-      </c>
-      <c r="N22">
-        <v>3.45</v>
-      </c>
-      <c r="O22">
-        <v>1.37</v>
-      </c>
-      <c r="P22">
-        <v>1.82</v>
-      </c>
-      <c r="Q22">
-        <v>2.06</v>
-      </c>
-      <c r="R22">
-        <v>1.32</v>
-      </c>
-      <c r="S22">
-        <v>3.85</v>
-      </c>
-      <c r="T22">
-        <v>1.93</v>
-      </c>
-      <c r="U22">
-        <v>1.96</v>
-      </c>
-      <c r="V22">
-        <v>1.24</v>
-      </c>
-      <c r="W22">
-        <v>2.08</v>
-      </c>
-      <c r="X22">
-        <v>15</v>
-      </c>
-      <c r="Y22">
-        <v>18</v>
-      </c>
-      <c r="Z22">
-        <v>38</v>
-      </c>
-      <c r="AA22">
-        <v>130</v>
-      </c>
-      <c r="AB22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC22">
-        <v>8.4</v>
-      </c>
-      <c r="AD22">
-        <v>21</v>
-      </c>
-      <c r="AE22">
-        <v>80</v>
-      </c>
-      <c r="AF22">
-        <v>11</v>
-      </c>
-      <c r="AG22">
-        <v>12</v>
-      </c>
-      <c r="AH22">
-        <v>24</v>
-      </c>
-      <c r="AI22">
-        <v>85</v>
-      </c>
-      <c r="AJ22">
-        <v>24</v>
-      </c>
-      <c r="AK22">
-        <v>25</v>
-      </c>
-      <c r="AL22">
-        <v>48</v>
-      </c>
-      <c r="AM22">
-        <v>150</v>
-      </c>
-      <c r="AN22">
-        <v>17</v>
-      </c>
-      <c r="AO22">
-        <v>95</v>
-      </c>
-      <c r="AP22">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22">
-        <v>13</v>
-      </c>
-      <c r="AR22">
-        <v>6.8</v>
-      </c>
-      <c r="AS22">
-        <v>7.2</v>
-      </c>
-      <c r="AT22">
-        <v>7.2</v>
-      </c>
-      <c r="AU22">
-        <v>7.4</v>
-      </c>
-      <c r="AV22">
-        <v>16.5</v>
-      </c>
-      <c r="AW22">
-        <v>7</v>
-      </c>
-      <c r="AX22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22">
-        <v>6</v>
-      </c>
-      <c r="BA22">
-        <v>7</v>
-      </c>
-      <c r="BB22">
-        <v>17.5</v>
-      </c>
-      <c r="BC22">
-        <v>18.5</v>
-      </c>
-      <c r="BD22">
-        <v>6.6</v>
-      </c>
-      <c r="BE22">
-        <v>7.2</v>
-      </c>
-      <c r="BF22">
-        <v>12.5</v>
-      </c>
-      <c r="BG22">
-        <v>7</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.95</v>
-      </c>
-      <c r="BJ22">
-        <v>14.5</v>
-      </c>
-      <c r="BK22">
-        <v>3.35</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.86</v>
-      </c>
-      <c r="BN22">
-        <v>5.9</v>
-      </c>
-      <c r="BO22">
-        <v>1.42</v>
-      </c>
-      <c r="BP22">
-        <v>18.5</v>
-      </c>
-      <c r="BQ22">
-        <v>1.69</v>
-      </c>
-      <c r="BR22">
-        <v>40</v>
-      </c>
-      <c r="BS22">
-        <v>1.78</v>
-      </c>
-      <c r="BT22">
-        <v>11</v>
-      </c>
-      <c r="BU22">
-        <v>5.4</v>
-      </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BZ22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="CB22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>94</v>
@@ -6187,411 +6193,411 @@
         <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F23">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="G23">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P23">
-        <v>1.07</v>
+        <v>1.82</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R23">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="S23">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP23">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR23">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU23">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW23">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AX23">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB23">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="CB23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F24">
-        <v>2.66</v>
+        <v>1.13</v>
       </c>
       <c r="G24">
-        <v>2.84</v>
+        <v>110</v>
       </c>
       <c r="H24">
-        <v>2.9</v>
+        <v>1.12</v>
       </c>
       <c r="I24">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="J24">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="K24">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>3.1</v>
+        <v>1.07</v>
       </c>
       <c r="O24">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.63</v>
+        <v>1.07</v>
       </c>
       <c r="Q24">
-        <v>2.16</v>
+        <v>1.29</v>
       </c>
       <c r="R24">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S24">
-        <v>3.9</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="W24">
-        <v>1.54</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>1.99</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>1.99</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6654,362 +6660,362 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
         <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F25">
-        <v>1.74</v>
+        <v>2.66</v>
       </c>
       <c r="G25">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="H25">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J25">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K25">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N25">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="O25">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="P25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q25">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="R25">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S25">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V25">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="W25">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA25">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F26">
-        <v>3.45</v>
+        <v>1.8</v>
       </c>
       <c r="G26">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="H26">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="I26">
-        <v>2.58</v>
+        <v>5.8</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K26">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L26">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O26">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="P26">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="Q26">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="R26">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S26">
-        <v>5.7</v>
+        <v>2.86</v>
       </c>
       <c r="T26">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="U26">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="V26">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="W26">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="X26">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
         <v>1000</v>
@@ -7018,132 +7024,132 @@
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS26">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW26">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY26">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA26">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BD26">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE26">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BF26">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>94</v>
@@ -7155,103 +7161,103 @@
         <v>135</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F27">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="G27">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="H27">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="I27">
-        <v>4.9</v>
+        <v>2.56</v>
       </c>
       <c r="J27">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="K27">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M27">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N27">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="O27">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="P27">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Q27">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="R27">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S27">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="U27">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V27">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="W27">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y27">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z27">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB27">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC27">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD27">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG27">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ27">
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL27">
         <v>1000</v>
@@ -7260,201 +7266,201 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>48</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
         <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F28">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="G28">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="H28">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="I28">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J28">
+        <v>2.7</v>
+      </c>
+      <c r="K28">
         <v>3.25</v>
       </c>
-      <c r="K28">
-        <v>4.3</v>
-      </c>
       <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.08</v>
+      </c>
+      <c r="N28">
+        <v>2.24</v>
+      </c>
+      <c r="O28">
         <v>1.5</v>
       </c>
-      <c r="M28">
-        <v>1.1</v>
-      </c>
-      <c r="N28">
-        <v>2.84</v>
-      </c>
-      <c r="O28">
-        <v>1.44</v>
-      </c>
       <c r="P28">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R28">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S28">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="T28">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="U28">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="V28">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="X28">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
         <v>1000</v>
@@ -7466,10 +7472,10 @@
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
         <v>1000</v>
@@ -7478,10 +7484,10 @@
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
         <v>1000</v>
@@ -7508,64 +7514,64 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AR28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AS28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AT28">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AW28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="AX28">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY28">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BA28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BB28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BC28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BD28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BE28">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="BF28">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
@@ -7583,7 +7589,7 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
         <v>1000</v>
@@ -7601,7 +7607,7 @@
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7622,12 +7628,12 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
         <v>94</v>
@@ -7639,232 +7645,474 @@
         <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F29">
-        <v>3.75</v>
+        <v>1.76</v>
       </c>
       <c r="G29">
-        <v>4.7</v>
+        <v>1.86</v>
       </c>
       <c r="H29">
-        <v>1.99</v>
+        <v>5.3</v>
       </c>
       <c r="I29">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="J29">
         <v>3.3</v>
       </c>
       <c r="K29">
+        <v>3.75</v>
+      </c>
+      <c r="L29">
+        <v>1.5</v>
+      </c>
+      <c r="M29">
+        <v>1.1</v>
+      </c>
+      <c r="N29">
+        <v>2.86</v>
+      </c>
+      <c r="O29">
+        <v>1.42</v>
+      </c>
+      <c r="P29">
+        <v>1.61</v>
+      </c>
+      <c r="Q29">
+        <v>2.28</v>
+      </c>
+      <c r="R29">
+        <v>1.21</v>
+      </c>
+      <c r="S29">
+        <v>4.2</v>
+      </c>
+      <c r="T29">
+        <v>2.1</v>
+      </c>
+      <c r="U29">
+        <v>1.73</v>
+      </c>
+      <c r="V29">
+        <v>1.19</v>
+      </c>
+      <c r="W29">
+        <v>2.14</v>
+      </c>
+      <c r="X29">
+        <v>970</v>
+      </c>
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>970</v>
+      </c>
+      <c r="AC29">
+        <v>970</v>
+      </c>
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>970</v>
+      </c>
+      <c r="AG29">
+        <v>970</v>
+      </c>
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>7.2</v>
+      </c>
+      <c r="AQ29">
+        <v>1.69</v>
+      </c>
+      <c r="AR29">
+        <v>1.59</v>
+      </c>
+      <c r="AS29">
+        <v>1.59</v>
+      </c>
+      <c r="AT29">
+        <v>5.2</v>
+      </c>
+      <c r="AU29">
+        <v>6.2</v>
+      </c>
+      <c r="AV29">
+        <v>1.59</v>
+      </c>
+      <c r="AW29">
+        <v>1.59</v>
+      </c>
+      <c r="AX29">
+        <v>6.8</v>
+      </c>
+      <c r="AY29">
+        <v>7.6</v>
+      </c>
+      <c r="AZ29">
+        <v>1.59</v>
+      </c>
+      <c r="BA29">
+        <v>1.59</v>
+      </c>
+      <c r="BB29">
+        <v>1.69</v>
+      </c>
+      <c r="BC29">
+        <v>1.59</v>
+      </c>
+      <c r="BD29">
+        <v>1.59</v>
+      </c>
+      <c r="BE29">
+        <v>1.59</v>
+      </c>
+      <c r="BF29">
+        <v>1.69</v>
+      </c>
+      <c r="BG29">
+        <v>1.59</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.27</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.01</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.01</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.5</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.01</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.01</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>2.18</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.01</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.01</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>4.5</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>2.18</v>
+      </c>
+      <c r="J30">
+        <v>3.3</v>
+      </c>
+      <c r="K30">
         <v>3.65</v>
       </c>
-      <c r="L29">
-        <v>1.01</v>
-      </c>
-      <c r="M29">
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
         <v>1.09</v>
       </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29">
+      <c r="N30">
+        <v>3.15</v>
+      </c>
+      <c r="O30">
         <v>1.39</v>
       </c>
-      <c r="P29">
-        <v>1.65</v>
-      </c>
-      <c r="Q29">
-        <v>2.1</v>
-      </c>
-      <c r="R29">
-        <v>1.22</v>
-      </c>
-      <c r="S29">
-        <v>3.6</v>
-      </c>
-      <c r="T29">
-        <v>1.9</v>
-      </c>
-      <c r="U29">
-        <v>1.84</v>
-      </c>
-      <c r="V29">
-        <v>1.84</v>
-      </c>
-      <c r="W29">
-        <v>1.27</v>
-      </c>
-      <c r="X29">
-        <v>46</v>
-      </c>
-      <c r="Y29">
-        <v>34</v>
-      </c>
-      <c r="Z29">
+      <c r="P30">
+        <v>1.74</v>
+      </c>
+      <c r="Q30">
+        <v>2.16</v>
+      </c>
+      <c r="R30">
+        <v>1.28</v>
+      </c>
+      <c r="S30">
+        <v>4</v>
+      </c>
+      <c r="T30">
+        <v>1.91</v>
+      </c>
+      <c r="U30">
+        <v>1.94</v>
+      </c>
+      <c r="V30">
+        <v>1.85</v>
+      </c>
+      <c r="W30">
+        <v>1.28</v>
+      </c>
+      <c r="X30">
+        <v>12</v>
+      </c>
+      <c r="Y30">
+        <v>8.4</v>
+      </c>
+      <c r="Z30">
+        <v>13</v>
+      </c>
+      <c r="AA30">
+        <v>27</v>
+      </c>
+      <c r="AB30">
+        <v>14</v>
+      </c>
+      <c r="AC30">
+        <v>8</v>
+      </c>
+      <c r="AD30">
+        <v>11</v>
+      </c>
+      <c r="AE30">
+        <v>25</v>
+      </c>
+      <c r="AF30">
+        <v>32</v>
+      </c>
+      <c r="AG30">
+        <v>18</v>
+      </c>
+      <c r="AH30">
+        <v>21</v>
+      </c>
+      <c r="AI30">
+        <v>55</v>
+      </c>
+      <c r="AJ30">
+        <v>120</v>
+      </c>
+      <c r="AK30">
+        <v>75</v>
+      </c>
+      <c r="AL30">
+        <v>85</v>
+      </c>
+      <c r="AM30">
+        <v>990</v>
+      </c>
+      <c r="AN30">
+        <v>95</v>
+      </c>
+      <c r="AO30">
+        <v>20</v>
+      </c>
+      <c r="AP30">
+        <v>10</v>
+      </c>
+      <c r="AQ30">
+        <v>7</v>
+      </c>
+      <c r="AR30">
+        <v>10.5</v>
+      </c>
+      <c r="AS30">
+        <v>18.5</v>
+      </c>
+      <c r="AT30">
+        <v>11.5</v>
+      </c>
+      <c r="AU30">
+        <v>6.8</v>
+      </c>
+      <c r="AV30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW30">
+        <v>21</v>
+      </c>
+      <c r="AX30">
+        <v>22</v>
+      </c>
+      <c r="AY30">
         <v>15</v>
       </c>
-      <c r="AA29">
-        <v>960</v>
-      </c>
-      <c r="AB29">
-        <v>70</v>
-      </c>
-      <c r="AC29">
+      <c r="AZ30">
+        <v>17</v>
+      </c>
+      <c r="BA30">
+        <v>30</v>
+      </c>
+      <c r="BB30">
         <v>9</v>
       </c>
-      <c r="AD29">
-        <v>48</v>
-      </c>
-      <c r="AE29">
-        <v>960</v>
-      </c>
-      <c r="AF29">
-        <v>44</v>
-      </c>
-      <c r="AG29">
-        <v>25</v>
-      </c>
-      <c r="AH29">
-        <v>29</v>
-      </c>
-      <c r="AI29">
-        <v>960</v>
-      </c>
-      <c r="AJ29">
-        <v>1000</v>
-      </c>
-      <c r="AK29">
-        <v>970</v>
-      </c>
-      <c r="AL29">
-        <v>960</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>960</v>
-      </c>
-      <c r="AO29">
-        <v>28</v>
-      </c>
-      <c r="AP29">
-        <v>2.4</v>
-      </c>
-      <c r="AQ29">
-        <v>7</v>
-      </c>
-      <c r="AR29">
+      <c r="BC30">
+        <v>9.4</v>
+      </c>
+      <c r="BD30">
+        <v>9.6</v>
+      </c>
+      <c r="BE30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG30">
+        <v>16.5</v>
+      </c>
+      <c r="BH30">
+        <v>3.75</v>
+      </c>
+      <c r="BI30">
         <v>2.48</v>
       </c>
-      <c r="AS29">
-        <v>18.5</v>
-      </c>
-      <c r="AT29">
-        <v>7</v>
-      </c>
-      <c r="AU29">
-        <v>2.26</v>
-      </c>
-      <c r="AV29">
-        <v>7.4</v>
-      </c>
-      <c r="AW29">
-        <v>17.5</v>
-      </c>
-      <c r="AX29">
-        <v>4.6</v>
-      </c>
-      <c r="AY29">
-        <v>12.5</v>
-      </c>
-      <c r="AZ29">
-        <v>14.5</v>
-      </c>
-      <c r="BA29">
-        <v>2.88</v>
-      </c>
-      <c r="BB29">
-        <v>6.6</v>
-      </c>
-      <c r="BC29">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD29">
-        <v>2.92</v>
-      </c>
-      <c r="BE29">
-        <v>3</v>
-      </c>
-      <c r="BF29">
-        <v>2.92</v>
-      </c>
-      <c r="BG29">
-        <v>11</v>
-      </c>
-      <c r="BH29">
-        <v>3.75</v>
-      </c>
-      <c r="BI29">
-        <v>2.48</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.37</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>1.37</v>
-      </c>
-      <c r="BN29">
-        <v>1000</v>
-      </c>
-      <c r="BO29">
-        <v>1.37</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>1.37</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>1.37</v>
-      </c>
-      <c r="BT29">
-        <v>1000</v>
-      </c>
-      <c r="BU29">
-        <v>1.37</v>
-      </c>
-      <c r="BV29">
-        <v>1000</v>
-      </c>
-      <c r="BW29">
-        <v>1.37</v>
-      </c>
-      <c r="BX29">
-        <v>1000</v>
-      </c>
-      <c r="BY29">
-        <v>1.37</v>
-      </c>
-      <c r="BZ29">
-        <v>1000</v>
-      </c>
-      <c r="CA29">
-        <v>1.37</v>
-      </c>
-      <c r="CB29" t="s">
-        <v>166</v>
+      <c r="BJ30">
+        <v>1000</v>
+      </c>
+      <c r="BK30">
+        <v>1.75</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>1.75</v>
+      </c>
+      <c r="BN30">
+        <v>1000</v>
+      </c>
+      <c r="BO30">
+        <v>1.75</v>
+      </c>
+      <c r="BP30">
+        <v>1000</v>
+      </c>
+      <c r="BQ30">
+        <v>1.75</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>1.75</v>
+      </c>
+      <c r="BT30">
+        <v>1000</v>
+      </c>
+      <c r="BU30">
+        <v>1.45</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>1.75</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>1.75</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>1.75</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -520,7 +520,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 14:26:14</t>
+    <t>2026-09-20 16:39:31</t>
   </si>
 </sst>
 </file>
@@ -1114,10 +1114,10 @@
         <v>139</v>
       </c>
       <c r="F2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H2">
         <v>11</v>
@@ -1126,7 +1126,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -1147,25 +1147,25 @@
         <v>3.45</v>
       </c>
       <c r="Q2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S2">
         <v>1.97</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
         <v>1.09</v>
       </c>
       <c r="W2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X2">
         <v>46</v>
@@ -1201,13 +1201,13 @@
         <v>28</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
         <v>11.5</v>
       </c>
       <c r="AK2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL2">
         <v>28</v>
@@ -1219,19 +1219,19 @@
         <v>3.45</v>
       </c>
       <c r="AO2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP2">
         <v>36</v>
       </c>
       <c r="AQ2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT2">
         <v>13.5</v>
@@ -1240,13 +1240,13 @@
         <v>16.5</v>
       </c>
       <c r="AV2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
@@ -1276,64 +1276,64 @@
         <v>75</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI2">
-        <v>1.12</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM2">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BQ2">
-        <v>1.27</v>
+        <v>5.9</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS2">
-        <v>1.12</v>
+        <v>7</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU2">
-        <v>1.12</v>
+        <v>6.6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW2">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>1.12</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="CA2">
-        <v>1.12</v>
+        <v>4.9</v>
       </c>
       <c r="CB2" t="s">
         <v>168</v>
@@ -1365,16 +1365,16 @@
         <v>5.1</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1386,7 +1386,7 @@
         <v>1.32</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3">
         <v>1.97</v>
@@ -1398,10 +1398,10 @@
         <v>3.45</v>
       </c>
       <c r="T3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
         <v>1.23</v>
@@ -1413,7 +1413,7 @@
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>40</v>
@@ -1458,7 +1458,7 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
         <v>85</v>
@@ -1476,7 +1476,7 @@
         <v>80</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>8.4</v>
@@ -1488,13 +1488,13 @@
         <v>60</v>
       </c>
       <c r="AX3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
         <v>60</v>
@@ -1506,7 +1506,7 @@
         <v>17</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE3">
         <v>90</v>
@@ -1518,64 +1518,64 @@
         <v>60</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI3">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>2.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.36</v>
+        <v>16</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS3">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU3">
-        <v>1.99</v>
+        <v>7.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW3">
-        <v>2.36</v>
+        <v>13</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>2.36</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>168</v>
@@ -1601,13 +1601,13 @@
         <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
         <v>3.95</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1619,16 +1619,16 @@
         <v>1.69</v>
       </c>
       <c r="M4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
         <v>3.05</v>
@@ -1640,16 +1640,16 @@
         <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1658,10 +1658,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
@@ -1673,13 +1673,13 @@
         <v>18.5</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AF4">
+        <v>13</v>
+      </c>
+      <c r="AG4">
         <v>12.5</v>
-      </c>
-      <c r="AG4">
-        <v>13</v>
       </c>
       <c r="AH4">
         <v>27</v>
@@ -1688,7 +1688,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK4">
         <v>42</v>
@@ -1700,19 +1700,19 @@
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4">
         <v>8.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AS4">
         <v>36</v>
@@ -1727,7 +1727,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
@@ -1742,25 +1742,25 @@
         <v>40</v>
       </c>
       <c r="BB4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE4">
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BG4">
         <v>40</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI4">
         <v>2.18</v>
@@ -1840,13 +1840,13 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G5">
         <v>4.9</v>
       </c>
       <c r="H5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I5">
         <v>1.91</v>
@@ -1855,10 +1855,10 @@
         <v>3.7</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1870,7 +1870,7 @@
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1882,7 +1882,7 @@
         <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
         <v>2</v>
@@ -1903,7 +1903,7 @@
         <v>13</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB5">
         <v>18</v>
@@ -1912,13 +1912,13 @@
         <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG5">
         <v>20</v>
@@ -1933,16 +1933,16 @@
         <v>140</v>
       </c>
       <c r="AK5">
+        <v>80</v>
+      </c>
+      <c r="AL5">
         <v>85</v>
       </c>
-      <c r="AL5">
-        <v>90</v>
-      </c>
       <c r="AM5">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO5">
         <v>15</v>
@@ -1963,7 +1963,7 @@
         <v>13.5</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>9</v>
@@ -1993,10 +1993,10 @@
         <v>46</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BG5">
         <v>12.5</v>
@@ -2082,175 +2082,175 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="I6">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
         <v>1.75</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.07</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="W6">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>15.5</v>
       </c>
       <c r="AB6">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
+        <v>17.5</v>
+      </c>
+      <c r="AF6">
+        <v>65</v>
+      </c>
+      <c r="AG6">
+        <v>28</v>
+      </c>
+      <c r="AH6">
+        <v>24</v>
+      </c>
+      <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
+        <v>240</v>
+      </c>
+      <c r="AK6">
+        <v>260</v>
+      </c>
+      <c r="AL6">
+        <v>110</v>
+      </c>
+      <c r="AM6">
+        <v>790</v>
+      </c>
+      <c r="AN6">
         <v>150</v>
       </c>
-      <c r="AF6">
-        <v>210</v>
-      </c>
-      <c r="AG6">
-        <v>160</v>
-      </c>
-      <c r="AH6">
-        <v>130</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
       <c r="AO6">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="AP6">
-        <v>1.15</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6">
-        <v>1.15</v>
+        <v>4.3</v>
       </c>
       <c r="AR6">
-        <v>1.12</v>
+        <v>4.4</v>
       </c>
       <c r="AS6">
         <v>6.2</v>
       </c>
       <c r="AT6">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="AU6">
-        <v>1.15</v>
+        <v>4.6</v>
       </c>
       <c r="AV6">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="AW6">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="AX6">
-        <v>1.15</v>
+        <v>7</v>
       </c>
       <c r="AY6">
-        <v>1.15</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="BA6">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="BB6">
-        <v>1.15</v>
+        <v>7.8</v>
       </c>
       <c r="BC6">
-        <v>1.15</v>
+        <v>7.4</v>
       </c>
       <c r="BD6">
-        <v>1.15</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>1.15</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="BG6">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI6">
         <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
@@ -2262,13 +2262,13 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO6">
         <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
@@ -2280,25 +2280,25 @@
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU6">
         <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2324,22 +2324,22 @@
         <v>144</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G7">
+        <v>2.84</v>
+      </c>
+      <c r="H7">
+        <v>2.7</v>
+      </c>
+      <c r="I7">
         <v>2.76</v>
       </c>
-      <c r="H7">
-        <v>2.72</v>
-      </c>
-      <c r="I7">
-        <v>2.8</v>
-      </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.38</v>
@@ -2366,25 +2366,25 @@
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W7">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA7">
         <v>40</v>
@@ -2399,10 +2399,10 @@
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
@@ -2414,22 +2414,22 @@
         <v>38</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL7">
         <v>38</v>
       </c>
       <c r="AM7">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -2444,7 +2444,7 @@
         <v>34</v>
       </c>
       <c r="AT7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU7">
         <v>7.4</v>
@@ -2453,7 +2453,7 @@
         <v>11</v>
       </c>
       <c r="AW7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX7">
         <v>17</v>
@@ -2465,85 +2465,85 @@
         <v>14</v>
       </c>
       <c r="BA7">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BB7">
+        <v>34</v>
+      </c>
+      <c r="BC7">
+        <v>22</v>
+      </c>
+      <c r="BD7">
+        <v>32</v>
+      </c>
+      <c r="BE7">
+        <v>12.5</v>
+      </c>
+      <c r="BF7">
+        <v>19</v>
+      </c>
+      <c r="BG7">
+        <v>18.5</v>
+      </c>
+      <c r="BH7">
+        <v>3.65</v>
+      </c>
+      <c r="BI7">
+        <v>3.4</v>
+      </c>
+      <c r="BJ7">
+        <v>9</v>
+      </c>
+      <c r="BK7">
+        <v>8</v>
+      </c>
+      <c r="BL7">
+        <v>100</v>
+      </c>
+      <c r="BM7">
+        <v>65</v>
+      </c>
+      <c r="BN7">
+        <v>6</v>
+      </c>
+      <c r="BO7">
+        <v>5.3</v>
+      </c>
+      <c r="BP7">
+        <v>21</v>
+      </c>
+      <c r="BQ7">
+        <v>17</v>
+      </c>
+      <c r="BR7">
+        <v>32</v>
+      </c>
+      <c r="BS7">
+        <v>19</v>
+      </c>
+      <c r="BT7">
+        <v>5.8</v>
+      </c>
+      <c r="BU7">
+        <v>5.2</v>
+      </c>
+      <c r="BV7">
+        <v>19</v>
+      </c>
+      <c r="BW7">
+        <v>16</v>
+      </c>
+      <c r="BX7">
         <v>30</v>
       </c>
-      <c r="BC7">
-        <v>7</v>
-      </c>
-      <c r="BD7">
-        <v>5.5</v>
-      </c>
-      <c r="BE7">
-        <v>5.9</v>
-      </c>
-      <c r="BF7">
-        <v>6.4</v>
-      </c>
-      <c r="BG7">
-        <v>18</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>3.1</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>6.4</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.01</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>4.5</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>11.5</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.01</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>4.8</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>11.5</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB7" t="s">
         <v>168</v>
@@ -2566,19 +2566,19 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G8">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="H8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2605,7 +2605,7 @@
         <v>1.07</v>
       </c>
       <c r="S8">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2614,10 +2614,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2808,19 +2808,19 @@
         <v>146</v>
       </c>
       <c r="F9">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G9">
         <v>110</v>
       </c>
       <c r="H9">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2832,22 +2832,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="O9">
         <v>1.16</v>
       </c>
       <c r="P9">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="Q9">
         <v>1.15</v>
       </c>
       <c r="R9">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="S9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2856,10 +2856,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3050,175 +3050,175 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="H10">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="K10">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
         <v>4.7</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q10">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="U10">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK10">
         <v>1.01</v>
@@ -3230,43 +3230,43 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU10">
         <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA10">
         <v>1.01</v>
@@ -3292,10 +3292,10 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G11">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
         <v>3.3</v>
@@ -3307,10 +3307,10 @@
         <v>3.2</v>
       </c>
       <c r="K11">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3319,19 +3319,19 @@
         <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q11">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
         <v>1.3</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
         <v>1.86</v>
@@ -3463,13 +3463,13 @@
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BN11">
         <v>1000</v>
@@ -3481,37 +3481,37 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="CB11" t="s">
         <v>168</v>
@@ -3534,19 +3534,19 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G12">
         <v>110</v>
       </c>
       <c r="H12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I12">
-        <v>950</v>
+        <v>830</v>
       </c>
       <c r="J12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3558,13 +3558,13 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q12">
         <v>1.39</v>
@@ -3582,10 +3582,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3776,19 +3776,19 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G13">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I13">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3800,16 +3800,16 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O13">
         <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R13">
         <v>1.08</v>
@@ -3824,10 +3824,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4030,7 +4030,7 @@
         <v>1000</v>
       </c>
       <c r="J14">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4042,22 +4042,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
         <v>1.17</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q14">
         <v>1.17</v>
       </c>
       <c r="R14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4066,10 +4066,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4260,19 +4260,19 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G15">
-        <v>950</v>
+        <v>220</v>
       </c>
       <c r="H15">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I15">
-        <v>950</v>
+        <v>740</v>
       </c>
       <c r="J15">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4284,13 +4284,13 @@
         <v>1.01</v>
       </c>
       <c r="N15">
+        <v>1.1</v>
+      </c>
+      <c r="O15">
         <v>1.02</v>
       </c>
-      <c r="O15">
-        <v>1.01</v>
-      </c>
       <c r="P15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q15">
         <v>1.45</v>
@@ -4308,10 +4308,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4532,7 +4532,7 @@
         <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q16">
         <v>1.57</v>
@@ -4610,58 +4610,58 @@
         <v>24</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH16">
         <v>4.8</v>
@@ -4744,19 +4744,19 @@
         <v>154</v>
       </c>
       <c r="F17">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G17">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="H17">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I17">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="J17">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4792,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4989,7 +4989,7 @@
         <v>1.57</v>
       </c>
       <c r="G18">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -5001,7 +5001,7 @@
         <v>3.85</v>
       </c>
       <c r="K18">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="L18">
         <v>1.31</v>
@@ -5013,7 +5013,7 @@
         <v>3.15</v>
       </c>
       <c r="O18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P18">
         <v>1.92</v>
@@ -5037,7 +5037,7 @@
         <v>1.12</v>
       </c>
       <c r="W18">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5228,13 +5228,13 @@
         <v>156</v>
       </c>
       <c r="F19">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G19">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H19">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>3.3</v>
@@ -5243,7 +5243,7 @@
         <v>3.7</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5267,7 +5267,7 @@
         <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="T19">
         <v>1.57</v>
@@ -5276,10 +5276,10 @@
         <v>2.28</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5470,19 +5470,19 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G20">
         <v>110</v>
       </c>
       <c r="H20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I20">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="J20">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5494,13 +5494,13 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
         <v>1.01</v>
       </c>
       <c r="P20">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
         <v>1.31</v>
@@ -5509,7 +5509,7 @@
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -5518,10 +5518,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5712,226 +5712,226 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G21">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="H21">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="I21">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L21">
         <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N21">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>1.22</v>
       </c>
       <c r="P21">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R21">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S21">
         <v>2.52</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="V21">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="W21">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BH21">
         <v>4.7</v>
       </c>
       <c r="BI21">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BJ21">
         <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BL21">
         <v>120</v>
       </c>
       <c r="BM21">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BN21">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO21">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BP21">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BQ21">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR21">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS21">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BT21">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU21">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="BV21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW21">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BX21">
         <v>28</v>
       </c>
       <c r="BY21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BZ21">
         <v>21</v>
       </c>
       <c r="CA21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="CB21" t="s">
         <v>168</v>
@@ -5957,49 +5957,49 @@
         <v>3.3</v>
       </c>
       <c r="G22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H22">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I22">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J22">
         <v>2.94</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L22">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M22">
         <v>1.14</v>
       </c>
       <c r="N22">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P22">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q22">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R22">
         <v>1.17</v>
       </c>
       <c r="S22">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T22">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U22">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V22">
         <v>1.58</v>
@@ -6008,25 +6008,25 @@
         <v>1.39</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y22">
         <v>7.6</v>
       </c>
       <c r="Z22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA22">
         <v>55</v>
       </c>
       <c r="AB22">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>7.2</v>
       </c>
       <c r="AD22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE22">
         <v>50</v>
@@ -6035,10 +6035,10 @@
         <v>21</v>
       </c>
       <c r="AG22">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22">
         <v>90</v>
@@ -6086,94 +6086,94 @@
         <v>34</v>
       </c>
       <c r="AX22">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY22">
         <v>14</v>
       </c>
       <c r="AZ22">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BA22">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB22">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC22">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BD22">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE22">
+        <v>10.5</v>
+      </c>
+      <c r="BF22">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BF22">
-        <v>9.199999999999999</v>
       </c>
       <c r="BG22">
         <v>27</v>
       </c>
       <c r="BH22">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="BI22">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK22">
-        <v>2.96</v>
+        <v>8</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>2.02</v>
+        <v>10.5</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO22">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ22">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS22">
-        <v>2.02</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU22">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW22">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY22">
-        <v>2.02</v>
+        <v>9.6</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA22">
-        <v>2.02</v>
+        <v>9.4</v>
       </c>
       <c r="CB22" t="s">
         <v>168</v>
@@ -6196,10 +6196,10 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G23">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="H23">
         <v>4.8</v>
@@ -6211,7 +6211,7 @@
         <v>3.55</v>
       </c>
       <c r="K23">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L23">
         <v>1.4</v>
@@ -6220,22 +6220,22 @@
         <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O23">
         <v>1.37</v>
       </c>
       <c r="P23">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q23">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
         <v>1.31</v>
       </c>
       <c r="S23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T23">
         <v>1.93</v>
@@ -6247,7 +6247,7 @@
         <v>1.23</v>
       </c>
       <c r="W23">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X23">
         <v>15</v>
@@ -6286,13 +6286,13 @@
         <v>85</v>
       </c>
       <c r="AJ23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK23">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL23">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM23">
         <v>150</v>
@@ -6313,7 +6313,7 @@
         <v>6.8</v>
       </c>
       <c r="AS23">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT23">
         <v>7.2</v>
@@ -6322,10 +6322,10 @@
         <v>7.4</v>
       </c>
       <c r="AV23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW23">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX23">
         <v>9.800000000000001</v>
@@ -6337,7 +6337,7 @@
         <v>6</v>
       </c>
       <c r="BA23">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB23">
         <v>17.5</v>
@@ -6346,22 +6346,22 @@
         <v>18.5</v>
       </c>
       <c r="BD23">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE23">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF23">
         <v>12.5</v>
       </c>
       <c r="BG23">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BJ23">
         <v>14.5</v>
@@ -6438,10 +6438,10 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G24">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="H24">
         <v>1.12</v>
@@ -6450,7 +6450,7 @@
         <v>110</v>
       </c>
       <c r="J24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6462,22 +6462,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Q24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6486,10 +6486,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6683,7 +6683,7 @@
         <v>2.66</v>
       </c>
       <c r="G25">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H25">
         <v>2.92</v>
@@ -6695,13 +6695,13 @@
         <v>3.15</v>
       </c>
       <c r="K25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L25">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25">
         <v>3.1</v>
@@ -6710,22 +6710,22 @@
         <v>1.42</v>
       </c>
       <c r="P25">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
         <v>1.26</v>
       </c>
       <c r="S25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T25">
         <v>1.88</v>
       </c>
       <c r="U25">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V25">
         <v>1.47</v>
@@ -6740,7 +6740,7 @@
         <v>10.5</v>
       </c>
       <c r="Z25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA25">
         <v>90</v>
@@ -6779,7 +6779,7 @@
         <v>60</v>
       </c>
       <c r="AM25">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AN25">
         <v>40</v>
@@ -6797,7 +6797,7 @@
         <v>16.5</v>
       </c>
       <c r="AS25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT25">
         <v>8.4</v>
@@ -6809,7 +6809,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX25">
         <v>14.5</v>
@@ -6830,10 +6830,10 @@
         <v>7.6</v>
       </c>
       <c r="BD25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF25">
         <v>7.6</v>
@@ -6863,7 +6863,7 @@
         <v>5.8</v>
       </c>
       <c r="BO25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP25">
         <v>23</v>
@@ -6881,7 +6881,7 @@
         <v>6.2</v>
       </c>
       <c r="BU25">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV25">
         <v>27</v>
@@ -6922,166 +6922,166 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G26">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H26">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="I26">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K26">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O26">
         <v>1.35</v>
       </c>
       <c r="P26">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Q26">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S26">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="T26">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="U26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W26">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP26">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS26">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW26">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA26">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE26">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7164,16 +7164,16 @@
         <v>164</v>
       </c>
       <c r="F27">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G27">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H27">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I27">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -7188,7 +7188,7 @@
         <v>1.13</v>
       </c>
       <c r="N27">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O27">
         <v>1.57</v>
@@ -7197,7 +7197,7 @@
         <v>1.54</v>
       </c>
       <c r="Q27">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R27">
         <v>1.19</v>
@@ -7212,7 +7212,7 @@
         <v>1.79</v>
       </c>
       <c r="V27">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W27">
         <v>1.37</v>
@@ -7233,7 +7233,7 @@
         <v>9.6</v>
       </c>
       <c r="AC27">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD27">
         <v>13</v>
@@ -7296,13 +7296,13 @@
         <v>22</v>
       </c>
       <c r="AX27">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY27">
         <v>14.5</v>
       </c>
       <c r="AZ27">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BA27">
         <v>34</v>
@@ -7326,22 +7326,22 @@
         <v>32</v>
       </c>
       <c r="BH27">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BI27">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BJ27">
         <v>12</v>
       </c>
       <c r="BK27">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BN27">
         <v>6.6</v>
@@ -7350,40 +7350,40 @@
         <v>5.8</v>
       </c>
       <c r="BP27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ27">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR27">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS27">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT27">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU27">
         <v>4.6</v>
       </c>
       <c r="BV27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW27">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX27">
         <v>48</v>
       </c>
       <c r="BY27">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ27">
         <v>55</v>
       </c>
       <c r="CA27">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CB27" t="s">
         <v>168</v>
@@ -7412,7 +7412,7 @@
         <v>2.62</v>
       </c>
       <c r="H28">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I28">
         <v>4.9</v>
@@ -7421,7 +7421,7 @@
         <v>2.7</v>
       </c>
       <c r="K28">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7430,28 +7430,28 @@
         <v>1.08</v>
       </c>
       <c r="N28">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="P28">
         <v>1.43</v>
       </c>
       <c r="Q28">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="R28">
         <v>1.13</v>
       </c>
       <c r="S28">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="T28">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U28">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V28">
         <v>1.33</v>
@@ -7648,226 +7648,226 @@
         <v>166</v>
       </c>
       <c r="F29">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G29">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I29">
         <v>6.4</v>
       </c>
       <c r="J29">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K29">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L29">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M29">
         <v>1.1</v>
       </c>
       <c r="N29">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O29">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P29">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q29">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R29">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S29">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T29">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U29">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V29">
         <v>1.19</v>
       </c>
       <c r="W29">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X29">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB29">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AC29">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF29">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AG29">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP29">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AQ29">
-        <v>1.69</v>
+        <v>13.5</v>
       </c>
       <c r="AR29">
-        <v>1.59</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29">
-        <v>1.59</v>
+        <v>10</v>
       </c>
       <c r="AT29">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AU29">
+        <v>7.4</v>
+      </c>
+      <c r="AV29">
+        <v>7.4</v>
+      </c>
+      <c r="AW29">
+        <v>9.6</v>
+      </c>
+      <c r="AX29">
+        <v>8.4</v>
+      </c>
+      <c r="AY29">
+        <v>9.4</v>
+      </c>
+      <c r="AZ29">
+        <v>21</v>
+      </c>
+      <c r="BA29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB29">
+        <v>17</v>
+      </c>
+      <c r="BC29">
+        <v>20</v>
+      </c>
+      <c r="BD29">
+        <v>9</v>
+      </c>
+      <c r="BE29">
+        <v>10</v>
+      </c>
+      <c r="BF29">
+        <v>14</v>
+      </c>
+      <c r="BG29">
+        <v>10</v>
+      </c>
+      <c r="BH29">
+        <v>2.92</v>
+      </c>
+      <c r="BI29">
+        <v>2.72</v>
+      </c>
+      <c r="BJ29">
+        <v>12.5</v>
+      </c>
+      <c r="BK29">
         <v>6.2</v>
       </c>
-      <c r="AV29">
-        <v>1.59</v>
-      </c>
-      <c r="AW29">
-        <v>1.59</v>
-      </c>
-      <c r="AX29">
-        <v>6.8</v>
-      </c>
-      <c r="AY29">
-        <v>7.6</v>
-      </c>
-      <c r="AZ29">
-        <v>1.59</v>
-      </c>
-      <c r="BA29">
-        <v>1.59</v>
-      </c>
-      <c r="BB29">
-        <v>1.69</v>
-      </c>
-      <c r="BC29">
-        <v>1.59</v>
-      </c>
-      <c r="BD29">
-        <v>1.59</v>
-      </c>
-      <c r="BE29">
-        <v>1.59</v>
-      </c>
-      <c r="BF29">
-        <v>1.69</v>
-      </c>
-      <c r="BG29">
-        <v>1.59</v>
-      </c>
-      <c r="BH29">
-        <v>1000</v>
-      </c>
-      <c r="BI29">
-        <v>1.27</v>
-      </c>
-      <c r="BJ29">
-        <v>1000</v>
-      </c>
-      <c r="BK29">
-        <v>1.01</v>
-      </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN29">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO29">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="BP29">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ29">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS29">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT29">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU29">
-        <v>2.18</v>
+        <v>5.6</v>
       </c>
       <c r="BV29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW29">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX29">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY29">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ29">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA29">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB29" t="s">
         <v>168</v>
@@ -7896,7 +7896,7 @@
         <v>4.5</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I30">
         <v>2.18</v>
@@ -7905,7 +7905,7 @@
         <v>3.3</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -7929,7 +7929,7 @@
         <v>1.28</v>
       </c>
       <c r="S30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T30">
         <v>1.91</v>
@@ -7941,7 +7941,7 @@
         <v>1.85</v>
       </c>
       <c r="W30">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X30">
         <v>12</v>
@@ -7950,7 +7950,7 @@
         <v>8.4</v>
       </c>
       <c r="Z30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA30">
         <v>27</v>
@@ -7989,10 +7989,10 @@
         <v>85</v>
       </c>
       <c r="AM30">
-        <v>990</v>
+        <v>880</v>
       </c>
       <c r="AN30">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO30">
         <v>20</v>
@@ -8034,7 +8034,7 @@
         <v>30</v>
       </c>
       <c r="BB30">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC30">
         <v>9.4</v>
@@ -8043,10 +8043,10 @@
         <v>9.6</v>
       </c>
       <c r="BE30">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF30">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG30">
         <v>16.5</v>
@@ -8055,61 +8055,61 @@
         <v>3.75</v>
       </c>
       <c r="BI30">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK30">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO30">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="BQ30">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="BT30">
         <v>1000</v>
       </c>
       <c r="BU30">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW30">
-        <v>1.75</v>
+        <v>2.94</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY30">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA30">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="CB30" t="s">
         <v>168</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -520,7 +520,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 16:39:31</t>
+    <t>2026-09-20 18:53:20</t>
   </si>
 </sst>
 </file>
@@ -1114,22 +1114,22 @@
         <v>139</v>
       </c>
       <c r="F2">
+        <v>1.24</v>
+      </c>
+      <c r="G2">
         <v>1.26</v>
       </c>
-      <c r="G2">
-        <v>1.28</v>
-      </c>
       <c r="H2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="L2">
         <v>1.21</v>
@@ -1138,67 +1138,67 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O2">
         <v>1.12</v>
       </c>
       <c r="P2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R2">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="T2">
         <v>1.82</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Y2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Z2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AA2">
-        <v>380</v>
+        <v>560</v>
       </c>
       <c r="AB2">
         <v>15</v>
       </c>
       <c r="AC2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AD2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AE2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF2">
         <v>11</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>110</v>
@@ -1207,43 +1207,43 @@
         <v>11.5</v>
       </c>
       <c r="AK2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL2">
         <v>28</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AR2">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="AS2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AT2">
         <v>13.5</v>
       </c>
       <c r="AU2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AV2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -1255,31 +1255,31 @@
         <v>24</v>
       </c>
       <c r="BA2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="BB2">
         <v>10</v>
       </c>
       <c r="BC2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BG2">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="BH2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI2">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
@@ -1288,52 +1288,52 @@
         <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
         <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BQ2">
         <v>5.9</v>
       </c>
       <c r="BR2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BT2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BV2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CA2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB2" t="s">
         <v>168</v>
@@ -1356,22 +1356,22 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.4</v>
@@ -1380,37 +1380,37 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T3">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.23</v>
       </c>
       <c r="W3">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y3">
         <v>18</v>
@@ -1419,16 +1419,16 @@
         <v>40</v>
       </c>
       <c r="AA3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE3">
         <v>70</v>
@@ -1437,13 +1437,13 @@
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH3">
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>19</v>
@@ -1461,19 +1461,19 @@
         <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AT3">
         <v>8</v>
@@ -1482,34 +1482,34 @@
         <v>8.4</v>
       </c>
       <c r="AV3">
+        <v>17</v>
+      </c>
+      <c r="AW3">
+        <v>55</v>
+      </c>
+      <c r="AX3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3">
+        <v>9</v>
+      </c>
+      <c r="AZ3">
         <v>18.5</v>
-      </c>
-      <c r="AW3">
-        <v>60</v>
-      </c>
-      <c r="AX3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3">
-        <v>19</v>
       </c>
       <c r="BA3">
         <v>60</v>
       </c>
       <c r="BB3">
+        <v>17.5</v>
+      </c>
+      <c r="BC3">
         <v>16.5</v>
       </c>
-      <c r="BC3">
-        <v>17</v>
-      </c>
       <c r="BD3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF3">
         <v>10</v>
@@ -1527,7 +1527,7 @@
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1545,13 +1545,13 @@
         <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>8.6</v>
@@ -1560,7 +1560,7 @@
         <v>7.8</v>
       </c>
       <c r="BV3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW3">
         <v>13</v>
@@ -1569,7 +1569,7 @@
         <v>55</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>22</v>
@@ -1598,37 +1598,37 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L4">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M4">
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O4">
         <v>1.66</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
         <v>3.05</v>
@@ -1640,28 +1640,28 @@
         <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U4">
         <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
         <v>26</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
@@ -1670,7 +1670,7 @@
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE4">
         <v>75</v>
@@ -1688,28 +1688,28 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AN4">
         <v>42</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR4">
         <v>23</v>
@@ -1727,7 +1727,7 @@
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
@@ -1736,88 +1736,88 @@
         <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BB4">
         <v>32</v>
       </c>
       <c r="BC4">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BE4">
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BH4">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="BI4">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>2.92</v>
+        <v>10.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU4">
-        <v>2.22</v>
+        <v>6.2</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="CB4" t="s">
         <v>168</v>
@@ -1840,19 +1840,19 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G5">
         <v>4.9</v>
       </c>
       <c r="H5">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I5">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
         <v>3.8</v>
@@ -1870,7 +1870,7 @@
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1882,52 +1882,52 @@
         <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W5">
         <v>1.25</v>
       </c>
       <c r="X5">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AG5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
         <v>140</v>
@@ -1942,22 +1942,22 @@
         <v>200</v>
       </c>
       <c r="AN5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO5">
         <v>15</v>
       </c>
       <c r="AP5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
         <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT5">
         <v>13.5</v>
@@ -1972,94 +1972,94 @@
         <v>17.5</v>
       </c>
       <c r="AX5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AY5">
         <v>16</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BC5">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BD5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="BF5">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BG5">
         <v>12.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="CB5" t="s">
         <v>168</v>
@@ -2082,16 +2082,16 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="I6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J6">
         <v>4.1</v>
@@ -2100,16 +2100,16 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
         <v>2.04</v>
@@ -2121,19 +2121,19 @@
         <v>1.4</v>
       </c>
       <c r="S6">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V6">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="W6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
         <v>21</v>
@@ -2175,13 +2175,13 @@
         <v>240</v>
       </c>
       <c r="AK6">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AL6">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM6">
-        <v>790</v>
+        <v>200</v>
       </c>
       <c r="AN6">
         <v>150</v>
@@ -2199,7 +2199,7 @@
         <v>4.4</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT6">
         <v>6</v>
@@ -2214,7 +2214,7 @@
         <v>5.5</v>
       </c>
       <c r="AX6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY6">
         <v>6.2</v>
@@ -2229,7 +2229,7 @@
         <v>7.8</v>
       </c>
       <c r="BC6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD6">
         <v>7.4</v>
@@ -2247,61 +2247,61 @@
         <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6">
         <v>11</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BP6">
         <v>65</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
         <v>4.3</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BV6">
         <v>10.5</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ6">
         <v>18</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="s">
         <v>168</v>
@@ -2324,10 +2324,10 @@
         <v>144</v>
       </c>
       <c r="F7">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G7">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H7">
         <v>2.7</v>
@@ -2339,7 +2339,7 @@
         <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L7">
         <v>1.38</v>
@@ -2354,28 +2354,28 @@
         <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q7">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R7">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S7">
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U7">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V7">
         <v>1.56</v>
       </c>
       <c r="W7">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X7">
         <v>17.5</v>
@@ -2426,7 +2426,7 @@
         <v>75</v>
       </c>
       <c r="AN7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7">
         <v>21</v>
@@ -2477,7 +2477,7 @@
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF7">
         <v>19</v>
@@ -2489,7 +2489,7 @@
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
         <v>9</v>
@@ -2501,25 +2501,25 @@
         <v>100</v>
       </c>
       <c r="BM7">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BN7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP7">
         <v>21</v>
       </c>
       <c r="BQ7">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>5.8</v>
@@ -2528,22 +2528,22 @@
         <v>5.2</v>
       </c>
       <c r="BV7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW7">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7">
         <v>30</v>
       </c>
       <c r="BY7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
         <v>23</v>
       </c>
       <c r="CA7">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>168</v>
@@ -2566,22 +2566,22 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>1.14</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
-        <v>830</v>
+        <v>2.74</v>
       </c>
       <c r="H8">
-        <v>1.14</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>2.34</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2593,7 +2593,7 @@
         <v>1.09</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>1.09</v>
@@ -2602,7 +2602,7 @@
         <v>1.36</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
         <v>1.37</v>
@@ -2614,118 +2614,118 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2808,19 +2808,19 @@
         <v>146</v>
       </c>
       <c r="F9">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>1.47</v>
       </c>
       <c r="H9">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="I9">
         <v>110</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>4.9</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2844,10 +2844,10 @@
         <v>1.15</v>
       </c>
       <c r="R9">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2856,10 +2856,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2910,64 +2910,64 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3053,7 +3053,7 @@
         <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H10">
         <v>5.6</v>
@@ -3065,7 +3065,7 @@
         <v>4.4</v>
       </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -3113,7 +3113,7 @@
         <v>65</v>
       </c>
       <c r="AA10">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3125,7 +3125,7 @@
         <v>28</v>
       </c>
       <c r="AE10">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF10">
         <v>13</v>
@@ -3137,7 +3137,7 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ10">
         <v>18</v>
@@ -3149,55 +3149,55 @@
         <v>38</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>8.6</v>
       </c>
       <c r="AO10">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AP10">
         <v>3.8</v>
       </c>
       <c r="AQ10">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS10">
         <v>4.3</v>
       </c>
       <c r="AT10">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AU10">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AV10">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AW10">
         <v>4.2</v>
       </c>
       <c r="AX10">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>15</v>
+        <v>3.75</v>
       </c>
       <c r="BA10">
         <v>4.2</v>
       </c>
       <c r="BB10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC10">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
         <v>4</v>
@@ -3206,7 +3206,7 @@
         <v>4.3</v>
       </c>
       <c r="BF10">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG10">
         <v>4.2</v>
@@ -3221,13 +3221,13 @@
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN10">
         <v>5</v>
@@ -3239,37 +3239,37 @@
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BR10">
         <v>27</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT10">
         <v>12</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV10">
         <v>60</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX10">
         <v>65</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ10">
         <v>18</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="CB10" t="s">
         <v>168</v>
@@ -3292,25 +3292,25 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G11">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I11">
         <v>3.55</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
         <v>3.3</v>
       </c>
       <c r="L11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3319,10 +3319,10 @@
         <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q11">
         <v>2.2</v>
@@ -3340,28 +3340,28 @@
         <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X11">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y11">
         <v>12</v>
       </c>
       <c r="Z11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB11">
         <v>11</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
         <v>17</v>
@@ -3379,7 +3379,7 @@
         <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ11">
         <v>42</v>
@@ -3391,7 +3391,7 @@
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AN11">
         <v>30</v>
@@ -3409,7 +3409,7 @@
         <v>20</v>
       </c>
       <c r="AS11">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT11">
         <v>8.199999999999999</v>
@@ -3421,7 +3421,7 @@
         <v>13</v>
       </c>
       <c r="AW11">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AX11">
         <v>13.5</v>
@@ -3433,85 +3433,85 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BB11">
+        <v>30</v>
+      </c>
+      <c r="BC11">
+        <v>14.5</v>
+      </c>
+      <c r="BD11">
+        <v>38</v>
+      </c>
+      <c r="BE11">
+        <v>7.8</v>
+      </c>
+      <c r="BF11">
+        <v>6.6</v>
+      </c>
+      <c r="BG11">
+        <v>7.8</v>
+      </c>
+      <c r="BH11">
+        <v>3.5</v>
+      </c>
+      <c r="BI11">
+        <v>2.6</v>
+      </c>
+      <c r="BJ11">
+        <v>11.5</v>
+      </c>
+      <c r="BK11">
+        <v>3.85</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>5.6</v>
+      </c>
+      <c r="BN11">
+        <v>6</v>
+      </c>
+      <c r="BO11">
+        <v>4.7</v>
+      </c>
+      <c r="BP11">
+        <v>23</v>
+      </c>
+      <c r="BQ11">
+        <v>4.6</v>
+      </c>
+      <c r="BR11">
+        <v>42</v>
+      </c>
+      <c r="BS11">
         <v>5.1</v>
       </c>
-      <c r="BC11">
+      <c r="BT11">
+        <v>7.2</v>
+      </c>
+      <c r="BU11">
         <v>5</v>
       </c>
-      <c r="BD11">
+      <c r="BV11">
+        <v>32</v>
+      </c>
+      <c r="BW11">
+        <v>4.9</v>
+      </c>
+      <c r="BX11">
+        <v>48</v>
+      </c>
+      <c r="BY11">
         <v>5.2</v>
       </c>
-      <c r="BE11">
-        <v>5.6</v>
-      </c>
-      <c r="BF11">
-        <v>4.8</v>
-      </c>
-      <c r="BG11">
-        <v>5.2</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.01</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.43</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.43</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.01</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.43</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.43</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.43</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.43</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.43</v>
-      </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11">
-        <v>1.43</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="s">
         <v>168</v>
@@ -3534,22 +3534,22 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="G12">
         <v>110</v>
       </c>
       <c r="H12">
-        <v>1.15</v>
+        <v>2.06</v>
       </c>
       <c r="I12">
-        <v>830</v>
+        <v>110</v>
       </c>
       <c r="J12">
-        <v>1.12</v>
+        <v>2.72</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3582,13 +3582,13 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y12">
         <v>1000</v>
@@ -3597,13 +3597,13 @@
         <v>1000</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12">
         <v>1000</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD12">
         <v>1000</v>
@@ -3624,7 +3624,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12">
         <v>1000</v>
@@ -3636,64 +3636,64 @@
         <v>1000</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3776,22 +3776,22 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>2.84</v>
       </c>
       <c r="H13">
-        <v>1.14</v>
+        <v>2.68</v>
       </c>
       <c r="I13">
-        <v>830</v>
+        <v>18.5</v>
       </c>
       <c r="J13">
-        <v>1.12</v>
+        <v>2.84</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3803,7 +3803,7 @@
         <v>1.1</v>
       </c>
       <c r="O13">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
         <v>1.1</v>
@@ -3824,10 +3824,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3845,7 +3845,7 @@
         <v>1000</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD13">
         <v>1000</v>
@@ -3866,7 +3866,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13">
         <v>1000</v>
@@ -3878,64 +3878,64 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU13">
         <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4021,16 +4021,16 @@
         <v>1.1</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H14">
         <v>1.1</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4066,10 +4066,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4126,52 +4126,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4260,16 +4260,16 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="G15">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="H15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I15">
-        <v>740</v>
+        <v>110</v>
       </c>
       <c r="J15">
         <v>1.12</v>
@@ -4308,10 +4308,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4368,52 +4368,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4502,31 +4502,31 @@
         <v>153</v>
       </c>
       <c r="F16">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G16">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H16">
         <v>2.7</v>
       </c>
       <c r="I16">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M16">
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O16">
         <v>1.21</v>
@@ -4535,31 +4535,31 @@
         <v>2.24</v>
       </c>
       <c r="Q16">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="R16">
         <v>1.5</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T16">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="U16">
         <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X16">
         <v>26</v>
       </c>
       <c r="Y16">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z16">
         <v>27</v>
@@ -4571,97 +4571,97 @@
         <v>17</v>
       </c>
       <c r="AC16">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16">
         <v>16</v>
       </c>
       <c r="AE16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF16">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG16">
         <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ16">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK16">
         <v>29</v>
       </c>
       <c r="AL16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM16">
         <v>75</v>
       </c>
       <c r="AN16">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO16">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AP16">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AQ16">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AR16">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AS16">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AT16">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AU16">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="AV16">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW16">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AX16">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AY16">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA16">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BB16">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BC16">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD16">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BE16">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF16">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG16">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH16">
         <v>4.8</v>
@@ -4685,7 +4685,7 @@
         <v>7</v>
       </c>
       <c r="BO16">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="BP16">
         <v>21</v>
@@ -4703,10 +4703,10 @@
         <v>7.4</v>
       </c>
       <c r="BU16">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BV16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW16">
         <v>3.9</v>
@@ -4715,13 +4715,13 @@
         <v>34</v>
       </c>
       <c r="BY16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ16">
         <v>22</v>
       </c>
       <c r="CA16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="CB16" t="s">
         <v>168</v>
@@ -4744,22 +4744,22 @@
         <v>154</v>
       </c>
       <c r="F17">
-        <v>1.15</v>
+        <v>1.74</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="H17">
-        <v>1.15</v>
+        <v>2.14</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4768,7 +4768,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O17">
         <v>1.02</v>
@@ -4792,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4807,13 +4807,13 @@
         <v>1000</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17">
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD17">
         <v>1000</v>
@@ -4828,13 +4828,13 @@
         <v>1000</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI17">
         <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17">
         <v>1000</v>
@@ -4843,7 +4843,7 @@
         <v>1000</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN17">
         <v>1000</v>
@@ -4852,58 +4852,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ17">
         <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4986,175 +4986,175 @@
         <v>155</v>
       </c>
       <c r="F18">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G18">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="H18">
+        <v>5.8</v>
+      </c>
+      <c r="I18">
+        <v>6.8</v>
+      </c>
+      <c r="J18">
+        <v>4.1</v>
+      </c>
+      <c r="K18">
+        <v>4.5</v>
+      </c>
+      <c r="L18">
+        <v>1.38</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>3.4</v>
+      </c>
+      <c r="O18">
+        <v>1.29</v>
+      </c>
+      <c r="P18">
+        <v>1.96</v>
+      </c>
+      <c r="Q18">
+        <v>1.87</v>
+      </c>
+      <c r="R18">
+        <v>1.35</v>
+      </c>
+      <c r="S18">
+        <v>2.96</v>
+      </c>
+      <c r="T18">
+        <v>1.92</v>
+      </c>
+      <c r="U18">
+        <v>1.89</v>
+      </c>
+      <c r="V18">
+        <v>1.17</v>
+      </c>
+      <c r="W18">
+        <v>2.52</v>
+      </c>
+      <c r="X18">
+        <v>18.5</v>
+      </c>
+      <c r="Y18">
+        <v>25</v>
+      </c>
+      <c r="Z18">
+        <v>160</v>
+      </c>
+      <c r="AA18">
+        <v>240</v>
+      </c>
+      <c r="AB18">
+        <v>8.4</v>
+      </c>
+      <c r="AC18">
+        <v>10</v>
+      </c>
+      <c r="AD18">
+        <v>30</v>
+      </c>
+      <c r="AE18">
+        <v>400</v>
+      </c>
+      <c r="AF18">
+        <v>11</v>
+      </c>
+      <c r="AG18">
+        <v>10.5</v>
+      </c>
+      <c r="AH18">
+        <v>27</v>
+      </c>
+      <c r="AI18">
+        <v>320</v>
+      </c>
+      <c r="AJ18">
+        <v>17.5</v>
+      </c>
+      <c r="AK18">
+        <v>20</v>
+      </c>
+      <c r="AL18">
+        <v>44</v>
+      </c>
+      <c r="AM18">
+        <v>390</v>
+      </c>
+      <c r="AN18">
+        <v>10.5</v>
+      </c>
+      <c r="AO18">
+        <v>530</v>
+      </c>
+      <c r="AP18">
+        <v>4.7</v>
+      </c>
+      <c r="AQ18">
         <v>5</v>
       </c>
-      <c r="I18">
-        <v>9.6</v>
-      </c>
-      <c r="J18">
-        <v>3.85</v>
-      </c>
-      <c r="K18">
+      <c r="AR18">
+        <v>5.8</v>
+      </c>
+      <c r="AS18">
         <v>6.2</v>
       </c>
-      <c r="L18">
-        <v>1.31</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>3.15</v>
-      </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>1.92</v>
-      </c>
-      <c r="Q18">
-        <v>1.84</v>
-      </c>
-      <c r="R18">
-        <v>1.28</v>
-      </c>
-      <c r="S18">
-        <v>2.82</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.12</v>
-      </c>
-      <c r="W18">
-        <v>2.4</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>1000</v>
-      </c>
-      <c r="AC18">
-        <v>1000</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>1000</v>
-      </c>
-      <c r="AG18">
-        <v>1000</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
-      <c r="AI18">
-        <v>1000</v>
-      </c>
-      <c r="AJ18">
-        <v>1000</v>
-      </c>
-      <c r="AK18">
-        <v>1000</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>1000</v>
-      </c>
-      <c r="AN18">
-        <v>1000</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18">
-        <v>1.03</v>
-      </c>
-      <c r="AR18">
-        <v>1.03</v>
-      </c>
-      <c r="AS18">
-        <v>1.03</v>
-      </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5166,25 +5166,25 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU18">
         <v>1.01</v>
@@ -5202,7 +5202,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5228,226 +5228,226 @@
         <v>156</v>
       </c>
       <c r="F19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J19">
         <v>3.7</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M19">
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O19">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q19">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R19">
+        <v>1.49</v>
+      </c>
+      <c r="S19">
+        <v>2.8</v>
+      </c>
+      <c r="T19">
+        <v>1.63</v>
+      </c>
+      <c r="U19">
+        <v>2.4</v>
+      </c>
+      <c r="V19">
         <v>1.46</v>
       </c>
-      <c r="S19">
-        <v>2.72</v>
-      </c>
-      <c r="T19">
-        <v>1.57</v>
-      </c>
-      <c r="U19">
-        <v>2.28</v>
-      </c>
-      <c r="V19">
-        <v>1.45</v>
-      </c>
       <c r="W19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y19">
+        <v>18</v>
+      </c>
+      <c r="Z19">
+        <v>28</v>
+      </c>
+      <c r="AA19">
+        <v>60</v>
+      </c>
+      <c r="AB19">
+        <v>13</v>
+      </c>
+      <c r="AC19">
+        <v>9</v>
+      </c>
+      <c r="AD19">
+        <v>14</v>
+      </c>
+      <c r="AE19">
+        <v>75</v>
+      </c>
+      <c r="AF19">
+        <v>18</v>
+      </c>
+      <c r="AG19">
+        <v>14.5</v>
+      </c>
+      <c r="AH19">
+        <v>19</v>
+      </c>
+      <c r="AI19">
+        <v>46</v>
+      </c>
+      <c r="AJ19">
         <v>42</v>
       </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>970</v>
-      </c>
-      <c r="AD19">
-        <v>36</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>23</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>16.5</v>
       </c>
       <c r="AQ19">
-        <v>1.17</v>
+        <v>13</v>
       </c>
       <c r="AR19">
-        <v>1.2</v>
+        <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="AT19">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="AU19">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="AV19">
-        <v>1.16</v>
+        <v>12</v>
       </c>
       <c r="AW19">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX19">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="AY19">
-        <v>1.14</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>1.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>1.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB19">
-        <v>1.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC19">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="BD19">
-        <v>1.2</v>
+        <v>16</v>
       </c>
       <c r="BE19">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF19">
-        <v>1.2</v>
+        <v>13.5</v>
       </c>
       <c r="BG19">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="s">
         <v>168</v>
@@ -5470,19 +5470,19 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G20">
         <v>110</v>
       </c>
       <c r="H20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="I20">
-        <v>830</v>
+        <v>110</v>
       </c>
       <c r="J20">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5518,10 +5518,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5578,52 +5578,52 @@
         <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
         <v>1.01</v>
@@ -5715,10 +5715,10 @@
         <v>4.1</v>
       </c>
       <c r="G21">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="H21">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I21">
         <v>1.88</v>
@@ -5727,7 +5727,7 @@
         <v>3.65</v>
       </c>
       <c r="K21">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -5736,13 +5736,13 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O21">
         <v>1.22</v>
       </c>
       <c r="P21">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q21">
         <v>1.66</v>
@@ -5751,10 +5751,10 @@
         <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="T21">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="U21">
         <v>2.18</v>
@@ -5763,7 +5763,7 @@
         <v>2.12</v>
       </c>
       <c r="W21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>25</v>
@@ -5781,25 +5781,25 @@
         <v>24</v>
       </c>
       <c r="AC21">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE21">
         <v>18.5</v>
       </c>
       <c r="AF21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ21">
         <v>120</v>
@@ -5811,7 +5811,7 @@
         <v>65</v>
       </c>
       <c r="AM21">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN21">
         <v>60</v>
@@ -5820,58 +5820,58 @@
         <v>11</v>
       </c>
       <c r="AP21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ21">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AR21">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AS21">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AT21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AU21">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV21">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="AW21">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AX21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AY21">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AZ21">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BA21">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB21">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC21">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD21">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE21">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF21">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG21">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BH21">
         <v>4.7</v>
@@ -5913,7 +5913,7 @@
         <v>5.5</v>
       </c>
       <c r="BU21">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV21">
         <v>12</v>
@@ -5960,16 +5960,16 @@
         <v>3.55</v>
       </c>
       <c r="H22">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I22">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="J22">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
         <v>1.66</v>
@@ -5978,16 +5978,16 @@
         <v>1.14</v>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O22">
         <v>1.62</v>
       </c>
       <c r="P22">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q22">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
         <v>1.17</v>
@@ -5999,37 +5999,37 @@
         <v>2.28</v>
       </c>
       <c r="U22">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V22">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
         <v>1.39</v>
       </c>
       <c r="X22">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z22">
         <v>15</v>
       </c>
       <c r="AA22">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB22">
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>14</v>
       </c>
       <c r="AE22">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>21</v>
@@ -6041,31 +6041,31 @@
         <v>26</v>
       </c>
       <c r="AI22">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AJ22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK22">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL22">
         <v>110</v>
       </c>
       <c r="AM22">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="AO22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP22">
+        <v>7.2</v>
+      </c>
+      <c r="AQ22">
         <v>7</v>
-      </c>
-      <c r="AQ22">
-        <v>6.8</v>
       </c>
       <c r="AR22">
         <v>13</v>
@@ -6074,13 +6074,13 @@
         <v>36</v>
       </c>
       <c r="AT22">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW22">
         <v>34</v>
@@ -6095,25 +6095,25 @@
         <v>22</v>
       </c>
       <c r="BA22">
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="BB22">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BC22">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BD22">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BE22">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="BF22">
-        <v>9.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BG22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH22">
         <v>2.52</v>
@@ -6122,16 +6122,16 @@
         <v>2.36</v>
       </c>
       <c r="BJ22">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK22">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BN22">
         <v>6.4</v>
@@ -6140,16 +6140,16 @@
         <v>5.7</v>
       </c>
       <c r="BP22">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BQ22">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BR22">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BS22">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BT22">
         <v>5.3</v>
@@ -6158,22 +6158,22 @@
         <v>4.8</v>
       </c>
       <c r="BV22">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BW22">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX22">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY22">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BZ22">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="CA22">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="CB22" t="s">
         <v>168</v>
@@ -6196,25 +6196,25 @@
         <v>160</v>
       </c>
       <c r="F23">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G23">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="H23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I23">
         <v>5.2</v>
       </c>
       <c r="J23">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K23">
         <v>3.8</v>
       </c>
       <c r="L23">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M23">
         <v>1.08</v>
@@ -6232,13 +6232,13 @@
         <v>2.1</v>
       </c>
       <c r="R23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
         <v>3.9</v>
       </c>
       <c r="T23">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U23">
         <v>1.95</v>
@@ -6247,19 +6247,19 @@
         <v>1.23</v>
       </c>
       <c r="W23">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X23">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y23">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z23">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AA23">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB23">
         <v>8.199999999999999</v>
@@ -6268,154 +6268,154 @@
         <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF23">
         <v>11</v>
       </c>
       <c r="AG23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI23">
         <v>85</v>
       </c>
       <c r="AJ23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM23">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN23">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AO23">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
+        <v>13.5</v>
+      </c>
+      <c r="AR23">
+        <v>32</v>
+      </c>
+      <c r="AS23">
         <v>13</v>
       </c>
-      <c r="AR23">
-        <v>6.8</v>
-      </c>
-      <c r="AS23">
-        <v>7.8</v>
-      </c>
       <c r="AT23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU23">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW23">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="AX23">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BA23">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BB23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC23">
         <v>18.5</v>
       </c>
       <c r="BD23">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BE23">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BF23">
         <v>12.5</v>
       </c>
       <c r="BG23">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI23">
-        <v>1.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ23">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK23">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.86</v>
+        <v>5.8</v>
       </c>
       <c r="BN23">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BO23">
-        <v>1.42</v>
+        <v>3.9</v>
       </c>
       <c r="BP23">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BQ23">
-        <v>1.69</v>
+        <v>10</v>
       </c>
       <c r="BR23">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS23">
-        <v>1.78</v>
+        <v>5.1</v>
       </c>
       <c r="BT23">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU23">
+        <v>6.8</v>
+      </c>
+      <c r="BV23">
+        <v>55</v>
+      </c>
+      <c r="BW23">
         <v>5.4</v>
       </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.9</v>
-      </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY23">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="BZ23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.78</v>
+        <v>4.9</v>
       </c>
       <c r="CB23" t="s">
         <v>168</v>
@@ -6438,19 +6438,19 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="G24">
-        <v>180</v>
+        <v>2.24</v>
       </c>
       <c r="H24">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="I24">
         <v>110</v>
       </c>
       <c r="J24">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="K24">
         <v>950</v>
@@ -6462,22 +6462,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O24">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q24">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R24">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6486,10 +6486,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.8</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6504,10 +6504,10 @@
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD24">
         <v>1000</v>
@@ -6516,10 +6516,10 @@
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH24">
         <v>1000</v>
@@ -6528,19 +6528,19 @@
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM24">
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO24">
         <v>1000</v>
@@ -6561,7 +6561,7 @@
         <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV24">
         <v>1.03</v>
@@ -6594,10 +6594,10 @@
         <v>1.03</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6680,13 +6680,13 @@
         <v>162</v>
       </c>
       <c r="F25">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G25">
         <v>2.82</v>
       </c>
       <c r="H25">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I25">
         <v>3.1</v>
@@ -6704,7 +6704,7 @@
         <v>1.09</v>
       </c>
       <c r="N25">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O25">
         <v>1.42</v>
@@ -6713,10 +6713,10 @@
         <v>1.74</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R25">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S25">
         <v>4.3</v>
@@ -6740,7 +6740,7 @@
         <v>10.5</v>
       </c>
       <c r="Z25">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA25">
         <v>90</v>
@@ -6755,37 +6755,37 @@
         <v>14</v>
       </c>
       <c r="AE25">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF25">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG25">
         <v>13.5</v>
       </c>
       <c r="AH25">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI25">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ25">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="AN25">
         <v>40</v>
       </c>
       <c r="AO25">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP25">
         <v>9.800000000000001</v>
@@ -6797,7 +6797,7 @@
         <v>16.5</v>
       </c>
       <c r="AS25">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT25">
         <v>8.4</v>
@@ -6809,7 +6809,7 @@
         <v>11.5</v>
       </c>
       <c r="AW25">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX25">
         <v>14.5</v>
@@ -6821,25 +6821,25 @@
         <v>16.5</v>
       </c>
       <c r="BA25">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB25">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC25">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BD25">
+        <v>8.4</v>
+      </c>
+      <c r="BE25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF25">
         <v>7.8</v>
       </c>
-      <c r="BE25">
-        <v>8</v>
-      </c>
-      <c r="BF25">
-        <v>7.6</v>
-      </c>
       <c r="BG25">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH25">
         <v>3.15</v>
@@ -6863,7 +6863,7 @@
         <v>5.8</v>
       </c>
       <c r="BO25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP25">
         <v>23</v>
@@ -6881,7 +6881,7 @@
         <v>6.2</v>
       </c>
       <c r="BU25">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV25">
         <v>27</v>
@@ -6922,22 +6922,22 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G26">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6946,10 +6946,10 @@
         <v>1.08</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P26">
         <v>1.81</v>
@@ -6961,19 +6961,19 @@
         <v>1.32</v>
       </c>
       <c r="S26">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T26">
-        <v>1.05</v>
+        <v>1.86</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V26">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X26">
         <v>15.5</v>
@@ -6985,103 +6985,103 @@
         <v>36</v>
       </c>
       <c r="AA26">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB26">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD26">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE26">
         <v>75</v>
       </c>
       <c r="AF26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI26">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ26">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AK26">
         <v>25</v>
       </c>
       <c r="AL26">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM26">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="AN26">
+        <v>17.5</v>
+      </c>
+      <c r="AO26">
+        <v>85</v>
+      </c>
+      <c r="AP26">
+        <v>11</v>
+      </c>
+      <c r="AQ26">
+        <v>13</v>
+      </c>
+      <c r="AR26">
+        <v>13</v>
+      </c>
+      <c r="AS26">
+        <v>6.8</v>
+      </c>
+      <c r="AT26">
+        <v>7.4</v>
+      </c>
+      <c r="AU26">
+        <v>7</v>
+      </c>
+      <c r="AV26">
+        <v>15.5</v>
+      </c>
+      <c r="AW26">
+        <v>6.6</v>
+      </c>
+      <c r="AX26">
+        <v>10</v>
+      </c>
+      <c r="AY26">
+        <v>9</v>
+      </c>
+      <c r="AZ26">
+        <v>16.5</v>
+      </c>
+      <c r="BA26">
+        <v>6.8</v>
+      </c>
+      <c r="BB26">
         <v>17</v>
       </c>
-      <c r="AO26">
-        <v>90</v>
-      </c>
-      <c r="AP26">
-        <v>4</v>
-      </c>
-      <c r="AQ26">
-        <v>4.1</v>
-      </c>
-      <c r="AR26">
-        <v>4.7</v>
-      </c>
-      <c r="AS26">
-        <v>5.2</v>
-      </c>
-      <c r="AT26">
-        <v>3.45</v>
-      </c>
-      <c r="AU26">
-        <v>3.45</v>
-      </c>
-      <c r="AV26">
-        <v>4.3</v>
-      </c>
-      <c r="AW26">
-        <v>5</v>
-      </c>
-      <c r="AX26">
-        <v>3.8</v>
-      </c>
-      <c r="AY26">
-        <v>3.75</v>
-      </c>
-      <c r="AZ26">
-        <v>4.4</v>
-      </c>
-      <c r="BA26">
-        <v>5.1</v>
-      </c>
-      <c r="BB26">
-        <v>4.5</v>
-      </c>
       <c r="BC26">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD26">
-        <v>4.8</v>
+        <v>23</v>
       </c>
       <c r="BE26">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF26">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BG26">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7230,7 +7230,7 @@
         <v>40</v>
       </c>
       <c r="AB27">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27">
         <v>7</v>
@@ -7239,7 +7239,7 @@
         <v>13</v>
       </c>
       <c r="AE27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF27">
         <v>23</v>
@@ -7254,13 +7254,13 @@
         <v>85</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK27">
         <v>65</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM27">
         <v>1000</v>
@@ -7287,7 +7287,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU27">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV27">
         <v>11</v>
@@ -7299,10 +7299,10 @@
         <v>16</v>
       </c>
       <c r="AY27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ27">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BA27">
         <v>34</v>
@@ -7317,7 +7317,7 @@
         <v>36</v>
       </c>
       <c r="BE27">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF27">
         <v>34</v>
@@ -7335,13 +7335,13 @@
         <v>12</v>
       </c>
       <c r="BK27">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN27">
         <v>6.6</v>
@@ -7359,10 +7359,10 @@
         <v>60</v>
       </c>
       <c r="BS27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT27">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU27">
         <v>4.6</v>
@@ -7371,19 +7371,19 @@
         <v>24</v>
       </c>
       <c r="BW27">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX27">
         <v>48</v>
       </c>
       <c r="BY27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ27">
         <v>55</v>
       </c>
       <c r="CA27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB27" t="s">
         <v>168</v>
@@ -7406,166 +7406,166 @@
         <v>165</v>
       </c>
       <c r="F28">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G28">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H28">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I28">
+        <v>3.9</v>
+      </c>
+      <c r="J28">
+        <v>2.92</v>
+      </c>
+      <c r="K28">
+        <v>3.25</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.11</v>
+      </c>
+      <c r="N28">
+        <v>2.64</v>
+      </c>
+      <c r="O28">
+        <v>1.49</v>
+      </c>
+      <c r="P28">
+        <v>1.56</v>
+      </c>
+      <c r="Q28">
+        <v>2.44</v>
+      </c>
+      <c r="R28">
+        <v>1.2</v>
+      </c>
+      <c r="S28">
         <v>4.9</v>
       </c>
-      <c r="J28">
-        <v>2.7</v>
-      </c>
-      <c r="K28">
-        <v>3.4</v>
-      </c>
-      <c r="L28">
-        <v>1.01</v>
-      </c>
-      <c r="M28">
-        <v>1.08</v>
-      </c>
-      <c r="N28">
-        <v>3</v>
-      </c>
-      <c r="O28">
-        <v>1.45</v>
-      </c>
-      <c r="P28">
-        <v>1.43</v>
-      </c>
-      <c r="Q28">
-        <v>2.24</v>
-      </c>
-      <c r="R28">
-        <v>1.13</v>
-      </c>
-      <c r="S28">
-        <v>2.8</v>
-      </c>
       <c r="T28">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U28">
         <v>1.8</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W28">
         <v>1.62</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP28">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR28">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS28">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU28">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV28">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW28">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX28">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY28">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA28">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB28">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC28">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD28">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE28">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7648,169 +7648,169 @@
         <v>166</v>
       </c>
       <c r="F29">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G29">
+        <v>1.81</v>
+      </c>
+      <c r="H29">
+        <v>5.5</v>
+      </c>
+      <c r="I29">
+        <v>6</v>
+      </c>
+      <c r="J29">
+        <v>3.65</v>
+      </c>
+      <c r="K29">
+        <v>3.75</v>
+      </c>
+      <c r="L29">
+        <v>1.51</v>
+      </c>
+      <c r="M29">
+        <v>1.09</v>
+      </c>
+      <c r="N29">
+        <v>3.15</v>
+      </c>
+      <c r="O29">
+        <v>1.38</v>
+      </c>
+      <c r="P29">
+        <v>1.71</v>
+      </c>
+      <c r="Q29">
+        <v>2.28</v>
+      </c>
+      <c r="R29">
+        <v>1.26</v>
+      </c>
+      <c r="S29">
+        <v>4.5</v>
+      </c>
+      <c r="T29">
+        <v>2.06</v>
+      </c>
+      <c r="U29">
         <v>1.83</v>
       </c>
-      <c r="H29">
-        <v>5.8</v>
-      </c>
-      <c r="I29">
-        <v>6.4</v>
-      </c>
-      <c r="J29">
-        <v>3.5</v>
-      </c>
-      <c r="K29">
-        <v>3.7</v>
-      </c>
-      <c r="L29">
-        <v>1.52</v>
-      </c>
-      <c r="M29">
-        <v>1.1</v>
-      </c>
-      <c r="N29">
-        <v>2.88</v>
-      </c>
-      <c r="O29">
-        <v>1.46</v>
-      </c>
-      <c r="P29">
-        <v>1.63</v>
-      </c>
-      <c r="Q29">
-        <v>2.38</v>
-      </c>
-      <c r="R29">
-        <v>1.24</v>
-      </c>
-      <c r="S29">
-        <v>4.6</v>
-      </c>
-      <c r="T29">
-        <v>2.18</v>
-      </c>
-      <c r="U29">
-        <v>1.77</v>
-      </c>
       <c r="V29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W29">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X29">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z29">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA29">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="AB29">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC29">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE29">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF29">
+        <v>9.6</v>
+      </c>
+      <c r="AG29">
         <v>9.4</v>
       </c>
-      <c r="AG29">
-        <v>10.5</v>
-      </c>
       <c r="AH29">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI29">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ29">
         <v>23</v>
       </c>
       <c r="AK29">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL29">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AM29">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN29">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO29">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP29">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR29">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS29">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT29">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU29">
         <v>7.4</v>
       </c>
       <c r="AV29">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="AW29">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX29">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA29">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE29">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG29">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH29">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI29">
         <v>2.72</v>
@@ -7819,16 +7819,16 @@
         <v>12.5</v>
       </c>
       <c r="BK29">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN29">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO29">
         <v>3.75</v>
@@ -7837,13 +7837,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ29">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR29">
         <v>36</v>
       </c>
       <c r="BS29">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT29">
         <v>9.6</v>
@@ -7855,19 +7855,19 @@
         <v>65</v>
       </c>
       <c r="BW29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX29">
         <v>90</v>
       </c>
       <c r="BY29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA29">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB29" t="s">
         <v>168</v>
@@ -7890,7 +7890,7 @@
         <v>167</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G30">
         <v>4.5</v>
@@ -7902,7 +7902,7 @@
         <v>2.18</v>
       </c>
       <c r="J30">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K30">
         <v>3.6</v>
@@ -7920,7 +7920,7 @@
         <v>1.39</v>
       </c>
       <c r="P30">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7989,7 +7989,7 @@
         <v>85</v>
       </c>
       <c r="AM30">
-        <v>880</v>
+        <v>450</v>
       </c>
       <c r="AN30">
         <v>90</v>
@@ -8034,19 +8034,19 @@
         <v>30</v>
       </c>
       <c r="BB30">
+        <v>9.4</v>
+      </c>
+      <c r="BC30">
+        <v>23</v>
+      </c>
+      <c r="BD30">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BC30">
-        <v>9.4</v>
-      </c>
-      <c r="BD30">
-        <v>9.6</v>
       </c>
       <c r="BE30">
         <v>9.800000000000001</v>
       </c>
       <c r="BF30">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG30">
         <v>16.5</v>
@@ -8061,13 +8061,13 @@
         <v>15</v>
       </c>
       <c r="BK30">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>2.2</v>
+        <v>2.92</v>
       </c>
       <c r="BN30">
         <v>10.5</v>
@@ -8076,16 +8076,16 @@
         <v>2.54</v>
       </c>
       <c r="BP30">
-        <v>930</v>
+        <v>840</v>
       </c>
       <c r="BQ30">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="BT30">
         <v>1000</v>
@@ -8103,7 +8103,7 @@
         <v>48</v>
       </c>
       <c r="BY30">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="BZ30">
         <v>46</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -520,7 +520,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-20 18:53:20</t>
+    <t>2026-09-20 21:06:52</t>
   </si>
 </sst>
 </file>
@@ -1114,226 +1114,226 @@
         <v>139</v>
       </c>
       <c r="F2">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="G2">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="I2">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="K2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="L2">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M2">
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S2">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W2">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="X2">
+        <v>46</v>
+      </c>
+      <c r="Y2">
+        <v>75</v>
+      </c>
+      <c r="Z2">
+        <v>180</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>14</v>
+      </c>
+      <c r="AC2">
+        <v>21</v>
+      </c>
+      <c r="AD2">
         <v>55</v>
       </c>
-      <c r="Y2">
-        <v>65</v>
-      </c>
-      <c r="Z2">
-        <v>150</v>
-      </c>
-      <c r="AA2">
-        <v>560</v>
-      </c>
-      <c r="AB2">
-        <v>15</v>
-      </c>
-      <c r="AC2">
-        <v>20</v>
-      </c>
-      <c r="AD2">
-        <v>46</v>
-      </c>
       <c r="AE2">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AJ2">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="AP2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AQ2">
         <v>50</v>
       </c>
       <c r="AR2">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AS2">
-        <v>16.5</v>
+        <v>320</v>
       </c>
       <c r="AT2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW2">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="AX2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BA2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="BG2">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="BH2">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BI2">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BL2">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>90</v>
       </c>
       <c r="BN2">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BT2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BU2">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BV2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BW2">
         <v>13</v>
       </c>
       <c r="BX2">
+        <v>950</v>
+      </c>
+      <c r="BY2">
         <v>60</v>
       </c>
-      <c r="BY2">
-        <v>12.5</v>
-      </c>
       <c r="BZ2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="CA2">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>168</v>
@@ -1356,157 +1356,157 @@
         <v>140</v>
       </c>
       <c r="F3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J3">
+        <v>3.9</v>
+      </c>
+      <c r="K3">
         <v>4</v>
       </c>
-      <c r="K3">
-        <v>4.2</v>
-      </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X3">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AA3">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB3">
         <v>9</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AF3">
+        <v>9.6</v>
+      </c>
+      <c r="AG3">
         <v>10.5</v>
       </c>
-      <c r="AG3">
-        <v>9.6</v>
-      </c>
       <c r="AH3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK3">
         <v>18.5</v>
       </c>
       <c r="AL3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM3">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS3">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AT3">
         <v>8</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW3">
         <v>55</v>
       </c>
       <c r="AX3">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE3">
         <v>85</v>
@@ -1515,25 +1515,25 @@
         <v>10</v>
       </c>
       <c r="BG3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH3">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BI3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="BK3">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="BN3">
         <v>4.3</v>
@@ -1542,40 +1542,40 @@
         <v>4</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="BT3">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BU3">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>3.65</v>
       </c>
       <c r="BZ3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="CB3" t="s">
         <v>168</v>
@@ -1598,22 +1598,22 @@
         <v>141</v>
       </c>
       <c r="F4">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
         <v>1.68</v>
@@ -1622,16 +1622,16 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <v>1.16</v>
@@ -1646,22 +1646,22 @@
         <v>1.7</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="X4">
         <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
@@ -1670,52 +1670,52 @@
         <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
         <v>34</v>
       </c>
       <c r="AK4">
+        <v>36</v>
+      </c>
+      <c r="AL4">
+        <v>70</v>
+      </c>
+      <c r="AM4">
+        <v>280</v>
+      </c>
+      <c r="AN4">
         <v>38</v>
       </c>
-      <c r="AL4">
-        <v>80</v>
-      </c>
-      <c r="AM4">
-        <v>240</v>
-      </c>
-      <c r="AN4">
-        <v>42</v>
-      </c>
       <c r="AO4">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR4">
         <v>23</v>
       </c>
       <c r="AS4">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -1724,49 +1724,49 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW4">
         <v>65</v>
       </c>
       <c r="AX4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BB4">
+        <v>29</v>
+      </c>
+      <c r="BC4">
         <v>32</v>
       </c>
-      <c r="BC4">
+      <c r="BD4">
+        <v>60</v>
+      </c>
+      <c r="BE4">
+        <v>220</v>
+      </c>
+      <c r="BF4">
         <v>34</v>
       </c>
-      <c r="BD4">
-        <v>65</v>
-      </c>
-      <c r="BE4">
-        <v>50</v>
-      </c>
-      <c r="BF4">
-        <v>36</v>
-      </c>
       <c r="BG4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
         <v>10.5</v>
@@ -1775,49 +1775,49 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BQ4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BT4">
         <v>7</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BW4">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BX4">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BY4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BZ4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CA4">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="CB4" t="s">
         <v>168</v>
@@ -1840,58 +1840,58 @@
         <v>142</v>
       </c>
       <c r="F5">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="G5">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H5">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="I5">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R5">
         <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="W5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X5">
         <v>14</v>
@@ -1900,166 +1900,166 @@
         <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AB5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF5">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AG5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH5">
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ5">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AK5">
+        <v>75</v>
+      </c>
+      <c r="AL5">
         <v>80</v>
       </c>
-      <c r="AL5">
-        <v>85</v>
-      </c>
       <c r="AM5">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AN5">
         <v>100</v>
       </c>
       <c r="AO5">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AP5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5">
         <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AT5">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
+        <v>17</v>
+      </c>
+      <c r="AX5">
+        <v>34</v>
+      </c>
+      <c r="AY5">
         <v>17.5</v>
       </c>
-      <c r="AX5">
-        <v>30</v>
-      </c>
-      <c r="AY5">
-        <v>16</v>
-      </c>
       <c r="AZ5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB5">
+        <v>15</v>
+      </c>
+      <c r="BC5">
+        <v>60</v>
+      </c>
+      <c r="BD5">
         <v>65</v>
-      </c>
-      <c r="BC5">
-        <v>55</v>
-      </c>
-      <c r="BD5">
-        <v>55</v>
       </c>
       <c r="BE5">
         <v>85</v>
       </c>
       <c r="BF5">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BG5">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.4</v>
+        <v>110</v>
       </c>
       <c r="BN5">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="BV5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>18</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>168</v>
@@ -2082,7 +2082,7 @@
         <v>143</v>
       </c>
       <c r="F6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G6">
         <v>7.8</v>
@@ -2091,64 +2091,64 @@
         <v>1.53</v>
       </c>
       <c r="I6">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="J6">
         <v>4.1</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
         <v>1.31</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T6">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V6">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="W6">
         <v>1.15</v>
       </c>
       <c r="X6">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z6">
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC6">
         <v>11</v>
@@ -2157,28 +2157,28 @@
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AK6">
         <v>110</v>
       </c>
       <c r="AL6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM6">
         <v>200</v>
@@ -2187,121 +2187,121 @@
         <v>150</v>
       </c>
       <c r="AO6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP6">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="AQ6">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AR6">
+        <v>5</v>
+      </c>
+      <c r="AS6">
+        <v>6</v>
+      </c>
+      <c r="AT6">
+        <v>6.2</v>
+      </c>
+      <c r="AU6">
+        <v>5.2</v>
+      </c>
+      <c r="AV6">
+        <v>5.1</v>
+      </c>
+      <c r="AW6">
+        <v>6.2</v>
+      </c>
+      <c r="AX6">
         <v>4.4</v>
       </c>
-      <c r="AS6">
-        <v>5.3</v>
-      </c>
-      <c r="AT6">
-        <v>6</v>
-      </c>
-      <c r="AU6">
+      <c r="AY6">
+        <v>4</v>
+      </c>
+      <c r="AZ6">
+        <v>6.2</v>
+      </c>
+      <c r="BA6">
+        <v>4.2</v>
+      </c>
+      <c r="BB6">
         <v>4.6</v>
       </c>
-      <c r="AV6">
+      <c r="BC6">
         <v>4.5</v>
       </c>
-      <c r="AW6">
+      <c r="BD6">
+        <v>4.5</v>
+      </c>
+      <c r="BE6">
+        <v>75</v>
+      </c>
+      <c r="BF6">
+        <v>4.6</v>
+      </c>
+      <c r="BG6">
+        <v>6.2</v>
+      </c>
+      <c r="BH6">
+        <v>3.85</v>
+      </c>
+      <c r="BI6">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6">
+        <v>11</v>
+      </c>
+      <c r="BK6">
         <v>5.5</v>
       </c>
-      <c r="AX6">
-        <v>7.2</v>
-      </c>
-      <c r="AY6">
-        <v>6.2</v>
-      </c>
-      <c r="AZ6">
-        <v>6</v>
-      </c>
-      <c r="BA6">
-        <v>6.6</v>
-      </c>
-      <c r="BB6">
-        <v>7.8</v>
-      </c>
-      <c r="BC6">
-        <v>7.6</v>
-      </c>
-      <c r="BD6">
-        <v>7.4</v>
-      </c>
-      <c r="BE6">
-        <v>7.6</v>
-      </c>
-      <c r="BF6">
-        <v>7.6</v>
-      </c>
-      <c r="BG6">
-        <v>4.1</v>
-      </c>
-      <c r="BH6">
-        <v>3.9</v>
-      </c>
-      <c r="BI6">
-        <v>2.74</v>
-      </c>
-      <c r="BJ6">
-        <v>11.5</v>
-      </c>
-      <c r="BK6">
-        <v>5.1</v>
-      </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>8.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="BN6">
         <v>11</v>
       </c>
       <c r="BO6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR6">
         <v>65</v>
       </c>
-      <c r="BQ6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
       <c r="BS6">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU6">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="BV6">
         <v>10.5</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="s">
         <v>168</v>
@@ -2327,10 +2327,10 @@
         <v>2.76</v>
       </c>
       <c r="G7">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H7">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
         <v>2.76</v>
@@ -2339,7 +2339,7 @@
         <v>3.55</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.38</v>
@@ -2354,10 +2354,10 @@
         <v>1.28</v>
       </c>
       <c r="P7">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R7">
         <v>1.45</v>
@@ -2366,7 +2366,7 @@
         <v>3.15</v>
       </c>
       <c r="T7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U7">
         <v>2.42</v>
@@ -2375,7 +2375,7 @@
         <v>1.56</v>
       </c>
       <c r="W7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X7">
         <v>17.5</v>
@@ -2393,13 +2393,13 @@
         <v>13</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF7">
         <v>20</v>
@@ -2426,7 +2426,7 @@
         <v>75</v>
       </c>
       <c r="AN7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7">
         <v>21</v>
@@ -2444,7 +2444,7 @@
         <v>34</v>
       </c>
       <c r="AT7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
         <v>7.4</v>
@@ -2489,19 +2489,19 @@
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7">
         <v>9</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM7">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="BN7">
         <v>5.9</v>
@@ -2519,13 +2519,13 @@
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
         <v>5.8</v>
       </c>
       <c r="BU7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV7">
         <v>19.5</v>
@@ -2537,7 +2537,7 @@
         <v>30</v>
       </c>
       <c r="BY7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>23</v>
@@ -2566,19 +2566,19 @@
         <v>145</v>
       </c>
       <c r="F8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G8">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I8">
         <v>22</v>
       </c>
       <c r="J8">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -2590,22 +2590,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="O8">
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="Q8">
         <v>1.36</v>
       </c>
       <c r="R8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2617,7 +2617,7 @@
         <v>1.17</v>
       </c>
       <c r="W8">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="X8">
         <v>500</v>
@@ -2674,52 +2674,52 @@
         <v>500</v>
       </c>
       <c r="AP8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AR8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AS8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AT8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AU8">
         <v>4.9</v>
       </c>
       <c r="AV8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AW8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AX8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AY8">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AZ8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BA8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BB8">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC8">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BD8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BE8">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BF8">
         <v>4</v>
@@ -2811,7 +2811,7 @@
         <v>1.18</v>
       </c>
       <c r="G9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H9">
         <v>6.6</v>
@@ -2856,7 +2856,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W9">
         <v>3.1</v>
@@ -2910,7 +2910,7 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -3050,10 +3050,10 @@
         <v>147</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G10">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H10">
         <v>5.6</v>
@@ -3062,10 +3062,10 @@
         <v>6.6</v>
       </c>
       <c r="J10">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -3098,10 +3098,10 @@
         <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X10">
         <v>26</v>
@@ -3170,10 +3170,10 @@
         <v>4.3</v>
       </c>
       <c r="AT10">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="AU10">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV10">
         <v>4.2</v>
@@ -3182,10 +3182,10 @@
         <v>4.2</v>
       </c>
       <c r="AX10">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AY10">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AZ10">
         <v>3.75</v>
@@ -3194,10 +3194,10 @@
         <v>4.2</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="BC10">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BD10">
         <v>4</v>
@@ -3206,7 +3206,7 @@
         <v>4.3</v>
       </c>
       <c r="BF10">
-        <v>6.2</v>
+        <v>2.94</v>
       </c>
       <c r="BG10">
         <v>4.2</v>
@@ -3292,19 +3292,19 @@
         <v>148</v>
       </c>
       <c r="F11">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G11">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
         <v>3.3</v>
@@ -3313,7 +3313,7 @@
         <v>1.4</v>
       </c>
       <c r="M11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
         <v>3.25</v>
@@ -3328,13 +3328,13 @@
         <v>2.2</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
         <v>4.1</v>
       </c>
       <c r="T11">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U11">
         <v>2.04</v>
@@ -3343,10 +3343,10 @@
         <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X11">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y11">
         <v>12</v>
@@ -3364,7 +3364,7 @@
         <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE11">
         <v>50</v>
@@ -3394,13 +3394,13 @@
         <v>450</v>
       </c>
       <c r="AN11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
         <v>10.5</v>
@@ -3409,10 +3409,10 @@
         <v>20</v>
       </c>
       <c r="AS11">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
@@ -3421,13 +3421,13 @@
         <v>13</v>
       </c>
       <c r="AW11">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX11">
         <v>13.5</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
         <v>16</v>
@@ -3439,16 +3439,16 @@
         <v>30</v>
       </c>
       <c r="BC11">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BD11">
         <v>38</v>
       </c>
       <c r="BE11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11">
         <v>7.8</v>
@@ -3475,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BP11">
         <v>23</v>
@@ -3493,7 +3493,7 @@
         <v>7.2</v>
       </c>
       <c r="BU11">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV11">
         <v>32</v>
@@ -3534,16 +3534,16 @@
         <v>149</v>
       </c>
       <c r="F12">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>3.55</v>
       </c>
       <c r="H12">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="I12">
-        <v>110</v>
+        <v>4.8</v>
       </c>
       <c r="J12">
         <v>2.72</v>
@@ -3585,109 +3585,109 @@
         <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="X12">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC12">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
         <v>900</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN12">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AO12">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP12">
         <v>5.6</v>
       </c>
       <c r="AQ12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AR12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AU12">
         <v>1.08</v>
       </c>
       <c r="AV12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AW12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AX12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AY12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AZ12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BA12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BB12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BC12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BD12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BE12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BF12">
         <v>1.55</v>
@@ -3776,13 +3776,13 @@
         <v>150</v>
       </c>
       <c r="F13">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G13">
-        <v>2.84</v>
+        <v>2.48</v>
       </c>
       <c r="H13">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>18.5</v>
@@ -3800,19 +3800,19 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="O13">
         <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
         <v>1.35</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S13">
         <v>1.36</v>
@@ -3827,109 +3827,109 @@
         <v>1.2</v>
       </c>
       <c r="W13">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC13">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ13">
         <v>900</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN13">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO13">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AP13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AQ13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AR13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AS13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AT13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AV13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AW13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AX13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AY13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AZ13">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BA13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BB13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BC13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BD13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BE13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BF13">
         <v>5</v>
@@ -4027,10 +4027,10 @@
         <v>1.1</v>
       </c>
       <c r="I14">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4042,22 +4042,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="O14">
         <v>1.17</v>
       </c>
       <c r="P14">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="Q14">
         <v>1.17</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S14">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4066,10 +4066,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4260,19 +4260,19 @@
         <v>152</v>
       </c>
       <c r="F15">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="G15">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="H15">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="I15">
         <v>110</v>
       </c>
       <c r="J15">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4290,13 +4290,13 @@
         <v>1.02</v>
       </c>
       <c r="P15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q15">
         <v>1.45</v>
       </c>
       <c r="R15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S15">
         <v>1.46</v>
@@ -4308,10 +4308,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4502,22 +4502,22 @@
         <v>153</v>
       </c>
       <c r="F16">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="G16">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H16">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K16">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
         <v>1.26</v>
@@ -4526,31 +4526,31 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q16">
         <v>1.63</v>
       </c>
       <c r="R16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S16">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="T16">
         <v>1.59</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
         <v>1.58</v>
@@ -4565,7 +4565,7 @@
         <v>27</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB16">
         <v>17</v>
@@ -4577,7 +4577,7 @@
         <v>16</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF16">
         <v>20</v>
@@ -4604,76 +4604,76 @@
         <v>75</v>
       </c>
       <c r="AN16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR16">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS16">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT16">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU16">
         <v>5.1</v>
       </c>
       <c r="AV16">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AW16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX16">
+        <v>4.8</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
         <v>4.5</v>
       </c>
-      <c r="AY16">
-        <v>6.4</v>
-      </c>
-      <c r="AZ16">
-        <v>4.3</v>
-      </c>
       <c r="BA16">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB16">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC16">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD16">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE16">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG16">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH16">
         <v>4.8</v>
       </c>
       <c r="BI16">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16">
         <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL16">
         <v>100</v>
@@ -4685,7 +4685,7 @@
         <v>7</v>
       </c>
       <c r="BO16">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP16">
         <v>21</v>
@@ -4703,7 +4703,7 @@
         <v>7.4</v>
       </c>
       <c r="BU16">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="BV16">
         <v>24</v>
@@ -4744,16 +4744,16 @@
         <v>154</v>
       </c>
       <c r="F17">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="G17">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="H17">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="I17">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="J17">
         <v>3.2</v>
@@ -4768,7 +4768,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="O17">
         <v>1.02</v>
@@ -4792,10 +4792,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W17">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4813,7 +4813,7 @@
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD17">
         <v>1000</v>
@@ -4843,7 +4843,7 @@
         <v>1000</v>
       </c>
       <c r="AM17">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17">
         <v>1000</v>
@@ -4989,13 +4989,13 @@
         <v>1.58</v>
       </c>
       <c r="G18">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H18">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>4.1</v>
@@ -5010,10 +5010,10 @@
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O18">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
         <v>1.96</v>
@@ -5025,7 +5025,7 @@
         <v>1.35</v>
       </c>
       <c r="S18">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T18">
         <v>1.92</v>
@@ -5037,7 +5037,7 @@
         <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X18">
         <v>18.5</v>
@@ -5079,7 +5079,7 @@
         <v>17.5</v>
       </c>
       <c r="AK18">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AL18">
         <v>44</v>
@@ -5088,22 +5088,22 @@
         <v>390</v>
       </c>
       <c r="AN18">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO18">
         <v>530</v>
       </c>
       <c r="AP18">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ18">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR18">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS18">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT18">
         <v>4.9</v>
@@ -5112,10 +5112,10 @@
         <v>5.1</v>
       </c>
       <c r="AV18">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW18">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX18">
         <v>5.1</v>
@@ -5124,28 +5124,28 @@
         <v>5.8</v>
       </c>
       <c r="AZ18">
+        <v>19.5</v>
+      </c>
+      <c r="BA18">
+        <v>6.6</v>
+      </c>
+      <c r="BB18">
         <v>5.1</v>
       </c>
-      <c r="BA18">
+      <c r="BC18">
+        <v>5.1</v>
+      </c>
+      <c r="BD18">
         <v>6</v>
       </c>
-      <c r="BB18">
-        <v>4.6</v>
-      </c>
-      <c r="BC18">
-        <v>4.8</v>
-      </c>
-      <c r="BD18">
-        <v>5.5</v>
-      </c>
       <c r="BE18">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG18">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH18">
         <v>4</v>
@@ -5157,13 +5157,13 @@
         <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BN18">
         <v>4.6</v>
@@ -5175,37 +5175,37 @@
         <v>12</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BR18">
         <v>30</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT18">
         <v>11.5</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ18">
         <v>22</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="s">
         <v>168</v>
@@ -5231,10 +5231,10 @@
         <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H19">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I19">
         <v>3.2</v>
@@ -5246,22 +5246,22 @@
         <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M19">
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O19">
         <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q19">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
         <v>1.49</v>
@@ -5273,13 +5273,13 @@
         <v>1.63</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X19">
         <v>24</v>
@@ -5288,7 +5288,7 @@
         <v>18</v>
       </c>
       <c r="Z19">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AA19">
         <v>60</v>
@@ -5318,10 +5318,10 @@
         <v>46</v>
       </c>
       <c r="AJ19">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="AK19">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AL19">
         <v>70</v>
@@ -5330,10 +5330,10 @@
         <v>200</v>
       </c>
       <c r="AN19">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO19">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AP19">
         <v>16.5</v>
@@ -5345,7 +5345,7 @@
         <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="AT19">
         <v>11</v>
@@ -5357,7 +5357,7 @@
         <v>12</v>
       </c>
       <c r="AW19">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX19">
         <v>15</v>
@@ -5366,10 +5366,10 @@
         <v>10</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA19">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB19">
         <v>14.5</v>
@@ -5381,7 +5381,7 @@
         <v>16</v>
       </c>
       <c r="BE19">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF19">
         <v>13.5</v>
@@ -5390,40 +5390,40 @@
         <v>17</v>
       </c>
       <c r="BH19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN19">
         <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BP19">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BQ19">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19">
         <v>6.4</v>
@@ -5435,19 +5435,19 @@
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB19" t="s">
         <v>168</v>
@@ -5470,19 +5470,19 @@
         <v>157</v>
       </c>
       <c r="F20">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G20">
         <v>110</v>
       </c>
       <c r="H20">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="I20">
         <v>110</v>
       </c>
       <c r="J20">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5518,10 +5518,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5712,7 +5712,7 @@
         <v>158</v>
       </c>
       <c r="F21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G21">
         <v>5.4</v>
@@ -5724,7 +5724,7 @@
         <v>1.88</v>
       </c>
       <c r="J21">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
         <v>4.7</v>
@@ -5739,10 +5739,10 @@
         <v>4.4</v>
       </c>
       <c r="O21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
         <v>1.66</v>
@@ -5760,7 +5760,7 @@
         <v>2.18</v>
       </c>
       <c r="V21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W21">
         <v>1.22</v>
@@ -5772,13 +5772,13 @@
         <v>13.5</v>
       </c>
       <c r="Z21">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA21">
         <v>20</v>
       </c>
       <c r="AB21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC21">
         <v>10.5</v>
@@ -5817,10 +5817,10 @@
         <v>60</v>
       </c>
       <c r="AO21">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AP21">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ21">
         <v>6.2</v>
@@ -5829,10 +5829,10 @@
         <v>6.4</v>
       </c>
       <c r="AS21">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT21">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AU21">
         <v>5.6</v>
@@ -5841,97 +5841,97 @@
         <v>5.8</v>
       </c>
       <c r="AW21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AX21">
+        <v>5.9</v>
+      </c>
+      <c r="AY21">
+        <v>5.1</v>
+      </c>
+      <c r="AZ21">
         <v>5</v>
       </c>
-      <c r="AY21">
-        <v>4.5</v>
-      </c>
-      <c r="AZ21">
-        <v>4.4</v>
-      </c>
       <c r="BA21">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB21">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC21">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD21">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE21">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF21">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG21">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BH21">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="BL21">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="BP21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>168</v>
@@ -5954,28 +5954,28 @@
         <v>159</v>
       </c>
       <c r="F22">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G22">
         <v>3.55</v>
       </c>
       <c r="H22">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I22">
         <v>2.68</v>
       </c>
       <c r="J22">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N22">
         <v>2.52</v>
@@ -5987,7 +5987,7 @@
         <v>1.49</v>
       </c>
       <c r="Q22">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
         <v>1.17</v>
@@ -5999,7 +5999,7 @@
         <v>2.28</v>
       </c>
       <c r="U22">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V22">
         <v>1.6</v>
@@ -6008,7 +6008,7 @@
         <v>1.39</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y22">
         <v>7.4</v>
@@ -6041,7 +6041,7 @@
         <v>26</v>
       </c>
       <c r="AI22">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="AJ22">
         <v>95</v>
@@ -6116,10 +6116,10 @@
         <v>28</v>
       </c>
       <c r="BH22">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BI22">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ22">
         <v>12</v>
@@ -6131,7 +6131,7 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BN22">
         <v>6.4</v>
@@ -6140,16 +6140,16 @@
         <v>5.7</v>
       </c>
       <c r="BP22">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BQ22">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BR22">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BS22">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BT22">
         <v>5.3</v>
@@ -6158,22 +6158,22 @@
         <v>4.8</v>
       </c>
       <c r="BV22">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BW22">
+        <v>8.6</v>
+      </c>
+      <c r="BX22">
+        <v>65</v>
+      </c>
+      <c r="BY22">
         <v>10</v>
-      </c>
-      <c r="BX22">
-        <v>55</v>
-      </c>
-      <c r="BY22">
-        <v>12.5</v>
       </c>
       <c r="BZ22">
         <v>70</v>
       </c>
       <c r="CA22">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB22" t="s">
         <v>168</v>
@@ -6199,13 +6199,13 @@
         <v>1.83</v>
       </c>
       <c r="G23">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H23">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I23">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J23">
         <v>3.7</v>
@@ -6214,7 +6214,7 @@
         <v>3.8</v>
       </c>
       <c r="L23">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M23">
         <v>1.08</v>
@@ -6244,10 +6244,10 @@
         <v>1.95</v>
       </c>
       <c r="V23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X23">
         <v>13</v>
@@ -6256,22 +6256,22 @@
         <v>16</v>
       </c>
       <c r="Z23">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA23">
         <v>140</v>
       </c>
       <c r="AB23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE23">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AF23">
         <v>11</v>
@@ -6301,7 +6301,7 @@
         <v>14.5</v>
       </c>
       <c r="AO23">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP23">
         <v>11</v>
@@ -6316,7 +6316,7 @@
         <v>13</v>
       </c>
       <c r="AT23">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU23">
         <v>7.6</v>
@@ -6340,7 +6340,7 @@
         <v>28</v>
       </c>
       <c r="BB23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC23">
         <v>18.5</v>
@@ -6349,31 +6349,31 @@
         <v>36</v>
       </c>
       <c r="BE23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF23">
         <v>12.5</v>
       </c>
       <c r="BG23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI23">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ23">
         <v>12</v>
       </c>
       <c r="BK23">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN23">
         <v>4.9</v>
@@ -6385,34 +6385,34 @@
         <v>15</v>
       </c>
       <c r="BQ23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS23">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT23">
         <v>9.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV23">
         <v>55</v>
       </c>
       <c r="BW23">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX23">
         <v>70</v>
       </c>
       <c r="BY23">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA23">
         <v>4.9</v>
@@ -6438,22 +6438,22 @@
         <v>161</v>
       </c>
       <c r="F24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G24">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="H24">
         <v>3.25</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="J24">
         <v>3.25</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6462,22 +6462,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.12</v>
+        <v>1.71</v>
       </c>
       <c r="O24">
         <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.12</v>
+        <v>1.71</v>
       </c>
       <c r="Q24">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R24">
         <v>1.09</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6489,7 +6489,7 @@
         <v>1.15</v>
       </c>
       <c r="W24">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6507,7 +6507,7 @@
         <v>500</v>
       </c>
       <c r="AC24">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD24">
         <v>1000</v>
@@ -6528,7 +6528,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK24">
         <v>500</v>
@@ -6546,52 +6546,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AU24">
         <v>5.6</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="BF24">
         <v>2.7</v>
@@ -6680,13 +6680,13 @@
         <v>162</v>
       </c>
       <c r="F25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G25">
         <v>2.82</v>
       </c>
       <c r="H25">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I25">
         <v>3.1</v>
@@ -6779,7 +6779,7 @@
         <v>55</v>
       </c>
       <c r="AM25">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN25">
         <v>40</v>
@@ -6845,7 +6845,7 @@
         <v>3.15</v>
       </c>
       <c r="BI25">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ25">
         <v>10.5</v>
@@ -6857,22 +6857,22 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN25">
         <v>5.8</v>
       </c>
       <c r="BO25">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP25">
         <v>23</v>
       </c>
       <c r="BQ25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR25">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS25">
         <v>8.4</v>
@@ -6893,7 +6893,7 @@
         <v>44</v>
       </c>
       <c r="BY25">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ25">
         <v>38</v>
@@ -6922,16 +6922,16 @@
         <v>163</v>
       </c>
       <c r="F26">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="G26">
         <v>2.02</v>
       </c>
       <c r="H26">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J26">
         <v>3.55</v>
@@ -6949,10 +6949,10 @@
         <v>3.5</v>
       </c>
       <c r="O26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P26">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q26">
         <v>2</v>
@@ -6961,7 +6961,7 @@
         <v>1.32</v>
       </c>
       <c r="S26">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T26">
         <v>1.86</v>
@@ -6970,7 +6970,7 @@
         <v>1.98</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W26">
         <v>1.98</v>
@@ -6979,10 +6979,10 @@
         <v>15.5</v>
       </c>
       <c r="Y26">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA26">
         <v>900</v>
@@ -7012,7 +7012,7 @@
         <v>80</v>
       </c>
       <c r="AJ26">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AK26">
         <v>25</v>
@@ -7024,7 +7024,7 @@
         <v>440</v>
       </c>
       <c r="AN26">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO26">
         <v>85</v>
@@ -7033,13 +7033,13 @@
         <v>11</v>
       </c>
       <c r="AQ26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR26">
         <v>13</v>
       </c>
       <c r="AS26">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT26">
         <v>7.4</v>
@@ -7051,7 +7051,7 @@
         <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX26">
         <v>10</v>
@@ -7063,7 +7063,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB26">
         <v>17</v>
@@ -7075,7 +7075,7 @@
         <v>23</v>
       </c>
       <c r="BE26">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF26">
         <v>13</v>
@@ -7167,13 +7167,13 @@
         <v>3.45</v>
       </c>
       <c r="G27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H27">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I27">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -7182,7 +7182,7 @@
         <v>3.15</v>
       </c>
       <c r="L27">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M27">
         <v>1.13</v>
@@ -7197,10 +7197,10 @@
         <v>1.54</v>
       </c>
       <c r="Q27">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R27">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S27">
         <v>6</v>
@@ -7215,7 +7215,7 @@
         <v>1.63</v>
       </c>
       <c r="W27">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X27">
         <v>8.4</v>
@@ -7254,13 +7254,13 @@
         <v>85</v>
       </c>
       <c r="AJ27">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK27">
         <v>65</v>
       </c>
       <c r="AL27">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="AM27">
         <v>1000</v>
@@ -7290,10 +7290,10 @@
         <v>6.4</v>
       </c>
       <c r="AV27">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AX27">
         <v>16</v>
@@ -7302,7 +7302,7 @@
         <v>14</v>
       </c>
       <c r="AZ27">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BA27">
         <v>34</v>
@@ -7326,64 +7326,64 @@
         <v>32</v>
       </c>
       <c r="BH27">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>2.48</v>
+        <v>1.38</v>
       </c>
       <c r="BJ27">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>5.8</v>
+        <v>2.06</v>
       </c>
       <c r="BP27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="BV27">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>168</v>
@@ -7409,55 +7409,55 @@
         <v>2.5</v>
       </c>
       <c r="G28">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H28">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I28">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J28">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N28">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="O28">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q28">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S28">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V28">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X28">
         <v>9.6</v>
@@ -7469,19 +7469,19 @@
         <v>29</v>
       </c>
       <c r="AA28">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="AB28">
         <v>8.199999999999999</v>
       </c>
       <c r="AC28">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28">
         <v>17</v>
       </c>
       <c r="AE28">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AF28">
         <v>15</v>
@@ -7496,13 +7496,13 @@
         <v>450</v>
       </c>
       <c r="AJ28">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AK28">
         <v>46</v>
       </c>
       <c r="AL28">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AM28">
         <v>500</v>
@@ -7523,7 +7523,7 @@
         <v>20</v>
       </c>
       <c r="AS28">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AT28">
         <v>6.6</v>
@@ -7535,7 +7535,7 @@
         <v>13.5</v>
       </c>
       <c r="AW28">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AX28">
         <v>12</v>
@@ -7547,25 +7547,25 @@
         <v>18.5</v>
       </c>
       <c r="BA28">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BB28">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC28">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BD28">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE28">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF28">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BG28">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7648,34 +7648,34 @@
         <v>166</v>
       </c>
       <c r="F29">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G29">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H29">
         <v>5.5</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J29">
         <v>3.65</v>
       </c>
       <c r="K29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L29">
         <v>1.51</v>
       </c>
       <c r="M29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O29">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P29">
         <v>1.71</v>
@@ -7687,25 +7687,25 @@
         <v>1.26</v>
       </c>
       <c r="S29">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T29">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U29">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V29">
         <v>1.2</v>
       </c>
       <c r="W29">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X29">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y29">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z29">
         <v>46</v>
@@ -7714,13 +7714,13 @@
         <v>900</v>
       </c>
       <c r="AB29">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC29">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE29">
         <v>110</v>
@@ -7729,10 +7729,10 @@
         <v>9.6</v>
       </c>
       <c r="AG29">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AH29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI29">
         <v>110</v>
@@ -7741,73 +7741,73 @@
         <v>23</v>
       </c>
       <c r="AK29">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL29">
         <v>48</v>
       </c>
       <c r="AM29">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN29">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29">
         <v>700</v>
       </c>
       <c r="AP29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR29">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AS29">
+        <v>12.5</v>
+      </c>
+      <c r="AT29">
+        <v>6.2</v>
+      </c>
+      <c r="AU29">
+        <v>8</v>
+      </c>
+      <c r="AV29">
+        <v>20</v>
+      </c>
+      <c r="AW29">
         <v>12</v>
       </c>
-      <c r="AT29">
-        <v>6.6</v>
-      </c>
-      <c r="AU29">
-        <v>7.4</v>
-      </c>
-      <c r="AV29">
-        <v>19</v>
-      </c>
-      <c r="AW29">
-        <v>11.5</v>
-      </c>
       <c r="AX29">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY29">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB29">
         <v>16.5</v>
       </c>
       <c r="BC29">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BE29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF29">
         <v>13.5</v>
       </c>
       <c r="BG29">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH29">
         <v>2.94</v>
@@ -7816,7 +7816,7 @@
         <v>2.72</v>
       </c>
       <c r="BJ29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK29">
         <v>6.4</v>
@@ -7825,7 +7825,7 @@
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN29">
         <v>4.2</v>
@@ -7843,31 +7843,31 @@
         <v>36</v>
       </c>
       <c r="BS29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT29">
         <v>9.6</v>
       </c>
       <c r="BU29">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV29">
         <v>65</v>
       </c>
       <c r="BW29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX29">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BY29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ29">
         <v>32</v>
       </c>
       <c r="CA29">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB29" t="s">
         <v>168</v>
@@ -7890,7 +7890,7 @@
         <v>167</v>
       </c>
       <c r="F30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G30">
         <v>4.5</v>
@@ -7899,28 +7899,28 @@
         <v>2.02</v>
       </c>
       <c r="I30">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J30">
         <v>3.35</v>
       </c>
       <c r="K30">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M30">
         <v>1.09</v>
       </c>
       <c r="N30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P30">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q30">
         <v>2.16</v>
@@ -7938,7 +7938,7 @@
         <v>1.94</v>
       </c>
       <c r="V30">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W30">
         <v>1.29</v>
@@ -7947,7 +7947,7 @@
         <v>12</v>
       </c>
       <c r="Y30">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z30">
         <v>12.5</v>
@@ -8001,7 +8001,7 @@
         <v>10</v>
       </c>
       <c r="AQ30">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR30">
         <v>10.5</v>
@@ -8016,7 +8016,7 @@
         <v>6.8</v>
       </c>
       <c r="AV30">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW30">
         <v>21</v>
@@ -8028,22 +8028,22 @@
         <v>15</v>
       </c>
       <c r="AZ30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
         <v>30</v>
       </c>
       <c r="BB30">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC30">
         <v>23</v>
       </c>
       <c r="BD30">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF30">
         <v>10</v>
@@ -8073,10 +8073,10 @@
         <v>10.5</v>
       </c>
       <c r="BO30">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="BP30">
-        <v>840</v>
+        <v>740</v>
       </c>
       <c r="BQ30">
         <v>3.15</v>
@@ -8097,7 +8097,7 @@
         <v>23</v>
       </c>
       <c r="BW30">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BX30">
         <v>48</v>
@@ -8109,7 +8109,7 @@
         <v>46</v>
       </c>
       <c r="CA30">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="CB30" t="s">
         <v>168</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -460,7 +460,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-21 01:29:42</t>
+    <t>2026-09-21 03:39:58</t>
   </si>
 </sst>
 </file>
@@ -1054,226 +1054,226 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="G2">
+        <v>1.7</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
+      </c>
+      <c r="I2">
+        <v>7.8</v>
+      </c>
+      <c r="J2">
+        <v>3.8</v>
+      </c>
+      <c r="K2">
+        <v>4.5</v>
+      </c>
+      <c r="L2">
+        <v>1.39</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.65</v>
+      </c>
+      <c r="O2">
+        <v>1.31</v>
+      </c>
+      <c r="P2">
+        <v>1.94</v>
+      </c>
+      <c r="Q2">
+        <v>1.92</v>
+      </c>
+      <c r="R2">
+        <v>1.33</v>
+      </c>
+      <c r="S2">
+        <v>3.3</v>
+      </c>
+      <c r="T2">
+        <v>1.94</v>
+      </c>
+      <c r="U2">
         <v>1.84</v>
       </c>
-      <c r="H2">
-        <v>2.98</v>
-      </c>
-      <c r="I2">
+      <c r="V2">
+        <v>1.15</v>
+      </c>
+      <c r="W2">
+        <v>2.42</v>
+      </c>
+      <c r="X2">
+        <v>15.5</v>
+      </c>
+      <c r="Y2">
         <v>22</v>
       </c>
-      <c r="J2">
-        <v>3.4</v>
-      </c>
-      <c r="K2">
-        <v>4.7</v>
-      </c>
-      <c r="L2">
-        <v>1.01</v>
-      </c>
-      <c r="M2">
-        <v>1.01</v>
-      </c>
-      <c r="N2">
-        <v>3.5</v>
-      </c>
-      <c r="O2">
-        <v>1.22</v>
-      </c>
-      <c r="P2">
-        <v>1.83</v>
-      </c>
-      <c r="Q2">
-        <v>1.24</v>
-      </c>
-      <c r="R2">
-        <v>1.25</v>
-      </c>
-      <c r="S2">
-        <v>1.4</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>1.01</v>
-      </c>
-      <c r="V2">
-        <v>1.16</v>
-      </c>
-      <c r="W2">
-        <v>1.74</v>
-      </c>
-      <c r="X2">
-        <v>500</v>
-      </c>
-      <c r="Y2">
-        <v>500</v>
-      </c>
       <c r="Z2">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="AB2">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AF2">
-        <v>500</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <v>500</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM2">
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
         <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.22</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2">
-        <v>1.28</v>
+        <v>6.2</v>
       </c>
       <c r="AR2">
-        <v>1.28</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>1.29</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AU2">
+        <v>4.6</v>
+      </c>
+      <c r="AV2">
+        <v>6.6</v>
+      </c>
+      <c r="AW2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2">
+        <v>4.6</v>
+      </c>
+      <c r="AY2">
         <v>4.9</v>
       </c>
-      <c r="AV2">
-        <v>1.28</v>
-      </c>
-      <c r="AW2">
-        <v>1.28</v>
-      </c>
-      <c r="AX2">
-        <v>1.25</v>
-      </c>
-      <c r="AY2">
-        <v>1.25</v>
-      </c>
       <c r="AZ2">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>1.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>1.28</v>
+        <v>5.8</v>
       </c>
       <c r="BC2">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="BD2">
-        <v>1.28</v>
+        <v>7.2</v>
       </c>
       <c r="BE2">
-        <v>1.29</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BG2">
-        <v>1.55</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1296,226 +1296,226 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="G3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="K3">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.63</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="S3">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
         <v>1.03</v>
       </c>
       <c r="W3">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE3">
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>3.95</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.07</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR3">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="AS3">
+        <v>7.2</v>
+      </c>
+      <c r="AT3">
         <v>4.2</v>
       </c>
-      <c r="AT3">
-        <v>1.07</v>
-      </c>
       <c r="AU3">
-        <v>1.07</v>
+        <v>5.3</v>
       </c>
       <c r="AV3">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW3">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX3">
-        <v>1.07</v>
+        <v>3.75</v>
       </c>
       <c r="AY3">
-        <v>1.07</v>
+        <v>4.7</v>
       </c>
       <c r="AZ3">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BA3">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="BB3">
-        <v>1.07</v>
+        <v>3.9</v>
       </c>
       <c r="BC3">
-        <v>1.07</v>
+        <v>5</v>
       </c>
       <c r="BD3">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>1.07</v>
+        <v>7</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BG3">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1538,28 +1538,28 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="G4">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H4">
+        <v>3.15</v>
+      </c>
+      <c r="I4">
+        <v>3.2</v>
+      </c>
+      <c r="J4">
+        <v>3.25</v>
+      </c>
+      <c r="K4">
         <v>3.3</v>
-      </c>
-      <c r="I4">
-        <v>3.4</v>
-      </c>
-      <c r="J4">
-        <v>3.2</v>
-      </c>
-      <c r="K4">
-        <v>3.25</v>
       </c>
       <c r="L4">
         <v>1.47</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.35</v>
@@ -1568,127 +1568,127 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.22</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB4">
         <v>10.5</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AF4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>40</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO4">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS4">
+        <v>48</v>
+      </c>
+      <c r="AT4">
+        <v>9</v>
+      </c>
+      <c r="AU4">
+        <v>6.8</v>
+      </c>
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>34</v>
+      </c>
+      <c r="AX4">
+        <v>14.5</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>16.5</v>
+      </c>
+      <c r="BA4">
         <v>46</v>
       </c>
-      <c r="AT4">
-        <v>8.4</v>
-      </c>
-      <c r="AU4">
-        <v>6.6</v>
-      </c>
-      <c r="AV4">
-        <v>13</v>
-      </c>
-      <c r="AW4">
-        <v>32</v>
-      </c>
-      <c r="AX4">
-        <v>13.5</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>16</v>
-      </c>
-      <c r="BA4">
-        <v>42</v>
-      </c>
       <c r="BB4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BC4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE4">
         <v>80</v>
@@ -1697,10 +1697,10 @@
         <v>22</v>
       </c>
       <c r="BG4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
         <v>2.62</v>
@@ -1715,10 +1715,10 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
         <v>4.7</v>
@@ -1733,31 +1733,31 @@
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
         <v>34</v>
       </c>
       <c r="CA4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="s">
         <v>148</v>
@@ -1780,22 +1780,22 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1807,31 +1807,31 @@
         <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
         <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
         <v>26</v>
@@ -1840,7 +1840,7 @@
         <v>28</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA5">
         <v>700</v>
@@ -1849,16 +1849,16 @@
         <v>12</v>
       </c>
       <c r="AC5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE5">
         <v>210</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1867,7 +1867,7 @@
         <v>25</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>15.5</v>
@@ -1882,7 +1882,7 @@
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO5">
         <v>530</v>
@@ -1894,31 +1894,31 @@
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS5">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
         <v>38</v>
@@ -1939,37 +1939,37 @@
         <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BR5">
         <v>27</v>
@@ -1981,25 +1981,25 @@
         <v>12</v>
       </c>
       <c r="BU5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
         <v>18</v>
       </c>
       <c r="CA5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,175 +2022,175 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>1.97</v>
+        <v>2.66</v>
       </c>
       <c r="G6">
+        <v>3.15</v>
+      </c>
+      <c r="H6">
+        <v>2.66</v>
+      </c>
+      <c r="I6">
+        <v>3.15</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
         <v>3.55</v>
       </c>
-      <c r="H6">
-        <v>2.24</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2.84</v>
-      </c>
-      <c r="K6">
-        <v>6.4</v>
-      </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
         <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="Q6">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X6">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AC6">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AE6">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AF6">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AG6">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AI6">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK6">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL6">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM6">
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AO6">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="AP6">
         <v>5.6</v>
       </c>
       <c r="AQ6">
-        <v>1.32</v>
+        <v>4.5</v>
       </c>
       <c r="AR6">
-        <v>1.33</v>
+        <v>5.7</v>
       </c>
       <c r="AS6">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="AT6">
-        <v>1.31</v>
+        <v>4.5</v>
       </c>
       <c r="AU6">
-        <v>1.23</v>
+        <v>3.95</v>
       </c>
       <c r="AV6">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="AW6">
-        <v>1.34</v>
+        <v>6.6</v>
       </c>
       <c r="AX6">
-        <v>1.33</v>
+        <v>5.7</v>
       </c>
       <c r="AY6">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6">
-        <v>1.32</v>
+        <v>5.8</v>
       </c>
       <c r="BA6">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="BB6">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="BC6">
-        <v>1.34</v>
+        <v>6.6</v>
       </c>
       <c r="BD6">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="BE6">
-        <v>1.35</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG6">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
@@ -2202,43 +2202,43 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2264,175 +2264,175 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="G7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H7">
-        <v>2.68</v>
+        <v>3.65</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
+        <v>3.8</v>
+      </c>
+      <c r="L7">
+        <v>1.44</v>
+      </c>
+      <c r="M7">
+        <v>1.08</v>
+      </c>
+      <c r="N7">
+        <v>3.05</v>
+      </c>
+      <c r="O7">
+        <v>1.38</v>
+      </c>
+      <c r="P7">
+        <v>1.7</v>
+      </c>
+      <c r="Q7">
+        <v>2.1</v>
+      </c>
+      <c r="R7">
+        <v>1.26</v>
+      </c>
+      <c r="S7">
+        <v>3.85</v>
+      </c>
+      <c r="T7">
+        <v>1.76</v>
+      </c>
+      <c r="U7">
+        <v>1.77</v>
+      </c>
+      <c r="V7">
+        <v>1.27</v>
+      </c>
+      <c r="W7">
+        <v>1.81</v>
+      </c>
+      <c r="X7">
+        <v>12.5</v>
+      </c>
+      <c r="Y7">
+        <v>14.5</v>
+      </c>
+      <c r="Z7">
+        <v>34</v>
+      </c>
+      <c r="AA7">
+        <v>120</v>
+      </c>
+      <c r="AB7">
         <v>8.6</v>
       </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>1.72</v>
-      </c>
-      <c r="O7">
-        <v>1.01</v>
-      </c>
-      <c r="P7">
-        <v>1.71</v>
-      </c>
-      <c r="Q7">
-        <v>1.35</v>
-      </c>
-      <c r="R7">
-        <v>1.25</v>
-      </c>
-      <c r="S7">
-        <v>1.37</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.2</v>
-      </c>
-      <c r="W7">
-        <v>1.8</v>
-      </c>
-      <c r="X7">
-        <v>500</v>
-      </c>
-      <c r="Y7">
-        <v>500</v>
-      </c>
-      <c r="Z7">
-        <v>500</v>
-      </c>
-      <c r="AA7">
-        <v>900</v>
-      </c>
-      <c r="AB7">
-        <v>500</v>
-      </c>
       <c r="AC7">
-        <v>95</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF7">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AG7">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>27</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AP7">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR7">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="AT7">
-        <v>1.16</v>
+        <v>4</v>
       </c>
       <c r="AU7">
-        <v>1.17</v>
+        <v>3.95</v>
       </c>
       <c r="AV7">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW7">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX7">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="AY7">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7">
-        <v>1.18</v>
+        <v>5.5</v>
       </c>
       <c r="BA7">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB7">
-        <v>1.19</v>
+        <v>5.8</v>
       </c>
       <c r="BC7">
-        <v>1.18</v>
+        <v>5.8</v>
       </c>
       <c r="BD7">
-        <v>1.19</v>
+        <v>6.4</v>
       </c>
       <c r="BE7">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="BF7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG7">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
         <v>1.01</v>
@@ -2444,43 +2444,43 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU7">
         <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW7">
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA7">
         <v>1.01</v>
@@ -2506,175 +2506,175 @@
         <v>131</v>
       </c>
       <c r="F8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="G8">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="H8">
-        <v>2.22</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="J8">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="K8">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
-        <v>1.02</v>
+        <v>2.48</v>
       </c>
       <c r="U8">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="V8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE8">
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>8.6</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AN8">
-        <v>29</v>
+        <v>4.4</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR8">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="AS8">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV8">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW8">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BA8">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG8">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI8">
         <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK8">
         <v>1.01</v>
@@ -2686,25 +2686,25 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BU8">
         <v>1.01</v>
@@ -2722,7 +2722,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA8">
         <v>1.01</v>
@@ -2748,226 +2748,226 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
+        <v>2.5</v>
+      </c>
+      <c r="H9">
+        <v>3.45</v>
+      </c>
+      <c r="I9">
+        <v>4.4</v>
+      </c>
+      <c r="J9">
+        <v>2.94</v>
+      </c>
+      <c r="K9">
+        <v>3.75</v>
+      </c>
+      <c r="L9">
+        <v>1.47</v>
+      </c>
+      <c r="M9">
+        <v>1.09</v>
+      </c>
+      <c r="N9">
+        <v>2.6</v>
+      </c>
+      <c r="O9">
+        <v>1.42</v>
+      </c>
+      <c r="P9">
+        <v>1.57</v>
+      </c>
+      <c r="Q9">
+        <v>2.08</v>
+      </c>
+      <c r="R9">
+        <v>1.22</v>
+      </c>
+      <c r="S9">
+        <v>3.85</v>
+      </c>
+      <c r="T9">
+        <v>1.87</v>
+      </c>
+      <c r="U9">
+        <v>1.74</v>
+      </c>
+      <c r="V9">
+        <v>1.3</v>
+      </c>
+      <c r="W9">
+        <v>1.66</v>
+      </c>
+      <c r="X9">
+        <v>11.5</v>
+      </c>
+      <c r="Y9">
+        <v>13</v>
+      </c>
+      <c r="Z9">
+        <v>30</v>
+      </c>
+      <c r="AA9">
+        <v>260</v>
+      </c>
+      <c r="AB9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD9">
+        <v>18.5</v>
+      </c>
+      <c r="AE9">
+        <v>70</v>
+      </c>
+      <c r="AF9">
+        <v>15</v>
+      </c>
+      <c r="AG9">
+        <v>12.5</v>
+      </c>
+      <c r="AH9">
+        <v>23</v>
+      </c>
+      <c r="AI9">
+        <v>90</v>
+      </c>
+      <c r="AJ9">
+        <v>100</v>
+      </c>
+      <c r="AK9">
+        <v>32</v>
+      </c>
+      <c r="AL9">
+        <v>60</v>
+      </c>
+      <c r="AM9">
+        <v>170</v>
+      </c>
+      <c r="AN9">
+        <v>29</v>
+      </c>
+      <c r="AO9">
+        <v>90</v>
+      </c>
+      <c r="AP9">
+        <v>4</v>
+      </c>
+      <c r="AQ9">
+        <v>4.2</v>
+      </c>
+      <c r="AR9">
+        <v>5.1</v>
+      </c>
+      <c r="AS9">
+        <v>5.9</v>
+      </c>
+      <c r="AT9">
+        <v>3.65</v>
+      </c>
+      <c r="AU9">
+        <v>3.55</v>
+      </c>
+      <c r="AV9">
+        <v>4.6</v>
+      </c>
+      <c r="AW9">
+        <v>5.7</v>
+      </c>
+      <c r="AX9">
+        <v>4.4</v>
+      </c>
+      <c r="AY9">
+        <v>4.1</v>
+      </c>
+      <c r="AZ9">
+        <v>4.9</v>
+      </c>
+      <c r="BA9">
+        <v>5.8</v>
+      </c>
+      <c r="BB9">
+        <v>5.3</v>
+      </c>
+      <c r="BC9">
         <v>5.2</v>
       </c>
-      <c r="H9">
-        <v>2.3</v>
-      </c>
-      <c r="I9">
-        <v>9.4</v>
-      </c>
-      <c r="J9">
-        <v>2.84</v>
-      </c>
-      <c r="K9">
-        <v>8.4</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.1</v>
-      </c>
-      <c r="N9">
-        <v>1.13</v>
-      </c>
-      <c r="O9">
-        <v>1.27</v>
-      </c>
-      <c r="P9">
-        <v>1.13</v>
-      </c>
-      <c r="Q9">
-        <v>1.45</v>
-      </c>
-      <c r="R9">
-        <v>1.09</v>
-      </c>
-      <c r="S9">
-        <v>1.45</v>
-      </c>
-      <c r="T9">
-        <v>1.01</v>
-      </c>
-      <c r="U9">
-        <v>1.01</v>
-      </c>
-      <c r="V9">
-        <v>1.21</v>
-      </c>
-      <c r="W9">
-        <v>1.33</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>110</v>
-      </c>
-      <c r="Z9">
-        <v>110</v>
-      </c>
-      <c r="AA9">
-        <v>900</v>
-      </c>
-      <c r="AB9">
-        <v>95</v>
-      </c>
-      <c r="AC9">
-        <v>95</v>
-      </c>
-      <c r="AD9">
-        <v>85</v>
-      </c>
-      <c r="AE9">
-        <v>260</v>
-      </c>
-      <c r="AF9">
-        <v>150</v>
-      </c>
-      <c r="AG9">
-        <v>110</v>
-      </c>
-      <c r="AH9">
-        <v>150</v>
-      </c>
-      <c r="AI9">
-        <v>340</v>
-      </c>
-      <c r="AJ9">
-        <v>900</v>
-      </c>
-      <c r="AK9">
-        <v>140</v>
-      </c>
-      <c r="AL9">
-        <v>200</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>600</v>
-      </c>
-      <c r="AO9">
-        <v>600</v>
-      </c>
-      <c r="AP9">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9">
-        <v>1.01</v>
-      </c>
-      <c r="AR9">
-        <v>1.01</v>
-      </c>
-      <c r="AS9">
-        <v>1.01</v>
-      </c>
-      <c r="AT9">
-        <v>1.01</v>
-      </c>
-      <c r="AU9">
-        <v>1.01</v>
-      </c>
-      <c r="AV9">
-        <v>1.01</v>
-      </c>
-      <c r="AW9">
-        <v>1.01</v>
-      </c>
-      <c r="AX9">
-        <v>1.01</v>
-      </c>
-      <c r="AY9">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9">
-        <v>1.01</v>
-      </c>
-      <c r="BA9">
-        <v>1.01</v>
-      </c>
-      <c r="BB9">
-        <v>1.01</v>
-      </c>
-      <c r="BC9">
-        <v>1.01</v>
-      </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF9">
-        <v>1.55</v>
+        <v>5.1</v>
       </c>
       <c r="BG9">
-        <v>1.55</v>
+        <v>5.8</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2993,13 +2993,13 @@
         <v>2.48</v>
       </c>
       <c r="G10">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I10">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J10">
         <v>3.85</v>
@@ -3014,16 +3014,16 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R10">
         <v>1.53</v>
@@ -3035,7 +3035,7 @@
         <v>1.59</v>
       </c>
       <c r="U10">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
         <v>1.54</v>
@@ -3071,7 +3071,7 @@
         <v>20</v>
       </c>
       <c r="AG10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH10">
         <v>16</v>
@@ -3101,25 +3101,25 @@
         <v>5</v>
       </c>
       <c r="AQ10">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AR10">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AS10">
         <v>5.6</v>
       </c>
       <c r="AT10">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AU10">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AV10">
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX10">
         <v>4.8</v>
@@ -3128,25 +3128,25 @@
         <v>10</v>
       </c>
       <c r="AZ10">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA10">
         <v>5.3</v>
       </c>
       <c r="BB10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC10">
+        <v>5.1</v>
+      </c>
+      <c r="BD10">
         <v>5.2</v>
       </c>
-      <c r="BD10">
-        <v>5.3</v>
-      </c>
       <c r="BE10">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF10">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BG10">
         <v>4.7</v>
@@ -3161,7 +3161,7 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL10">
         <v>100</v>
@@ -3173,25 +3173,25 @@
         <v>7</v>
       </c>
       <c r="BO10">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BP10">
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>13</v>
+        <v>3.8</v>
       </c>
       <c r="BR10">
         <v>32</v>
       </c>
       <c r="BS10">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="BT10">
         <v>7.4</v>
       </c>
       <c r="BU10">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
         <v>24</v>
@@ -3209,7 +3209,7 @@
         <v>22</v>
       </c>
       <c r="CA10">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3232,220 +3232,220 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
         <v>2.92</v>
       </c>
       <c r="I11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L11">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="R11">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="S11">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
         <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X11">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="Y11">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="Z11">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AA11">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB11">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AC11">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="AD11">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AE11">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF11">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AG11">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AJ11">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK11">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AL11">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AP11">
-        <v>1.27</v>
+        <v>4.5</v>
       </c>
       <c r="AQ11">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="AR11">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>1.27</v>
+        <v>5</v>
       </c>
       <c r="AT11">
-        <v>1.24</v>
+        <v>4.1</v>
       </c>
       <c r="AU11">
-        <v>1.24</v>
+        <v>4</v>
       </c>
       <c r="AV11">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="AW11">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="AX11">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AY11">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="AZ11">
-        <v>1.21</v>
+        <v>4.1</v>
       </c>
       <c r="BA11">
-        <v>1.27</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="BC11">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="BD11">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>1.26</v>
+        <v>5</v>
       </c>
       <c r="BF11">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="BG11">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>1.63</v>
       </c>
       <c r="H12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I12">
         <v>7.6</v>
@@ -3489,46 +3489,46 @@
         <v>4.2</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12">
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U12">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="V12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y12">
         <v>25</v>
@@ -3537,13 +3537,13 @@
         <v>160</v>
       </c>
       <c r="AA12">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AB12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
         <v>30</v>
@@ -3555,10 +3555,10 @@
         <v>11</v>
       </c>
       <c r="AG12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI12">
         <v>320</v>
@@ -3573,19 +3573,19 @@
         <v>42</v>
       </c>
       <c r="AM12">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO12">
-        <v>530</v>
+        <v>700</v>
       </c>
       <c r="AP12">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR12">
         <v>6.8</v>
@@ -3594,67 +3594,67 @@
         <v>7.2</v>
       </c>
       <c r="AT12">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AV12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW12">
         <v>7</v>
       </c>
       <c r="AX12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA12">
         <v>7</v>
       </c>
       <c r="BB12">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BC12">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE12">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG12">
         <v>7.2</v>
       </c>
       <c r="BH12">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI12">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK12">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BN12">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BO12">
         <v>3.6</v>
@@ -3663,37 +3663,37 @@
         <v>12</v>
       </c>
       <c r="BQ12">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BR12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS12">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BT12">
         <v>11.5</v>
       </c>
       <c r="BU12">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BZ12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA12">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3716,226 +3716,226 @@
         <v>136</v>
       </c>
       <c r="F13">
+        <v>2.92</v>
+      </c>
+      <c r="G13">
+        <v>3.25</v>
+      </c>
+      <c r="H13">
+        <v>2.36</v>
+      </c>
+      <c r="I13">
+        <v>2.56</v>
+      </c>
+      <c r="J13">
+        <v>3.5</v>
+      </c>
+      <c r="K13">
+        <v>3.8</v>
+      </c>
+      <c r="L13">
+        <v>1.39</v>
+      </c>
+      <c r="M13">
+        <v>1.07</v>
+      </c>
+      <c r="N13">
+        <v>3.85</v>
+      </c>
+      <c r="O13">
         <v>1.31</v>
       </c>
-      <c r="G13">
-        <v>110</v>
-      </c>
-      <c r="H13">
-        <v>1.31</v>
-      </c>
-      <c r="I13">
-        <v>110</v>
-      </c>
-      <c r="J13">
-        <v>1.35</v>
-      </c>
-      <c r="K13">
-        <v>950</v>
-      </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>1.3</v>
-      </c>
-      <c r="O13">
-        <v>1.01</v>
-      </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="Q13">
-        <v>1.31</v>
+        <v>1.9</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>1.31</v>
+        <v>3.3</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V13">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,184 +3958,184 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="G14">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H14">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J14">
         <v>3.7</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L14">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P14">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q14">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="R14">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T14">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V14">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Y14">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AA14">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="AB14">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC14">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AF14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG14">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI14">
         <v>46</v>
       </c>
       <c r="AJ14">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK14">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL14">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM14">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AN14">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AO14">
         <v>50</v>
       </c>
       <c r="AP14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS14">
         <v>32</v>
       </c>
       <c r="AT14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU14">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV14">
         <v>11.5</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AX14">
         <v>15</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BB14">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BC14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BD14">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>60</v>
       </c>
       <c r="BF14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BG14">
         <v>17</v>
       </c>
       <c r="BH14">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BI14">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN14">
         <v>5.6</v>
@@ -4144,40 +4144,40 @@
         <v>4.9</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ14">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS14">
+        <v>11</v>
+      </c>
+      <c r="BT14">
+        <v>6.2</v>
+      </c>
+      <c r="BU14">
+        <v>5.4</v>
+      </c>
+      <c r="BV14">
+        <v>23</v>
+      </c>
+      <c r="BW14">
+        <v>9.6</v>
+      </c>
+      <c r="BX14">
+        <v>40</v>
+      </c>
+      <c r="BY14">
+        <v>11</v>
+      </c>
+      <c r="BZ14">
+        <v>29</v>
+      </c>
+      <c r="CA14">
         <v>10</v>
-      </c>
-      <c r="BT14">
-        <v>6.4</v>
-      </c>
-      <c r="BU14">
-        <v>5.6</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>10.5</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
-      <c r="CA14">
-        <v>9</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4203,19 +4203,19 @@
         <v>4.4</v>
       </c>
       <c r="G15">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H15">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I15">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J15">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.32</v>
@@ -4224,19 +4224,19 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
         <v>1.23</v>
       </c>
       <c r="P15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
         <v>1.68</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
         <v>2.74</v>
@@ -4245,7 +4245,7 @@
         <v>1.72</v>
       </c>
       <c r="U15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
         <v>2.16</v>
@@ -4281,10 +4281,10 @@
         <v>42</v>
       </c>
       <c r="AG15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
         <v>32</v>
@@ -4308,16 +4308,16 @@
         <v>9.4</v>
       </c>
       <c r="AP15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ15">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AS15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT15">
         <v>17</v>
@@ -4326,31 +4326,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15">
+        <v>5.2</v>
+      </c>
+      <c r="AX15">
+        <v>6</v>
+      </c>
+      <c r="AY15">
+        <v>5.3</v>
+      </c>
+      <c r="AZ15">
+        <v>5.2</v>
+      </c>
+      <c r="BA15">
         <v>5.8</v>
       </c>
-      <c r="AW15">
-        <v>5</v>
-      </c>
-      <c r="AX15">
-        <v>5.9</v>
-      </c>
-      <c r="AY15">
-        <v>5.1</v>
-      </c>
-      <c r="AZ15">
-        <v>5</v>
-      </c>
-      <c r="BA15">
-        <v>5.6</v>
-      </c>
       <c r="BB15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC15">
         <v>6.2</v>
       </c>
       <c r="BD15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE15">
         <v>6.4</v>
@@ -4359,7 +4359,7 @@
         <v>6.2</v>
       </c>
       <c r="BG15">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="BH15">
         <v>4.7</v>
@@ -4377,7 +4377,7 @@
         <v>120</v>
       </c>
       <c r="BM15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BN15">
         <v>8.800000000000001</v>
@@ -4386,7 +4386,7 @@
         <v>6.4</v>
       </c>
       <c r="BP15">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BQ15">
         <v>6.2</v>
@@ -4413,13 +4413,13 @@
         <v>28</v>
       </c>
       <c r="BY15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ15">
         <v>17.5</v>
       </c>
       <c r="CA15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB15" t="s">
         <v>148</v>
@@ -4442,22 +4442,22 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G16">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I16">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="J16">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L16">
         <v>1.66</v>
@@ -4475,40 +4475,40 @@
         <v>1.48</v>
       </c>
       <c r="Q16">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R16">
         <v>1.17</v>
       </c>
       <c r="S16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T16">
         <v>2.3</v>
       </c>
       <c r="U16">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V16">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y16">
         <v>7.4</v>
       </c>
       <c r="Z16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA16">
         <v>48</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC16">
         <v>7.2</v>
@@ -4520,7 +4520,7 @@
         <v>46</v>
       </c>
       <c r="AF16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG16">
         <v>16.5</v>
@@ -4532,13 +4532,13 @@
         <v>150</v>
       </c>
       <c r="AJ16">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AK16">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AL16">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AM16">
         <v>1000</v>
@@ -4553,19 +4553,19 @@
         <v>7</v>
       </c>
       <c r="AQ16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS16">
         <v>36</v>
       </c>
       <c r="AT16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV16">
         <v>12</v>
@@ -4583,16 +4583,16 @@
         <v>22</v>
       </c>
       <c r="BA16">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB16">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BC16">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BD16">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BE16">
         <v>70</v>
@@ -4601,16 +4601,16 @@
         <v>48</v>
       </c>
       <c r="BG16">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH16">
         <v>2.58</v>
       </c>
       <c r="BI16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK16">
         <v>8.4</v>
@@ -4619,7 +4619,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN16">
         <v>6.4</v>
@@ -4631,37 +4631,37 @@
         <v>42</v>
       </c>
       <c r="BQ16">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR16">
         <v>75</v>
       </c>
       <c r="BS16">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV16">
         <v>30</v>
       </c>
       <c r="BW16">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX16">
         <v>60</v>
       </c>
       <c r="BY16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ16">
         <v>70</v>
       </c>
       <c r="CA16">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,76 +4684,76 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="G17">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="H17">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O17">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="P17">
+        <v>1.99</v>
+      </c>
+      <c r="Q17">
+        <v>1.96</v>
+      </c>
+      <c r="R17">
+        <v>1.38</v>
+      </c>
+      <c r="S17">
+        <v>3.5</v>
+      </c>
+      <c r="T17">
         <v>1.88</v>
       </c>
-      <c r="Q17">
-        <v>2.08</v>
-      </c>
-      <c r="R17">
-        <v>1.33</v>
-      </c>
-      <c r="S17">
-        <v>3.85</v>
-      </c>
-      <c r="T17">
-        <v>1.94</v>
-      </c>
       <c r="U17">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="V17">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W17">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="X17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z17">
         <v>40</v>
       </c>
       <c r="AA17">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17">
         <v>21</v>
@@ -4768,142 +4768,142 @@
         <v>10.5</v>
       </c>
       <c r="AH17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI17">
+        <v>320</v>
+      </c>
+      <c r="AJ17">
+        <v>18</v>
+      </c>
+      <c r="AK17">
+        <v>19</v>
+      </c>
+      <c r="AL17">
+        <v>95</v>
+      </c>
+      <c r="AM17">
+        <v>580</v>
+      </c>
+      <c r="AN17">
+        <v>11.5</v>
+      </c>
+      <c r="AO17">
         <v>85</v>
       </c>
-      <c r="AJ17">
-        <v>21</v>
-      </c>
-      <c r="AK17">
-        <v>21</v>
-      </c>
-      <c r="AL17">
-        <v>42</v>
-      </c>
-      <c r="AM17">
-        <v>140</v>
-      </c>
-      <c r="AN17">
-        <v>14</v>
-      </c>
-      <c r="AO17">
-        <v>100</v>
-      </c>
       <c r="AP17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ17">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR17">
         <v>32</v>
       </c>
       <c r="AS17">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="AT17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV17">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX17">
         <v>9.6</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
         <v>18.5</v>
       </c>
       <c r="BA17">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB17">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC17">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE17">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="BF17">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BG17">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="BH17">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BI17">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BJ17">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BN17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO17">
         <v>3.95</v>
       </c>
       <c r="BP17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ17">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BT17">
         <v>9.800000000000001</v>
       </c>
       <c r="BU17">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BV17">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CA17">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,175 +4926,175 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="G18">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="H18">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I18">
+        <v>6.4</v>
+      </c>
+      <c r="J18">
+        <v>3.5</v>
+      </c>
+      <c r="K18">
+        <v>4.6</v>
+      </c>
+      <c r="L18">
+        <v>1.37</v>
+      </c>
+      <c r="M18">
+        <v>1.06</v>
+      </c>
+      <c r="N18">
+        <v>3.5</v>
+      </c>
+      <c r="O18">
+        <v>1.28</v>
+      </c>
+      <c r="P18">
+        <v>1.84</v>
+      </c>
+      <c r="Q18">
+        <v>1.82</v>
+      </c>
+      <c r="R18">
+        <v>1.33</v>
+      </c>
+      <c r="S18">
+        <v>3</v>
+      </c>
+      <c r="T18">
+        <v>1.78</v>
+      </c>
+      <c r="U18">
+        <v>1.91</v>
+      </c>
+      <c r="V18">
+        <v>1.2</v>
+      </c>
+      <c r="W18">
+        <v>2.16</v>
+      </c>
+      <c r="X18">
+        <v>18</v>
+      </c>
+      <c r="Y18">
+        <v>22</v>
+      </c>
+      <c r="Z18">
+        <v>50</v>
+      </c>
+      <c r="AA18">
+        <v>900</v>
+      </c>
+      <c r="AB18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC18">
+        <v>10</v>
+      </c>
+      <c r="AD18">
+        <v>25</v>
+      </c>
+      <c r="AE18">
+        <v>190</v>
+      </c>
+      <c r="AF18">
+        <v>12.5</v>
+      </c>
+      <c r="AG18">
+        <v>11</v>
+      </c>
+      <c r="AH18">
         <v>24</v>
       </c>
-      <c r="J18">
-        <v>3.25</v>
-      </c>
-      <c r="K18">
-        <v>13.5</v>
-      </c>
-      <c r="L18">
-        <v>1.01</v>
-      </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>1.72</v>
-      </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>1.71</v>
-      </c>
-      <c r="Q18">
-        <v>1.29</v>
-      </c>
-      <c r="R18">
-        <v>1.25</v>
-      </c>
-      <c r="S18">
-        <v>1.31</v>
-      </c>
-      <c r="T18">
-        <v>1.01</v>
-      </c>
-      <c r="U18">
-        <v>1.01</v>
-      </c>
-      <c r="V18">
-        <v>1.15</v>
-      </c>
-      <c r="W18">
-        <v>1.98</v>
-      </c>
-      <c r="X18">
-        <v>1000</v>
-      </c>
-      <c r="Y18">
-        <v>1000</v>
-      </c>
-      <c r="Z18">
-        <v>1000</v>
-      </c>
-      <c r="AA18">
-        <v>1000</v>
-      </c>
-      <c r="AB18">
-        <v>500</v>
-      </c>
-      <c r="AC18">
-        <v>95</v>
-      </c>
-      <c r="AD18">
-        <v>1000</v>
-      </c>
-      <c r="AE18">
-        <v>1000</v>
-      </c>
-      <c r="AF18">
-        <v>500</v>
-      </c>
-      <c r="AG18">
-        <v>500</v>
-      </c>
-      <c r="AH18">
-        <v>1000</v>
-      </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>22</v>
       </c>
       <c r="AK18">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL18">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN18">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP18">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ18">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="AR18">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS18">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT18">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="AU18">
         <v>5.6</v>
       </c>
       <c r="AV18">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW18">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX18">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="AY18">
-        <v>1.07</v>
+        <v>3.65</v>
       </c>
       <c r="AZ18">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA18">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB18">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC18">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="BD18">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE18">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF18">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG18">
-        <v>1.55</v>
+        <v>5.2</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5106,31 +5106,31 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ18">
         <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS18">
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU18">
         <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
@@ -5142,7 +5142,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5171,13 +5171,13 @@
         <v>2.68</v>
       </c>
       <c r="G19">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H19">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J19">
         <v>3.15</v>
@@ -5189,7 +5189,7 @@
         <v>1.49</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
         <v>3.2</v>
@@ -5204,7 +5204,7 @@
         <v>2.28</v>
       </c>
       <c r="R19">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S19">
         <v>4.3</v>
@@ -5219,7 +5219,7 @@
         <v>1.46</v>
       </c>
       <c r="W19">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X19">
         <v>11.5</v>
@@ -5345,7 +5345,7 @@
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN19">
         <v>5.7</v>
@@ -5357,7 +5357,7 @@
         <v>23</v>
       </c>
       <c r="BQ19">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR19">
         <v>40</v>
@@ -5410,118 +5410,118 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="G20">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="H20">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I20">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J20">
+        <v>3.75</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>1.42</v>
+      </c>
+      <c r="M20">
+        <v>1.07</v>
+      </c>
+      <c r="N20">
         <v>3.6</v>
       </c>
-      <c r="K20">
-        <v>3.8</v>
-      </c>
-      <c r="L20">
-        <v>1.43</v>
-      </c>
-      <c r="M20">
-        <v>1.08</v>
-      </c>
-      <c r="N20">
-        <v>3.55</v>
-      </c>
       <c r="O20">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P20">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q20">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R20">
         <v>1.33</v>
       </c>
       <c r="S20">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T20">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U20">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W20">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="X20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y20">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA20">
         <v>900</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE20">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF20">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20">
+        <v>23</v>
+      </c>
+      <c r="AI20">
+        <v>90</v>
+      </c>
+      <c r="AJ20">
+        <v>22</v>
+      </c>
+      <c r="AK20">
         <v>21</v>
       </c>
-      <c r="AI20">
-        <v>75</v>
-      </c>
-      <c r="AJ20">
-        <v>24</v>
-      </c>
-      <c r="AK20">
-        <v>25</v>
-      </c>
       <c r="AL20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM20">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN20">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AP20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ20">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR20">
         <v>13</v>
@@ -5530,55 +5530,55 @@
         <v>7.8</v>
       </c>
       <c r="AT20">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV20">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX20">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA20">
         <v>7.8</v>
       </c>
       <c r="BB20">
+        <v>16</v>
+      </c>
+      <c r="BC20">
         <v>17</v>
       </c>
-      <c r="BC20">
-        <v>16.5</v>
-      </c>
       <c r="BD20">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF20">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BG20">
         <v>13.5</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK20">
         <v>1.01</v>
@@ -5590,43 +5590,43 @@
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU20">
         <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY20">
         <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -5652,73 +5652,73 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G21">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H21">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I21">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J21">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L21">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="M21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N21">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="O21">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P21">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S21">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T21">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U21">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V21">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W21">
         <v>1.38</v>
       </c>
       <c r="X21">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y21">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Z21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA21">
         <v>40</v>
       </c>
       <c r="AB21">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -5727,7 +5727,7 @@
         <v>13</v>
       </c>
       <c r="AE21">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AF21">
         <v>23</v>
@@ -5736,13 +5736,13 @@
         <v>16.5</v>
       </c>
       <c r="AH21">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI21">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AJ21">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK21">
         <v>70</v>
@@ -5754,43 +5754,43 @@
         <v>1000</v>
       </c>
       <c r="AN21">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AO21">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP21">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ21">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR21">
         <v>12.5</v>
       </c>
       <c r="AS21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT21">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU21">
         <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW21">
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA21">
         <v>55</v>
@@ -5814,10 +5814,10 @@
         <v>32</v>
       </c>
       <c r="BH21">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="BI21">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BJ21">
         <v>12</v>
@@ -5829,7 +5829,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BN21">
         <v>6.4</v>
@@ -5841,37 +5841,37 @@
         <v>36</v>
       </c>
       <c r="BQ21">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BR21">
         <v>60</v>
       </c>
       <c r="BS21">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT21">
         <v>5.1</v>
       </c>
       <c r="BU21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV21">
         <v>23</v>
       </c>
       <c r="BW21">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BX21">
         <v>48</v>
       </c>
       <c r="BY21">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ21">
         <v>55</v>
       </c>
       <c r="CA21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CB21" t="s">
         <v>148</v>
@@ -5894,61 +5894,61 @@
         <v>145</v>
       </c>
       <c r="F22">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G22">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I22">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L22">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="M22">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N22">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="O22">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q22">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R22">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S22">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="T22">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U22">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X22">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y22">
         <v>11</v>
@@ -5963,10 +5963,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE22">
         <v>150</v>
@@ -5978,7 +5978,7 @@
         <v>12.5</v>
       </c>
       <c r="AH22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI22">
         <v>450</v>
@@ -5993,7 +5993,7 @@
         <v>130</v>
       </c>
       <c r="AM22">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN22">
         <v>42</v>
@@ -6002,10 +6002,10 @@
         <v>500</v>
       </c>
       <c r="AP22">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22">
         <v>20</v>
@@ -6044,76 +6044,76 @@
         <v>19.5</v>
       </c>
       <c r="BD22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF22">
         <v>21</v>
       </c>
       <c r="BG22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB22" t="s">
         <v>148</v>
@@ -6139,7 +6139,7 @@
         <v>1.77</v>
       </c>
       <c r="G23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H23">
         <v>5.7</v>
@@ -6166,28 +6166,28 @@
         <v>1.45</v>
       </c>
       <c r="P23">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q23">
         <v>2.36</v>
       </c>
       <c r="R23">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S23">
         <v>4.7</v>
       </c>
       <c r="T23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U23">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V23">
         <v>1.2</v>
       </c>
       <c r="W23">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X23">
         <v>11</v>
@@ -6205,22 +6205,22 @@
         <v>6.8</v>
       </c>
       <c r="AC23">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE23">
         <v>110</v>
       </c>
       <c r="AF23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG23">
         <v>9.6</v>
       </c>
       <c r="AH23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23">
         <v>110</v>
@@ -6232,13 +6232,13 @@
         <v>23</v>
       </c>
       <c r="AL23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM23">
         <v>200</v>
       </c>
       <c r="AN23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO23">
         <v>170</v>
@@ -6253,22 +6253,22 @@
         <v>36</v>
       </c>
       <c r="AS23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV23">
         <v>21</v>
       </c>
       <c r="AW23">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY23">
         <v>9.199999999999999</v>
@@ -6280,7 +6280,7 @@
         <v>29</v>
       </c>
       <c r="BB23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC23">
         <v>20</v>
@@ -6289,16 +6289,16 @@
         <v>40</v>
       </c>
       <c r="BE23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BF23">
         <v>14</v>
       </c>
       <c r="BG23">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH23">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BI23">
         <v>2.72</v>
@@ -6307,13 +6307,13 @@
         <v>12</v>
       </c>
       <c r="BK23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN23">
         <v>4.2</v>
@@ -6325,13 +6325,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ23">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR23">
         <v>36</v>
       </c>
       <c r="BS23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT23">
         <v>9.4</v>
@@ -6343,19 +6343,19 @@
         <v>65</v>
       </c>
       <c r="BW23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX23">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BY23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23">
         <v>32</v>
       </c>
       <c r="CA23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6390,7 +6390,7 @@
         <v>2.16</v>
       </c>
       <c r="J24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K24">
         <v>3.6</v>
@@ -6417,10 +6417,10 @@
         <v>1.28</v>
       </c>
       <c r="S24">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T24">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U24">
         <v>1.94</v>
@@ -6540,64 +6540,64 @@
         <v>16.5</v>
       </c>
       <c r="BH24">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BI24">
-        <v>1.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ24">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK24">
-        <v>2.76</v>
+        <v>6.4</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="BN24">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO24">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="BP24">
-        <v>610</v>
+        <v>46</v>
       </c>
       <c r="BQ24">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="BR24">
+        <v>55</v>
+      </c>
+      <c r="BS24">
+        <v>6.2</v>
+      </c>
+      <c r="BT24">
+        <v>5.6</v>
+      </c>
+      <c r="BU24">
+        <v>4.2</v>
+      </c>
+      <c r="BV24">
+        <v>19</v>
+      </c>
+      <c r="BW24">
+        <v>5.1</v>
+      </c>
+      <c r="BX24">
         <v>1000</v>
       </c>
-      <c r="BS24">
-        <v>3.2</v>
-      </c>
-      <c r="BT24">
-        <v>1000</v>
-      </c>
-      <c r="BU24">
-        <v>2.2</v>
-      </c>
-      <c r="BV24">
-        <v>23</v>
-      </c>
-      <c r="BW24">
-        <v>2.98</v>
-      </c>
-      <c r="BX24">
-        <v>48</v>
-      </c>
       <c r="BY24">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA24">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="CB24" t="s">
         <v>148</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -466,7 +466,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-21 05:50:28</t>
+    <t>2026-09-21 08:00:59</t>
   </si>
 </sst>
 </file>
@@ -1060,178 +1060,178 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y2">
         <v>22</v>
       </c>
       <c r="Z2">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE2">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AF2">
         <v>10.5</v>
       </c>
       <c r="AG2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK2">
         <v>19</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
         <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT2">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
+        <v>46</v>
+      </c>
+      <c r="AX2">
+        <v>8.4</v>
+      </c>
+      <c r="AY2">
         <v>7.8</v>
       </c>
-      <c r="AX2">
-        <v>8</v>
-      </c>
-      <c r="AY2">
-        <v>4.6</v>
-      </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
+        <v>46</v>
+      </c>
+      <c r="BB2">
+        <v>14.5</v>
+      </c>
+      <c r="BC2">
+        <v>15</v>
+      </c>
+      <c r="BD2">
+        <v>23</v>
+      </c>
+      <c r="BE2">
+        <v>80</v>
+      </c>
+      <c r="BF2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG2">
+        <v>50</v>
+      </c>
+      <c r="BH2">
+        <v>3.6</v>
+      </c>
+      <c r="BI2">
+        <v>2.96</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
         <v>7.8</v>
-      </c>
-      <c r="BB2">
-        <v>6.2</v>
-      </c>
-      <c r="BC2">
-        <v>5.9</v>
-      </c>
-      <c r="BD2">
-        <v>7</v>
-      </c>
-      <c r="BE2">
-        <v>8</v>
-      </c>
-      <c r="BF2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG2">
-        <v>8</v>
-      </c>
-      <c r="BH2">
-        <v>3.65</v>
-      </c>
-      <c r="BI2">
-        <v>2.88</v>
-      </c>
-      <c r="BJ2">
-        <v>11.5</v>
-      </c>
-      <c r="BK2">
-        <v>5.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1240,16 +1240,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR2">
         <v>28</v>
@@ -1258,28 +1258,28 @@
         <v>7.6</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
         <v>9</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>150</v>
@@ -1302,31 +1302,31 @@
         <v>127</v>
       </c>
       <c r="F3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G3">
         <v>1.24</v>
       </c>
       <c r="H3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M3">
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O3">
         <v>1.16</v>
@@ -1335,34 +1335,34 @@
         <v>2.68</v>
       </c>
       <c r="Q3">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R3">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S3">
         <v>2.26</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
         <v>1.04</v>
       </c>
       <c r="W3">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="X3">
         <v>34</v>
       </c>
       <c r="Y3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z3">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1374,10 +1374,10 @@
         <v>21</v>
       </c>
       <c r="AD3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE3">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="AF3">
         <v>8.6</v>
@@ -1386,10 +1386,10 @@
         <v>14</v>
       </c>
       <c r="AH3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI3">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AJ3">
         <v>9.199999999999999</v>
@@ -1398,22 +1398,22 @@
         <v>16</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AN3">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="AR3">
         <v>6.6</v>
@@ -1422,25 +1422,25 @@
         <v>6.8</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
         <v>14.5</v>
       </c>
       <c r="AV3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX3">
         <v>6.4</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BA3">
         <v>6.6</v>
@@ -1452,7 +1452,7 @@
         <v>11.5</v>
       </c>
       <c r="BD3">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
         <v>6.6</v>
@@ -1464,13 +1464,13 @@
         <v>15</v>
       </c>
       <c r="BH3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BK3">
         <v>5</v>
@@ -1479,28 +1479,28 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BN3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BS3">
         <v>5.7</v>
       </c>
       <c r="BT3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BU3">
         <v>5.4</v>
@@ -1509,7 +1509,7 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1518,10 +1518,10 @@
         <v>6.8</v>
       </c>
       <c r="BZ3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="CB3" t="s">
         <v>150</v>
@@ -1544,79 +1544,79 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="G4">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H4">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AA4">
         <v>70</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
         <v>48</v>
@@ -1625,28 +1625,28 @@
         <v>17</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL4">
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO4">
         <v>50</v>
@@ -1655,10 +1655,10 @@
         <v>10</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS4">
         <v>38</v>
@@ -1667,52 +1667,52 @@
         <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX4">
         <v>14</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
+        <v>40</v>
+      </c>
+      <c r="BB4">
+        <v>30</v>
+      </c>
+      <c r="BC4">
+        <v>25</v>
+      </c>
+      <c r="BD4">
         <v>36</v>
-      </c>
-      <c r="BB4">
-        <v>26</v>
-      </c>
-      <c r="BC4">
-        <v>23</v>
-      </c>
-      <c r="BD4">
-        <v>32</v>
       </c>
       <c r="BE4">
         <v>80</v>
       </c>
       <c r="BF4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BG4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
         <v>7.6</v>
@@ -1721,10 +1721,10 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
         <v>4.8</v>
@@ -1733,13 +1733,13 @@
         <v>22</v>
       </c>
       <c r="BQ4">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BR4">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BS4">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BT4">
         <v>6.2</v>
@@ -1748,22 +1748,22 @@
         <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW4">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BX4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BY4">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB4" t="s">
         <v>150</v>
@@ -1786,22 +1786,22 @@
         <v>129</v>
       </c>
       <c r="F5">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="G5">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="I5">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="J5">
+        <v>3.2</v>
+      </c>
+      <c r="K5">
         <v>3.25</v>
-      </c>
-      <c r="K5">
-        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.48</v>
@@ -1825,184 +1825,184 @@
         <v>1.29</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="X5">
         <v>11</v>
       </c>
       <c r="Y5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z5">
+        <v>16.5</v>
+      </c>
+      <c r="AA5">
+        <v>40</v>
+      </c>
+      <c r="AB5">
         <v>11</v>
-      </c>
-      <c r="Z5">
-        <v>20</v>
-      </c>
-      <c r="AA5">
-        <v>60</v>
-      </c>
-      <c r="AB5">
-        <v>10</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
+        <v>12.5</v>
+      </c>
+      <c r="AE5">
+        <v>32</v>
+      </c>
+      <c r="AF5">
+        <v>21</v>
+      </c>
+      <c r="AG5">
         <v>13.5</v>
       </c>
-      <c r="AE5">
-        <v>38</v>
-      </c>
-      <c r="AF5">
-        <v>17.5</v>
-      </c>
-      <c r="AG5">
-        <v>12.5</v>
-      </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI5">
+        <v>50</v>
+      </c>
+      <c r="AJ5">
         <v>55</v>
       </c>
-      <c r="AJ5">
-        <v>44</v>
-      </c>
       <c r="AK5">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5">
         <v>120</v>
       </c>
       <c r="AN5">
+        <v>44</v>
+      </c>
+      <c r="AO5">
         <v>32</v>
-      </c>
-      <c r="AO5">
-        <v>42</v>
       </c>
       <c r="AP5">
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AT5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX5">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
+        <v>42</v>
+      </c>
+      <c r="BB5">
+        <v>42</v>
+      </c>
+      <c r="BC5">
+        <v>34</v>
+      </c>
+      <c r="BD5">
         <v>46</v>
-      </c>
-      <c r="BB5">
-        <v>36</v>
-      </c>
-      <c r="BC5">
-        <v>28</v>
-      </c>
-      <c r="BD5">
-        <v>40</v>
       </c>
       <c r="BE5">
         <v>85</v>
       </c>
       <c r="BF5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
       </c>
       <c r="BI5">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
         <v>4.6</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ5">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BW5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="CA5">
         <v>7</v>
@@ -2034,16 +2034,16 @@
         <v>1.74</v>
       </c>
       <c r="H6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
         <v>1.31</v>
@@ -2052,7 +2052,7 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>1.21</v>
@@ -2061,49 +2061,49 @@
         <v>2.4</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S6">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z6">
         <v>55</v>
       </c>
       <c r="AA6">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AB6">
         <v>12.5</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE6">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="AF6">
         <v>13</v>
@@ -2112,82 +2112,82 @@
         <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL6">
+        <v>30</v>
+      </c>
+      <c r="AM6">
+        <v>95</v>
+      </c>
+      <c r="AN6">
+        <v>8.6</v>
+      </c>
+      <c r="AO6">
+        <v>55</v>
+      </c>
+      <c r="AP6">
+        <v>18</v>
+      </c>
+      <c r="AQ6">
+        <v>20</v>
+      </c>
+      <c r="AR6">
         <v>36</v>
       </c>
-      <c r="AM6">
-        <v>380</v>
-      </c>
-      <c r="AN6">
-        <v>8.4</v>
-      </c>
-      <c r="AO6">
-        <v>70</v>
-      </c>
-      <c r="AP6">
-        <v>20</v>
-      </c>
-      <c r="AQ6">
-        <v>21</v>
-      </c>
-      <c r="AR6">
-        <v>38</v>
-      </c>
       <c r="AS6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU6">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AV6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX6">
         <v>10</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB6">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BC6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE6">
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH6">
         <v>4.9</v>
@@ -2199,7 +2199,7 @@
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2208,37 +2208,37 @@
         <v>4.4</v>
       </c>
       <c r="BN6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BR6">
         <v>27</v>
       </c>
       <c r="BS6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BT6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU6">
         <v>3.2</v>
       </c>
       <c r="BV6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY6">
         <v>4.2</v>
@@ -2247,7 +2247,7 @@
         <v>18.5</v>
       </c>
       <c r="CA6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CB6" t="s">
         <v>150</v>
@@ -2270,22 +2270,22 @@
         <v>131</v>
       </c>
       <c r="F7">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G7">
         <v>3.15</v>
       </c>
       <c r="H7">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J7">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
         <v>1.46</v>
@@ -2294,16 +2294,16 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R7">
         <v>1.25</v>
@@ -2312,28 +2312,28 @@
         <v>4.1</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
         <v>1.46</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y7">
         <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA7">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2342,31 +2342,31 @@
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG7">
         <v>14</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK7">
         <v>40</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2375,70 +2375,70 @@
         <v>40</v>
       </c>
       <c r="AO7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP7">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7">
+        <v>15</v>
+      </c>
+      <c r="AS7">
+        <v>7.4</v>
+      </c>
+      <c r="AT7">
+        <v>8.4</v>
+      </c>
+      <c r="AU7">
+        <v>6.2</v>
+      </c>
+      <c r="AV7">
+        <v>10.5</v>
+      </c>
+      <c r="AW7">
+        <v>7</v>
+      </c>
+      <c r="AX7">
+        <v>15.5</v>
+      </c>
+      <c r="AY7">
         <v>5.7</v>
       </c>
-      <c r="AS7">
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>7.6</v>
+      </c>
+      <c r="BB7">
+        <v>7.4</v>
+      </c>
+      <c r="BC7">
+        <v>8</v>
+      </c>
+      <c r="BD7">
+        <v>7.6</v>
+      </c>
+      <c r="BE7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF7">
+        <v>7.2</v>
+      </c>
+      <c r="BG7">
         <v>7</v>
-      </c>
-      <c r="AT7">
-        <v>5</v>
-      </c>
-      <c r="AU7">
-        <v>4.3</v>
-      </c>
-      <c r="AV7">
-        <v>5.1</v>
-      </c>
-      <c r="AW7">
-        <v>6.6</v>
-      </c>
-      <c r="AX7">
-        <v>5.7</v>
-      </c>
-      <c r="AY7">
-        <v>5.1</v>
-      </c>
-      <c r="AZ7">
-        <v>5.8</v>
-      </c>
-      <c r="BA7">
-        <v>7</v>
-      </c>
-      <c r="BB7">
-        <v>7</v>
-      </c>
-      <c r="BC7">
-        <v>6.6</v>
-      </c>
-      <c r="BD7">
-        <v>7</v>
-      </c>
-      <c r="BE7">
-        <v>7.4</v>
-      </c>
-      <c r="BF7">
-        <v>6.6</v>
-      </c>
-      <c r="BG7">
-        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>3.15</v>
       </c>
       <c r="BI7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
         <v>5.1</v>
@@ -2447,22 +2447,22 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BN7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ7">
         <v>7</v>
       </c>
       <c r="BR7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS7">
         <v>8</v>
@@ -2471,7 +2471,7 @@
         <v>6</v>
       </c>
       <c r="BU7">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV7">
         <v>25</v>
@@ -2480,13 +2480,13 @@
         <v>7</v>
       </c>
       <c r="BX7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>8</v>
+        <v>2.26</v>
       </c>
       <c r="BZ7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA7">
         <v>7.8</v>
@@ -2512,163 +2512,163 @@
         <v>132</v>
       </c>
       <c r="F8">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="G8">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K8">
         <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
         <v>1.35</v>
       </c>
       <c r="P8">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q8">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
+        <v>1.87</v>
+      </c>
+      <c r="V8">
+        <v>1.3</v>
+      </c>
+      <c r="W8">
         <v>1.79</v>
       </c>
-      <c r="V8">
-        <v>1.26</v>
-      </c>
-      <c r="W8">
-        <v>1.98</v>
-      </c>
       <c r="X8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC8">
         <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG8">
         <v>11.5</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI8">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM8">
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO8">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AP8">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AS8">
         <v>7.2</v>
       </c>
       <c r="AT8">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV8">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AX8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY8">
         <v>4.6</v>
       </c>
       <c r="AZ8">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="BA8">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="BC8">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="BD8">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BE8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF8">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="BG8">
         <v>7</v>
@@ -2677,10 +2677,10 @@
         <v>3.6</v>
       </c>
       <c r="BI8">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK8">
         <v>4.4</v>
@@ -2689,46 +2689,46 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BN8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO8">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BP8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS8">
         <v>6</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BV8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BW8">
+        <v>5.9</v>
+      </c>
+      <c r="BX8">
+        <v>65</v>
+      </c>
+      <c r="BY8">
         <v>6.2</v>
       </c>
-      <c r="BX8">
-        <v>55</v>
-      </c>
-      <c r="BY8">
-        <v>6.4</v>
-      </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA8">
         <v>6</v>
@@ -2754,118 +2754,118 @@
         <v>133</v>
       </c>
       <c r="F9">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="G9">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K9">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="L9">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P9">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R9">
         <v>1.5</v>
       </c>
       <c r="S9">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="T9">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W9">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="X9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y9">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z9">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AD9">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AI9">
-        <v>400</v>
+        <v>280</v>
       </c>
       <c r="AJ9">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AK9">
         <v>16</v>
       </c>
       <c r="AL9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AN9">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AQ9">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AR9">
         <v>7.8</v>
@@ -2874,106 +2874,106 @@
         <v>8</v>
       </c>
       <c r="AT9">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AU9">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AV9">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9">
         <v>8</v>
       </c>
       <c r="AX9">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY9">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA9">
+        <v>7.6</v>
+      </c>
+      <c r="BB9">
         <v>7.8</v>
       </c>
-      <c r="BB9">
-        <v>4.2</v>
-      </c>
       <c r="BC9">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF9">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH9">
+        <v>4.6</v>
+      </c>
+      <c r="BI9">
+        <v>3.5</v>
+      </c>
+      <c r="BJ9">
+        <v>16.5</v>
+      </c>
+      <c r="BK9">
         <v>4.9</v>
-      </c>
-      <c r="BI9">
-        <v>2.68</v>
-      </c>
-      <c r="BJ9">
-        <v>18.5</v>
-      </c>
-      <c r="BK9">
-        <v>4.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BN9">
         <v>3.85</v>
       </c>
       <c r="BO9">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BQ9">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="BR9">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BS9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BT9">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA9">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="CB9" t="s">
         <v>150</v>
@@ -2996,82 +2996,82 @@
         <v>134</v>
       </c>
       <c r="F10">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
         <v>3.55</v>
       </c>
       <c r="L10">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O10">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T10">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="U10">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA10">
         <v>260</v>
       </c>
       <c r="AB10">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD10">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10">
         <v>15</v>
@@ -3080,88 +3080,88 @@
         <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
         <v>34</v>
       </c>
       <c r="AK10">
+        <v>30</v>
+      </c>
+      <c r="AL10">
+        <v>75</v>
+      </c>
+      <c r="AM10">
+        <v>580</v>
+      </c>
+      <c r="AN10">
+        <v>27</v>
+      </c>
+      <c r="AO10">
+        <v>85</v>
+      </c>
+      <c r="AP10">
+        <v>9.4</v>
+      </c>
+      <c r="AQ10">
+        <v>10</v>
+      </c>
+      <c r="AR10">
+        <v>21</v>
+      </c>
+      <c r="AS10">
+        <v>46</v>
+      </c>
+      <c r="AT10">
+        <v>7.2</v>
+      </c>
+      <c r="AU10">
+        <v>6.2</v>
+      </c>
+      <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
+        <v>40</v>
+      </c>
+      <c r="AX10">
+        <v>11</v>
+      </c>
+      <c r="AY10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10">
+        <v>15.5</v>
+      </c>
+      <c r="BA10">
         <v>32</v>
       </c>
-      <c r="AL10">
-        <v>60</v>
-      </c>
-      <c r="AM10">
-        <v>170</v>
-      </c>
-      <c r="AN10">
-        <v>29</v>
-      </c>
-      <c r="AO10">
-        <v>90</v>
-      </c>
-      <c r="AP10">
-        <v>4.5</v>
-      </c>
-      <c r="AQ10">
-        <v>4.2</v>
-      </c>
-      <c r="AR10">
-        <v>5.2</v>
-      </c>
-      <c r="AS10">
-        <v>5.9</v>
-      </c>
-      <c r="AT10">
-        <v>4</v>
-      </c>
-      <c r="AU10">
-        <v>3.95</v>
-      </c>
-      <c r="AV10">
-        <v>4.7</v>
-      </c>
-      <c r="AW10">
-        <v>5.7</v>
-      </c>
-      <c r="AX10">
-        <v>4.4</v>
-      </c>
-      <c r="AY10">
-        <v>4.1</v>
-      </c>
-      <c r="AZ10">
-        <v>4.9</v>
-      </c>
-      <c r="BA10">
-        <v>5.8</v>
-      </c>
       <c r="BB10">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BC10">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BD10">
-        <v>5.7</v>
+        <v>27</v>
       </c>
       <c r="BE10">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="BF10">
-        <v>5.1</v>
+        <v>18.5</v>
       </c>
       <c r="BG10">
-        <v>5.8</v>
+        <v>27</v>
       </c>
       <c r="BH10">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
@@ -3173,49 +3173,49 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN10">
         <v>5.8</v>
       </c>
       <c r="BO10">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="BP10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ10">
         <v>4</v>
       </c>
       <c r="BR10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT10">
         <v>8.199999999999999</v>
       </c>
       <c r="BU10">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BW10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY10">
         <v>4.6</v>
       </c>
       <c r="BZ10">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="CA10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB10" t="s">
         <v>150</v>
@@ -3241,7 +3241,7 @@
         <v>2.66</v>
       </c>
       <c r="G11">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H11">
         <v>2.56</v>
@@ -3250,7 +3250,7 @@
         <v>2.72</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
         <v>4.1</v>
@@ -3262,55 +3262,55 @@
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R11">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V11">
         <v>1.58</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X11">
         <v>26</v>
       </c>
       <c r="Y11">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA11">
         <v>40</v>
       </c>
       <c r="AB11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE11">
         <v>27</v>
@@ -3328,7 +3328,7 @@
         <v>34</v>
       </c>
       <c r="AJ11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK11">
         <v>29</v>
@@ -3340,25 +3340,25 @@
         <v>75</v>
       </c>
       <c r="AN11">
+        <v>17.5</v>
+      </c>
+      <c r="AO11">
+        <v>16.5</v>
+      </c>
+      <c r="AP11">
         <v>18.5</v>
       </c>
-      <c r="AO11">
-        <v>17</v>
-      </c>
-      <c r="AP11">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AQ11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR11">
         <v>16.5</v>
       </c>
       <c r="AS11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU11">
         <v>7.8</v>
@@ -3367,10 +3367,10 @@
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="AX11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
         <v>10.5</v>
@@ -3385,58 +3385,58 @@
         <v>7.8</v>
       </c>
       <c r="BC11">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BE11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG11">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="BH11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>95</v>
       </c>
       <c r="BM11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BN11">
         <v>7.4</v>
       </c>
       <c r="BO11">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP11">
         <v>23</v>
       </c>
       <c r="BQ11">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="BR11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS11">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BT11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU11">
         <v>4.5</v>
@@ -3445,19 +3445,19 @@
         <v>22</v>
       </c>
       <c r="BW11">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="BX11">
         <v>32</v>
       </c>
       <c r="BY11">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ11">
         <v>22</v>
       </c>
       <c r="CA11">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="CB11" t="s">
         <v>150</v>
@@ -3480,22 +3480,22 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H12">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I12">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.29</v>
@@ -3504,37 +3504,37 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P12">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q12">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S12">
         <v>2.38</v>
       </c>
       <c r="T12">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X12">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y12">
         <v>21</v>
@@ -3543,7 +3543,7 @@
         <v>30</v>
       </c>
       <c r="AA12">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB12">
         <v>16.5</v>
@@ -3582,19 +3582,19 @@
         <v>200</v>
       </c>
       <c r="AN12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP12">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR12">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS12">
         <v>5.5</v>
@@ -3612,7 +3612,7 @@
         <v>4.6</v>
       </c>
       <c r="AX12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY12">
         <v>5.2</v>
@@ -3627,10 +3627,10 @@
         <v>4.6</v>
       </c>
       <c r="BC12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE12">
         <v>5.5</v>
@@ -3639,61 +3639,61 @@
         <v>3.8</v>
       </c>
       <c r="BG12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BI12">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="BJ12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK12">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
+        <v>6</v>
+      </c>
+      <c r="BN12">
+        <v>6.2</v>
+      </c>
+      <c r="BO12">
+        <v>3.15</v>
+      </c>
+      <c r="BP12">
+        <v>16.5</v>
+      </c>
+      <c r="BQ12">
+        <v>4.7</v>
+      </c>
+      <c r="BR12">
+        <v>25</v>
+      </c>
+      <c r="BS12">
+        <v>5.2</v>
+      </c>
+      <c r="BT12">
+        <v>7.4</v>
+      </c>
+      <c r="BU12">
+        <v>3.45</v>
+      </c>
+      <c r="BV12">
+        <v>24</v>
+      </c>
+      <c r="BW12">
+        <v>5.1</v>
+      </c>
+      <c r="BX12">
+        <v>30</v>
+      </c>
+      <c r="BY12">
         <v>5.3</v>
-      </c>
-      <c r="BN12">
-        <v>6.4</v>
-      </c>
-      <c r="BO12">
-        <v>3</v>
-      </c>
-      <c r="BP12">
-        <v>17.5</v>
-      </c>
-      <c r="BQ12">
-        <v>4.2</v>
-      </c>
-      <c r="BR12">
-        <v>27</v>
-      </c>
-      <c r="BS12">
-        <v>4.6</v>
-      </c>
-      <c r="BT12">
-        <v>7.8</v>
-      </c>
-      <c r="BU12">
-        <v>3.25</v>
-      </c>
-      <c r="BV12">
-        <v>25</v>
-      </c>
-      <c r="BW12">
-        <v>4.6</v>
-      </c>
-      <c r="BX12">
-        <v>32</v>
-      </c>
-      <c r="BY12">
-        <v>4.8</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>137</v>
       </c>
       <c r="F13">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="G13">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H13">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I13">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J13">
         <v>4.1</v>
@@ -3740,49 +3740,49 @@
         <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M13">
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P13">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T13">
         <v>1.87</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W13">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="X13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z13">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AA13">
         <v>700</v>
@@ -3794,7 +3794,7 @@
         <v>10</v>
       </c>
       <c r="AD13">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE13">
         <v>400</v>
@@ -3812,19 +3812,19 @@
         <v>240</v>
       </c>
       <c r="AJ13">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM13">
         <v>700</v>
       </c>
       <c r="AN13">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO13">
         <v>700</v>
@@ -3833,13 +3833,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ13">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR13">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13">
         <v>7.8</v>
@@ -3848,67 +3848,67 @@
         <v>8.6</v>
       </c>
       <c r="AV13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX13">
         <v>8.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13">
         <v>18.5</v>
       </c>
       <c r="BA13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD13">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BE13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF13">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI13">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ13">
         <v>3.85</v>
@@ -3917,19 +3917,19 @@
         <v>30</v>
       </c>
       <c r="BS13">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT13">
         <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BX13">
         <v>1000</v>
@@ -3938,7 +3938,7 @@
         <v>5.2</v>
       </c>
       <c r="BZ13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA13">
         <v>4.5</v>
@@ -3973,7 +3973,7 @@
         <v>1.76</v>
       </c>
       <c r="I14">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -3982,37 +3982,37 @@
         <v>4.6</v>
       </c>
       <c r="L14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M14">
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S14">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T14">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U14">
         <v>2.24</v>
       </c>
       <c r="V14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W14">
         <v>1.25</v>
@@ -4039,7 +4039,7 @@
         <v>11</v>
       </c>
       <c r="AE14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF14">
         <v>40</v>
@@ -4051,7 +4051,7 @@
         <v>18.5</v>
       </c>
       <c r="AI14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ14">
         <v>120</v>
@@ -4063,16 +4063,16 @@
         <v>65</v>
       </c>
       <c r="AM14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP14">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
         <v>9.4</v>
@@ -4099,49 +4099,49 @@
         <v>16</v>
       </c>
       <c r="AY14">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AZ14">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA14">
         <v>14.5</v>
       </c>
       <c r="BB14">
+        <v>7.2</v>
+      </c>
+      <c r="BC14">
         <v>7</v>
       </c>
-      <c r="BC14">
-        <v>6.6</v>
-      </c>
       <c r="BD14">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE14">
+        <v>7.2</v>
+      </c>
+      <c r="BF14">
         <v>6.8</v>
       </c>
-      <c r="BF14">
-        <v>6.4</v>
-      </c>
       <c r="BG14">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK14">
         <v>7.2</v>
       </c>
       <c r="BL14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM14">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BN14">
         <v>8.800000000000001</v>
@@ -4153,13 +4153,13 @@
         <v>38</v>
       </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR14">
         <v>42</v>
       </c>
       <c r="BS14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BT14">
         <v>4.9</v>
@@ -4174,16 +4174,16 @@
         <v>8.6</v>
       </c>
       <c r="BX14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BY14">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BZ14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="CB14" t="s">
         <v>150</v>
@@ -4206,13 +4206,13 @@
         <v>139</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G15">
         <v>3.15</v>
       </c>
       <c r="H15">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I15">
         <v>2.54</v>
@@ -4221,124 +4221,124 @@
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L15">
         <v>1.4</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q15">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
         <v>1.46</v>
       </c>
       <c r="X15">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z15">
         <v>17.5</v>
       </c>
       <c r="AA15">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AB15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC15">
         <v>8.4</v>
       </c>
       <c r="AD15">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE15">
         <v>34</v>
       </c>
       <c r="AF15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AG15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH15">
         <v>18</v>
       </c>
       <c r="AI15">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AJ15">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK15">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AL15">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AM15">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN15">
         <v>600</v>
       </c>
       <c r="AO15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR15">
         <v>14</v>
       </c>
       <c r="AS15">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AT15">
         <v>10.5</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV15">
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="AX15">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY15">
         <v>11</v>
@@ -4347,22 +4347,22 @@
         <v>14</v>
       </c>
       <c r="BA15">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BB15">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BC15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD15">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BE15">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF15">
-        <v>5.8</v>
+        <v>22</v>
       </c>
       <c r="BG15">
         <v>17</v>
@@ -4371,7 +4371,7 @@
         <v>4</v>
       </c>
       <c r="BI15">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15">
         <v>11.5</v>
@@ -4386,31 +4386,31 @@
         <v>4.6</v>
       </c>
       <c r="BN15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW15">
         <v>3.9</v>
@@ -4448,70 +4448,70 @@
         <v>140</v>
       </c>
       <c r="F16">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="H16">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="J16">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P16">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q16">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U16">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="X16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA16">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AB16">
         <v>11.5</v>
@@ -4520,154 +4520,154 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE16">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF16">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ16">
         <v>42</v>
       </c>
       <c r="AK16">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL16">
         <v>48</v>
       </c>
       <c r="AM16">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN16">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO16">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AP16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ16">
         <v>11</v>
       </c>
       <c r="AR16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU16">
         <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW16">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX16">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BC16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG16">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BH16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI16">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN16">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ16">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX16">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
         <v>150</v>
@@ -4693,19 +4693,19 @@
         <v>3.45</v>
       </c>
       <c r="G17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H17">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I17">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J17">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L17">
         <v>1.67</v>
@@ -4714,34 +4714,34 @@
         <v>1.14</v>
       </c>
       <c r="N17">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O17">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P17">
         <v>1.5</v>
       </c>
       <c r="Q17">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U17">
         <v>1.76</v>
       </c>
       <c r="V17">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W17">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -4768,7 +4768,7 @@
         <v>40</v>
       </c>
       <c r="AF17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG17">
         <v>16</v>
@@ -4780,16 +4780,16 @@
         <v>75</v>
       </c>
       <c r="AJ17">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AK17">
         <v>60</v>
       </c>
       <c r="AL17">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="AM17">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN17">
         <v>85</v>
@@ -4798,22 +4798,22 @@
         <v>46</v>
       </c>
       <c r="AP17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS17">
         <v>36</v>
       </c>
       <c r="AT17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV17">
         <v>12</v>
@@ -4825,13 +4825,13 @@
         <v>19</v>
       </c>
       <c r="AY17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA17">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB17">
         <v>60</v>
@@ -4840,10 +4840,10 @@
         <v>50</v>
       </c>
       <c r="BD17">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BE17">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BF17">
         <v>55</v>
@@ -4852,40 +4852,40 @@
         <v>38</v>
       </c>
       <c r="BH17">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BI17">
         <v>2.42</v>
       </c>
       <c r="BJ17">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BM17">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN17">
         <v>6.4</v>
       </c>
       <c r="BO17">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP17">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BQ17">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR17">
         <v>75</v>
       </c>
       <c r="BS17">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BT17">
         <v>5.2</v>
@@ -4894,22 +4894,22 @@
         <v>4.7</v>
       </c>
       <c r="BV17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BX17">
         <v>60</v>
       </c>
       <c r="BY17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BZ17">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="CA17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CB17" t="s">
         <v>150</v>
@@ -4932,202 +4932,202 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="G18">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="H18">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L18">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O18">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P18">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q18">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="R18">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T18">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U18">
         <v>2.02</v>
       </c>
       <c r="V18">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="X18">
+        <v>17.5</v>
+      </c>
+      <c r="Y18">
+        <v>23</v>
+      </c>
+      <c r="Z18">
+        <v>55</v>
+      </c>
+      <c r="AA18">
+        <v>900</v>
+      </c>
+      <c r="AB18">
+        <v>8.6</v>
+      </c>
+      <c r="AC18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18">
+        <v>25</v>
+      </c>
+      <c r="AE18">
+        <v>200</v>
+      </c>
+      <c r="AF18">
+        <v>9.4</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+      <c r="AH18">
+        <v>22</v>
+      </c>
+      <c r="AI18">
+        <v>90</v>
+      </c>
+      <c r="AJ18">
         <v>15.5</v>
       </c>
-      <c r="Y18">
-        <v>19.5</v>
-      </c>
-      <c r="Z18">
-        <v>44</v>
-      </c>
-      <c r="AA18">
-        <v>150</v>
-      </c>
-      <c r="AB18">
+      <c r="AK18">
+        <v>17</v>
+      </c>
+      <c r="AL18">
+        <v>34</v>
+      </c>
+      <c r="AM18">
+        <v>120</v>
+      </c>
+      <c r="AN18">
+        <v>8.6</v>
+      </c>
+      <c r="AO18">
+        <v>600</v>
+      </c>
+      <c r="AP18">
+        <v>15</v>
+      </c>
+      <c r="AQ18">
+        <v>20</v>
+      </c>
+      <c r="AR18">
+        <v>46</v>
+      </c>
+      <c r="AS18">
+        <v>110</v>
+      </c>
+      <c r="AT18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU18">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC18">
-        <v>9</v>
-      </c>
-      <c r="AD18">
-        <v>22</v>
-      </c>
-      <c r="AE18">
-        <v>80</v>
-      </c>
-      <c r="AF18">
-        <v>10</v>
-      </c>
-      <c r="AG18">
-        <v>10.5</v>
-      </c>
-      <c r="AH18">
+      <c r="AV18">
         <v>21</v>
-      </c>
-      <c r="AI18">
-        <v>320</v>
-      </c>
-      <c r="AJ18">
-        <v>18</v>
-      </c>
-      <c r="AK18">
-        <v>19</v>
-      </c>
-      <c r="AL18">
-        <v>95</v>
-      </c>
-      <c r="AM18">
-        <v>580</v>
-      </c>
-      <c r="AN18">
-        <v>10.5</v>
-      </c>
-      <c r="AO18">
-        <v>85</v>
-      </c>
-      <c r="AP18">
-        <v>13.5</v>
-      </c>
-      <c r="AQ18">
-        <v>17</v>
-      </c>
-      <c r="AR18">
-        <v>32</v>
-      </c>
-      <c r="AS18">
-        <v>90</v>
-      </c>
-      <c r="AT18">
-        <v>8</v>
-      </c>
-      <c r="AU18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV18">
-        <v>18.5</v>
       </c>
       <c r="AW18">
         <v>60</v>
       </c>
       <c r="AX18">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY18">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA18">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BB18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE18">
         <v>80</v>
       </c>
       <c r="BF18">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BG18">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BH18">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BI18">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BN18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO18">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS18">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BT18">
         <v>9.800000000000001</v>
@@ -5139,19 +5139,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BZ18">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="CA18">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="CB18" t="s">
         <v>150</v>
@@ -5174,64 +5174,64 @@
         <v>143</v>
       </c>
       <c r="F19">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="L19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q19">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="R19">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S19">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T19">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="U19">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V19">
         <v>1.2</v>
       </c>
       <c r="W19">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z19">
         <v>120</v>
@@ -5240,25 +5240,25 @@
         <v>900</v>
       </c>
       <c r="AB19">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE19">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF19">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG19">
         <v>11.5</v>
       </c>
       <c r="AH19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI19">
         <v>190</v>
@@ -5270,82 +5270,82 @@
         <v>21</v>
       </c>
       <c r="AL19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM19">
         <v>580</v>
       </c>
       <c r="AN19">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO19">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP19">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AQ19">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR19">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AS19">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="AT19">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AU19">
         <v>5.6</v>
       </c>
       <c r="AV19">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AW19">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AX19">
+        <v>3.35</v>
+      </c>
+      <c r="AY19">
+        <v>2.96</v>
+      </c>
+      <c r="AZ19">
+        <v>3.35</v>
+      </c>
+      <c r="BA19">
+        <v>3.75</v>
+      </c>
+      <c r="BB19">
+        <v>3.35</v>
+      </c>
+      <c r="BC19">
+        <v>3.35</v>
+      </c>
+      <c r="BD19">
+        <v>3.6</v>
+      </c>
+      <c r="BE19">
+        <v>3.85</v>
+      </c>
+      <c r="BF19">
+        <v>2.96</v>
+      </c>
+      <c r="BG19">
         <v>3.8</v>
       </c>
-      <c r="AY19">
-        <v>3.65</v>
-      </c>
-      <c r="AZ19">
-        <v>4.4</v>
-      </c>
-      <c r="BA19">
-        <v>5</v>
-      </c>
-      <c r="BB19">
-        <v>4.3</v>
-      </c>
-      <c r="BC19">
-        <v>4.2</v>
-      </c>
-      <c r="BD19">
-        <v>4.7</v>
-      </c>
-      <c r="BE19">
-        <v>5.1</v>
-      </c>
-      <c r="BF19">
-        <v>3.75</v>
-      </c>
-      <c r="BG19">
-        <v>5.1</v>
-      </c>
       <c r="BH19">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI19">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5354,46 +5354,46 @@
         <v>5.6</v>
       </c>
       <c r="BN19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO19">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BP19">
         <v>13.5</v>
       </c>
       <c r="BQ19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS19">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BT19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW19">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY19">
         <v>5.3</v>
       </c>
       <c r="BZ19">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB19" t="s">
         <v>150</v>
@@ -5416,19 +5416,19 @@
         <v>144</v>
       </c>
       <c r="F20">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="G20">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="H20">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="I20">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="J20">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K20">
         <v>3.35</v>
@@ -5437,37 +5437,37 @@
         <v>1.49</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O20">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P20">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q20">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R20">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T20">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U20">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X20">
         <v>11.5</v>
@@ -5476,40 +5476,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z20">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA20">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC20">
         <v>7.6</v>
       </c>
       <c r="AD20">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE20">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL20">
         <v>55</v>
@@ -5518,37 +5518,37 @@
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO20">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP20">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR20">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS20">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AT20">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU20">
         <v>6.6</v>
       </c>
       <c r="AV20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW20">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX20">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY20">
         <v>11</v>
@@ -5557,13 +5557,13 @@
         <v>16.5</v>
       </c>
       <c r="BA20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB20">
         <v>36</v>
       </c>
       <c r="BC20">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD20">
         <v>38</v>
@@ -5572,70 +5572,70 @@
         <v>85</v>
       </c>
       <c r="BF20">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG20">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BH20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI20">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="BJ20">
         <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN20">
         <v>6</v>
       </c>
       <c r="BO20">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP20">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BQ20">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS20">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT20">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BU20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY20">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20">
         <v>38</v>
       </c>
       <c r="CA20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB20" t="s">
         <v>150</v>
@@ -5658,19 +5658,19 @@
         <v>145</v>
       </c>
       <c r="F21">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G21">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H21">
         <v>4.9</v>
       </c>
       <c r="I21">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J21">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K21">
         <v>4</v>
@@ -5682,37 +5682,37 @@
         <v>1.07</v>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O21">
         <v>1.34</v>
       </c>
       <c r="P21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q21">
         <v>2.04</v>
       </c>
       <c r="R21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T21">
         <v>1.89</v>
       </c>
       <c r="U21">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V21">
         <v>1.23</v>
       </c>
       <c r="W21">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X21">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y21">
         <v>17</v>
@@ -5745,7 +5745,7 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ21">
         <v>21</v>
@@ -5754,19 +5754,19 @@
         <v>21</v>
       </c>
       <c r="AL21">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM21">
         <v>440</v>
       </c>
       <c r="AN21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO21">
         <v>100</v>
       </c>
       <c r="AP21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21">
         <v>14</v>
@@ -5775,10 +5775,10 @@
         <v>29</v>
       </c>
       <c r="AS21">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AT21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU21">
         <v>7.6</v>
@@ -5799,7 +5799,7 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB21">
         <v>16.5</v>
@@ -5811,7 +5811,7 @@
         <v>32</v>
       </c>
       <c r="BE21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF21">
         <v>11</v>
@@ -5820,7 +5820,7 @@
         <v>50</v>
       </c>
       <c r="BH21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI21">
         <v>2.76</v>
@@ -5829,13 +5829,13 @@
         <v>11</v>
       </c>
       <c r="BK21">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN21">
         <v>4.5</v>
@@ -5847,37 +5847,37 @@
         <v>13</v>
       </c>
       <c r="BQ21">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BR21">
         <v>30</v>
       </c>
       <c r="BS21">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT21">
         <v>8.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV21">
         <v>48</v>
       </c>
       <c r="BW21">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BX21">
         <v>60</v>
       </c>
       <c r="BY21">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ21">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="CA21">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB21" t="s">
         <v>150</v>
@@ -5900,7 +5900,7 @@
         <v>146</v>
       </c>
       <c r="F22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G22">
         <v>3.65</v>
@@ -5915,22 +5915,22 @@
         <v>3</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
         <v>1.67</v>
       </c>
       <c r="M22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N22">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P22">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q22">
         <v>2.98</v>
@@ -5948,7 +5948,7 @@
         <v>1.73</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W22">
         <v>1.37</v>
@@ -5957,7 +5957,7 @@
         <v>7.8</v>
       </c>
       <c r="Y22">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z22">
         <v>14</v>
@@ -5981,7 +5981,7 @@
         <v>23</v>
       </c>
       <c r="AG22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH22">
         <v>28</v>
@@ -5990,25 +5990,25 @@
         <v>150</v>
       </c>
       <c r="AJ22">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AK22">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AL22">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AM22">
         <v>1000</v>
       </c>
       <c r="AN22">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AO22">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AP22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ22">
         <v>6.6</v>
@@ -6020,7 +6020,7 @@
         <v>32</v>
       </c>
       <c r="AT22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU22">
         <v>6.4</v>
@@ -6035,28 +6035,28 @@
         <v>19.5</v>
       </c>
       <c r="AY22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA22">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BB22">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BC22">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BD22">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BE22">
         <v>70</v>
       </c>
       <c r="BF22">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BG22">
         <v>32</v>
@@ -6083,7 +6083,7 @@
         <v>6.6</v>
       </c>
       <c r="BO22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP22">
         <v>40</v>
@@ -6101,7 +6101,7 @@
         <v>5.1</v>
       </c>
       <c r="BU22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV22">
         <v>24</v>
@@ -6142,10 +6142,10 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G23">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H23">
         <v>3.5</v>
@@ -6154,10 +6154,10 @@
         <v>3.7</v>
       </c>
       <c r="J23">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L23">
         <v>1.52</v>
@@ -6184,7 +6184,7 @@
         <v>4.8</v>
       </c>
       <c r="T23">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U23">
         <v>1.9</v>
@@ -6202,10 +6202,10 @@
         <v>11</v>
       </c>
       <c r="Z23">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA23">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="AB23">
         <v>8.199999999999999</v>
@@ -6229,16 +6229,16 @@
         <v>22</v>
       </c>
       <c r="AI23">
-        <v>450</v>
+        <v>170</v>
       </c>
       <c r="AJ23">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AK23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL23">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AM23">
         <v>580</v>
@@ -6250,7 +6250,7 @@
         <v>500</v>
       </c>
       <c r="AP23">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ23">
         <v>9.199999999999999</v>
@@ -6259,10 +6259,10 @@
         <v>20</v>
       </c>
       <c r="AS23">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU23">
         <v>6.2</v>
@@ -6271,7 +6271,7 @@
         <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX23">
         <v>12</v>
@@ -6283,25 +6283,25 @@
         <v>17.5</v>
       </c>
       <c r="BA23">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB23">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC23">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD23">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BE23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="BF23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG23">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="BH23">
         <v>2.96</v>
@@ -6384,25 +6384,25 @@
         <v>148</v>
       </c>
       <c r="F24">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H24">
         <v>5.2</v>
       </c>
       <c r="I24">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K24">
         <v>3.6</v>
       </c>
       <c r="L24">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M24">
         <v>1.1</v>
@@ -6411,13 +6411,13 @@
         <v>3.05</v>
       </c>
       <c r="O24">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P24">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q24">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
         <v>1.25</v>
@@ -6426,19 +6426,19 @@
         <v>4.8</v>
       </c>
       <c r="T24">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U24">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y24">
         <v>14.5</v>
@@ -6450,25 +6450,25 @@
         <v>160</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>22</v>
       </c>
       <c r="AE24">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AF24">
         <v>10</v>
       </c>
       <c r="AG24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24">
         <v>110</v>
@@ -6477,7 +6477,7 @@
         <v>21</v>
       </c>
       <c r="AK24">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL24">
         <v>55</v>
@@ -6486,13 +6486,13 @@
         <v>580</v>
       </c>
       <c r="AN24">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO24">
         <v>130</v>
       </c>
       <c r="AP24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ24">
         <v>13</v>
@@ -6501,49 +6501,49 @@
         <v>32</v>
       </c>
       <c r="AS24">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT24">
         <v>6.4</v>
       </c>
       <c r="AU24">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV24">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW24">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AX24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY24">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24">
         <v>22</v>
       </c>
       <c r="BA24">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BB24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC24">
         <v>20</v>
       </c>
       <c r="BD24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE24">
+        <v>20</v>
+      </c>
+      <c r="BF24">
         <v>16.5</v>
       </c>
-      <c r="BF24">
-        <v>16</v>
-      </c>
       <c r="BG24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BH24">
         <v>2.96</v>
@@ -6552,58 +6552,58 @@
         <v>2.72</v>
       </c>
       <c r="BJ24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN24">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO24">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP24">
         <v>15</v>
       </c>
       <c r="BQ24">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR24">
         <v>36</v>
       </c>
       <c r="BS24">
+        <v>10</v>
+      </c>
+      <c r="BT24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU24">
         <v>7.2</v>
       </c>
-      <c r="BT24">
-        <v>8.4</v>
-      </c>
-      <c r="BU24">
-        <v>5.4</v>
-      </c>
       <c r="BV24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW24">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BX24">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY24">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BZ24">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="CA24">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="s">
         <v>150</v>
@@ -6626,7 +6626,7 @@
         <v>149</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G25">
         <v>4.4</v>
@@ -6635,7 +6635,7 @@
         <v>2.06</v>
       </c>
       <c r="I25">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J25">
         <v>3.4</v>
@@ -6671,10 +6671,10 @@
         <v>1.93</v>
       </c>
       <c r="U25">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V25">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W25">
         <v>1.3</v>
@@ -6743,22 +6743,22 @@
         <v>10.5</v>
       </c>
       <c r="AS25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT25">
         <v>11.5</v>
       </c>
       <c r="AU25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV25">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW25">
         <v>21</v>
       </c>
       <c r="AX25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY25">
         <v>15</v>
@@ -6770,19 +6770,19 @@
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC25">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BD25">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE25">
         <v>10</v>
       </c>
       <c r="BF25">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BG25">
         <v>16.5</v>
@@ -6791,25 +6791,25 @@
         <v>3.55</v>
       </c>
       <c r="BI25">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BJ25">
         <v>12.5</v>
       </c>
       <c r="BK25">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN25">
         <v>8.800000000000001</v>
       </c>
       <c r="BO25">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP25">
         <v>46</v>
@@ -6833,7 +6833,7 @@
         <v>19</v>
       </c>
       <c r="BW25">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BX25">
         <v>40</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -466,7 +466,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-21 08:00:59</t>
+    <t>2026-09-21 10:12:17</t>
   </si>
 </sst>
 </file>
@@ -1060,22 +1060,22 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="G2">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.39</v>
@@ -1084,202 +1084,202 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z2">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AB2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
         <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
         <v>36</v>
       </c>
       <c r="AM2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AP2">
         <v>14</v>
       </c>
       <c r="AQ2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AR2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
+        <v>8.6</v>
+      </c>
+      <c r="AV2">
+        <v>22</v>
+      </c>
+      <c r="AW2">
+        <v>14</v>
+      </c>
+      <c r="AX2">
         <v>7.8</v>
       </c>
-      <c r="AV2">
-        <v>18.5</v>
-      </c>
-      <c r="AW2">
-        <v>46</v>
-      </c>
-      <c r="AX2">
-        <v>8.4</v>
-      </c>
       <c r="AY2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BC2">
         <v>15</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="BH2">
         <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
         <v>28</v>
       </c>
       <c r="BS2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
+        <v>10.5</v>
+      </c>
+      <c r="BU2">
+        <v>5.3</v>
+      </c>
+      <c r="BV2">
+        <v>60</v>
+      </c>
+      <c r="BW2">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU2">
-        <v>4.9</v>
-      </c>
-      <c r="BV2">
-        <v>55</v>
-      </c>
-      <c r="BW2">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
         <v>150</v>
@@ -1302,226 +1302,226 @@
         <v>127</v>
       </c>
       <c r="F3">
+        <v>1.18</v>
+      </c>
+      <c r="G3">
+        <v>1.22</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <v>8.4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
         <v>1.2</v>
       </c>
-      <c r="G3">
-        <v>1.24</v>
-      </c>
-      <c r="H3">
-        <v>17</v>
-      </c>
-      <c r="I3">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>1.26</v>
-      </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="O3">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="P3">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="Q3">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="R3">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W3">
         <v>5.5</v>
       </c>
       <c r="X3">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="Y3">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="Z3">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
+        <v>15</v>
+      </c>
+      <c r="AC3">
+        <v>23</v>
+      </c>
+      <c r="AD3">
+        <v>80</v>
+      </c>
+      <c r="AE3">
+        <v>270</v>
+      </c>
+      <c r="AF3">
         <v>11</v>
       </c>
-      <c r="AC3">
-        <v>21</v>
-      </c>
-      <c r="AD3">
-        <v>90</v>
-      </c>
-      <c r="AE3">
-        <v>510</v>
-      </c>
-      <c r="AF3">
-        <v>8.6</v>
-      </c>
       <c r="AG3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI3">
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AK3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AM3">
-        <v>340</v>
+        <v>180</v>
       </c>
       <c r="AN3">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP3">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AQ3">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AU3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AV3">
-        <v>6.4</v>
+        <v>42</v>
       </c>
       <c r="AW3">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AX3">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BB3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC3">
         <v>11.5</v>
       </c>
       <c r="BD3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE3">
+        <v>10.5</v>
+      </c>
+      <c r="BF3">
+        <v>2.64</v>
+      </c>
+      <c r="BG3">
+        <v>10</v>
+      </c>
+      <c r="BH3">
+        <v>5.9</v>
+      </c>
+      <c r="BI3">
+        <v>4.4</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
         <v>6.2</v>
-      </c>
-      <c r="BE3">
-        <v>6.6</v>
-      </c>
-      <c r="BF3">
-        <v>3.1</v>
-      </c>
-      <c r="BG3">
-        <v>15</v>
-      </c>
-      <c r="BH3">
-        <v>5.2</v>
-      </c>
-      <c r="BI3">
-        <v>3.65</v>
-      </c>
-      <c r="BJ3">
-        <v>17.5</v>
-      </c>
-      <c r="BK3">
-        <v>5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="BP3">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BQ3">
         <v>4.9</v>
       </c>
       <c r="BR3">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BS3">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BU3">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
+        <v>10</v>
+      </c>
+      <c r="BZ3">
         <v>6.8</v>
       </c>
-      <c r="BZ3">
-        <v>9.199999999999999</v>
-      </c>
       <c r="CA3">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="CB3" t="s">
         <v>150</v>
@@ -1544,37 +1544,37 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="G4">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.48</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -1586,184 +1586,184 @@
         <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U4">
         <v>1.98</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
         <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
         <v>48</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AK4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL4">
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AO4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP4">
         <v>10</v>
       </c>
       <c r="AQ4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
+        <v>34</v>
+      </c>
+      <c r="AX4">
+        <v>13.5</v>
+      </c>
+      <c r="AY4">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4">
+        <v>17.5</v>
+      </c>
+      <c r="BA4">
+        <v>42</v>
+      </c>
+      <c r="BB4">
+        <v>32</v>
+      </c>
+      <c r="BC4">
         <v>27</v>
       </c>
-      <c r="AX4">
-        <v>14</v>
-      </c>
-      <c r="AY4">
-        <v>11</v>
-      </c>
-      <c r="AZ4">
-        <v>16.5</v>
-      </c>
-      <c r="BA4">
+      <c r="BD4">
         <v>40</v>
       </c>
-      <c r="BB4">
-        <v>30</v>
-      </c>
-      <c r="BC4">
-        <v>25</v>
-      </c>
-      <c r="BD4">
-        <v>36</v>
-      </c>
       <c r="BE4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF4">
         <v>24</v>
       </c>
       <c r="BG4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BN4">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
         <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BQ4">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR4">
         <v>38</v>
       </c>
       <c r="BS4">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BT4">
         <v>6.2</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BW4">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BX4">
         <v>42</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB4" t="s">
         <v>150</v>
@@ -1786,46 +1786,46 @@
         <v>129</v>
       </c>
       <c r="F5">
+        <v>2.8</v>
+      </c>
+      <c r="G5">
+        <v>2.88</v>
+      </c>
+      <c r="H5">
+        <v>2.96</v>
+      </c>
+      <c r="I5">
+        <v>3.05</v>
+      </c>
+      <c r="J5">
         <v>3.15</v>
       </c>
-      <c r="G5">
+      <c r="K5">
         <v>3.2</v>
       </c>
-      <c r="H5">
-        <v>2.62</v>
-      </c>
-      <c r="I5">
-        <v>2.66</v>
-      </c>
-      <c r="J5">
-        <v>3.2</v>
-      </c>
-      <c r="K5">
-        <v>3.25</v>
-      </c>
       <c r="L5">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M5">
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T5">
         <v>1.89</v>
@@ -1834,178 +1834,178 @@
         <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="X5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL5">
         <v>55</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO5">
+        <v>40</v>
+      </c>
+      <c r="AP5">
+        <v>9.6</v>
+      </c>
+      <c r="AQ5">
+        <v>9.4</v>
+      </c>
+      <c r="AR5">
+        <v>17</v>
+      </c>
+      <c r="AS5">
+        <v>38</v>
+      </c>
+      <c r="AT5">
+        <v>9</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>11.5</v>
+      </c>
+      <c r="AW5">
         <v>32</v>
       </c>
-      <c r="AP5">
-        <v>10</v>
-      </c>
-      <c r="AQ5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR5">
-        <v>14.5</v>
-      </c>
-      <c r="AS5">
-        <v>34</v>
-      </c>
-      <c r="AT5">
-        <v>10</v>
-      </c>
-      <c r="AU5">
-        <v>6.8</v>
-      </c>
-      <c r="AV5">
-        <v>11</v>
-      </c>
-      <c r="AW5">
-        <v>28</v>
-      </c>
       <c r="AX5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF5">
+        <v>32</v>
+      </c>
+      <c r="BG5">
         <v>36</v>
       </c>
-      <c r="BG5">
-        <v>26</v>
-      </c>
       <c r="BH5">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BI5">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5">
         <v>170</v>
       </c>
       <c r="BM5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BO5">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BQ5">
+        <v>6.4</v>
+      </c>
+      <c r="BR5">
+        <v>42</v>
+      </c>
+      <c r="BS5">
+        <v>7</v>
+      </c>
+      <c r="BT5">
+        <v>6.6</v>
+      </c>
+      <c r="BU5">
+        <v>5.3</v>
+      </c>
+      <c r="BV5">
+        <v>28</v>
+      </c>
+      <c r="BW5">
+        <v>6.4</v>
+      </c>
+      <c r="BX5">
+        <v>40</v>
+      </c>
+      <c r="BY5">
         <v>6.8</v>
       </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>7.4</v>
-      </c>
-      <c r="BT5">
-        <v>6.2</v>
-      </c>
-      <c r="BU5">
-        <v>4.9</v>
-      </c>
-      <c r="BV5">
-        <v>21</v>
-      </c>
-      <c r="BW5">
-        <v>6.2</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>7.2</v>
-      </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="s">
         <v>150</v>
@@ -2028,70 +2028,70 @@
         <v>130</v>
       </c>
       <c r="F6">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G6">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="H6">
         <v>5.1</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R6">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
         <v>1.22</v>
       </c>
       <c r="W6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="X6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z6">
         <v>55</v>
       </c>
       <c r="AA6">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB6">
         <v>12.5</v>
@@ -2103,67 +2103,67 @@
         <v>23</v>
       </c>
       <c r="AE6">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AF6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI6">
         <v>60</v>
       </c>
       <c r="AJ6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL6">
         <v>30</v>
       </c>
       <c r="AM6">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
         <v>20</v>
       </c>
       <c r="AR6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AV6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW6">
         <v>42</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
         <v>16</v>
@@ -2172,82 +2172,82 @@
         <v>46</v>
       </c>
       <c r="BB6">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE6">
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN6">
         <v>5.4</v>
       </c>
       <c r="BO6">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BR6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BT6">
         <v>11</v>
       </c>
       <c r="BU6">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BV6">
         <v>48</v>
       </c>
       <c r="BW6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY6">
         <v>4.2</v>
       </c>
       <c r="BZ6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA6">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="CB6" t="s">
         <v>150</v>
@@ -2270,46 +2270,46 @@
         <v>131</v>
       </c>
       <c r="F7">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G7">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="H7">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
+        <v>2.96</v>
+      </c>
+      <c r="J7">
         <v>3.1</v>
-      </c>
-      <c r="J7">
-        <v>3.05</v>
       </c>
       <c r="K7">
         <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P7">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
         <v>1.84</v>
@@ -2318,10 +2318,10 @@
         <v>1.94</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X7">
         <v>12</v>
@@ -2333,7 +2333,7 @@
         <v>19</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2357,16 +2357,16 @@
         <v>20</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ7">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AK7">
         <v>40</v>
       </c>
       <c r="AL7">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2387,7 +2387,7 @@
         <v>15</v>
       </c>
       <c r="AS7">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT7">
         <v>8.4</v>
@@ -2399,37 +2399,37 @@
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX7">
         <v>15.5</v>
       </c>
       <c r="AY7">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
+        <v>7.8</v>
+      </c>
+      <c r="BB7">
+        <v>10</v>
+      </c>
+      <c r="BC7">
+        <v>16.5</v>
+      </c>
+      <c r="BD7">
+        <v>11.5</v>
+      </c>
+      <c r="BE7">
+        <v>9.6</v>
+      </c>
+      <c r="BF7">
         <v>7.6</v>
       </c>
-      <c r="BB7">
-        <v>7.4</v>
-      </c>
-      <c r="BC7">
-        <v>8</v>
-      </c>
-      <c r="BD7">
-        <v>7.6</v>
-      </c>
-      <c r="BE7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF7">
-        <v>7.2</v>
-      </c>
       <c r="BG7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BH7">
         <v>3.15</v>
@@ -2447,7 +2447,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7">
         <v>6.2</v>
@@ -2483,7 +2483,7 @@
         <v>42</v>
       </c>
       <c r="BY7">
-        <v>2.26</v>
+        <v>8</v>
       </c>
       <c r="BZ7">
         <v>38</v>
@@ -2512,178 +2512,178 @@
         <v>132</v>
       </c>
       <c r="F8">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="G8">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="H8">
-        <v>3.65</v>
+        <v>2.96</v>
       </c>
       <c r="I8">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="J8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
         <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="X8">
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AA8">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
         <v>8.199999999999999</v>
       </c>
       <c r="AD8">
+        <v>14</v>
+      </c>
+      <c r="AE8">
+        <v>36</v>
+      </c>
+      <c r="AF8">
+        <v>19</v>
+      </c>
+      <c r="AG8">
+        <v>13</v>
+      </c>
+      <c r="AH8">
+        <v>18</v>
+      </c>
+      <c r="AI8">
+        <v>55</v>
+      </c>
+      <c r="AJ8">
+        <v>55</v>
+      </c>
+      <c r="AK8">
+        <v>32</v>
+      </c>
+      <c r="AL8">
+        <v>55</v>
+      </c>
+      <c r="AM8">
+        <v>120</v>
+      </c>
+      <c r="AN8">
+        <v>28</v>
+      </c>
+      <c r="AO8">
+        <v>36</v>
+      </c>
+      <c r="AP8">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8">
+        <v>9.6</v>
+      </c>
+      <c r="AR8">
         <v>17</v>
       </c>
-      <c r="AE8">
-        <v>65</v>
-      </c>
-      <c r="AF8">
-        <v>14</v>
-      </c>
-      <c r="AG8">
-        <v>11.5</v>
-      </c>
-      <c r="AH8">
-        <v>19</v>
-      </c>
-      <c r="AI8">
-        <v>70</v>
-      </c>
-      <c r="AJ8">
-        <v>30</v>
-      </c>
-      <c r="AK8">
+      <c r="AS8">
+        <v>36</v>
+      </c>
+      <c r="AT8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>11</v>
+      </c>
+      <c r="AW8">
         <v>25</v>
       </c>
-      <c r="AL8">
-        <v>46</v>
-      </c>
-      <c r="AM8">
-        <v>500</v>
-      </c>
-      <c r="AN8">
-        <v>19</v>
-      </c>
-      <c r="AO8">
-        <v>75</v>
-      </c>
-      <c r="AP8">
-        <v>4.9</v>
-      </c>
-      <c r="AQ8">
-        <v>11.5</v>
-      </c>
-      <c r="AR8">
-        <v>18</v>
-      </c>
-      <c r="AS8">
-        <v>7.2</v>
-      </c>
-      <c r="AT8">
-        <v>7.6</v>
-      </c>
-      <c r="AU8">
-        <v>4</v>
-      </c>
-      <c r="AV8">
-        <v>13.5</v>
-      </c>
-      <c r="AW8">
-        <v>23</v>
-      </c>
       <c r="AX8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AY8">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BE8">
         <v>7.4</v>
       </c>
       <c r="BF8">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BH8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2692,46 +2692,46 @@
         <v>6.8</v>
       </c>
       <c r="BN8">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP8">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BQ8">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS8">
         <v>6</v>
       </c>
       <c r="BT8">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU8">
+        <v>5.1</v>
+      </c>
+      <c r="BV8">
+        <v>29</v>
+      </c>
+      <c r="BW8">
+        <v>5.7</v>
+      </c>
+      <c r="BX8">
+        <v>40</v>
+      </c>
+      <c r="BY8">
         <v>6</v>
       </c>
-      <c r="BV8">
-        <v>36</v>
-      </c>
-      <c r="BW8">
+      <c r="BZ8">
+        <v>34</v>
+      </c>
+      <c r="CA8">
         <v>5.9</v>
-      </c>
-      <c r="BX8">
-        <v>65</v>
-      </c>
-      <c r="BY8">
-        <v>6.2</v>
-      </c>
-      <c r="BZ8">
-        <v>38</v>
-      </c>
-      <c r="CA8">
-        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>150</v>
@@ -2754,22 +2754,22 @@
         <v>133</v>
       </c>
       <c r="F9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G9">
         <v>1.28</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I9">
         <v>21</v>
       </c>
       <c r="J9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L9">
         <v>1.31</v>
@@ -2778,19 +2778,19 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P9">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R9">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S9">
         <v>2.62</v>
@@ -2799,7 +2799,7 @@
         <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V9">
         <v>1.05</v>
@@ -2808,25 +2808,25 @@
         <v>4.5</v>
       </c>
       <c r="X9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z9">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE9">
         <v>400</v>
@@ -2844,19 +2844,19 @@
         <v>280</v>
       </c>
       <c r="AJ9">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK9">
         <v>16</v>
       </c>
       <c r="AL9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM9">
         <v>300</v>
       </c>
       <c r="AN9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -2865,13 +2865,13 @@
         <v>19</v>
       </c>
       <c r="AQ9">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AR9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT9">
         <v>7</v>
@@ -2880,22 +2880,22 @@
         <v>12.5</v>
       </c>
       <c r="AV9">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AW9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX9">
         <v>6.2</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
         <v>9.199999999999999</v>
       </c>
       <c r="BA9">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9">
         <v>7.8</v>
@@ -2904,76 +2904,76 @@
         <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BI9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BK9">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BN9">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BO9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BQ9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR9">
         <v>27</v>
       </c>
       <c r="BS9">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BT9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BU9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9">
         <v>12</v>
       </c>
       <c r="CA9">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB9" t="s">
         <v>150</v>
@@ -2996,85 +2996,85 @@
         <v>134</v>
       </c>
       <c r="F10">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
         <v>2.4</v>
       </c>
       <c r="H10">
+        <v>3.25</v>
+      </c>
+      <c r="I10">
+        <v>3.6</v>
+      </c>
+      <c r="J10">
+        <v>3.35</v>
+      </c>
+      <c r="K10">
+        <v>3.7</v>
+      </c>
+      <c r="L10">
+        <v>1.42</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
         <v>3.4</v>
       </c>
-      <c r="I10">
-        <v>4.2</v>
-      </c>
-      <c r="J10">
-        <v>3.1</v>
-      </c>
-      <c r="K10">
-        <v>3.55</v>
-      </c>
-      <c r="L10">
-        <v>1.44</v>
-      </c>
-      <c r="M10">
-        <v>1.08</v>
-      </c>
-      <c r="N10">
-        <v>3.15</v>
-      </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X10">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA10">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="AB10">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE10">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG10">
         <v>12.5</v>
@@ -3083,139 +3083,139 @@
         <v>22</v>
       </c>
       <c r="AI10">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ10">
         <v>34</v>
       </c>
       <c r="AK10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO10">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AP10">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
         <v>10</v>
       </c>
       <c r="AR10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS10">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="AT10">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="AX10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY10">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
+        <v>24</v>
+      </c>
+      <c r="BB10">
+        <v>13.5</v>
+      </c>
+      <c r="BC10">
+        <v>20</v>
+      </c>
+      <c r="BD10">
         <v>32</v>
       </c>
-      <c r="BB10">
-        <v>20</v>
-      </c>
-      <c r="BC10">
-        <v>17</v>
-      </c>
-      <c r="BD10">
-        <v>27</v>
-      </c>
       <c r="BE10">
-        <v>75</v>
+        <v>7.4</v>
       </c>
       <c r="BF10">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BG10">
-        <v>27</v>
+        <v>6.6</v>
       </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BI10">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP10">
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BR10">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BS10">
+        <v>4.3</v>
+      </c>
+      <c r="BT10">
+        <v>8</v>
+      </c>
+      <c r="BU10">
+        <v>5.5</v>
+      </c>
+      <c r="BV10">
+        <v>36</v>
+      </c>
+      <c r="BW10">
+        <v>4.3</v>
+      </c>
+      <c r="BX10">
+        <v>50</v>
+      </c>
+      <c r="BY10">
         <v>4.4</v>
       </c>
-      <c r="BT10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU10">
-        <v>5.7</v>
-      </c>
-      <c r="BV10">
-        <v>40</v>
-      </c>
-      <c r="BW10">
-        <v>4.4</v>
-      </c>
-      <c r="BX10">
-        <v>60</v>
-      </c>
-      <c r="BY10">
-        <v>4.6</v>
-      </c>
       <c r="BZ10">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB10" t="s">
         <v>150</v>
@@ -3241,13 +3241,13 @@
         <v>2.66</v>
       </c>
       <c r="G11">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H11">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I11">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J11">
         <v>3.75</v>
@@ -3256,7 +3256,7 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
         <v>1.05</v>
@@ -3268,16 +3268,16 @@
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R11">
         <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T11">
         <v>1.6</v>
@@ -3286,16 +3286,16 @@
         <v>2.48</v>
       </c>
       <c r="V11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X11">
         <v>26</v>
       </c>
       <c r="Y11">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z11">
         <v>22</v>
@@ -3307,7 +3307,7 @@
         <v>16.5</v>
       </c>
       <c r="AC11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>15.5</v>
@@ -3337,22 +3337,22 @@
         <v>34</v>
       </c>
       <c r="AM11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
         <v>13</v>
       </c>
       <c r="AR11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS11">
         <v>23</v>
@@ -3361,13 +3361,13 @@
         <v>13</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV11">
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AX11">
         <v>17.5</v>
@@ -3391,25 +3391,25 @@
         <v>10</v>
       </c>
       <c r="BE11">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF11">
         <v>14</v>
       </c>
       <c r="BG11">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="BL11">
         <v>95</v>
@@ -3427,7 +3427,7 @@
         <v>23</v>
       </c>
       <c r="BQ11">
-        <v>13.5</v>
+        <v>3.75</v>
       </c>
       <c r="BR11">
         <v>32</v>
@@ -3439,13 +3439,13 @@
         <v>7.2</v>
       </c>
       <c r="BU11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV11">
         <v>22</v>
       </c>
       <c r="BW11">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="BX11">
         <v>32</v>
@@ -3454,10 +3454,10 @@
         <v>3.95</v>
       </c>
       <c r="BZ11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA11">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="CB11" t="s">
         <v>150</v>
@@ -3480,19 +3480,19 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G12">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H12">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
         <v>4.2</v>
@@ -3507,31 +3507,31 @@
         <v>5.5</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R12">
+        <v>1.62</v>
+      </c>
+      <c r="S12">
+        <v>2.4</v>
+      </c>
+      <c r="T12">
+        <v>1.56</v>
+      </c>
+      <c r="U12">
+        <v>2.46</v>
+      </c>
+      <c r="V12">
+        <v>1.49</v>
+      </c>
+      <c r="W12">
         <v>1.64</v>
-      </c>
-      <c r="S12">
-        <v>2.38</v>
-      </c>
-      <c r="T12">
-        <v>1.47</v>
-      </c>
-      <c r="U12">
-        <v>2.38</v>
-      </c>
-      <c r="V12">
-        <v>1.45</v>
-      </c>
-      <c r="W12">
-        <v>1.67</v>
       </c>
       <c r="X12">
         <v>29</v>
@@ -3540,40 +3540,40 @@
         <v>21</v>
       </c>
       <c r="Z12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB12">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC12">
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH12">
         <v>17.5</v>
       </c>
       <c r="AI12">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -3582,19 +3582,19 @@
         <v>200</v>
       </c>
       <c r="AN12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AR12">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS12">
         <v>5.5</v>
@@ -3621,13 +3621,13 @@
         <v>6.6</v>
       </c>
       <c r="BA12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB12">
         <v>4.6</v>
       </c>
       <c r="BC12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD12">
         <v>4.6</v>
@@ -3636,64 +3636,64 @@
         <v>5.5</v>
       </c>
       <c r="BF12">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG12">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH12">
         <v>5</v>
       </c>
       <c r="BI12">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="BJ12">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BN12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO12">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BP12">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BQ12">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BR12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS12">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BT12">
         <v>7.4</v>
       </c>
       <c r="BU12">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="BV12">
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BX12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY12">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3722,22 +3722,22 @@
         <v>137</v>
       </c>
       <c r="F13">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G13">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I13">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13">
         <v>1.38</v>
@@ -3746,49 +3746,49 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q13">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R13">
         <v>1.4</v>
       </c>
       <c r="S13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T13">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U13">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
         <v>1.19</v>
       </c>
       <c r="W13">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X13">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y13">
         <v>19.5</v>
       </c>
       <c r="Z13">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AA13">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB13">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -3797,61 +3797,61 @@
         <v>23</v>
       </c>
       <c r="AE13">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="AF13">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>23</v>
+      </c>
+      <c r="AI13">
+        <v>90</v>
+      </c>
+      <c r="AJ13">
+        <v>17.5</v>
+      </c>
+      <c r="AK13">
+        <v>18.5</v>
+      </c>
+      <c r="AL13">
+        <v>38</v>
+      </c>
+      <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
         <v>10</v>
       </c>
-      <c r="AH13">
-        <v>25</v>
-      </c>
-      <c r="AI13">
-        <v>240</v>
-      </c>
-      <c r="AJ13">
-        <v>18.5</v>
-      </c>
-      <c r="AK13">
-        <v>27</v>
-      </c>
-      <c r="AL13">
-        <v>44</v>
-      </c>
-      <c r="AM13">
-        <v>700</v>
-      </c>
-      <c r="AN13">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AO13">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AP13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AS13">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AT13">
         <v>7.8</v>
       </c>
       <c r="AU13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW13">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AX13">
         <v>8.800000000000001</v>
@@ -3863,25 +3863,25 @@
         <v>18.5</v>
       </c>
       <c r="BA13">
+        <v>36</v>
+      </c>
+      <c r="BB13">
+        <v>14</v>
+      </c>
+      <c r="BC13">
+        <v>15.5</v>
+      </c>
+      <c r="BD13">
+        <v>29</v>
+      </c>
+      <c r="BE13">
+        <v>29</v>
+      </c>
+      <c r="BF13">
         <v>8.6</v>
       </c>
-      <c r="BB13">
-        <v>13.5</v>
-      </c>
-      <c r="BC13">
-        <v>15</v>
-      </c>
-      <c r="BD13">
-        <v>7.6</v>
-      </c>
-      <c r="BE13">
-        <v>9</v>
-      </c>
-      <c r="BF13">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
         <v>4</v>
@@ -3893,7 +3893,7 @@
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3923,7 +3923,7 @@
         <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3964,19 +3964,19 @@
         <v>138</v>
       </c>
       <c r="F14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G14">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H14">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I14">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
         <v>4.6</v>
@@ -3988,34 +3988,34 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q14">
         <v>1.66</v>
       </c>
       <c r="R14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S14">
         <v>2.68</v>
       </c>
       <c r="T14">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U14">
         <v>2.24</v>
       </c>
       <c r="V14">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X14">
         <v>25</v>
@@ -4027,7 +4027,7 @@
         <v>13</v>
       </c>
       <c r="AA14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB14">
         <v>22</v>
@@ -4042,7 +4042,7 @@
         <v>18</v>
       </c>
       <c r="AF14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG14">
         <v>20</v>
@@ -4069,10 +4069,10 @@
         <v>55</v>
       </c>
       <c r="AO14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14">
         <v>9.4</v>
@@ -4087,10 +4087,10 @@
         <v>17</v>
       </c>
       <c r="AU14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW14">
         <v>14.5</v>
@@ -4108,31 +4108,31 @@
         <v>14.5</v>
       </c>
       <c r="BB14">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC14">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD14">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF14">
         <v>6.8</v>
       </c>
       <c r="BG14">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK14">
         <v>7.2</v>
@@ -4141,10 +4141,10 @@
         <v>110</v>
       </c>
       <c r="BM14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN14">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BO14">
         <v>6.4</v>
@@ -4156,10 +4156,10 @@
         <v>5.9</v>
       </c>
       <c r="BR14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BT14">
         <v>4.9</v>
@@ -4168,7 +4168,7 @@
         <v>4</v>
       </c>
       <c r="BV14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW14">
         <v>8.6</v>
@@ -4177,13 +4177,13 @@
         <v>23</v>
       </c>
       <c r="BY14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA14">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB14" t="s">
         <v>150</v>
@@ -4206,22 +4206,22 @@
         <v>139</v>
       </c>
       <c r="F15">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="G15">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="H15">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="I15">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="J15">
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L15">
         <v>1.4</v>
@@ -4239,67 +4239,67 @@
         <v>2.02</v>
       </c>
       <c r="Q15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U15">
         <v>2.14</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="X15">
+        <v>18</v>
+      </c>
+      <c r="Y15">
+        <v>13</v>
+      </c>
+      <c r="Z15">
         <v>18.5</v>
       </c>
-      <c r="Y15">
-        <v>12</v>
-      </c>
-      <c r="Z15">
+      <c r="AA15">
+        <v>34</v>
+      </c>
+      <c r="AB15">
+        <v>14</v>
+      </c>
+      <c r="AC15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD15">
+        <v>11.5</v>
+      </c>
+      <c r="AE15">
+        <v>28</v>
+      </c>
+      <c r="AF15">
+        <v>32</v>
+      </c>
+      <c r="AG15">
         <v>17.5</v>
       </c>
-      <c r="AA15">
-        <v>65</v>
-      </c>
-      <c r="AB15">
-        <v>13.5</v>
-      </c>
-      <c r="AC15">
-        <v>8.4</v>
-      </c>
-      <c r="AD15">
-        <v>12.5</v>
-      </c>
-      <c r="AE15">
-        <v>34</v>
-      </c>
-      <c r="AF15">
-        <v>27</v>
-      </c>
-      <c r="AG15">
-        <v>14</v>
-      </c>
       <c r="AH15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI15">
         <v>110</v>
       </c>
       <c r="AJ15">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AK15">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AL15">
         <v>150</v>
@@ -4308,25 +4308,25 @@
         <v>200</v>
       </c>
       <c r="AN15">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AO15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AP15">
         <v>13</v>
       </c>
       <c r="AQ15">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS15">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AT15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU15">
         <v>7.2</v>
@@ -4335,94 +4335,94 @@
         <v>10</v>
       </c>
       <c r="AW15">
+        <v>19.5</v>
+      </c>
+      <c r="AX15">
+        <v>21</v>
+      </c>
+      <c r="AY15">
+        <v>12.5</v>
+      </c>
+      <c r="AZ15">
+        <v>14.5</v>
+      </c>
+      <c r="BA15">
+        <v>28</v>
+      </c>
+      <c r="BB15">
         <v>23</v>
       </c>
-      <c r="AX15">
-        <v>18.5</v>
-      </c>
-      <c r="AY15">
-        <v>11</v>
-      </c>
-      <c r="AZ15">
-        <v>14</v>
-      </c>
-      <c r="BA15">
-        <v>16</v>
-      </c>
-      <c r="BB15">
-        <v>28</v>
-      </c>
       <c r="BC15">
+        <v>18</v>
+      </c>
+      <c r="BD15">
         <v>24</v>
       </c>
-      <c r="BD15">
-        <v>30</v>
-      </c>
       <c r="BE15">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="BF15">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BG15">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BH15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI15">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ15">
         <v>11.5</v>
       </c>
       <c r="BK15">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BN15">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO15">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BS15">
+        <v>4.5</v>
+      </c>
+      <c r="BT15">
+        <v>6</v>
+      </c>
+      <c r="BU15">
+        <v>3.9</v>
+      </c>
+      <c r="BV15">
+        <v>19</v>
+      </c>
+      <c r="BW15">
+        <v>3.95</v>
+      </c>
+      <c r="BX15">
+        <v>36</v>
+      </c>
+      <c r="BY15">
         <v>4.3</v>
       </c>
-      <c r="BT15">
-        <v>6.4</v>
-      </c>
-      <c r="BU15">
-        <v>4.1</v>
-      </c>
-      <c r="BV15">
-        <v>22</v>
-      </c>
-      <c r="BW15">
-        <v>3.9</v>
-      </c>
-      <c r="BX15">
-        <v>38</v>
-      </c>
-      <c r="BY15">
-        <v>4.2</v>
-      </c>
       <c r="BZ15">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CA15">
         <v>4.1</v>
@@ -4448,19 +4448,19 @@
         <v>140</v>
       </c>
       <c r="F16">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="G16">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H16">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I16">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
         <v>3.65</v>
@@ -4472,64 +4472,64 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O16">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q16">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R16">
         <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T16">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB16">
         <v>11.5</v>
       </c>
       <c r="AC16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD16">
         <v>12.5</v>
       </c>
       <c r="AE16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF16">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH16">
         <v>18</v>
@@ -4538,19 +4538,19 @@
         <v>44</v>
       </c>
       <c r="AJ16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL16">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM16">
         <v>90</v>
       </c>
       <c r="AN16">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO16">
         <v>29</v>
@@ -4565,7 +4565,7 @@
         <v>17</v>
       </c>
       <c r="AS16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT16">
         <v>10.5</v>
@@ -4574,13 +4574,13 @@
         <v>7.2</v>
       </c>
       <c r="AV16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
         <v>27</v>
       </c>
       <c r="AX16">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4592,22 +4592,22 @@
         <v>34</v>
       </c>
       <c r="BB16">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE16">
         <v>65</v>
       </c>
       <c r="BF16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG16">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BH16">
         <v>3.4</v>
@@ -4619,37 +4619,37 @@
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN16">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO16">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP16">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ16">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BR16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT16">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
@@ -4661,13 +4661,13 @@
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB16" t="s">
         <v>150</v>
@@ -4690,16 +4690,16 @@
         <v>141</v>
       </c>
       <c r="F17">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G17">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H17">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="I17">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4708,7 +4708,7 @@
         <v>3.1</v>
       </c>
       <c r="L17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M17">
         <v>1.14</v>
@@ -4717,10 +4717,10 @@
         <v>2.58</v>
       </c>
       <c r="O17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q17">
         <v>2.86</v>
@@ -4729,46 +4729,46 @@
         <v>1.17</v>
       </c>
       <c r="S17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T17">
         <v>2.24</v>
       </c>
       <c r="U17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V17">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y17">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Z17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB17">
         <v>9.4</v>
       </c>
       <c r="AC17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE17">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG17">
         <v>16</v>
@@ -4786,16 +4786,16 @@
         <v>60</v>
       </c>
       <c r="AL17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM17">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AN17">
         <v>85</v>
       </c>
       <c r="AO17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP17">
         <v>7.4</v>
@@ -4807,31 +4807,31 @@
         <v>13</v>
       </c>
       <c r="AS17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
         <v>34</v>
       </c>
       <c r="AX17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ17">
         <v>22</v>
       </c>
       <c r="BA17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB17">
         <v>60</v>
@@ -4840,76 +4840,76 @@
         <v>50</v>
       </c>
       <c r="BD17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE17">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="BF17">
         <v>55</v>
       </c>
       <c r="BG17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH17">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BI17">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ17">
         <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BL17">
         <v>270</v>
       </c>
       <c r="BM17">
-        <v>16.5</v>
+        <v>200</v>
       </c>
       <c r="BN17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO17">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ17">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BR17">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BS17">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BT17">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU17">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX17">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BY17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA17">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="CB17" t="s">
         <v>150</v>
@@ -4935,58 +4935,58 @@
         <v>1.6</v>
       </c>
       <c r="G18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H18">
         <v>6.2</v>
       </c>
       <c r="I18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K18">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L18">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M18">
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q18">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T18">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U18">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V18">
         <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X18">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y18">
         <v>23</v>
@@ -4995,37 +4995,37 @@
         <v>55</v>
       </c>
       <c r="AA18">
-        <v>900</v>
+        <v>190</v>
       </c>
       <c r="AB18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE18">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF18">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG18">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ18">
         <v>15.5</v>
       </c>
       <c r="AK18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL18">
         <v>34</v>
@@ -5034,19 +5034,19 @@
         <v>120</v>
       </c>
       <c r="AN18">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO18">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS18">
         <v>110</v>
@@ -5055,31 +5055,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW18">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AX18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY18">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA18">
         <v>70</v>
       </c>
       <c r="BB18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD18">
         <v>30</v>
@@ -5088,70 +5088,70 @@
         <v>80</v>
       </c>
       <c r="BF18">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG18">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BH18">
         <v>4.3</v>
       </c>
       <c r="BI18">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM18">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BN18">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BO18">
         <v>3.85</v>
       </c>
       <c r="BP18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ18">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="BR18">
         <v>28</v>
       </c>
       <c r="BS18">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BT18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU18">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ18">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="CB18" t="s">
         <v>150</v>
@@ -5174,193 +5174,193 @@
         <v>143</v>
       </c>
       <c r="F19">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="G19">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="H19">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K19">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O19">
+        <v>1.25</v>
+      </c>
+      <c r="P19">
+        <v>2.08</v>
+      </c>
+      <c r="Q19">
+        <v>1.75</v>
+      </c>
+      <c r="R19">
+        <v>1.42</v>
+      </c>
+      <c r="S19">
+        <v>2.82</v>
+      </c>
+      <c r="T19">
+        <v>1.66</v>
+      </c>
+      <c r="U19">
+        <v>2.08</v>
+      </c>
+      <c r="V19">
         <v>1.27</v>
       </c>
-      <c r="P19">
-        <v>1.92</v>
-      </c>
-      <c r="Q19">
-        <v>1.72</v>
-      </c>
-      <c r="R19">
-        <v>1.36</v>
-      </c>
-      <c r="S19">
-        <v>2.84</v>
-      </c>
-      <c r="T19">
-        <v>1.69</v>
-      </c>
-      <c r="U19">
-        <v>1.94</v>
-      </c>
-      <c r="V19">
-        <v>1.2</v>
-      </c>
       <c r="W19">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="X19">
+        <v>19.5</v>
+      </c>
+      <c r="Y19">
         <v>19</v>
       </c>
-      <c r="Y19">
-        <v>23</v>
-      </c>
       <c r="Z19">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AA19">
         <v>900</v>
       </c>
       <c r="AB19">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC19">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE19">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AF19">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI19">
         <v>190</v>
       </c>
       <c r="AJ19">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK19">
         <v>21</v>
       </c>
       <c r="AL19">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM19">
         <v>580</v>
       </c>
       <c r="AN19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO19">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="AP19">
-        <v>3.25</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19">
-        <v>3.35</v>
+        <v>14</v>
       </c>
       <c r="AR19">
+        <v>14</v>
+      </c>
+      <c r="AS19">
+        <v>5.7</v>
+      </c>
+      <c r="AT19">
+        <v>7.8</v>
+      </c>
+      <c r="AU19">
+        <v>7.4</v>
+      </c>
+      <c r="AV19">
+        <v>14</v>
+      </c>
+      <c r="AW19">
+        <v>5.5</v>
+      </c>
+      <c r="AX19">
+        <v>10</v>
+      </c>
+      <c r="AY19">
+        <v>8.4</v>
+      </c>
+      <c r="AZ19">
+        <v>13.5</v>
+      </c>
+      <c r="BA19">
+        <v>5.5</v>
+      </c>
+      <c r="BB19">
+        <v>16.5</v>
+      </c>
+      <c r="BC19">
+        <v>14.5</v>
+      </c>
+      <c r="BD19">
+        <v>13</v>
+      </c>
+      <c r="BE19">
+        <v>5.7</v>
+      </c>
+      <c r="BF19">
+        <v>9</v>
+      </c>
+      <c r="BG19">
+        <v>5.5</v>
+      </c>
+      <c r="BH19">
+        <v>4.3</v>
+      </c>
+      <c r="BI19">
+        <v>3.1</v>
+      </c>
+      <c r="BJ19">
+        <v>11</v>
+      </c>
+      <c r="BK19">
         <v>3.65</v>
-      </c>
-      <c r="AS19">
-        <v>3.85</v>
-      </c>
-      <c r="AT19">
-        <v>3.2</v>
-      </c>
-      <c r="AU19">
-        <v>5.6</v>
-      </c>
-      <c r="AV19">
-        <v>3.4</v>
-      </c>
-      <c r="AW19">
-        <v>3.75</v>
-      </c>
-      <c r="AX19">
-        <v>3.35</v>
-      </c>
-      <c r="AY19">
-        <v>2.96</v>
-      </c>
-      <c r="AZ19">
-        <v>3.35</v>
-      </c>
-      <c r="BA19">
-        <v>3.75</v>
-      </c>
-      <c r="BB19">
-        <v>3.35</v>
-      </c>
-      <c r="BC19">
-        <v>3.35</v>
-      </c>
-      <c r="BD19">
-        <v>3.6</v>
-      </c>
-      <c r="BE19">
-        <v>3.85</v>
-      </c>
-      <c r="BF19">
-        <v>2.96</v>
-      </c>
-      <c r="BG19">
-        <v>3.8</v>
-      </c>
-      <c r="BH19">
-        <v>4.1</v>
-      </c>
-      <c r="BI19">
-        <v>3</v>
-      </c>
-      <c r="BJ19">
-        <v>11.5</v>
-      </c>
-      <c r="BK19">
-        <v>3.85</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BN19">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BO19">
-        <v>2.68</v>
+        <v>3.8</v>
       </c>
       <c r="BP19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ19">
         <v>4</v>
@@ -5369,31 +5369,31 @@
         <v>29</v>
       </c>
       <c r="BS19">
+        <v>4.6</v>
+      </c>
+      <c r="BT19">
+        <v>9</v>
+      </c>
+      <c r="BU19">
+        <v>3.4</v>
+      </c>
+      <c r="BV19">
+        <v>40</v>
+      </c>
+      <c r="BW19">
         <v>4.8</v>
       </c>
-      <c r="BT19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU19">
-        <v>3.65</v>
-      </c>
-      <c r="BV19">
-        <v>50</v>
-      </c>
-      <c r="BW19">
-        <v>5.2</v>
-      </c>
       <c r="BX19">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BY19">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ19">
         <v>23</v>
       </c>
       <c r="CA19">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="CB19" t="s">
         <v>150</v>
@@ -5419,28 +5419,28 @@
         <v>2.98</v>
       </c>
       <c r="G20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H20">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I20">
         <v>2.76</v>
       </c>
       <c r="J20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K20">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L20">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
         <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O20">
         <v>1.41</v>
@@ -5449,31 +5449,31 @@
         <v>1.77</v>
       </c>
       <c r="Q20">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R20">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T20">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U20">
         <v>2.04</v>
       </c>
       <c r="V20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z20">
         <v>17.5</v>
@@ -5485,7 +5485,7 @@
         <v>11</v>
       </c>
       <c r="AC20">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD20">
         <v>12.5</v>
@@ -5500,7 +5500,7 @@
         <v>14</v>
       </c>
       <c r="AH20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI20">
         <v>55</v>
@@ -5509,7 +5509,7 @@
         <v>55</v>
       </c>
       <c r="AK20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL20">
         <v>55</v>
@@ -5521,10 +5521,10 @@
         <v>44</v>
       </c>
       <c r="AO20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP20">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ20">
         <v>8.6</v>
@@ -5533,10 +5533,10 @@
         <v>14.5</v>
       </c>
       <c r="AS20">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU20">
         <v>6.6</v>
@@ -5551,19 +5551,19 @@
         <v>17.5</v>
       </c>
       <c r="AY20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA20">
         <v>38</v>
       </c>
       <c r="BB20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC20">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BD20">
         <v>38</v>
@@ -5572,28 +5572,28 @@
         <v>85</v>
       </c>
       <c r="BF20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG20">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BH20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BI20">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ20">
         <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN20">
         <v>6</v>
@@ -5605,16 +5605,16 @@
         <v>27</v>
       </c>
       <c r="BQ20">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR20">
         <v>44</v>
       </c>
       <c r="BS20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT20">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BU20">
         <v>4.9</v>
@@ -5623,19 +5623,19 @@
         <v>23</v>
       </c>
       <c r="BW20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX20">
         <v>40</v>
       </c>
       <c r="BY20">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ20">
         <v>38</v>
       </c>
       <c r="CA20">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB20" t="s">
         <v>150</v>
@@ -5658,16 +5658,16 @@
         <v>145</v>
       </c>
       <c r="F21">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G21">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J21">
         <v>3.7</v>
@@ -5691,16 +5691,16 @@
         <v>1.89</v>
       </c>
       <c r="Q21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R21">
         <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T21">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U21">
         <v>1.94</v>
@@ -5709,7 +5709,7 @@
         <v>1.23</v>
       </c>
       <c r="W21">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X21">
         <v>14.5</v>
@@ -5721,31 +5721,31 @@
         <v>40</v>
       </c>
       <c r="AA21">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AB21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC21">
         <v>9.199999999999999</v>
       </c>
       <c r="AD21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE21">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG21">
         <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ21">
         <v>21</v>
@@ -5754,40 +5754,40 @@
         <v>21</v>
       </c>
       <c r="AL21">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM21">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="AN21">
         <v>13.5</v>
       </c>
       <c r="AO21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ21">
         <v>14</v>
       </c>
       <c r="AR21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS21">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT21">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU21">
         <v>7.6</v>
       </c>
       <c r="AV21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW21">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AX21">
         <v>9.199999999999999</v>
@@ -5796,13 +5796,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA21">
         <v>48</v>
       </c>
       <c r="BB21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC21">
         <v>17</v>
@@ -5817,7 +5817,7 @@
         <v>11</v>
       </c>
       <c r="BG21">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH21">
         <v>3.75</v>
@@ -5829,13 +5829,13 @@
         <v>11</v>
       </c>
       <c r="BK21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN21">
         <v>4.5</v>
@@ -5847,13 +5847,13 @@
         <v>13</v>
       </c>
       <c r="BQ21">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR21">
         <v>30</v>
       </c>
       <c r="BS21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT21">
         <v>8.800000000000001</v>
@@ -5865,16 +5865,16 @@
         <v>48</v>
       </c>
       <c r="BW21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX21">
         <v>60</v>
       </c>
       <c r="BY21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ21">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CA21">
         <v>6.4</v>
@@ -5900,22 +5900,22 @@
         <v>146</v>
       </c>
       <c r="F22">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G22">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H22">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I22">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
       <c r="K22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L22">
         <v>1.67</v>
@@ -5924,40 +5924,40 @@
         <v>1.15</v>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O22">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="P22">
         <v>1.48</v>
       </c>
       <c r="Q22">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>1.17</v>
       </c>
       <c r="S22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T22">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U22">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V22">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X22">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y22">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z22">
         <v>14</v>
@@ -5972,31 +5972,31 @@
         <v>7</v>
       </c>
       <c r="AD22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF22">
         <v>23</v>
       </c>
       <c r="AG22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH22">
         <v>28</v>
       </c>
       <c r="AI22">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AJ22">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK22">
         <v>70</v>
       </c>
       <c r="AL22">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="AM22">
         <v>1000</v>
@@ -6005,13 +6005,13 @@
         <v>100</v>
       </c>
       <c r="AO22">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AP22">
         <v>7</v>
       </c>
       <c r="AQ22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR22">
         <v>12.5</v>
@@ -6023,7 +6023,7 @@
         <v>8.4</v>
       </c>
       <c r="AU22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
         <v>12</v>
@@ -6044,25 +6044,25 @@
         <v>55</v>
       </c>
       <c r="BB22">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC22">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD22">
         <v>70</v>
       </c>
       <c r="BE22">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="BF22">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BG22">
         <v>32</v>
       </c>
       <c r="BH22">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BI22">
         <v>2.4</v>
@@ -6074,10 +6074,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM22">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="BN22">
         <v>6.6</v>
@@ -6092,16 +6092,16 @@
         <v>11.5</v>
       </c>
       <c r="BR22">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BS22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT22">
         <v>5.1</v>
       </c>
       <c r="BU22">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV22">
         <v>24</v>
@@ -6119,7 +6119,7 @@
         <v>60</v>
       </c>
       <c r="CA22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB22" t="s">
         <v>150</v>
@@ -6142,31 +6142,31 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G23">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J23">
         <v>3.05</v>
       </c>
       <c r="K23">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M23">
         <v>1.11</v>
       </c>
       <c r="N23">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O23">
         <v>1.47</v>
@@ -6178,7 +6178,7 @@
         <v>2.46</v>
       </c>
       <c r="R23">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S23">
         <v>4.8</v>
@@ -6187,7 +6187,7 @@
         <v>1.98</v>
       </c>
       <c r="U23">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V23">
         <v>1.37</v>
@@ -6202,7 +6202,7 @@
         <v>11</v>
       </c>
       <c r="Z23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA23">
         <v>170</v>
@@ -6295,13 +6295,13 @@
         <v>38</v>
       </c>
       <c r="BE23">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BF23">
         <v>23</v>
       </c>
       <c r="BG23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH23">
         <v>2.96</v>
@@ -6313,55 +6313,55 @@
         <v>11</v>
       </c>
       <c r="BK23">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="BN23">
         <v>5.2</v>
       </c>
       <c r="BO23">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BP23">
         <v>21</v>
       </c>
       <c r="BQ23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR23">
         <v>42</v>
       </c>
       <c r="BS23">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT23">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU23">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV23">
         <v>36</v>
       </c>
       <c r="BW23">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23">
         <v>44</v>
       </c>
       <c r="CA23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB23" t="s">
         <v>150</v>
@@ -6384,52 +6384,52 @@
         <v>148</v>
       </c>
       <c r="F24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G24">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H24">
+        <v>5.1</v>
+      </c>
+      <c r="I24">
         <v>5.2</v>
-      </c>
-      <c r="I24">
-        <v>5.3</v>
       </c>
       <c r="J24">
         <v>3.5</v>
       </c>
       <c r="K24">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L24">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N24">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O24">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P24">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S24">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T24">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U24">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V24">
         <v>1.23</v>
@@ -6438,16 +6438,16 @@
         <v>2.08</v>
       </c>
       <c r="X24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA24">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB24">
         <v>6.8</v>
@@ -6456,154 +6456,154 @@
         <v>8</v>
       </c>
       <c r="AD24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE24">
         <v>110</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG24">
         <v>9.800000000000001</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI24">
         <v>110</v>
       </c>
       <c r="AJ24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL24">
         <v>55</v>
       </c>
       <c r="AM24">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="AN24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO24">
         <v>130</v>
       </c>
       <c r="AP24">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR24">
         <v>32</v>
       </c>
       <c r="AS24">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AT24">
         <v>6.4</v>
       </c>
       <c r="AU24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW24">
-        <v>18.5</v>
+        <v>50</v>
       </c>
       <c r="AX24">
+        <v>9.6</v>
+      </c>
+      <c r="AY24">
         <v>9.4</v>
-      </c>
-      <c r="AY24">
-        <v>9.6</v>
       </c>
       <c r="AZ24">
         <v>22</v>
       </c>
       <c r="BA24">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BB24">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD24">
         <v>42</v>
       </c>
       <c r="BE24">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="BF24">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG24">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="BH24">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BI24">
         <v>2.72</v>
       </c>
       <c r="BJ24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK24">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM24">
-        <v>13.5</v>
+        <v>140</v>
       </c>
       <c r="BN24">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BO24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP24">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BQ24">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR24">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BS24">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BT24">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU24">
         <v>7.2</v>
       </c>
       <c r="BV24">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BW24">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BX24">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BY24">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ24">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="CB24" t="s">
         <v>150</v>
@@ -6626,22 +6626,22 @@
         <v>149</v>
       </c>
       <c r="F25">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G25">
         <v>4.4</v>
       </c>
       <c r="H25">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I25">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="J25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>1.47</v>
@@ -6659,25 +6659,25 @@
         <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S25">
         <v>4.2</v>
       </c>
       <c r="T25">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U25">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V25">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="W25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X25">
         <v>12</v>
@@ -6686,28 +6686,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA25">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB25">
         <v>13.5</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD25">
         <v>11</v>
       </c>
       <c r="AE25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF25">
         <v>32</v>
       </c>
       <c r="AG25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH25">
         <v>21</v>
@@ -6716,22 +6716,22 @@
         <v>55</v>
       </c>
       <c r="AJ25">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK25">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL25">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM25">
         <v>450</v>
       </c>
       <c r="AN25">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AO25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP25">
         <v>10</v>
@@ -6770,25 +6770,25 @@
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BC25">
         <v>42</v>
       </c>
       <c r="BD25">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BE25">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="BF25">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BG25">
         <v>16.5</v>
       </c>
       <c r="BH25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI25">
         <v>2.84</v>
@@ -6797,25 +6797,25 @@
         <v>12.5</v>
       </c>
       <c r="BK25">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="BN25">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BO25">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="BP25">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BQ25">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR25">
         <v>65</v>
@@ -6824,25 +6824,25 @@
         <v>4.6</v>
       </c>
       <c r="BT25">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU25">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW25">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BX25">
         <v>40</v>
       </c>
       <c r="BY25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA25">
         <v>4.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-21.xlsx
@@ -466,7 +466,7 @@
     <t>Torque</t>
   </si>
   <si>
-    <t>2026-09-21 10:12:17</t>
+    <t>2026-09-21 12:23:53</t>
   </si>
 </sst>
 </file>
@@ -1060,226 +1060,226 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="G2">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>7.4</v>
+        <v>420</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>22</v>
       </c>
       <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>3.4</v>
+      </c>
+      <c r="O2">
         <v>1.39</v>
       </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4</v>
-      </c>
-      <c r="O2">
-        <v>1.31</v>
-      </c>
       <c r="P2">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="S2">
+        <v>10</v>
+      </c>
+      <c r="T2">
+        <v>6.8</v>
+      </c>
+      <c r="U2">
+        <v>1.14</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>17.5</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>3.55</v>
+      </c>
+      <c r="AC2">
+        <v>34</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>3.2</v>
+      </c>
+      <c r="AG2">
+        <v>25</v>
+      </c>
+      <c r="AH2">
+        <v>490</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>6</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>15</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2">
+        <v>12.5</v>
+      </c>
+      <c r="AR2">
+        <v>12.5</v>
+      </c>
+      <c r="AS2">
+        <v>12.5</v>
+      </c>
+      <c r="AT2">
         <v>3.4</v>
       </c>
-      <c r="T2">
-        <v>1.92</v>
-      </c>
-      <c r="U2">
-        <v>1.93</v>
-      </c>
-      <c r="V2">
-        <v>1.15</v>
-      </c>
-      <c r="W2">
-        <v>2.6</v>
-      </c>
-      <c r="X2">
-        <v>17</v>
-      </c>
-      <c r="Y2">
-        <v>25</v>
-      </c>
-      <c r="Z2">
+      <c r="AU2">
+        <v>22</v>
+      </c>
+      <c r="AV2">
+        <v>160</v>
+      </c>
+      <c r="AW2">
+        <v>70</v>
+      </c>
+      <c r="AX2">
+        <v>2.88</v>
+      </c>
+      <c r="AY2">
+        <v>20</v>
+      </c>
+      <c r="AZ2">
+        <v>11.5</v>
+      </c>
+      <c r="BA2">
+        <v>70</v>
+      </c>
+      <c r="BB2">
+        <v>5.4</v>
+      </c>
+      <c r="BC2">
+        <v>30</v>
+      </c>
+      <c r="BD2">
+        <v>46</v>
+      </c>
+      <c r="BE2">
+        <v>10.5</v>
+      </c>
+      <c r="BF2">
+        <v>9.6</v>
+      </c>
+      <c r="BG2">
         <v>65</v>
       </c>
-      <c r="AA2">
-        <v>250</v>
-      </c>
-      <c r="AB2">
-        <v>7.8</v>
-      </c>
-      <c r="AC2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>28</v>
-      </c>
-      <c r="AE2">
-        <v>120</v>
-      </c>
-      <c r="AF2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2">
-        <v>9.4</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>110</v>
-      </c>
-      <c r="AJ2">
-        <v>15.5</v>
-      </c>
-      <c r="AK2">
-        <v>17.5</v>
-      </c>
-      <c r="AL2">
-        <v>36</v>
-      </c>
-      <c r="AM2">
-        <v>200</v>
-      </c>
-      <c r="AN2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO2">
-        <v>180</v>
-      </c>
-      <c r="AP2">
-        <v>14</v>
-      </c>
-      <c r="AQ2">
-        <v>20</v>
-      </c>
-      <c r="AR2">
-        <v>30</v>
-      </c>
-      <c r="AS2">
-        <v>13</v>
-      </c>
-      <c r="AT2">
-        <v>7.2</v>
-      </c>
-      <c r="AU2">
-        <v>8.6</v>
-      </c>
-      <c r="AV2">
-        <v>22</v>
-      </c>
-      <c r="AW2">
-        <v>14</v>
-      </c>
-      <c r="AX2">
-        <v>7.8</v>
-      </c>
-      <c r="AY2">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2">
-        <v>20</v>
-      </c>
-      <c r="BA2">
-        <v>14</v>
-      </c>
-      <c r="BB2">
-        <v>13</v>
-      </c>
-      <c r="BC2">
-        <v>15</v>
-      </c>
-      <c r="BD2">
-        <v>30</v>
-      </c>
-      <c r="BE2">
-        <v>14</v>
-      </c>
-      <c r="BF2">
-        <v>8.6</v>
-      </c>
-      <c r="BG2">
-        <v>13</v>
-      </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>150</v>
@@ -1302,226 +1302,226 @@
         <v>127</v>
       </c>
       <c r="F3">
+        <v>1.74</v>
+      </c>
+      <c r="G3">
+        <v>1.81</v>
+      </c>
+      <c r="H3">
+        <v>10.5</v>
+      </c>
+      <c r="I3">
+        <v>11.5</v>
+      </c>
+      <c r="J3">
+        <v>2.84</v>
+      </c>
+      <c r="K3">
+        <v>3.05</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.28</v>
+      </c>
+      <c r="N3">
+        <v>1.56</v>
+      </c>
+      <c r="O3">
+        <v>2.58</v>
+      </c>
+      <c r="P3">
+        <v>1.12</v>
+      </c>
+      <c r="Q3">
+        <v>6.8</v>
+      </c>
+      <c r="R3">
+        <v>1.03</v>
+      </c>
+      <c r="S3">
+        <v>26</v>
+      </c>
+      <c r="T3">
+        <v>5.1</v>
+      </c>
+      <c r="U3">
         <v>1.18</v>
-      </c>
-      <c r="G3">
-        <v>1.22</v>
-      </c>
-      <c r="H3">
-        <v>15</v>
-      </c>
-      <c r="I3">
-        <v>19</v>
-      </c>
-      <c r="J3">
-        <v>8.4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>1.2</v>
-      </c>
-      <c r="M3">
-        <v>1.01</v>
-      </c>
-      <c r="N3">
-        <v>9</v>
-      </c>
-      <c r="O3">
-        <v>1.11</v>
-      </c>
-      <c r="P3">
-        <v>3.85</v>
-      </c>
-      <c r="Q3">
-        <v>1.33</v>
-      </c>
-      <c r="R3">
-        <v>2.06</v>
-      </c>
-      <c r="S3">
-        <v>1.87</v>
-      </c>
-      <c r="T3">
-        <v>2</v>
-      </c>
-      <c r="U3">
-        <v>1.84</v>
       </c>
       <c r="V3">
         <v>1.06</v>
       </c>
       <c r="W3">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="X3">
-        <v>65</v>
+        <v>4.4</v>
       </c>
       <c r="Y3">
-        <v>95</v>
+        <v>810</v>
       </c>
       <c r="Z3">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>15</v>
+        <v>3.55</v>
       </c>
       <c r="AC3">
-        <v>23</v>
+        <v>990</v>
       </c>
       <c r="AD3">
-        <v>80</v>
+        <v>990</v>
       </c>
       <c r="AE3">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="AH3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.75</v>
+      </c>
+      <c r="AQ3">
+        <v>11.5</v>
+      </c>
+      <c r="AR3">
+        <v>3.55</v>
+      </c>
+      <c r="AS3">
+        <v>10</v>
+      </c>
+      <c r="AT3">
+        <v>1.77</v>
+      </c>
+      <c r="AU3">
+        <v>3.25</v>
+      </c>
+      <c r="AV3">
+        <v>48</v>
+      </c>
+      <c r="AW3">
+        <v>3.5</v>
+      </c>
+      <c r="AX3">
+        <v>5.6</v>
+      </c>
+      <c r="AY3">
+        <v>3.55</v>
+      </c>
+      <c r="AZ3">
+        <v>3.55</v>
+      </c>
+      <c r="BA3">
+        <v>3.55</v>
+      </c>
+      <c r="BB3">
         <v>14.5</v>
       </c>
-      <c r="AL3">
-        <v>40</v>
-      </c>
-      <c r="AM3">
-        <v>180</v>
-      </c>
-      <c r="AN3">
-        <v>3.05</v>
-      </c>
-      <c r="AO3">
-        <v>300</v>
-      </c>
-      <c r="AP3">
-        <v>42</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
-        <v>10.5</v>
-      </c>
-      <c r="AS3">
-        <v>10.5</v>
-      </c>
-      <c r="AT3">
-        <v>12</v>
-      </c>
-      <c r="AU3">
-        <v>17</v>
-      </c>
-      <c r="AV3">
-        <v>42</v>
-      </c>
-      <c r="AW3">
-        <v>10</v>
-      </c>
-      <c r="AX3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
+      <c r="BC3">
+        <v>3.55</v>
+      </c>
+      <c r="BD3">
+        <v>3.5</v>
+      </c>
+      <c r="BE3">
+        <v>3.5</v>
+      </c>
+      <c r="BF3">
         <v>30</v>
       </c>
-      <c r="BA3">
-        <v>10</v>
-      </c>
-      <c r="BB3">
-        <v>8</v>
-      </c>
-      <c r="BC3">
-        <v>11.5</v>
-      </c>
-      <c r="BD3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE3">
-        <v>10.5</v>
-      </c>
-      <c r="BF3">
-        <v>2.64</v>
-      </c>
       <c r="BG3">
-        <v>10</v>
+        <v>3.55</v>
       </c>
       <c r="BH3">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>150</v>
@@ -1544,226 +1544,226 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="H4">
+        <v>2.92</v>
+      </c>
+      <c r="I4">
+        <v>3.05</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>3.15</v>
+      </c>
+      <c r="L4">
+        <v>1.99</v>
+      </c>
+      <c r="M4">
+        <v>1.15</v>
+      </c>
+      <c r="N4">
+        <v>2.44</v>
+      </c>
+      <c r="O4">
+        <v>1.65</v>
+      </c>
+      <c r="P4">
+        <v>1.45</v>
+      </c>
+      <c r="Q4">
         <v>3.1</v>
       </c>
-      <c r="I4">
-        <v>3.3</v>
-      </c>
-      <c r="J4">
-        <v>3.35</v>
-      </c>
-      <c r="K4">
-        <v>3.5</v>
-      </c>
-      <c r="L4">
-        <v>1.48</v>
-      </c>
-      <c r="M4">
-        <v>1.09</v>
-      </c>
-      <c r="N4">
-        <v>3.15</v>
-      </c>
-      <c r="O4">
-        <v>1.42</v>
-      </c>
-      <c r="P4">
-        <v>1.74</v>
-      </c>
-      <c r="Q4">
-        <v>2.3</v>
-      </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
+        <v>65</v>
+      </c>
+      <c r="AB4">
+        <v>8</v>
+      </c>
+      <c r="AC4">
+        <v>7.2</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
         <v>60</v>
       </c>
-      <c r="AB4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC4">
-        <v>7.6</v>
-      </c>
-      <c r="AD4">
-        <v>16.5</v>
-      </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AI4">
+        <v>100</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
         <v>60</v>
       </c>
-      <c r="AJ4">
-        <v>38</v>
-      </c>
-      <c r="AK4">
-        <v>32</v>
-      </c>
       <c r="AL4">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AM4">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AR4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AS4">
         <v>46</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AX4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BA4">
+        <v>65</v>
+      </c>
+      <c r="BB4">
+        <v>46</v>
+      </c>
+      <c r="BC4">
         <v>42</v>
       </c>
-      <c r="BB4">
-        <v>32</v>
-      </c>
-      <c r="BC4">
-        <v>27</v>
-      </c>
       <c r="BD4">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="BF4">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BG4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BH4">
-        <v>3.55</v>
+        <v>1.97</v>
       </c>
       <c r="BI4">
-        <v>2.84</v>
+        <v>1.9</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BK4">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BL4">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP4">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BQ4">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="BR4">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="BS4">
-        <v>5.3</v>
+        <v>95</v>
       </c>
       <c r="BT4">
         <v>6.2</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BW4">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BX4">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="BY4">
-        <v>5.4</v>
+        <v>85</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="CA4">
-        <v>5.3</v>
+        <v>100</v>
       </c>
       <c r="CB4" t="s">
         <v>150</v>
@@ -1786,226 +1786,226 @@
         <v>129</v>
       </c>
       <c r="F5">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G5">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="H5">
+        <v>3.1</v>
+      </c>
+      <c r="I5">
+        <v>3.15</v>
+      </c>
+      <c r="J5">
         <v>2.96</v>
       </c>
-      <c r="I5">
-        <v>3.05</v>
-      </c>
-      <c r="J5">
-        <v>3.15</v>
-      </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="L5">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>2.44</v>
       </c>
       <c r="W5">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z5">
         <v>18.5</v>
       </c>
       <c r="AA5">
+        <v>60</v>
+      </c>
+      <c r="AB5">
+        <v>8</v>
+      </c>
+      <c r="AC5">
+        <v>6.8</v>
+      </c>
+      <c r="AD5">
+        <v>15.5</v>
+      </c>
+      <c r="AE5">
         <v>50</v>
       </c>
-      <c r="AB5">
-        <v>10</v>
-      </c>
-      <c r="AC5">
-        <v>7</v>
-      </c>
-      <c r="AD5">
-        <v>13</v>
-      </c>
-      <c r="AE5">
-        <v>38</v>
-      </c>
       <c r="AF5">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ5">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AM5">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AP5">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AR5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT5">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
+        <v>42</v>
+      </c>
+      <c r="AX5">
+        <v>15</v>
+      </c>
+      <c r="AY5">
+        <v>13</v>
+      </c>
+      <c r="AZ5">
+        <v>22</v>
+      </c>
+      <c r="BA5">
+        <v>80</v>
+      </c>
+      <c r="BB5">
+        <v>42</v>
+      </c>
+      <c r="BC5">
+        <v>40</v>
+      </c>
+      <c r="BD5">
+        <v>80</v>
+      </c>
+      <c r="BE5">
+        <v>190</v>
+      </c>
+      <c r="BF5">
+        <v>48</v>
+      </c>
+      <c r="BG5">
+        <v>60</v>
+      </c>
+      <c r="BH5">
+        <v>2</v>
+      </c>
+      <c r="BI5">
+        <v>1.95</v>
+      </c>
+      <c r="BJ5">
+        <v>16.5</v>
+      </c>
+      <c r="BK5">
+        <v>15</v>
+      </c>
+      <c r="BL5">
+        <v>880</v>
+      </c>
+      <c r="BM5">
+        <v>30</v>
+      </c>
+      <c r="BN5">
+        <v>5.7</v>
+      </c>
+      <c r="BO5">
+        <v>5.4</v>
+      </c>
+      <c r="BP5">
+        <v>40</v>
+      </c>
+      <c r="BQ5">
         <v>32</v>
       </c>
-      <c r="AX5">
-        <v>16</v>
-      </c>
-      <c r="AY5">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5">
-        <v>16.5</v>
-      </c>
-      <c r="BA5">
-        <v>46</v>
-      </c>
-      <c r="BB5">
-        <v>40</v>
-      </c>
-      <c r="BC5">
-        <v>30</v>
-      </c>
-      <c r="BD5">
-        <v>44</v>
-      </c>
-      <c r="BE5">
+      <c r="BR5">
+        <v>140</v>
+      </c>
+      <c r="BS5">
+        <v>85</v>
+      </c>
+      <c r="BT5">
+        <v>6</v>
+      </c>
+      <c r="BU5">
+        <v>5.7</v>
+      </c>
+      <c r="BV5">
+        <v>48</v>
+      </c>
+      <c r="BW5">
+        <v>34</v>
+      </c>
+      <c r="BX5">
+        <v>140</v>
+      </c>
+      <c r="BY5">
         <v>90</v>
       </c>
-      <c r="BF5">
-        <v>32</v>
-      </c>
-      <c r="BG5">
-        <v>36</v>
-      </c>
-      <c r="BH5">
-        <v>3</v>
-      </c>
-      <c r="BI5">
-        <v>2.82</v>
-      </c>
-      <c r="BJ5">
-        <v>11.5</v>
-      </c>
-      <c r="BK5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL5">
+      <c r="BZ5">
         <v>170</v>
       </c>
-      <c r="BM5">
-        <v>8</v>
-      </c>
-      <c r="BN5">
-        <v>6.4</v>
-      </c>
-      <c r="BO5">
-        <v>5.1</v>
-      </c>
-      <c r="BP5">
-        <v>27</v>
-      </c>
-      <c r="BQ5">
-        <v>6.4</v>
-      </c>
-      <c r="BR5">
-        <v>42</v>
-      </c>
-      <c r="BS5">
-        <v>7</v>
-      </c>
-      <c r="BT5">
-        <v>6.6</v>
-      </c>
-      <c r="BU5">
-        <v>5.3</v>
-      </c>
-      <c r="BV5">
-        <v>28</v>
-      </c>
-      <c r="BW5">
-        <v>6.4</v>
-      </c>
-      <c r="BX5">
-        <v>40</v>
-      </c>
-      <c r="BY5">
-        <v>6.8</v>
-      </c>
-      <c r="BZ5">
-        <v>38</v>
-      </c>
       <c r="CA5">
-        <v>6.8</v>
+        <v>100</v>
       </c>
       <c r="CB5" t="s">
         <v>150</v>
@@ -2028,226 +2028,226 @@
         <v>130</v>
       </c>
       <c r="F6">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="G6">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="H6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>4.4</v>
       </c>
-      <c r="K6">
-        <v>4.7</v>
-      </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="P6">
-        <v>2.52</v>
+        <v>1.86</v>
       </c>
       <c r="Q6">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="S6">
-        <v>2.56</v>
+        <v>3.75</v>
       </c>
       <c r="T6">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
+        <v>1.86</v>
+      </c>
+      <c r="V6">
+        <v>1.21</v>
+      </c>
+      <c r="W6">
         <v>2.34</v>
       </c>
-      <c r="V6">
-        <v>1.22</v>
-      </c>
-      <c r="W6">
-        <v>2.4</v>
-      </c>
       <c r="X6">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="Y6">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="Z6">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA6">
         <v>150</v>
       </c>
       <c r="AB6">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE6">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF6">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
       </c>
       <c r="AH6">
+        <v>29</v>
+      </c>
+      <c r="AI6">
+        <v>100</v>
+      </c>
+      <c r="AJ6">
+        <v>20</v>
+      </c>
+      <c r="AK6">
+        <v>25</v>
+      </c>
+      <c r="AL6">
+        <v>55</v>
+      </c>
+      <c r="AM6">
+        <v>180</v>
+      </c>
+      <c r="AN6">
+        <v>12</v>
+      </c>
+      <c r="AO6">
+        <v>130</v>
+      </c>
+      <c r="AP6">
+        <v>12.5</v>
+      </c>
+      <c r="AQ6">
+        <v>18</v>
+      </c>
+      <c r="AR6">
+        <v>34</v>
+      </c>
+      <c r="AS6">
+        <v>110</v>
+      </c>
+      <c r="AT6">
+        <v>7.2</v>
+      </c>
+      <c r="AU6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV6">
+        <v>6.4</v>
+      </c>
+      <c r="AW6">
+        <v>65</v>
+      </c>
+      <c r="AX6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY6">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6">
         <v>19</v>
       </c>
-      <c r="AI6">
-        <v>60</v>
-      </c>
-      <c r="AJ6">
+      <c r="BA6">
+        <v>75</v>
+      </c>
+      <c r="BB6">
+        <v>15</v>
+      </c>
+      <c r="BC6">
         <v>17.5</v>
       </c>
-      <c r="AK6">
-        <v>19</v>
-      </c>
-      <c r="AL6">
-        <v>30</v>
-      </c>
-      <c r="AM6">
-        <v>80</v>
-      </c>
-      <c r="AN6">
-        <v>8.4</v>
-      </c>
-      <c r="AO6">
-        <v>65</v>
-      </c>
-      <c r="AP6">
-        <v>20</v>
-      </c>
-      <c r="AQ6">
-        <v>20</v>
-      </c>
-      <c r="AR6">
-        <v>38</v>
-      </c>
-      <c r="AS6">
-        <v>75</v>
-      </c>
-      <c r="AT6">
+      <c r="BD6">
+        <v>40</v>
+      </c>
+      <c r="BE6">
+        <v>110</v>
+      </c>
+      <c r="BF6">
         <v>10.5</v>
       </c>
-      <c r="AU6">
-        <v>9.6</v>
-      </c>
-      <c r="AV6">
-        <v>18</v>
-      </c>
-      <c r="AW6">
-        <v>42</v>
-      </c>
-      <c r="AX6">
-        <v>10.5</v>
-      </c>
-      <c r="AY6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>16</v>
-      </c>
-      <c r="BA6">
-        <v>46</v>
-      </c>
-      <c r="BB6">
-        <v>14.5</v>
-      </c>
-      <c r="BC6">
-        <v>13.5</v>
-      </c>
-      <c r="BD6">
-        <v>23</v>
-      </c>
-      <c r="BE6">
-        <v>55</v>
-      </c>
-      <c r="BF6">
-        <v>6.6</v>
-      </c>
       <c r="BG6">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="BH6">
-        <v>5</v>
+        <v>2.32</v>
       </c>
       <c r="BI6">
-        <v>3.8</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BK6">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP6">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BQ6">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="BR6">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="BS6">
-        <v>3.95</v>
+        <v>55</v>
       </c>
       <c r="BT6">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BV6">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="BW6">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="BX6">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="BY6">
-        <v>4.2</v>
+        <v>95</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="CA6">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="CB6" t="s">
         <v>150</v>
@@ -2270,76 +2270,76 @@
         <v>131</v>
       </c>
       <c r="F7">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="G7">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H7">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="I7">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
         <v>4.2</v>
       </c>
       <c r="T7">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA7">
         <v>48</v>
       </c>
       <c r="AB7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
         <v>13.5</v>
@@ -2348,148 +2348,148 @@
         <v>38</v>
       </c>
       <c r="AF7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
         <v>20</v>
       </c>
       <c r="AI7">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO7">
         <v>38</v>
       </c>
       <c r="AP7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR7">
         <v>15</v>
       </c>
       <c r="AS7">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AT7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AX7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BB7">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BC7">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="BD7">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BE7">
-        <v>9.6</v>
+        <v>85</v>
       </c>
       <c r="BF7">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="BG7">
         <v>22</v>
       </c>
       <c r="BH7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BN7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BR7">
         <v>42</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU7">
         <v>4.9</v>
       </c>
       <c r="BV7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY7">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7">
         <v>38</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="s">
         <v>150</v>
@@ -2512,19 +2512,19 @@
         <v>132</v>
       </c>
       <c r="F8">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="G8">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="H8">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="I8">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
         <v>3.6</v>
@@ -2536,7 +2536,7 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O8">
         <v>1.36</v>
@@ -2548,190 +2548,190 @@
         <v>2.06</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="U8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="X8">
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AA8">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
         <v>8.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE8">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AF8">
+        <v>14.5</v>
+      </c>
+      <c r="AG8">
+        <v>11.5</v>
+      </c>
+      <c r="AH8">
         <v>19</v>
       </c>
-      <c r="AG8">
+      <c r="AI8">
+        <v>65</v>
+      </c>
+      <c r="AJ8">
+        <v>38</v>
+      </c>
+      <c r="AK8">
+        <v>30</v>
+      </c>
+      <c r="AL8">
+        <v>46</v>
+      </c>
+      <c r="AM8">
+        <v>130</v>
+      </c>
+      <c r="AN8">
+        <v>20</v>
+      </c>
+      <c r="AO8">
+        <v>65</v>
+      </c>
+      <c r="AP8">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8">
+        <v>11.5</v>
+      </c>
+      <c r="AR8">
+        <v>19.5</v>
+      </c>
+      <c r="AS8">
+        <v>46</v>
+      </c>
+      <c r="AT8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU8">
+        <v>7</v>
+      </c>
+      <c r="AV8">
         <v>13</v>
       </c>
-      <c r="AH8">
-        <v>18</v>
-      </c>
-      <c r="AI8">
-        <v>55</v>
-      </c>
-      <c r="AJ8">
-        <v>55</v>
-      </c>
-      <c r="AK8">
-        <v>32</v>
-      </c>
-      <c r="AL8">
-        <v>55</v>
-      </c>
-      <c r="AM8">
-        <v>120</v>
-      </c>
-      <c r="AN8">
-        <v>28</v>
-      </c>
-      <c r="AO8">
-        <v>36</v>
-      </c>
-      <c r="AP8">
-        <v>10.5</v>
-      </c>
-      <c r="AQ8">
+      <c r="AW8">
+        <v>30</v>
+      </c>
+      <c r="AX8">
+        <v>12</v>
+      </c>
+      <c r="AY8">
         <v>9.6</v>
       </c>
-      <c r="AR8">
-        <v>17</v>
-      </c>
-      <c r="AS8">
-        <v>36</v>
-      </c>
-      <c r="AT8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8">
-        <v>6.6</v>
-      </c>
-      <c r="AV8">
-        <v>11</v>
-      </c>
-      <c r="AW8">
-        <v>25</v>
-      </c>
-      <c r="AX8">
-        <v>15</v>
-      </c>
-      <c r="AY8">
-        <v>10</v>
-      </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BB8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD8">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BE8">
-        <v>7.4</v>
+        <v>75</v>
       </c>
       <c r="BF8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG8">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI8">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BN8">
         <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP8">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR8">
         <v>38</v>
       </c>
       <c r="BS8">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BU8">
+        <v>5.7</v>
+      </c>
+      <c r="BV8">
+        <v>32</v>
+      </c>
+      <c r="BW8">
         <v>5.1</v>
       </c>
-      <c r="BV8">
-        <v>29</v>
-      </c>
-      <c r="BW8">
-        <v>5.7</v>
-      </c>
       <c r="BX8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BY8">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA8">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB8" t="s">
         <v>150</v>
@@ -2760,43 +2760,43 @@
         <v>1.28</v>
       </c>
       <c r="H9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K9">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O9">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U9">
         <v>1.65</v>
@@ -2808,70 +2808,70 @@
         <v>4.5</v>
       </c>
       <c r="X9">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y9">
         <v>50</v>
       </c>
       <c r="Z9">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD9">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AE9">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="AF9">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI9">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AJ9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AN9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO9">
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ9">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="AR9">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AS9">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AT9">
         <v>7</v>
@@ -2880,10 +2880,10 @@
         <v>12.5</v>
       </c>
       <c r="AV9">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AW9">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AX9">
         <v>6.2</v>
@@ -2892,88 +2892,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BA9">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BB9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC9">
         <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BE9">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BF9">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BG9">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="BH9">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BI9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ9">
         <v>17</v>
       </c>
       <c r="BK9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BN9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BO9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP9">
         <v>7.6</v>
       </c>
       <c r="BQ9">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="BR9">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BS9">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BT9">
         <v>22</v>
       </c>
       <c r="BU9">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BZ9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA9">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="s">
         <v>150</v>
@@ -2996,103 +2996,103 @@
         <v>134</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J10">
         <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
+        <v>1.84</v>
+      </c>
+      <c r="Q10">
+        <v>2.04</v>
+      </c>
+      <c r="R10">
+        <v>1.33</v>
+      </c>
+      <c r="S10">
+        <v>3.7</v>
+      </c>
+      <c r="T10">
         <v>1.82</v>
       </c>
-      <c r="Q10">
-        <v>2.02</v>
-      </c>
-      <c r="R10">
-        <v>1.31</v>
-      </c>
-      <c r="S10">
-        <v>3.6</v>
-      </c>
-      <c r="T10">
-        <v>1.8</v>
-      </c>
       <c r="U10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X10">
+        <v>14.5</v>
+      </c>
+      <c r="Y10">
+        <v>13</v>
+      </c>
+      <c r="Z10">
+        <v>26</v>
+      </c>
+      <c r="AA10">
+        <v>75</v>
+      </c>
+      <c r="AB10">
+        <v>10.5</v>
+      </c>
+      <c r="AC10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>16.5</v>
+      </c>
+      <c r="AE10">
+        <v>44</v>
+      </c>
+      <c r="AF10">
         <v>15.5</v>
       </c>
-      <c r="Y10">
-        <v>14</v>
-      </c>
-      <c r="Z10">
-        <v>27</v>
-      </c>
-      <c r="AA10">
-        <v>170</v>
-      </c>
-      <c r="AB10">
-        <v>11</v>
-      </c>
-      <c r="AC10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD10">
-        <v>15.5</v>
-      </c>
-      <c r="AE10">
-        <v>46</v>
-      </c>
-      <c r="AF10">
-        <v>16</v>
-      </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI10">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL10">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AM10">
         <v>580</v>
@@ -3101,64 +3101,64 @@
         <v>23</v>
       </c>
       <c r="AO10">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AP10">
         <v>11</v>
       </c>
       <c r="AQ10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS10">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="AT10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AX10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA10">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BC10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10">
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>7.4</v>
+        <v>75</v>
       </c>
       <c r="BF10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BH10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI10">
         <v>2.66</v>
@@ -3167,37 +3167,37 @@
         <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN10">
         <v>6</v>
       </c>
       <c r="BO10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
         <v>21</v>
       </c>
       <c r="BQ10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR10">
         <v>38</v>
       </c>
       <c r="BS10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT10">
         <v>8</v>
       </c>
       <c r="BU10">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV10">
         <v>36</v>
@@ -3206,16 +3206,16 @@
         <v>4.3</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ10">
         <v>34</v>
       </c>
       <c r="CA10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="s">
         <v>150</v>
@@ -3238,13 +3238,13 @@
         <v>135</v>
       </c>
       <c r="F11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G11">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H11">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I11">
         <v>2.68</v>
@@ -3253,10 +3253,10 @@
         <v>3.75</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M11">
         <v>1.05</v>
@@ -3268,13 +3268,13 @@
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S11">
         <v>2.62</v>
@@ -3283,22 +3283,22 @@
         <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA11">
         <v>40</v>
@@ -3307,25 +3307,25 @@
         <v>16.5</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11">
         <v>15.5</v>
       </c>
       <c r="AE11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG11">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH11">
         <v>16</v>
       </c>
       <c r="AI11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ11">
         <v>48</v>
@@ -3370,19 +3370,19 @@
         <v>20</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BB11">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BC11">
         <v>11.5</v>
@@ -3397,22 +3397,22 @@
         <v>14</v>
       </c>
       <c r="BG11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH11">
         <v>5</v>
       </c>
       <c r="BI11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BL11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM11">
         <v>4.3</v>
@@ -3421,7 +3421,7 @@
         <v>7.4</v>
       </c>
       <c r="BO11">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP11">
         <v>23</v>
@@ -3439,7 +3439,7 @@
         <v>7.2</v>
       </c>
       <c r="BU11">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV11">
         <v>22</v>
@@ -3480,97 +3480,97 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G12">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H12">
         <v>2.78</v>
       </c>
       <c r="I12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q12">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T12">
         <v>1.56</v>
       </c>
       <c r="U12">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
         <v>1.64</v>
       </c>
       <c r="X12">
+        <v>42</v>
+      </c>
+      <c r="Y12">
+        <v>22</v>
+      </c>
+      <c r="Z12">
+        <v>27</v>
+      </c>
+      <c r="AA12">
+        <v>48</v>
+      </c>
+      <c r="AB12">
+        <v>21</v>
+      </c>
+      <c r="AC12">
+        <v>12</v>
+      </c>
+      <c r="AD12">
+        <v>15</v>
+      </c>
+      <c r="AE12">
         <v>29</v>
       </c>
-      <c r="Y12">
-        <v>21</v>
-      </c>
-      <c r="Z12">
-        <v>28</v>
-      </c>
-      <c r="AA12">
-        <v>55</v>
-      </c>
-      <c r="AB12">
-        <v>17.5</v>
-      </c>
-      <c r="AC12">
-        <v>11</v>
-      </c>
-      <c r="AD12">
-        <v>16</v>
-      </c>
-      <c r="AE12">
-        <v>32</v>
-      </c>
       <c r="AF12">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG12">
         <v>14</v>
       </c>
       <c r="AH12">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI12">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK12">
         <v>26</v>
@@ -3579,76 +3579,76 @@
         <v>32</v>
       </c>
       <c r="AM12">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO12">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AP12">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ12">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AR12">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AS12">
         <v>5.5</v>
       </c>
       <c r="AT12">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AU12">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX12">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AY12">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA12">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="BB12">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="BC12">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD12">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="BE12">
         <v>5.5</v>
       </c>
       <c r="BF12">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG12">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH12">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BI12">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BJ12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK12">
         <v>3.5</v>
@@ -3657,25 +3657,25 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BN12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO12">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ12">
         <v>4.2</v>
       </c>
       <c r="BR12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT12">
         <v>7.4</v>
@@ -3684,16 +3684,16 @@
         <v>3.15</v>
       </c>
       <c r="BV12">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BW12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BX12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BY12">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ12">
         <v>0</v>
@@ -3731,10 +3731,10 @@
         <v>5.5</v>
       </c>
       <c r="I13">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
         <v>4.4</v>
@@ -3746,91 +3746,91 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O13">
         <v>1.3</v>
       </c>
       <c r="P13">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q13">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S13">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T13">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U13">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V13">
         <v>1.19</v>
       </c>
       <c r="W13">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y13">
         <v>19.5</v>
       </c>
       <c r="Z13">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AA13">
         <v>900</v>
       </c>
       <c r="AB13">
+        <v>9.4</v>
+      </c>
+      <c r="AC13">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AC13">
-        <v>10</v>
       </c>
       <c r="AD13">
         <v>23</v>
       </c>
       <c r="AE13">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="AF13">
+        <v>10</v>
+      </c>
+      <c r="AG13">
         <v>12</v>
       </c>
-      <c r="AG13">
-        <v>11</v>
-      </c>
       <c r="AH13">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI13">
         <v>90</v>
       </c>
       <c r="AJ13">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL13">
         <v>38</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO13">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AP13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13">
         <v>17</v>
@@ -3857,49 +3857,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA13">
         <v>36</v>
       </c>
       <c r="BB13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC13">
         <v>15.5</v>
       </c>
       <c r="BD13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE13">
         <v>29</v>
       </c>
       <c r="BF13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BH13">
         <v>4</v>
       </c>
       <c r="BI13">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13">
         <v>12.5</v>
       </c>
       <c r="BK13">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN13">
         <v>4.7</v>
@@ -3908,7 +3908,7 @@
         <v>3.7</v>
       </c>
       <c r="BP13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ13">
         <v>3.85</v>
@@ -3917,31 +3917,31 @@
         <v>30</v>
       </c>
       <c r="BS13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT13">
         <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ13">
         <v>23</v>
       </c>
       <c r="CA13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB13" t="s">
         <v>150</v>
@@ -3964,67 +3964,67 @@
         <v>138</v>
       </c>
       <c r="F14">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G14">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H14">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="I14">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L14">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q14">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="S14">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T14">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U14">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="V14">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="W14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y14">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA14">
         <v>19.5</v>
@@ -4039,25 +4039,25 @@
         <v>11</v>
       </c>
       <c r="AE14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF14">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AG14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ14">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK14">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AL14">
         <v>65</v>
@@ -4066,28 +4066,28 @@
         <v>90</v>
       </c>
       <c r="AN14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP14">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ14">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR14">
         <v>10</v>
       </c>
       <c r="AS14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV14">
         <v>9</v>
@@ -4099,37 +4099,37 @@
         <v>16</v>
       </c>
       <c r="AY14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ14">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA14">
         <v>14.5</v>
       </c>
       <c r="BB14">
+        <v>7.6</v>
+      </c>
+      <c r="BC14">
+        <v>13.5</v>
+      </c>
+      <c r="BD14">
         <v>7.8</v>
       </c>
-      <c r="BC14">
-        <v>7.4</v>
-      </c>
-      <c r="BD14">
-        <v>7.4</v>
-      </c>
       <c r="BE14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG14">
         <v>7</v>
       </c>
       <c r="BH14">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BI14">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BJ14">
         <v>9.6</v>
@@ -4141,49 +4141,49 @@
         <v>110</v>
       </c>
       <c r="BM14">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BO14">
         <v>6.4</v>
       </c>
       <c r="BP14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BQ14">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BS14">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BT14">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY14">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BZ14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA14">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="CB14" t="s">
         <v>150</v>
@@ -4209,19 +4209,19 @@
         <v>3.35</v>
       </c>
       <c r="G15">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H15">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I15">
         <v>2.32</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.4</v>
@@ -4245,28 +4245,28 @@
         <v>1.39</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T15">
         <v>1.71</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
         <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X15">
+        <v>19</v>
+      </c>
+      <c r="Y15">
+        <v>11.5</v>
+      </c>
+      <c r="Z15">
         <v>18</v>
-      </c>
-      <c r="Y15">
-        <v>13</v>
-      </c>
-      <c r="Z15">
-        <v>18.5</v>
       </c>
       <c r="AA15">
         <v>34</v>
@@ -4275,40 +4275,40 @@
         <v>14</v>
       </c>
       <c r="AC15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG15">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI15">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AK15">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL15">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AM15">
         <v>200</v>
       </c>
       <c r="AN15">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO15">
         <v>18</v>
@@ -4317,13 +4317,13 @@
         <v>13</v>
       </c>
       <c r="AQ15">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT15">
         <v>11.5</v>
@@ -4335,58 +4335,58 @@
         <v>10</v>
       </c>
       <c r="AW15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX15">
         <v>21</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ15">
         <v>14.5</v>
       </c>
       <c r="BA15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB15">
+        <v>40</v>
+      </c>
+      <c r="BC15">
+        <v>30</v>
+      </c>
+      <c r="BD15">
+        <v>32</v>
+      </c>
+      <c r="BE15">
+        <v>60</v>
+      </c>
+      <c r="BF15">
         <v>23</v>
       </c>
-      <c r="BC15">
-        <v>18</v>
-      </c>
-      <c r="BD15">
-        <v>24</v>
-      </c>
-      <c r="BE15">
-        <v>15.5</v>
-      </c>
-      <c r="BF15">
-        <v>7.4</v>
-      </c>
       <c r="BG15">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH15">
         <v>4.1</v>
       </c>
       <c r="BI15">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK15">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BN15">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BO15">
         <v>5.2</v>
@@ -4395,37 +4395,37 @@
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR15">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BT15">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BU15">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV15">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BW15">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="BX15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BZ15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="CB15" t="s">
         <v>150</v>
@@ -4448,19 +4448,19 @@
         <v>140</v>
       </c>
       <c r="F16">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="G16">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="I16">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
         <v>3.65</v>
@@ -4472,7 +4472,7 @@
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>1.31</v>
@@ -4487,187 +4487,187 @@
         <v>1.39</v>
       </c>
       <c r="S16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T16">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="X16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y16">
+        <v>12</v>
+      </c>
+      <c r="Z16">
+        <v>18.5</v>
+      </c>
+      <c r="AA16">
+        <v>44</v>
+      </c>
+      <c r="AB16">
         <v>12.5</v>
-      </c>
-      <c r="Z16">
-        <v>21</v>
-      </c>
-      <c r="AA16">
-        <v>50</v>
-      </c>
-      <c r="AB16">
-        <v>11.5</v>
       </c>
       <c r="AC16">
         <v>8</v>
       </c>
       <c r="AD16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE16">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AF16">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG16">
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI16">
+        <v>40</v>
+      </c>
+      <c r="AJ16">
         <v>44</v>
       </c>
-      <c r="AJ16">
-        <v>40</v>
-      </c>
       <c r="AK16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL16">
         <v>40</v>
       </c>
       <c r="AM16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP16">
         <v>13.5</v>
       </c>
       <c r="AQ16">
+        <v>10.5</v>
+      </c>
+      <c r="AR16">
+        <v>16.5</v>
+      </c>
+      <c r="AS16">
+        <v>38</v>
+      </c>
+      <c r="AT16">
         <v>11</v>
       </c>
-      <c r="AR16">
+      <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
+        <v>11</v>
+      </c>
+      <c r="AW16">
+        <v>26</v>
+      </c>
+      <c r="AX16">
         <v>17</v>
       </c>
-      <c r="AS16">
-        <v>40</v>
-      </c>
-      <c r="AT16">
-        <v>10.5</v>
-      </c>
-      <c r="AU16">
-        <v>7.2</v>
-      </c>
-      <c r="AV16">
-        <v>11.5</v>
-      </c>
-      <c r="AW16">
-        <v>27</v>
-      </c>
-      <c r="AX16">
-        <v>15.5</v>
-      </c>
       <c r="AY16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA16">
         <v>34</v>
       </c>
       <c r="BB16">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BC16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE16">
         <v>65</v>
       </c>
       <c r="BF16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI16">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16">
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN16">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BQ16">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT16">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW16">
         <v>9.6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
         <v>150</v>
@@ -4690,16 +4690,16 @@
         <v>141</v>
       </c>
       <c r="F17">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G17">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H17">
         <v>2.48</v>
       </c>
       <c r="I17">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J17">
         <v>3.05</v>
@@ -4708,52 +4708,52 @@
         <v>3.1</v>
       </c>
       <c r="L17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O17">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P17">
         <v>1.52</v>
       </c>
       <c r="Q17">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R17">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>2.24</v>
       </c>
       <c r="U17">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W17">
         <v>1.37</v>
       </c>
       <c r="X17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB17">
         <v>9.4</v>
@@ -4780,37 +4780,37 @@
         <v>75</v>
       </c>
       <c r="AJ17">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL17">
+        <v>95</v>
+      </c>
+      <c r="AM17">
+        <v>280</v>
+      </c>
+      <c r="AN17">
         <v>90</v>
-      </c>
-      <c r="AM17">
-        <v>270</v>
-      </c>
-      <c r="AN17">
-        <v>85</v>
       </c>
       <c r="AO17">
         <v>42</v>
       </c>
       <c r="AP17">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ17">
         <v>6.8</v>
       </c>
       <c r="AR17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU17">
         <v>6.6</v>
@@ -4819,7 +4819,7 @@
         <v>11.5</v>
       </c>
       <c r="AW17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX17">
         <v>20</v>
@@ -4828,7 +4828,7 @@
         <v>15</v>
       </c>
       <c r="AZ17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA17">
         <v>60</v>
@@ -4852,7 +4852,7 @@
         <v>36</v>
       </c>
       <c r="BH17">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BI17">
         <v>2.44</v>
@@ -4861,10 +4861,10 @@
         <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BL17">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="BM17">
         <v>200</v>
@@ -4873,19 +4873,19 @@
         <v>6.6</v>
       </c>
       <c r="BO17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP17">
         <v>38</v>
       </c>
       <c r="BQ17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BR17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BT17">
         <v>5.1</v>
@@ -4897,19 +4897,19 @@
         <v>22</v>
       </c>
       <c r="BW17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX17">
         <v>48</v>
       </c>
       <c r="BY17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BZ17">
         <v>55</v>
       </c>
       <c r="CA17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CB17" t="s">
         <v>150</v>
@@ -4932,28 +4932,28 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G18">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H18">
         <v>6.2</v>
       </c>
       <c r="I18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L18">
         <v>1.36</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
         <v>4.4</v>
@@ -4962,10 +4962,10 @@
         <v>1.27</v>
       </c>
       <c r="P18">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R18">
         <v>1.44</v>
@@ -4974,184 +4974,184 @@
         <v>3.1</v>
       </c>
       <c r="T18">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U18">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W18">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y18">
         <v>23</v>
       </c>
       <c r="Z18">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA18">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC18">
+        <v>9.6</v>
+      </c>
+      <c r="AD18">
+        <v>23</v>
+      </c>
+      <c r="AE18">
+        <v>90</v>
+      </c>
+      <c r="AF18">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AD18">
-        <v>24</v>
-      </c>
-      <c r="AE18">
-        <v>100</v>
-      </c>
-      <c r="AF18">
-        <v>9.199999999999999</v>
       </c>
       <c r="AG18">
         <v>9.6</v>
       </c>
       <c r="AH18">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI18">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL18">
         <v>34</v>
       </c>
       <c r="AM18">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP18">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR18">
         <v>48</v>
       </c>
       <c r="AS18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU18">
         <v>9.199999999999999</v>
       </c>
       <c r="AV18">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA18">
         <v>70</v>
       </c>
       <c r="BB18">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC18">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF18">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG18">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="BH18">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BI18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL18">
         <v>140</v>
       </c>
       <c r="BM18">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN18">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP18">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="BR18">
         <v>28</v>
       </c>
       <c r="BS18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU18">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ18">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="CA18">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB18" t="s">
         <v>150</v>
@@ -5174,226 +5174,226 @@
         <v>143</v>
       </c>
       <c r="F19">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="G19">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H19">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="P19">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="R19">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S19">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="U19">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V19">
         <v>1.27</v>
       </c>
       <c r="W19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X19">
+        <v>16.5</v>
+      </c>
+      <c r="Y19">
+        <v>17.5</v>
+      </c>
+      <c r="Z19">
+        <v>36</v>
+      </c>
+      <c r="AA19">
+        <v>500</v>
+      </c>
+      <c r="AB19">
+        <v>10.5</v>
+      </c>
+      <c r="AC19">
+        <v>9.4</v>
+      </c>
+      <c r="AD19">
         <v>19.5</v>
-      </c>
-      <c r="Y19">
-        <v>19</v>
-      </c>
-      <c r="Z19">
-        <v>40</v>
-      </c>
-      <c r="AA19">
-        <v>900</v>
-      </c>
-      <c r="AB19">
-        <v>11.5</v>
-      </c>
-      <c r="AC19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD19">
-        <v>21</v>
       </c>
       <c r="AE19">
         <v>190</v>
       </c>
       <c r="AF19">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19">
         <v>20</v>
       </c>
       <c r="AI19">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AJ19">
         <v>25</v>
       </c>
       <c r="AK19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL19">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AM19">
         <v>580</v>
       </c>
       <c r="AN19">
+        <v>14.5</v>
+      </c>
+      <c r="AO19">
+        <v>260</v>
+      </c>
+      <c r="AP19">
         <v>12</v>
       </c>
-      <c r="AO19">
-        <v>310</v>
-      </c>
-      <c r="AP19">
-        <v>13.5</v>
-      </c>
       <c r="AQ19">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR19">
         <v>14</v>
       </c>
       <c r="AS19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT19">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA19">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB19">
+        <v>17.5</v>
+      </c>
+      <c r="BC19">
         <v>16.5</v>
-      </c>
-      <c r="BC19">
-        <v>14.5</v>
       </c>
       <c r="BD19">
         <v>13</v>
       </c>
       <c r="BE19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF19">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG19">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH19">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BI19">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK19">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN19">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO19">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR19">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS19">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BT19">
         <v>9</v>
       </c>
       <c r="BU19">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV19">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW19">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX19">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BY19">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BZ19">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CA19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB19" t="s">
         <v>150</v>
@@ -5416,73 +5416,73 @@
         <v>144</v>
       </c>
       <c r="F20">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H20">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I20">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J20">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M20">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P20">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Q20">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="R20">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T20">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="U20">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W20">
         <v>1.46</v>
       </c>
       <c r="X20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z20">
         <v>17.5</v>
       </c>
       <c r="AA20">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20">
         <v>7.4</v>
@@ -5491,7 +5491,7 @@
         <v>12.5</v>
       </c>
       <c r="AE20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF20">
         <v>21</v>
@@ -5500,43 +5500,43 @@
         <v>14</v>
       </c>
       <c r="AH20">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI20">
         <v>55</v>
       </c>
       <c r="AJ20">
+        <v>60</v>
+      </c>
+      <c r="AK20">
         <v>55</v>
       </c>
-      <c r="AK20">
-        <v>40</v>
-      </c>
       <c r="AL20">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM20">
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO20">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP20">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ20">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR20">
         <v>14.5</v>
       </c>
       <c r="AS20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT20">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20">
         <v>6.6</v>
@@ -5554,46 +5554,46 @@
         <v>11.5</v>
       </c>
       <c r="AZ20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA20">
         <v>38</v>
       </c>
       <c r="BB20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC20">
         <v>32</v>
       </c>
       <c r="BD20">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE20">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF20">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BG20">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH20">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BI20">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK20">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN20">
         <v>6</v>
@@ -5602,40 +5602,40 @@
         <v>5.3</v>
       </c>
       <c r="BP20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR20">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS20">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT20">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU20">
         <v>4.9</v>
       </c>
       <c r="BV20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW20">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ20">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA20">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="s">
         <v>150</v>
@@ -5658,13 +5658,13 @@
         <v>145</v>
       </c>
       <c r="F21">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G21">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H21">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I21">
         <v>5.4</v>
@@ -5691,7 +5691,7 @@
         <v>1.89</v>
       </c>
       <c r="Q21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R21">
         <v>1.34</v>
@@ -5700,7 +5700,7 @@
         <v>3.7</v>
       </c>
       <c r="T21">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U21">
         <v>1.94</v>
@@ -5709,40 +5709,40 @@
         <v>1.23</v>
       </c>
       <c r="W21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z21">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA21">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB21">
         <v>8.6</v>
       </c>
       <c r="AC21">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD21">
         <v>20</v>
       </c>
       <c r="AE21">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF21">
         <v>11.5</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21">
         <v>90</v>
@@ -5766,46 +5766,46 @@
         <v>95</v>
       </c>
       <c r="AP21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS21">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU21">
         <v>7.6</v>
       </c>
       <c r="AV21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW21">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX21">
+        <v>9.4</v>
+      </c>
+      <c r="AY21">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AY21">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
         <v>18</v>
       </c>
       <c r="BA21">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB21">
         <v>17</v>
       </c>
       <c r="BC21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD21">
         <v>32</v>
@@ -5817,34 +5817,34 @@
         <v>11</v>
       </c>
       <c r="BG21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH21">
         <v>3.75</v>
       </c>
       <c r="BI21">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ21">
         <v>11</v>
       </c>
       <c r="BK21">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN21">
         <v>4.5</v>
       </c>
       <c r="BO21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP21">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BQ21">
         <v>5.2</v>
@@ -5853,31 +5853,31 @@
         <v>30</v>
       </c>
       <c r="BS21">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT21">
         <v>8.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="BV21">
         <v>48</v>
       </c>
       <c r="BW21">
+        <v>7</v>
+      </c>
+      <c r="BX21">
+        <v>55</v>
+      </c>
+      <c r="BY21">
         <v>7.2</v>
-      </c>
-      <c r="BX21">
-        <v>60</v>
-      </c>
-      <c r="BY21">
-        <v>7.6</v>
       </c>
       <c r="BZ21">
         <v>26</v>
       </c>
       <c r="CA21">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB21" t="s">
         <v>150</v>
@@ -5900,73 +5900,73 @@
         <v>146</v>
       </c>
       <c r="F22">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G22">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H22">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I22">
         <v>2.52</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K22">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M22">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N22">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P22">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R22">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S22">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="U22">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V22">
         <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X22">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y22">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC22">
         <v>7</v>
@@ -5975,52 +5975,52 @@
         <v>13</v>
       </c>
       <c r="AE22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH22">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI22">
+        <v>70</v>
+      </c>
+      <c r="AJ22">
         <v>80</v>
       </c>
-      <c r="AJ22">
+      <c r="AK22">
+        <v>65</v>
+      </c>
+      <c r="AL22">
         <v>90</v>
       </c>
-      <c r="AK22">
-        <v>70</v>
-      </c>
-      <c r="AL22">
-        <v>190</v>
-      </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO22">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP22">
+        <v>7.6</v>
+      </c>
+      <c r="AQ22">
         <v>7</v>
       </c>
-      <c r="AQ22">
-        <v>6.4</v>
-      </c>
       <c r="AR22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS22">
         <v>32</v>
       </c>
       <c r="AT22">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22">
         <v>6.6</v>
@@ -6029,25 +6029,25 @@
         <v>12</v>
       </c>
       <c r="AW22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ22">
         <v>23</v>
       </c>
       <c r="BA22">
+        <v>60</v>
+      </c>
+      <c r="BB22">
+        <v>65</v>
+      </c>
+      <c r="BC22">
         <v>55</v>
-      </c>
-      <c r="BB22">
-        <v>50</v>
-      </c>
-      <c r="BC22">
-        <v>50</v>
       </c>
       <c r="BD22">
         <v>70</v>
@@ -6059,22 +6059,22 @@
         <v>65</v>
       </c>
       <c r="BG22">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH22">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BI22">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK22">
         <v>8.800000000000001</v>
       </c>
       <c r="BL22">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
         <v>200</v>
@@ -6089,10 +6089,10 @@
         <v>40</v>
       </c>
       <c r="BQ22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BS22">
         <v>13.5</v>
@@ -6104,22 +6104,22 @@
         <v>4.6</v>
       </c>
       <c r="BV22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW22">
         <v>13.5</v>
       </c>
       <c r="BX22">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY22">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ22">
         <v>60</v>
       </c>
       <c r="CA22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB22" t="s">
         <v>150</v>
@@ -6142,22 +6142,22 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G23">
         <v>2.52</v>
       </c>
       <c r="H23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I23">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J23">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L23">
         <v>1.53</v>
@@ -6166,10 +6166,10 @@
         <v>1.11</v>
       </c>
       <c r="N23">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O23">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P23">
         <v>1.63</v>
@@ -6178,22 +6178,22 @@
         <v>2.46</v>
       </c>
       <c r="R23">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T23">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U23">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V23">
         <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X23">
         <v>10.5</v>
@@ -6202,7 +6202,7 @@
         <v>11</v>
       </c>
       <c r="Z23">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA23">
         <v>170</v>
@@ -6211,7 +6211,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD23">
         <v>16.5</v>
@@ -6232,7 +6232,7 @@
         <v>170</v>
       </c>
       <c r="AJ23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK23">
         <v>44</v>
@@ -6250,10 +6250,10 @@
         <v>500</v>
       </c>
       <c r="AP23">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR23">
         <v>20</v>
@@ -6271,7 +6271,7 @@
         <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX23">
         <v>12</v>
@@ -6301,19 +6301,19 @@
         <v>23</v>
       </c>
       <c r="BG23">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BH23">
         <v>2.96</v>
       </c>
       <c r="BI23">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ23">
         <v>11</v>
       </c>
       <c r="BK23">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL23">
         <v>1000</v>
@@ -6325,16 +6325,16 @@
         <v>5.2</v>
       </c>
       <c r="BO23">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP23">
         <v>21</v>
       </c>
       <c r="BQ23">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR23">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
         <v>9</v>
@@ -6343,25 +6343,25 @@
         <v>6.8</v>
       </c>
       <c r="BU23">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV23">
         <v>36</v>
       </c>
       <c r="BW23">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ23">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB23" t="s">
         <v>150</v>
@@ -6384,19 +6384,19 @@
         <v>148</v>
       </c>
       <c r="F24">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="G24">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H24">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I24">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K24">
         <v>3.55</v>
@@ -6408,13 +6408,13 @@
         <v>1.11</v>
       </c>
       <c r="N24">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q24">
         <v>2.44</v>
@@ -6426,19 +6426,19 @@
         <v>4.9</v>
       </c>
       <c r="T24">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U24">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V24">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W24">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y24">
         <v>14</v>
@@ -6453,28 +6453,28 @@
         <v>6.8</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD24">
         <v>21</v>
       </c>
       <c r="AE24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF24">
         <v>10.5</v>
       </c>
       <c r="AG24">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AH24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK24">
         <v>25</v>
@@ -6486,7 +6486,7 @@
         <v>180</v>
       </c>
       <c r="AN24">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO24">
         <v>130</v>
@@ -6498,10 +6498,10 @@
         <v>12.5</v>
       </c>
       <c r="AR24">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS24">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AT24">
         <v>6.4</v>
@@ -6510,7 +6510,7 @@
         <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW24">
         <v>50</v>
@@ -6519,16 +6519,16 @@
         <v>9.6</v>
       </c>
       <c r="AY24">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ24">
         <v>22</v>
       </c>
       <c r="BA24">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BB24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC24">
         <v>22</v>
@@ -6540,10 +6540,10 @@
         <v>120</v>
       </c>
       <c r="BF24">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG24">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BH24">
         <v>2.9</v>
@@ -6552,10 +6552,10 @@
         <v>2.72</v>
       </c>
       <c r="BJ24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL24">
         <v>230</v>
@@ -6564,7 +6564,7 @@
         <v>140</v>
       </c>
       <c r="BN24">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BO24">
         <v>4</v>
@@ -6573,16 +6573,16 @@
         <v>18</v>
       </c>
       <c r="BQ24">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR24">
         <v>44</v>
       </c>
       <c r="BS24">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT24">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU24">
         <v>7.2</v>
@@ -6591,19 +6591,19 @@
         <v>60</v>
       </c>
       <c r="BW24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BX24">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY24">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BZ24">
         <v>42</v>
       </c>
       <c r="CA24">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="CB24" t="s">
         <v>150</v>
@@ -6626,7 +6626,7 @@
         <v>149</v>
       </c>
       <c r="F25">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G25">
         <v>4.4</v>
@@ -6635,7 +6635,7 @@
         <v>2.02</v>
       </c>
       <c r="I25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J25">
         <v>3.45</v>
@@ -6644,7 +6644,7 @@
         <v>3.65</v>
       </c>
       <c r="L25">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M25">
         <v>1.09</v>
@@ -6656,10 +6656,10 @@
         <v>1.4</v>
       </c>
       <c r="P25">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
         <v>1.29</v>
@@ -6671,10 +6671,10 @@
         <v>1.94</v>
       </c>
       <c r="U25">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V25">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W25">
         <v>1.29</v>
@@ -6692,10 +6692,10 @@
         <v>25</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD25">
         <v>11</v>
@@ -6707,7 +6707,7 @@
         <v>32</v>
       </c>
       <c r="AG25">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH25">
         <v>21</v>
@@ -6716,25 +6716,25 @@
         <v>55</v>
       </c>
       <c r="AJ25">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK25">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL25">
         <v>90</v>
       </c>
       <c r="AM25">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="AN25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO25">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25">
         <v>7.2</v>
@@ -6752,10 +6752,10 @@
         <v>7</v>
       </c>
       <c r="AV25">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX25">
         <v>23</v>
@@ -6770,7 +6770,7 @@
         <v>30</v>
       </c>
       <c r="BB25">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BC25">
         <v>42</v>
@@ -6797,7 +6797,7 @@
         <v>12.5</v>
       </c>
       <c r="BK25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -6809,7 +6809,7 @@
         <v>9</v>
       </c>
       <c r="BO25">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="BP25">
         <v>48</v>
@@ -6824,7 +6824,7 @@
         <v>4.6</v>
       </c>
       <c r="BT25">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU25">
         <v>4.1</v>
@@ -6833,7 +6833,7 @@
         <v>18.5</v>
       </c>
       <c r="BW25">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BX25">
         <v>40</v>
